--- a/EI_ENBD_3post.xlsx
+++ b/EI_ENBD_3post.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:V126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -593,7 +593,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>47m</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         <v>3</v>
       </c>
       <c r="U3" t="n">
-        <v>234</v>
+        <v>281</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2h</t>
+          <t>3h</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -982,7 +982,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2h</t>
+          <t>3h</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>5h</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>5h</t>
+          <t>6h</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1420,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>5h</t>
+          <t>6h</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1506,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2120,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2210,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2390,7 +2390,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2480,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2570,7 +2570,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2660,7 +2660,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2755,6 +2755,8896 @@
       <c r="V26" t="inlineStr">
         <is>
           <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2035956416520069280</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://x.com/parulghalout/status/2035956416520069280</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://x.com/parulghalout</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>parulghalout</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>parul ghalout</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/589412760515031040/ehckyrV3_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD  @mnsadiq84 @skrana111 @dxb_sknj</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD  &lt;a href="/mnsadiq84" title="naveed sadiq"&gt;@mnsadiq84&lt;/a&gt; &lt;a href="/skrana111" title="sandeep kumar"&gt;@skrana111&lt;/a&gt; &lt;a href="/dxb_sknj" title="dxb_sknj"&gt;@dxb_sknj&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 5:46 AM UTC</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2026-03-23T05:46:00Z</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>['https://x.com/mnsadiq84', 'https://x.com/skrana111', 'https://x.com/dxb_sknj']</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>14</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2035956407212925393</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035956407212925393</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program @semeet @SelmaRomola @ibushra_03</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 5:46 AM UTC</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2026-03-23T05:46:00Z</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/ibushra_03']</t>
+        </is>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>8</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2035956342763258332</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035956342763258332</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 5:46 AM UTC</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2026-03-23T05:46:00Z</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>9</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2035956152442449955</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035956152442449955</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD @parulghalout @Emy191990 @Salma2232019</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 5:45 AM UTC</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2026-03-23T05:45:00Z</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>['https://x.com/parulghalout', 'https://x.com/Emy191990', 'https://x.com/Salma2232019']</t>
+        </is>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>17</v>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2035956075355361747</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035956075355361747</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Salma2232019 @semeet</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 5:45 AM UTC</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2026-03-23T05:45:00Z</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>['https://x.com/SelmaRomola', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
+        </is>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>10</v>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2035956001279775104</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035956001279775104</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD @Emy191990 @parulghalout @ibushra_03</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 5:45 AM UTC</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>2026-03-23T05:45:00Z</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/ibushra_03']</t>
+        </is>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>18</v>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2035955834002501721</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035955834002501721</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Via the ENBD X Mobile App. @Emy191990 @Salma2232019 @Salma2232019</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 5:44 AM UTC</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2026-03-23T05:44:00Z</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/Salma2232019', 'https://x.com/Salma2232019']</t>
+        </is>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>12</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2035955759859834985</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035955759859834985</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Via the ENBD X Mobile App. @SelmaRomola @semeet @ibushra_03</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Via the ENBD X Mobile App. &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 5:44 AM UTC</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2026-03-23T05:44:00Z</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>['https://x.com/SelmaRomola', 'https://x.com/semeet', 'https://x.com/ibushra_03']</t>
+        </is>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>9</v>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2035955684098163029</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035955684098163029</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Via the ENBD X Mobile App. @Emy191990 @parulghalout @Salma2232019</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 5:43 AM UTC</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>2026-03-23T05:43:00Z</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
+        </is>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>13</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2035955579966173454</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035955579966173454</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Via the ENBD X Mobile App. @semeet @SelmaRomola @Salma2232019</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Via the ENBD X Mobile App. &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J36" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 5:43 AM UTC</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2026-03-23T05:43:00Z</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/Salma2232019']</t>
+        </is>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>9</v>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2035955485564936537</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035955485564936537</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Via the ENBD X Mobile App. @SelmaRomola @Emy191990 @parulghalout</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Via the ENBD X Mobile App. &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J37" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 5:43 AM UTC</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>2026-03-23T05:43:00Z</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>['https://x.com/SelmaRomola', 'https://x.com/Emy191990', 'https://x.com/parulghalout']</t>
+        </is>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>15</v>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2035955401255235904</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035955401255235904</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Via the ENBD X Mobile App. @Emy191990 @Salma2232019 @semeet</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J38" t="b">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 5:42 AM UTC</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2026-03-23T05:42:00Z</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
+        </is>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>12</v>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2035947184114344234</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2035947184114344234</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Thank you for reaching out to us. To ensure a seamless and secure banking experience, please reach out to our customer support on call 24/7.
+Or WhatsApp banking services from 9AM to 7PM at 971600540000 to assist, this helps us maintain the highest security standards for your account. Thank you for your understanding.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Thank you for reaching out to us. To ensure a seamless and secure banking experience, please reach out to our customer support on call 24/7.
+Or WhatsApp banking services from 9AM to 7PM at 971600540000 to assist, this helps us maintain the highest security standards for your account. Thank you for your understanding.</t>
+        </is>
+      </c>
+      <c r="J39" t="b">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>['ShagilShams']</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 5:10 AM UTC</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2026-03-23T05:10:00Z</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>20</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2035937800336384350</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2035937800336384350</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_KSA</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>EmiratesNBD KSA</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>مرحباً بك, يمكنك الأن معرفة المزيد عن اماكن الفروع و أوقات العمل من خلال الضغط على الرابط ادناه.
+ms.spr.ly/6016Qszsr</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>مرحباً بك, يمكنك الأن معرفة المزيد عن اماكن الفروع و أوقات العمل من خلال الضغط على الرابط ادناه.
+&lt;a href="http://ms.spr.ly/6016Qszsr"&gt;ms.spr.ly/6016Qszsr&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J40" t="b">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>['c65kg']</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>9h</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 4:32 AM UTC</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2026-03-23T04:32:00Z</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>['http://ms.spr.ly/6016Qszsr']</t>
+        </is>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>21</v>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2035887867075948831</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://x.com/ahmd_4050/status/2035887867075948831</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://x.com/ahmd_4050</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ahmd_4050</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>ahmd</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1686557037948276736/wZXFbO-o_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>كم تعطون قروض</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>كم تعطون قروض</t>
+        </is>
+      </c>
+      <c r="J41" t="b">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>12h</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 1:14 AM UTC</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2026-03-23T01:14:00Z</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>9</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2035879255176093818</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://x.com/ShagilShams/status/2035879255176093818</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://x.com/ShagilShams</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ShagilShams</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Shagil Shams</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1618258890503901184/GcGIQNmE_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Hi Team , 
+I'm in India , Unable to transfer money to myself. Payment getting declined . 
+Please check .</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; Hi Team , 
+I&amp;#39;m in India , Unable to transfer money to myself. Payment getting declined . 
+Please check .</t>
+        </is>
+      </c>
+      <c r="J42" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 12:40 AM UTC</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2026-03-23T00:40:00Z</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>22</v>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2035854031839781077</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://x.com/sahmmediacenter/status/2035854031839781077</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>https://x.com/sahmmediacenter</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>sahmmediacenter</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>سهم - SAHM</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1781335149558280192/f-jZEPW4_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>#سهم | #الإمارات تعزز مكانتها كمركز عالمي للتكنولوجيا المالية مع توقعات بنمو حجم السوق إلى 5.71 مليار دولار بحلول 2029.. المزيد في هذا التقرير من #قناة_أزهري_الفضائية
+@azharitv</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23سهم"&gt;#سهم&lt;/a&gt; | &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات"&gt;#الإمارات&lt;/a&gt; تعزز مكانتها كمركز عالمي للتكنولوجيا المالية مع توقعات بنمو حجم السوق إلى 5.71 مليار دولار بحلول 2029.. المزيد في هذا التقرير من &lt;a href="/search?f=tweets&amp;amp;q=%23قناة_أزهري_الفضائية"&gt;#قناة_أزهري_الفضائية&lt;/a&gt;
+&lt;a href="/azharitv" title="قناة أزهري الفضائية"&gt;@azharitv&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J43" t="b">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 11:00 PM UTC</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2026-03-22T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23سهم', 'https://x.com/search?f=tweets&amp;q=%23الإمارات', 'https://x.com/search?f=tweets&amp;q=%23قناة_أزهري_الفضائية', 'https://x.com/azharitv']</t>
+        </is>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>66</v>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2035807067764560156</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://x.com/emUrz7g0GrelBIO/status/2035807067764560156</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>https://x.com/emUrz7g0GrelBIO</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>emUrz7g0GrelBIO</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ابو نزاااهه</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1192162310812508162/GYUN4pxo_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'Turki_alalshikh', 'RabehSaqer', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 7:53 PM UTC</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2026-03-22T19:53:00Z</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>49</v>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2035789123034751105</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://x.com/c65kg/status/2035789123034751105</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://x.com/c65kg</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>c65kg</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>عبدالله</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>متى ترجع تفتح باقي الفروع بعد العيد ؟</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>متى ترجع تفتح باقي الفروع بعد العيد ؟</t>
+        </is>
+      </c>
+      <c r="J45" t="b">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 6:42 PM UTC</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2026-03-22T18:42:00Z</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="n">
+        <v>1</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>18</v>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2035782256367698327</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://x.com/Kuwait_law77/status/2035782256367698327</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://x.com/Kuwait_law77</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Kuwait_law77</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>ΝỐÚ₣ ⚜ Al-Dhaferi</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1996321986214084609/DdEzch_R_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ذوقيا يعني بس موعن شي ان بوقت وفاة شهداء الخليج مايكون في احتفالات المفروض</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ذوقيا يعني بس موعن شي ان بوقت وفاة شهداء الخليج مايكون في احتفالات المفروض</t>
+        </is>
+      </c>
+      <c r="J46" t="b">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'Turki_alalshikh', 'RabehSaqer', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 6:14 PM UTC</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>2026-03-22T18:14:00Z</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>35</v>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2035779479163851129</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://x.com/wlla771/status/2035779479163851129</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://x.com/wlla771</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>wlla771</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>WA⚖️</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2035850293976735744/qS7sg9hh_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ابرك الساعات 
+عندي يوم اشوفـك
+@RabehSaqer</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>ابرك الساعات 
+عندي يوم اشوفـك
+&lt;a href="/RabehSaqer" title="Rabeh Saqer رابح صقر"&gt;@RabehSaqer&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J47" t="b">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 6:03 PM UTC</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>2026-03-22T18:03:00Z</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>['https://x.com/RabehSaqer']</t>
+        </is>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>65</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2211</v>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2035776470040334397</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://x.com/AlDawlaTv/status/2035776470040334397</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://x.com/AlDawlaTv</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AlDawlaTv</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>قناة الدولة الفضائية</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1975976036291547136/WPZHmzWA_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>تقارير دولية: مستثمرون اجانب سحبوا من البنوك الاماراتية 800 مليار دولار وغادروا دبي
+#قناة_الدولة_الفضائية
+التردد 12688 V
+تابعونا على رابط البث المباشر :ffs3.gulfsat.com/aldawlatv/i…
+07755556393 إدارة قسم الأخبار
+07855556393 إدارة قسم البرامج وشكاوى المواطنين
+07855556292 إدارة قسم التسويق والإعلانات
+الإشـراف العــام
+ســعد الأوســي</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>تقارير دولية: مستثمرون اجانب سحبوا من البنوك الاماراتية 800 مليار دولار وغادروا دبي
+&lt;a href="/search?f=tweets&amp;amp;q=%23قناة_الدولة_الفضائية"&gt;#قناة_الدولة_الفضائية&lt;/a&gt;
+التردد 12688 V
+تابعونا على رابط البث المباشر :&lt;a href="https://ffs3.gulfsat.com/aldawlatv/index.m3u8"&gt;ffs3.gulfsat.com/aldawlatv/i…&lt;/a&gt;
+07755556393 إدارة قسم الأخبار
+07855556393 إدارة قسم البرامج وشكاوى المواطنين
+07855556292 إدارة قسم التسويق والإعلانات
+الإشـراف العــام
+ســعد الأوســي</t>
+        </is>
+      </c>
+      <c r="J48" t="b">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 5:51 PM UTC</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>2026-03-22T17:51:00Z</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23قناة_الدولة_الفضائية', 'https://ffs3.gulfsat.com/aldawlatv/index.m3u8']</t>
+        </is>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>56</v>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2035766399084445762</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://x.com/RotanaLive/status/2035766399084445762</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://x.com/RotanaLive</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>RotanaLive</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Rotana Live</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1840760580371599361/gqQxhEkP_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>🛑 تنويه وإعتذار 
+نظراً لتعرض الفنان راشد الماجد لظرف صحي طارئ فقد تقرر إلغاء إحيائه لحفل العيد والذي كان من المقرر ان يقام غداً الإثنين ٢٣ مارس ضمن فعاليات العيد.
+كما نفيدكم بأنه سيتم إرجاع قيمة التذاكر بشكل تلقائي في المحفظة عبر تطبيق webook.
+مع تمنياتنا للفنان راشد الماجد الشفاء العاجل</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>🛑 تنويه وإعتذار 
+نظراً لتعرض الفنان راشد الماجد لظرف صحي طارئ فقد تقرر إلغاء إحيائه لحفل العيد والذي كان من المقرر ان يقام غداً الإثنين ٢٣ مارس ضمن فعاليات العيد.
+كما نفيدكم بأنه سيتم إرجاع قيمة التذاكر بشكل تلقائي في المحفظة عبر تطبيق webook.
+مع تمنياتنا للفنان راشد الماجد الشفاء العاجل</t>
+        </is>
+      </c>
+      <c r="J49" t="b">
+        <v>1</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Mohammed Abdo Arena by Emirates NBD</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 5:11 PM UTC</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>2026-03-22T17:11:00Z</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="n">
+        <v>379</v>
+      </c>
+      <c r="S49" t="n">
+        <v>153</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1049</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1770077</v>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2035756208804552943</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2035756208804552943</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>We are extremely sorry for the inconvenience caused to you, and we have replied you via direct message already.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>We are extremely sorry for the inconvenience caused to you, and we have replied you via direct message already.</t>
+        </is>
+      </c>
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>['koko_isa8']</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 4:31 PM UTC</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>2026-03-22T16:31:00Z</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>28</v>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2035752651795861698</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://x.com/koko_isa8/status/2035752651795861698</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://x.com/koko_isa8</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>koko_isa8</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>κoκo мadeмöıseιιe⁸ 💅🏽</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2035262775103242240/J6m7iJmF_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE @AppleSupport i have been struggling with my apple wallet for 4 months now. Since i changed from iphone14 to 17. I cannot add my cards (contact issuer) i have spoken to both of you &amp; the problem has not been resolved yet. All steps were done from both sides too!</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; &lt;a href="/AppleSupport" title="Apple Support"&gt;@AppleSupport&lt;/a&gt; i have been struggling with my apple wallet for 4 months now. Since i changed from iphone14 to 17. I cannot add my cards (contact issuer) i have spoken to both of you &amp;amp; the problem has not been resolved yet. All steps were done from both sides too!</t>
+        </is>
+      </c>
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 4:17 PM UTC</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>2026-03-22T16:17:00Z</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE', 'https://x.com/AppleSupport']</t>
+        </is>
+      </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>46</v>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2035741438630117821</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://x.com/HashemTakriti/status/2035741438630117821</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://x.com/HashemTakriti</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>HashemTakriti</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Hashem Takriti</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1081667250761990144/23AHZt15_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Thanks, I’ve sent already and waiting for the response.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Thanks, I’ve sent already and waiting for the response.</t>
+        </is>
+      </c>
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 3:32 PM UTC</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>2026-03-22T15:32:00Z</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>14</v>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2035729026812121155</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://x.com/Majjd04/status/2035729026812121155</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://x.com/Majjd04</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Majjd04</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Majd 🇸🇦</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1483815254819844098/qp571X_o_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>كيف احجز للاحتياجات الخاصة؟ جربت ارفع ولا ضبطت معي ما تظهر لي و تواصلت بس محد افادني</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>كيف احجز للاحتياجات الخاصة؟ جربت ارفع ولا ضبطت معي ما تظهر لي و تواصلت بس محد افادني</t>
+        </is>
+      </c>
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 2:43 PM UTC</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2026-03-22T14:43:00Z</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>66</v>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2035725580147298546</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://x.com/JarirBookstore/status/2035725580147298546</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://x.com/JarirBookstore</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>JarirBookstore</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>مكتبة جرير</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/912218642770743296/lhLkOEqF_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>يمكنك التقسيط عن طريق ( الوطنية - كوارا  - تمارا  - تابي ) على الرابط التالي :
+jarir.com/installment-servic… 
+التقسيط عن طريق بنك ساب على الرابط التالي :
+ jarir.com/0percent-installme… 
+التقسيط عن طريق بنك الامارت دبي الوطني على الرابط التالي :
+jarir.com/enbd-zero-percent-… 
+ شكرًا لك</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>يمكنك التقسيط عن طريق ( الوطنية - كوارا  - تمارا  - تابي ) على الرابط التالي :
+&lt;a href="https://www.jarir.com/installment-service-methods"&gt;jarir.com/installment-servic…&lt;/a&gt; 
+التقسيط عن طريق بنك ساب على الرابط التالي :
+ &lt;a href="https://www.jarir.com/0percent-installment-sabb-bank"&gt;jarir.com/0percent-installme…&lt;/a&gt; 
+التقسيط عن طريق بنك الامارت دبي الوطني على الرابط التالي :
+&lt;a href="https://www.jarir.com/enbd-zero-percent-installment"&gt;jarir.com/enbd-zero-percent-…&lt;/a&gt; 
+ شكرًا لك</t>
+        </is>
+      </c>
+      <c r="J54" t="b">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>['Ra_50_']</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 2:29 PM UTC</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2026-03-22T14:29:00Z</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>['https://www.jarir.com/installment-service-methods', 'https://www.jarir.com/0percent-installment-sabb-bank', 'https://www.jarir.com/enbd-zero-percent-installment']</t>
+        </is>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3239</v>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2035685942602989979</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://x.com/RotanaLive/status/2035685942602989979</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://x.com/RotanaLive</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>RotanaLive</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Rotana Live</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1840760580371599361/gqQxhEkP_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>رابح صقر يفتتح "فعاليات العيد" في الرياض معلنا "حنا لآل سعود دروع لأراضيك" في ليلة لن تنسى بدعم من هيئة الترفيه وتنظيم روتانا 
+اعتاد الجمهور دوما ان تأتي الحفلات التي تقيمها مجموعة روتانا للموسيقى مختلفة على المستوى الفني والتنظيمي، وتحقق هذا بنجاح وتفاعل كبيرين في الحدث الجماهيري الضخم الذي افتتح به "صقر الاغنية السعودية والعربية" النجم رابح صقر حفلات عيد الفطر السعيد 2026 الذي أقيم في مدينة الرياض ضمن شعار "فعاليات العيد والفرحة تزيد" بدعم من الهيئة العامة للترفيه التي يرأس مجلس ادارتها معالي المستشار تركي بن عبد المحسن آل الشيخ، ومن تنظيم وإشراف مجموعة روتانا للموسيقى في مسرح "محمد عبده أرينا -بنك الإمارات دبي الوطني". 
+ولأن العيد في هذه الليلة جاء عيدين، حيث تزامن موعده مع ثاني ايام عيد الفطر، ومناسبة عيد الأم ، لذا أمتع الصقر الحضور الغفير سواء الذي ملئ  المسرح او تابع النقل المباشر له على قنوات روتانا، بليلة استثنائية جمعت الحب، بأشكاله ومعانيه الوطنية والعاطفية، وألوانه وموسيقاه الطربية والشعبية ، استعد لها جيدا "بوصقر" والفرقة الموسيقة بقيادة المايسترو هاني فرحات، حيث اجرى رابح بروفات مكثفة على قرابة 33 اغنية اختار بينها ثلاثين عملا غناها في برنامج تضمن هذه الروائع: (ابرك الساعات، افهمك، عيدي مبارك ، عمار يادار السعد، تقدر ، الصراحه، اللي ماخطر ع البال، لاتجي يمي، كل انسان يخطي، صدقيني، البشاره، غرام أطفال ، خلنا كذا حلوين، خلاص، وش رأيك الليله، العباة الرهيفة، انت ملك، الذهب اصلي، سرى الليل، ما عاد تسأل، لا تمنن، عشر أشياء، عيونه، الواقع، سقي، ضعفي محبة، مغرورة ازعل عليك، يا دار) قدمها على فقرتين تخللتهما استراحة قصيرة. 
+وكان الأستاذ سالم الهندي رئيس مجلس الإدارة والرئيس التنفيذي لمجموعة روتانا للموسيقى، في استقبال رابح صقر عند وصوله الحفل، والتقطا الصور التذكارية امام الـMediaWall ثم التقيا سويا مع أهل الإعلام والسوشيال ميديا، فقال الصقر ان رسالته من خلال هذا الحفل هي إسعاد الناس، مضيفا: "جئت أعايد عليكم في حفل عنوانه العيد والفرح .. وادعوا الله تعالى ان يديم على وطننا نعمة الأمن والأمان في ظل قيادة مولاي خادم الحرمين الشريفين الملك سلمان بن عبد العزير حفظه الله، وولي عهده الأمين صاحب السمو الملكي الأمير محمد بن سلمان رعاه الله، مشيدا بالقوات السعودية التي تقوم بواجبها في مختلف القطاعات". وكشف رابح انه يستعد في القريب لتقديم مجموعة من الأعمال الجديدة بينها اغاني وطنية، وأغنية رياضية لمؤازرة المنتخب السعودي لكرة القدم الذي سيشارك في كأس العالم 2026 . واثنى الصقر بالدور الذي تقدمه روتانا في صناعة الموسيقى والترفيه مشيدا بما شاهده من اداء كبير قام به طاقمها لتنظيم هذا الحفل الكبير . 
+اما ختام الحفل ، فجاء رائعا ومؤثرا اختصر معناه ورسالته بصوت رابح صقر وترديد الجمهور معه رائعته "يا دار" وجملته  القائلة "حنا لآل سعود دروع لأراضيك…" ، وحرص رابح ان يوثق نجاح ليلة العيد فالتقط فيديو سيلفي يجمعه والجمهور ، متمنيا "عسى الله يجعل أيامكم جميعها أعياد" .
+@Turki_alalshikh 
+@RabehSaqer 
+@salhendi 
+@EidSeason 
+@EmiratesNBD_KSA 
+@Mabdoarena</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>رابح صقر يفتتح &amp;#34;فعاليات العيد&amp;#34; في الرياض معلنا &amp;#34;حنا لآل سعود دروع لأراضيك&amp;#34; في ليلة لن تنسى بدعم من هيئة الترفيه وتنظيم روتانا 
+اعتاد الجمهور دوما ان تأتي الحفلات التي تقيمها مجموعة روتانا للموسيقى مختلفة على المستوى الفني والتنظيمي، وتحقق هذا بنجاح وتفاعل كبيرين في الحدث الجماهيري الضخم الذي افتتح به &amp;#34;صقر الاغنية السعودية والعربية&amp;#34; النجم رابح صقر حفلات عيد الفطر السعيد 2026 الذي أقيم في مدينة الرياض ضمن شعار &amp;#34;فعاليات العيد والفرحة تزيد&amp;#34; بدعم من الهيئة العامة للترفيه التي يرأس مجلس ادارتها معالي المستشار تركي بن عبد المحسن آل الشيخ، ومن تنظيم وإشراف مجموعة روتانا للموسيقى في مسرح &amp;#34;محمد عبده أرينا -بنك الإمارات دبي الوطني&amp;#34;. 
+ولأن العيد في هذه الليلة جاء عيدين، حيث تزامن موعده مع ثاني ايام عيد الفطر، ومناسبة عيد الأم ، لذا أمتع الصقر الحضور الغفير سواء الذي ملئ  المسرح او تابع النقل المباشر له على قنوات روتانا، بليلة استثنائية جمعت الحب، بأشكاله ومعانيه الوطنية والعاطفية، وألوانه وموسيقاه الطربية والشعبية ، استعد لها جيدا &amp;#34;بوصقر&amp;#34; والفرقة الموسيقة بقيادة المايسترو هاني فرحات، حيث اجرى رابح بروفات مكثفة على قرابة 33 اغنية اختار بينها ثلاثين عملا غناها في برنامج تضمن هذه الروائع: (ابرك الساعات، افهمك، عيدي مبارك ، عمار يادار السعد، تقدر ، الصراحه، اللي ماخطر ع البال، لاتجي يمي، كل انسان يخطي، صدقيني، البشاره، غرام أطفال ، خلنا كذا حلوين، خلاص، وش رأيك الليله، العباة الرهيفة، انت ملك، الذهب اصلي، سرى الليل، ما عاد تسأل، لا تمنن، عشر أشياء، عيونه، الواقع، سقي، ضعفي محبة، مغرورة ازعل عليك، يا دار) قدمها على فقرتين تخللتهما استراحة قصيرة. 
+وكان الأستاذ سالم الهندي رئيس مجلس الإدارة والرئيس التنفيذي لمجموعة روتانا للموسيقى، في استقبال رابح صقر عند وصوله الحفل، والتقطا الصور التذكارية امام الـMediaWall ثم التقيا سويا مع أهل الإعلام والسوشيال ميديا، فقال الصقر ان رسالته من خلال هذا الحفل هي إسعاد الناس، مضيفا: &amp;#34;جئت أعايد عليكم في حفل عنوانه العيد والفرح .. وادعوا الله تعالى ان يديم على وطننا نعمة الأمن والأمان في ظل قيادة مولاي خادم الحرمين الشريفين الملك سلمان بن عبد العزير حفظه الله، وولي عهده الأمين صاحب السمو الملكي الأمير محمد بن سلمان رعاه الله، مشيدا بالقوات السعودية التي تقوم بواجبها في مختلف القطاعات&amp;#34;. وكشف رابح انه يستعد في القريب لتقديم مجموعة من الأعمال الجديدة بينها اغاني وطنية، وأغنية رياضية لمؤازرة المنتخب السعودي لكرة القدم الذي سيشارك في كأس العالم 2026 . واثنى الصقر بالدور الذي تقدمه روتانا في صناعة الموسيقى والترفيه مشيدا بما شاهده من اداء كبير قام به طاقمها لتنظيم هذا الحفل الكبير . 
+اما ختام الحفل ، فجاء رائعا ومؤثرا اختصر معناه ورسالته بصوت رابح صقر وترديد الجمهور معه رائعته &amp;#34;يا دار&amp;#34; وجملته  القائلة &amp;#34;حنا لآل سعود دروع لأراضيك…&amp;#34; ، وحرص رابح ان يوثق نجاح ليلة العيد فالتقط فيديو سيلفي يجمعه والجمهور ، متمنيا &amp;#34;عسى الله يجعل أيامكم جميعها أعياد&amp;#34; .
+&lt;a href="/Turki_alalshikh" title="TURKI ALALSHIKH"&gt;@Turki_alalshikh&lt;/a&gt; 
+&lt;a href="/RabehSaqer" title="Rabeh Saqer رابح صقر"&gt;@RabehSaqer&lt;/a&gt; 
+&lt;a href="/salhendi" title="سالم الهندي"&gt;@salhendi&lt;/a&gt; 
+&lt;a href="/EidSeason" title="فعاليات العيد"&gt;@EidSeason&lt;/a&gt; 
+&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; 
+&lt;a href="/Mabdoarena" title="Mohammed Abdo Arena by Emirates NBD"&gt;@Mabdoarena&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J55" t="b">
+        <v>1</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Mohammed Abdo Arena by Emirates NBD</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 11:52 AM UTC</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2026-03-22T11:52:00Z</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>['https://x.com/Turki_alalshikh', 'https://x.com/RabehSaqer', 'https://x.com/salhendi', 'https://x.com/EidSeason', 'https://x.com/EmiratesNBD_KSA', 'https://x.com/Mabdoarena']</t>
+        </is>
+      </c>
+      <c r="R55" t="n">
+        <v>2</v>
+      </c>
+      <c r="S55" t="n">
+        <v>7</v>
+      </c>
+      <c r="T55" t="n">
+        <v>59</v>
+      </c>
+      <c r="U55" t="n">
+        <v>12686</v>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2035517418068472286</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>https://x.com/RotanaLive/status/2035517418068472286</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://x.com/RotanaLive</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>RotanaLive</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Rotana Live</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1840760580371599361/gqQxhEkP_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>سيلفي الصقر مع الجمهور🦅❤️‍🔥
+#روتانا_لايف
+#فعاليات_العيد
+#رابح_صقر_في_الرياض
+@Turki_alalshikh 
+@RabehSaqer 
+@GEA_SA 
+@EidSeason 
+@Mabdoarena 
+@EmiratesNBD_KSA</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>سيلفي الصقر مع الجمهور🦅❤️‍🔥
+&lt;a href="/search?f=tweets&amp;amp;q=%23روتانا_لايف"&gt;#روتانا_لايف&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23فعاليات_العيد"&gt;#فعاليات_العيد&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23رابح_صقر_في_الرياض"&gt;#رابح_صقر_في_الرياض&lt;/a&gt;
+&lt;a href="/Turki_alalshikh" title="TURKI ALALSHIKH"&gt;@Turki_alalshikh&lt;/a&gt; 
+&lt;a href="/RabehSaqer" title="Rabeh Saqer رابح صقر"&gt;@RabehSaqer&lt;/a&gt; 
+&lt;a href="/GEA_SA" title="الهيئة العامة للترفيه"&gt;@GEA_SA&lt;/a&gt; 
+&lt;a href="/EidSeason" title="فعاليات العيد"&gt;@EidSeason&lt;/a&gt; 
+&lt;a href="/Mabdoarena" title="Mohammed Abdo Arena by Emirates NBD"&gt;@Mabdoarena&lt;/a&gt; 
+&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J56" t="b">
+        <v>1</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Mohammed Abdo Arena by Emirates NBD</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 12:42 AM UTC</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>2026-03-22T00:42:00Z</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23روتانا_لايف', 'https://x.com/search?f=tweets&amp;q=%23فعاليات_العيد', 'https://x.com/search?f=tweets&amp;q=%23رابح_صقر_في_الرياض', 'https://x.com/Turki_alalshikh', 'https://x.com/RabehSaqer', 'https://x.com/GEA_SA', 'https://x.com/EidSeason', 'https://x.com/Mabdoarena', 'https://x.com/EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="R56" t="n">
+        <v>4</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="n">
+        <v>41</v>
+      </c>
+      <c r="U56" t="n">
+        <v>9600</v>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2035516933039079770</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://x.com/RotanaLive/status/2035516933039079770</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://x.com/RotanaLive</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>RotanaLive</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Rotana Live</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1840760580371599361/gqQxhEkP_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>الصقر بعد ختام حفلة الليلة🦅
+انتظروا الألبوم الجديد قريباً على #روتانا 💚😍
+#روتانا_لايف
+#فعاليات_العيد
+#رابح_صقر_في_الرياض 
+@Turki_alalshikh 
+@RabehSaqer 
+@salhendi 
+@GEA_SA 
+@EidSeason 
+@Mabdoarena 
+@EmiratesNBD_KSA</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>الصقر بعد ختام حفلة الليلة🦅
+انتظروا الألبوم الجديد قريباً على &lt;a href="/search?f=tweets&amp;amp;q=%23روتانا"&gt;#روتانا&lt;/a&gt; 💚😍
+&lt;a href="/search?f=tweets&amp;amp;q=%23روتانا_لايف"&gt;#روتانا_لايف&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23فعاليات_العيد"&gt;#فعاليات_العيد&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23رابح_صقر_في_الرياض"&gt;#رابح_صقر_في_الرياض&lt;/a&gt; 
+&lt;a href="/Turki_alalshikh" title="TURKI ALALSHIKH"&gt;@Turki_alalshikh&lt;/a&gt; 
+&lt;a href="/RabehSaqer" title="Rabeh Saqer رابح صقر"&gt;@RabehSaqer&lt;/a&gt; 
+&lt;a href="/salhendi" title="سالم الهندي"&gt;@salhendi&lt;/a&gt; 
+&lt;a href="/GEA_SA" title="الهيئة العامة للترفيه"&gt;@GEA_SA&lt;/a&gt; 
+&lt;a href="/EidSeason" title="فعاليات العيد"&gt;@EidSeason&lt;/a&gt; 
+&lt;a href="/Mabdoarena" title="Mohammed Abdo Arena by Emirates NBD"&gt;@Mabdoarena&lt;/a&gt; 
+&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J57" t="b">
+        <v>1</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Mohammed Abdo Arena by Emirates NBD</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 12:40 AM UTC</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>2026-03-22T00:40:00Z</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23روتانا', 'https://x.com/search?f=tweets&amp;q=%23روتانا_لايف', 'https://x.com/search?f=tweets&amp;q=%23فعاليات_العيد', 'https://x.com/search?f=tweets&amp;q=%23رابح_صقر_في_الرياض', 'https://x.com/Turki_alalshikh', 'https://x.com/RabehSaqer', 'https://x.com/salhendi', 'https://x.com/GEA_SA', 'https://x.com/EidSeason', 'https://x.com/Mabdoarena', 'https://x.com/EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" t="n">
+        <v>19</v>
+      </c>
+      <c r="T57" t="n">
+        <v>134</v>
+      </c>
+      <c r="U57" t="n">
+        <v>26582</v>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2035724584830591430</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://x.com/AbhishekSu38296/status/2035724584830591430</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://x.com/AbhishekSu38296</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AbhishekSu38296</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Stock market information</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2029994100305580035/frXXlTOf_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>The 60.72% IDBI Bank sale was scrapped in March 2026 after bids from Fairfax and Emirates NBD missed the ₹70,000–72,000 crore reserve. This triggered a 15% share crash, leaving the government and LIC with a 94.72% stake. A smaller 10–15% OFS is now being considered.
+#IDBI</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>The 60.72% IDBI Bank sale was scrapped in March 2026 after bids from Fairfax and Emirates NBD missed the ₹70,000–72,000 crore reserve. This triggered a 15% share crash, leaving the government and LIC with a 94.72% stake. A smaller 10–15% OFS is now being considered.
+&lt;a href="/search?f=tweets&amp;amp;q=%23IDBI"&gt;#IDBI&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J58" t="b">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 2:25 PM UTC</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>2026-03-22T14:25:00Z</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23IDBI']</t>
+        </is>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>104</v>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2035722359915626934</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://x.com/shamarihm1991/status/2035722359915626934</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://x.com/shamarihm1991</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>shamarihm1991</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>HY91 🤍</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1944820888567713792/Vxafwksb_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>🇸🇦🇸🇦🇸🇦🇸🇦🤍🤍🤍🤍</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>🇸🇦🇸🇦🇸🇦🇸🇦🤍🤍🤍🤍</t>
+        </is>
+      </c>
+      <c r="J59" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'Turki_alalshikh', 'RabehSaqer', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 2:16 PM UTC</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>2026-03-22T14:16:00Z</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>40</v>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2035718138407374875</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_EGY/status/2035718138407374875</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_EGY</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_EGY</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Sports, teamwork, and Ramadan spirit came alive at Emirates NBD Ramadan Tournament 2026 !
+68 teams and 100 players competed across multiple sports in an amazing display of energy and friendly competition.
+Thank you to all participants and congrats to the winners!
+Tax Registration Number: 204-897-319</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Sports, teamwork, and Ramadan spirit came alive at Emirates NBD Ramadan Tournament 2026 !
+68 teams and 100 players competed across multiple sports in an amazing display of energy and friendly competition.
+Thank you to all participants and congrats to the winners!
+Tax Registration Number: 204-897-319</t>
+        </is>
+      </c>
+      <c r="J60" t="b">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 2:00 PM UTC</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>2026-03-22T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>46</v>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2035718138285719777</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_EGY/status/2035718138285719777</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_EGY</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_EGY</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>أجواء رمضان والرياضة وروح الفريق في بطولة بنك الإمارات دبي الوطني الرمضانية 2026 !
+بمشاركة 68 فريقًا و100 لاعب تنافسوا في رياضات متنوعة  في أجواء مليئة بالحماس والروح الرياضية.
+شكرًا لكل المشاركين على مساهمتهم في نجاحها، ومبروك للفائزين!
+رقم التسجيل الضريبي: 319-897-204</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>أجواء رمضان والرياضة وروح الفريق في بطولة بنك الإمارات دبي الوطني الرمضانية 2026 !
+بمشاركة 68 فريقًا و100 لاعب تنافسوا في رياضات متنوعة  في أجواء مليئة بالحماس والروح الرياضية.
+شكرًا لكل المشاركين على مساهمتهم في نجاحها، ومبروك للفائزين!
+رقم التسجيل الضريبي: 319-897-204</t>
+        </is>
+      </c>
+      <c r="J61" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 2:00 PM UTC</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>2026-03-22T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>93</v>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2035716601996317089</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://x.com/getferel/status/2035716601996317089</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://x.com/getferel</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>getferel</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Ferel</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2033220007656873984/jNeAtQ4g_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>IDBI Bank divestment story continues... 📋
+After the strategic sale fell through (bids from Emirates NBD and Fairfax India fell short of reserve price), the government is now exploring OFS route.
+Current setup:
+• Govt: 45.48%
+• LIC: 49.24%
+• Public float: Just 5.29% 👀
+Low float = poor price discovery. Expanding it to 15-20% could be a game-changer for valuation.
+Worth watching when it happens. #GetFreel</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>IDBI Bank divestment story continues... 📋
+After the strategic sale fell through (bids from Emirates NBD and Fairfax India fell short of reserve price), the government is now exploring OFS route.
+Current setup:
+• Govt: 45.48%
+• LIC: 49.24%
+• Public float: Just 5.29% 👀
+Low float = poor price discovery. Expanding it to 15-20% could be a game-changer for valuation.
+Worth watching when it happens. &lt;a href="/search?f=tweets&amp;amp;q=%23GetFreel"&gt;#GetFreel&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 1:53 PM UTC</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>2026-03-22T13:53:00Z</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23GetFreel']</t>
+        </is>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>68</v>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2035716516130562209</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035716516130562209</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>B- 1.89% @SelmaRomola @semeet @ibushra_03</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>B- 1.89% &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J63" t="b">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 1:53 PM UTC</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>2026-03-22T13:53:00Z</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>['https://x.com/SelmaRomola', 'https://x.com/semeet', 'https://x.com/ibushra_03']</t>
+        </is>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>13</v>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2035716452444234063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035716452444234063</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>B- 1.89% @Emy191990 @parulghalout @Salma2232019</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>B- 1.89% &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J64" t="b">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 1:53 PM UTC</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>2026-03-22T13:53:00Z</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
+        </is>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>15</v>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2035716232872399173</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035716232872399173</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program @Salma2232019 @semeet @SelmaRomola</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J65" t="b">
+        <v>0</v>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 1:52 PM UTC</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>2026-03-22T13:52:00Z</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>['https://x.com/Salma2232019', 'https://x.com/semeet', 'https://x.com/SelmaRomola']</t>
+        </is>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>11</v>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2035716104497369325</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035716104497369325</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J66" t="b">
+        <v>0</v>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 1:51 PM UTC</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>2026-03-22T13:51:00Z</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
+        </is>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>11</v>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2035715949375152148</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035715949375152148</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @semeet @parulghalout</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J67" t="b">
+        <v>0</v>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 1:51 PM UTC</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>2026-03-22T13:51:00Z</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>['https://x.com/SelmaRomola', 'https://x.com/semeet', 'https://x.com/parulghalout']</t>
+        </is>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>22</v>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2035715849328435711</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035715849328435711</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD 
+@Emy191990 @zeynp_qas @Salma2232019</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD 
+&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J68" t="b">
+        <v>0</v>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 1:50 PM UTC</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>2026-03-22T13:50:00Z</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/zeynp_qas', 'https://x.com/Salma2232019']</t>
+        </is>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>19</v>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2035715583749357698</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035715583749357698</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Via the ENBD X Mobile App. @parulghalout @SelmaRomola @semeet</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Via the ENBD X Mobile App. &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J69" t="b">
+        <v>0</v>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 1:49 PM UTC</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>2026-03-22T13:49:00Z</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>['https://x.com/parulghalout', 'https://x.com/SelmaRomola', 'https://x.com/semeet']</t>
+        </is>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>17</v>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2035715466585665903</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2035715466585665903</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Via the ENBD X Mobile App. @Emy191990 @zeynp_qas @Salma2232019</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J70" t="b">
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 1:49 PM UTC</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>2026-03-22T13:49:00Z</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/zeynp_qas', 'https://x.com/Salma2232019']</t>
+        </is>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>17</v>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2035705111163347210</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://x.com/TIM7bmc/status/2035705111163347210</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://x.com/TIM7bmc</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>TIM7bmc</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>TIM</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2017633682152955904/-dY3RGIB_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>متى يوم كم</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>متى يوم كم</t>
+        </is>
+      </c>
+      <c r="J71" t="b">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'Turki_alalshikh', 'RabehSaqer', 'salhendi', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 1:08 PM UTC</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>2026-03-22T13:08:00Z</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>21</v>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2035699923010687223</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://x.com/Hrashid50798422/status/2035699923010687223</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://x.com/Hrashid50798422</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Hrashid50798422</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>H rashid</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1248165934700748800/Is_z54rr_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>التذاكر مبالغ فيها جدا المتبقي اقل تذكرة 1150  ريال وبعدها2300 , 2875 ,3450  شدعوه والناس بعد رمضان والعيد آخر اسبوع على الرواتب 
+ثانيا يا روتانا رفقا بالناس ناس ودها تحضر لكن عدم المبالغة في قيمة التذاكر ومراعاة ظروف الناس وعلى هيئة الترفيه وضع حد لاسعار التذاكر</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>التذاكر مبالغ فيها جدا المتبقي اقل تذكرة 1150  ريال وبعدها2300 , 2875 ,3450  شدعوه والناس بعد رمضان والعيد آخر اسبوع على الرواتب 
+ثانيا يا روتانا رفقا بالناس ناس ودها تحضر لكن عدم المبالغة في قيمة التذاكر ومراعاة ظروف الناس وعلى هيئة الترفيه وضع حد لاسعار التذاكر</t>
+        </is>
+      </c>
+      <c r="J72" t="b">
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'Turki_alalshikh', 'RashedTV', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 12:47 PM UTC</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>2026-03-22T12:47:00Z</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>61</v>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2035659271359131969</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://x.com/Bnok24/status/2035659271359131969</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://x.com/Bnok24</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Bnok24</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>bnok 24</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2035297929708113920/61ymWMLp_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>#بنك_الإمارات_دبي_الوطني_مصر يحتفي بعيد الأم مع موظفيه بتجربة مبتكرة «فيديو»
+التفاصيل|  bnok24.com/?p=255004</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_دبي_الوطني_مصر"&gt;#بنك_الإمارات_دبي_الوطني_مصر&lt;/a&gt; يحتفي بعيد الأم مع موظفيه بتجربة مبتكرة «فيديو»
+التفاصيل|  &lt;a href="https://www.bnok24.com/?p=255004"&gt;bnok24.com/?p=255004&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 10:06 AM UTC</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>2026-03-22T10:06:00Z</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_دبي_الوطني_مصر', 'https://www.bnok24.com/?p=255004']</t>
+        </is>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>28</v>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2035656314034995295</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2035656314034995295</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #987132 in the subject line.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #987132 in the subject line.</t>
+        </is>
+      </c>
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>['ZahidanMuhamma']</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 9:54 AM UTC</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>2026-03-22T09:54:00Z</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>34</v>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2035654269152420335</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://x.com/i2idz/status/2035654269152420335</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://x.com/i2idz</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>i2idz</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>ابو غامد</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1998178287772741634/Tt5OF6Ex_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>اقسم بالله جدة مدينة سعوديه 
+اقسم بالله جدة مدينة سعوديه 
+اقسم بالله جدة مدينة سعوديه 
+اقسم بالله جدة مدينة سعوديه 
+اقسم بالله جدة مدينة سعوديه 
+اقسم بالله جدة مدينة سعوديه 
+اقسم بالله جدة مدينة سعوديه 
+اقسم بالله جدة مدينة سعوديه 
+اقسم بالله جدة مدينة سعوديه</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>اقسم بالله جدة مدينة سعوديه 
+اقسم بالله جدة مدينة سعوديه 
+اقسم بالله جدة مدينة سعوديه 
+اقسم بالله جدة مدينة سعوديه 
+اقسم بالله جدة مدينة سعوديه 
+اقسم بالله جدة مدينة سعوديه 
+اقسم بالله جدة مدينة سعوديه 
+اقسم بالله جدة مدينة سعوديه 
+اقسم بالله جدة مدينة سعوديه</t>
+        </is>
+      </c>
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 9:46 AM UTC</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>2026-03-22T09:46:00Z</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>97</v>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2035650681592217835</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://x.com/GogoSs398132/status/2035650681592217835</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://x.com/GogoSs398132</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>GogoSs398132</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>🤍🇺🇸🇺🇸</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1641828887070998532/iWgS2ZxH_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>انا من اعلن ملفات ابستين من البيت الابيض 🇺🇸
+انا صوتت علي ذلك حتي يظهر الحق ولا يتستر 
+علي مجرمين</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>انا من اعلن ملفات ابستين من البيت الابيض 🇺🇸
+انا صوتت علي ذلك حتي يظهر الحق ولا يتستر 
+علي مجرمين</t>
+        </is>
+      </c>
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 9:31 AM UTC</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>2026-03-22T09:31:00Z</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>347</v>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2035648439355158926</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://x.com/0O1LR/status/2035648439355158926</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://x.com/0O1LR</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>0O1LR</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>𐑞.</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2018851871562014720/__sb1sYW_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>ملفات ابستين لاشكالك النجسة مثل الذباب ما تروحون الا للاشياء الوصخه</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>ملفات ابستين لاشكالك النجسة مثل الذباب ما تروحون الا للاشياء الوصخه</t>
+        </is>
+      </c>
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>['GogoSs398132', 'RotanaLive', 'RotanaMusic', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 9:23 AM UTC</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>2026-03-22T09:23:00Z</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>16</v>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2035648196832121041</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://x.com/0O1LR/status/2035648196832121041</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://x.com/0O1LR</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>0O1LR</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>𐑞.</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2018851871562014720/__sb1sYW_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>الكل يدري ان حكامنا مافي شي اثبت عليهم بملفات ابستين لكن انتم صغار العقول ينضحك عليكم بسهولة</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>الكل يدري ان حكامنا مافي شي اثبت عليهم بملفات ابستين لكن انتم صغار العقول ينضحك عليكم بسهولة</t>
+        </is>
+      </c>
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>['GogoSs398132', 'RotanaLive', 'RotanaMusic', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 9:22 AM UTC</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>2026-03-22T09:22:00Z</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="n">
+        <v>14</v>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2035648162216427779</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://x.com/GogoSs398132/status/2035648162216427779</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://x.com/GogoSs398132</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>GogoSs398132</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>🤍🇺🇸🇺🇸</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1641828887070998532/iWgS2ZxH_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>انت نايم اصحه و شوف ملفات ابستين</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>انت نايم اصحه و شوف ملفات ابستين</t>
+        </is>
+      </c>
+      <c r="J79" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>['0O1LR', 'RotanaLive', 'RotanaMusic', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 9:21 AM UTC</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>2026-03-22T09:21:00Z</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="n">
+        <v>1</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>28</v>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2035647968301257100</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://x.com/GogoSs398132/status/2035647968301257100</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://x.com/GogoSs398132</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>GogoSs398132</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>🤍🇺🇸🇺🇸</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1641828887070998532/iWgS2ZxH_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>كفي دفاع عن فاسسسسدين</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>كفي دفاع عن فاسسسسدين</t>
+        </is>
+      </c>
+      <c r="J80" t="b">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>['0O1LR', 'RotanaLive', 'RotanaMusic', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 9:21 AM UTC</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>2026-03-22T09:21:00Z</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="n">
+        <v>19</v>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2035647830564520020</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://x.com/GogoSs398132/status/2035647830564520020</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://x.com/GogoSs398132</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>GogoSs398132</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>🤍🇺🇸🇺🇸</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1641828887070998532/iWgS2ZxH_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>ملفات ابستين قالت لي كل شئ ابحث في قوقل</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>ملفات ابستين قالت لي كل شئ ابحث في قوقل</t>
+        </is>
+      </c>
+      <c r="J81" t="b">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>['0O1LR', 'RotanaLive', 'RotanaMusic', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 9:20 AM UTC</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>2026-03-22T09:20:00Z</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="n">
+        <v>1</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="n">
+        <v>28</v>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2035647595045851359</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://x.com/0O1LR/status/2035647595045851359</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://x.com/0O1LR</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>0O1LR</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>𐑞.</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2018851871562014720/__sb1sYW_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>من قالك؟ هذا عيشتكم انتم لانكم ما تعرفون لا الشرف ولا السمعه ولا الاخلاق</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>من قالك؟ هذا عيشتكم انتم لانكم ما تعرفون لا الشرف ولا السمعه ولا الاخلاق</t>
+        </is>
+      </c>
+      <c r="J82" t="b">
+        <v>0</v>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>['GogoSs398132', 'RotanaLive', 'RotanaMusic', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 9:19 AM UTC</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>2026-03-22T09:19:00Z</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="n">
+        <v>3</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" t="n">
+        <v>35</v>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2035647538724745343</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://x.com/GogoSs398132/status/2035647538724745343</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://x.com/GogoSs398132</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>GogoSs398132</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>🤍🇺🇸🇺🇸</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1641828887070998532/iWgS2ZxH_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>الذي يمدح الرخيص الفاسد اذا هو مثله</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>الذي يمدح الرخيص الفاسد اذا هو مثله</t>
+        </is>
+      </c>
+      <c r="J83" t="b">
+        <v>0</v>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>['0O1LR', 'RotanaLive', 'RotanaMusic', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 9:19 AM UTC</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>2026-03-22T09:19:00Z</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="n">
+        <v>17</v>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2035647384156311837</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://x.com/GogoSs398132/status/2035647384156311837</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://x.com/GogoSs398132</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>GogoSs398132</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>🤍🇺🇸🇺🇸</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1641828887070998532/iWgS2ZxH_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>الله علي عيشه بلا شرف و سمعه واخلاق انقلع</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>الله علي عيشه بلا شرف و سمعه واخلاق انقلع</t>
+        </is>
+      </c>
+      <c r="J84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>['0O1LR', 'RotanaLive', 'RotanaMusic', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 9:18 AM UTC</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>2026-03-22T09:18:00Z</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="n">
+        <v>1</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" t="n">
+        <v>37</v>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2035647372311588967</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://x.com/0O1LR/status/2035647372311588967</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://x.com/0O1LR</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>0O1LR</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>𐑞.</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2018851871562014720/__sb1sYW_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>كلن يرى الناس بعين طبعه</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>كلن يرى الناس بعين طبعه</t>
+        </is>
+      </c>
+      <c r="J85" t="b">
+        <v>0</v>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>['GogoSs398132', 'RotanaLive', 'RotanaMusic', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 9:18 AM UTC</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>2026-03-22T09:18:00Z</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="n">
+        <v>1</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" t="n">
+        <v>28</v>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2035647244636991565</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://x.com/GogoSs398132/status/2035647244636991565</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://x.com/GogoSs398132</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>GogoSs398132</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>🤍🇺🇸🇺🇸</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1641828887070998532/iWgS2ZxH_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>لكن فاسسسسدين يبيعون في شرفكم</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>لكن فاسسسسدين يبيعون في شرفكم</t>
+        </is>
+      </c>
+      <c r="J86" t="b">
+        <v>0</v>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>['0O1LR', 'RotanaLive', 'RotanaMusic', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 9:18 AM UTC</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>2026-03-22T09:18:00Z</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="n">
+        <v>1</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" t="n">
+        <v>26</v>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2035647241768091714</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>https://x.com/0O1LR/status/2035647241768091714</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://x.com/0O1LR</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>0O1LR</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>𐑞.</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2018851871562014720/__sb1sYW_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>تتكلم عن الفساد وهذا كلامك؟ انك تشبه شخص بواحد نجس زي ابستين يدل على فساد عقلك حرفيا</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>تتكلم عن الفساد وهذا كلامك؟ انك تشبه شخص بواحد نجس زي ابستين يدل على فساد عقلك حرفيا</t>
+        </is>
+      </c>
+      <c r="J87" t="b">
+        <v>0</v>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>['GogoSs398132', 'RotanaLive', 'RotanaMusic', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 9:18 AM UTC</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>2026-03-22T09:18:00Z</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" t="n">
+        <v>13</v>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2035646986280427927</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://x.com/0O1LR/status/2035646986280427927</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://x.com/0O1LR</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>0O1LR</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>𐑞.</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2018851871562014720/__sb1sYW_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>امرائي معيشيني عيشة تحلم فيها انت واشكالك</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>امرائي معيشيني عيشة تحلم فيها انت واشكالك</t>
+        </is>
+      </c>
+      <c r="J88" t="b">
+        <v>0</v>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>['GogoSs398132', 'RotanaLive', 'RotanaMusic', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 9:17 AM UTC</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>2026-03-22T09:17:00Z</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="n">
+        <v>2</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="n">
+        <v>48</v>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2035646908497047919</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>https://x.com/GogoSs398132/status/2035646908497047919</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://x.com/GogoSs398132</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>GogoSs398132</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>🤍🇺🇸🇺🇸</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1641828887070998532/iWgS2ZxH_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>اقصد ابستين ليبيا و الخليج</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>اقصد ابستين ليبيا و الخليج</t>
+        </is>
+      </c>
+      <c r="J89" t="b">
+        <v>0</v>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>['0O1LR', 'RotanaLive', 'RotanaMusic', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 9:16 AM UTC</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>2026-03-22T09:16:00Z</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="n">
+        <v>1</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>22</v>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2035646831242137950</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://x.com/0O1LR/status/2035646831242137950</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://x.com/0O1LR</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>0O1LR</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>𐑞.</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2018851871562014720/__sb1sYW_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>الفساد في عقلك والله تارك كل بلاوي الدنيا وجاي تكشف فساد العرب في حفلة غنائية</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>الفساد في عقلك والله تارك كل بلاوي الدنيا وجاي تكشف فساد العرب في حفلة غنائية</t>
+        </is>
+      </c>
+      <c r="J90" t="b">
+        <v>0</v>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>['GogoSs398132', 'RotanaLive', 'RotanaMusic', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 9:16 AM UTC</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>2026-03-22T09:16:00Z</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" t="n">
+        <v>13</v>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2035646781757726779</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://x.com/GogoSs398132/status/2035646781757726779</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://x.com/GogoSs398132</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>GogoSs398132</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>🤍🇺🇸🇺🇸</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1641828887070998532/iWgS2ZxH_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>اقصد امرائك الفاسسسسدين انقلع</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>اقصد امرائك الفاسسسسدين انقلع</t>
+        </is>
+      </c>
+      <c r="J91" t="b">
+        <v>0</v>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>['0O1LR', 'RotanaLive', 'RotanaMusic', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 9:16 AM UTC</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>2026-03-22T09:16:00Z</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="n">
+        <v>1</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
+        <v>0</v>
+      </c>
+      <c r="U91" t="n">
+        <v>57</v>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2035646446356009023</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://x.com/GogoSs398132/status/2035646446356009023</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://x.com/GogoSs398132</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>GogoSs398132</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>🤍🇺🇸🇺🇸</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1641828887070998532/iWgS2ZxH_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>ابي اكشف فسسسسساد العرب الرخصيييين
+انت توقف عن نباح في شي ما تفهمه كل تبن</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>ابي اكشف فسسسسساد العرب الرخصيييين
+انت توقف عن نباح في شي ما تفهمه كل تبن</t>
+        </is>
+      </c>
+      <c r="J92" t="b">
+        <v>0</v>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>['0O1LR', 'RotanaLive', 'RotanaMusic', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 9:15 AM UTC</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>2026-03-22T09:15:00Z</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="n">
+        <v>1</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="n">
+        <v>21</v>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2035646264096723099</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://x.com/0O1LR/status/2035646264096723099</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://x.com/0O1LR</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>0O1LR</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>𐑞.</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2018851871562014720/__sb1sYW_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>تقصد اشخاص خل عندك شجاعة وقل من تقصد لا ترمي كلام عام زي كذا وتقول اقصد ناس معينين</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>تقصد اشخاص خل عندك شجاعة وقل من تقصد لا ترمي كلام عام زي كذا وتقول اقصد ناس معينين</t>
+        </is>
+      </c>
+      <c r="J93" t="b">
+        <v>0</v>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>['GogoSs398132', 'RotanaLive', 'RotanaMusic', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 9:14 AM UTC</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>2026-03-22T09:14:00Z</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="n">
+        <v>2</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" t="n">
+        <v>0</v>
+      </c>
+      <c r="U93" t="n">
+        <v>63</v>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2035645979207086206</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://x.com/0O1LR/status/2035645979207086206</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://x.com/0O1LR</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>0O1LR</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>𐑞.</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2018851871562014720/__sb1sYW_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>ليبي وحاط علم امريكا وتنبح على السعودية يعني وش تبي ما ادري</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>ليبي وحاط علم امريكا وتنبح على السعودية يعني وش تبي ما ادري</t>
+        </is>
+      </c>
+      <c r="J94" t="b">
+        <v>0</v>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>['GogoSs398132', 'RotanaLive', 'RotanaMusic', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 9:13 AM UTC</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>2026-03-22T09:13:00Z</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="n">
+        <v>1</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" t="n">
+        <v>24</v>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2035645560116392314</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://x.com/GogoSs398132/status/2035645560116392314</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://x.com/GogoSs398132</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>GogoSs398132</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>🤍🇺🇸🇺🇸</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1641828887070998532/iWgS2ZxH_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>اقصد اشخاص يعرفون انفسهم انت لماذ تتكلم</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>اقصد اشخاص يعرفون انفسهم انت لماذ تتكلم</t>
+        </is>
+      </c>
+      <c r="J95" t="b">
+        <v>0</v>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>['0O1LR', 'RotanaLive', 'RotanaMusic', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 9:11 AM UTC</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>2026-03-22T09:11:00Z</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="n">
+        <v>1</v>
+      </c>
+      <c r="S95" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" t="n">
+        <v>44</v>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2035645292490465638</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://x.com/GogoSs398132/status/2035645292490465638</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://x.com/GogoSs398132</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>GogoSs398132</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>🤍🇺🇸🇺🇸</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1641828887070998532/iWgS2ZxH_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>انقلععععععععع</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>انقلععععععععع</t>
+        </is>
+      </c>
+      <c r="J96" t="b">
+        <v>0</v>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>['0O1LR', 'RotanaLive', 'RotanaMusic', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 9:10 AM UTC</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>2026-03-22T09:10:00Z</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="n">
+        <v>1</v>
+      </c>
+      <c r="S96" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" t="n">
+        <v>32</v>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2035644800280547792</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://x.com/0O1LR/status/2035644800280547792</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://x.com/0O1LR</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>0O1LR</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>𐑞.</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2018851871562014720/__sb1sYW_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>سد حلقك</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>سد حلقك</t>
+        </is>
+      </c>
+      <c r="J97" t="b">
+        <v>0</v>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>['GogoSs398132', 'RotanaLive', 'RotanaMusic', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 9:08 AM UTC</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>2026-03-22T09:08:00Z</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="n">
+        <v>2</v>
+      </c>
+      <c r="S97" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" t="n">
+        <v>28</v>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2035633307124212087</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://x.com/GogoSs398132/status/2035633307124212087</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://x.com/GogoSs398132</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>GogoSs398132</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>🤍🇺🇸🇺🇸</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1641828887070998532/iWgS2ZxH_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>يكفي يا حثثثثثثثثثاله العرب</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>يكفي يا حثثثثثثثثثاله العرب</t>
+        </is>
+      </c>
+      <c r="J98" t="b">
+        <v>0</v>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'RotanaMusic', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 8:22 AM UTC</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>2026-03-22T08:22:00Z</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="n">
+        <v>1</v>
+      </c>
+      <c r="S98" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" t="n">
+        <v>0</v>
+      </c>
+      <c r="U98" t="n">
+        <v>477</v>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2035631300061585868</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://x.com/rebekahpierce/status/2035631300061585868</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://x.com/rebekahpierce</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>rebekahpierce</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>تيكيت ماستر</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1966481551916417024/GEq1e0sW_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>موعدنا غداً مع الفنان الكبير راشد الماجد 🔥
+Webook.com
+#فعاليات_العيد
+#روتانا_لايف  
+@Turki_alalshikh  
+@RashedTV  
+@walidfayed 
+@GEA_SA  
+@EidSeason  
+@Mabdoarena  
+@EmiratesNBD_KSA</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>موعدنا غداً مع الفنان الكبير راشد الماجد 🔥
+&lt;a href="http://Webook.com"&gt;Webook.com&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23فعاليات_العيد"&gt;#فعاليات_العيد&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23روتانا_لايف"&gt;#روتانا_لايف&lt;/a&gt;  
+&lt;a href="/Turki_alalshikh" title="TURKI ALALSHIKH"&gt;@Turki_alalshikh&lt;/a&gt;  
+&lt;a href="/RashedTV" title="راشد الماجد"&gt;@RashedTV&lt;/a&gt;  
+&lt;a href="/walidfayed" title="Walid Fayed وليد فايد"&gt;@walidfayed&lt;/a&gt; 
+&lt;a href="/GEA_SA" title="الهيئة العامة للترفيه"&gt;@GEA_SA&lt;/a&gt;  
+&lt;a href="/EidSeason" title="فعاليات العيد"&gt;@EidSeason&lt;/a&gt;  
+&lt;a href="/Mabdoarena" title="Mohammed Abdo Arena by Emirates NBD"&gt;@Mabdoarena&lt;/a&gt;  
+&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J99" t="b">
+        <v>0</v>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 8:14 AM UTC</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>2026-03-22T08:14:00Z</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>['http://Webook.com', 'https://x.com/search?f=tweets&amp;q=%23فعاليات_العيد', 'https://x.com/search?f=tweets&amp;q=%23روتانا_لايف', 'https://x.com/Turki_alalshikh', 'https://x.com/RashedTV', 'https://x.com/walidfayed', 'https://x.com/GEA_SA', 'https://x.com/EidSeason', 'https://x.com/Mabdoarena', 'https://x.com/EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="n">
+        <v>1</v>
+      </c>
+      <c r="T99" t="n">
+        <v>1</v>
+      </c>
+      <c r="U99" t="n">
+        <v>63</v>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2035631055676543154</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://x.com/Londoner____/status/2035631055676543154</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://x.com/Londoner____</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Londoner____</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Londoner</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1796934582421331968/sZzCe04S_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>. 
+👏🏽😍</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>. 
+👏🏽😍</t>
+        </is>
+      </c>
+      <c r="J100" t="b">
+        <v>0</v>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 8:13 AM UTC</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>2026-03-22T08:13:00Z</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="n">
+        <v>0</v>
+      </c>
+      <c r="S100" t="n">
+        <v>0</v>
+      </c>
+      <c r="T100" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" t="n">
+        <v>435</v>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2035628322084827202</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://x.com/Wecom_Ticket/status/2035628322084827202</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://x.com/Wecom_Ticket</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Wecom_Ticket</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>تذاكر ويكوم Ticket</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2016963430436007936/jVE--p_u_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>متوفر تذاكر حفل الفنان الكبير #راشد_الماجد  في الرياض 😍🤍
+إحجز تذكرتك الأن وإضمن دخولك ❤️ 
+رابط الشراء في البايو 💜🫶</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>متوفر تذاكر حفل الفنان الكبير &lt;a href="/search?f=tweets&amp;amp;q=%23راشد_الماجد"&gt;#راشد_الماجد&lt;/a&gt;  في الرياض 😍🤍
+إحجز تذكرتك الأن وإضمن دخولك ❤️ 
+رابط الشراء في البايو 💜🫶</t>
+        </is>
+      </c>
+      <c r="J101" t="b">
+        <v>0</v>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 8:03 AM UTC</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>2026-03-22T08:03:00Z</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23راشد_الماجد']</t>
+        </is>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" t="n">
+        <v>0</v>
+      </c>
+      <c r="U101" t="n">
+        <v>75</v>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2035628151070507218</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://x.com/vurg2n/status/2035628151070507218</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://x.com/vurg2n</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>vurg2n</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>تذاكر زون || Ticket zone</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2031049559921557504/kC_pPQZD_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>متوفر لدينا تذاكر حفل الفنان #راشد_الماجد 😍😍
+لتواصل عبر الواتس آب في البايو 📍</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>متوفر لدينا تذاكر حفل الفنان &lt;a href="/search?f=tweets&amp;amp;q=%23راشد_الماجد"&gt;#راشد_الماجد&lt;/a&gt; 😍😍
+لتواصل عبر الواتس آب في البايو 📍</t>
+        </is>
+      </c>
+      <c r="J102" t="b">
+        <v>0</v>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 8:02 AM UTC</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>2026-03-22T08:02:00Z</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23راشد_الماجد']</t>
+        </is>
+      </c>
+      <c r="R102" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" t="n">
+        <v>1</v>
+      </c>
+      <c r="U102" t="n">
+        <v>83</v>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2035627541105348902</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2035627541105348902</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Don’t click unfamiliar links.
+Especially in SMS, WhatsApp, or DMs. When in doubt, don’t tap.
+Stay safe. Stay vigilant. #UnitedAgainstFraud
+emiratesnbd.com/en/campaigns…</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Don’t click unfamiliar links.
+Especially in SMS, WhatsApp, or DMs. When in doubt, don’t tap.
+Stay safe. Stay vigilant. &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;
+&lt;a href="https://www.emiratesnbd.com/en/campaigns/united-against-fraud"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J103" t="b">
+        <v>0</v>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>2026-03-22T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud', 'https://www.emiratesnbd.com/en/campaigns/united-against-fraud']</t>
+        </is>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" t="n">
+        <v>5</v>
+      </c>
+      <c r="U103" t="n">
+        <v>939</v>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2035620402559410420</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://x.com/alking9882/status/2035620402559410420</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://x.com/alking9882</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>alking9882</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>aDm</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/3753963142/492b1380cad1cc1340b94dcf1542b024_bigger.jpeg</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>لايوجد فرع بمنطقتي</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>لايوجد فرع بمنطقتي</t>
+        </is>
+      </c>
+      <c r="J104" t="b">
+        <v>0</v>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 7:31 AM UTC</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>2026-03-22T07:31:00Z</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" t="n">
+        <v>23</v>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2035620229947035798</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2035620229947035798</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>لفتح حساب بنكي في المملكة يجب زيارة أقرب فرع. شكراً لك.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>لفتح حساب بنكي في المملكة يجب زيارة أقرب فرع. شكراً لك.</t>
+        </is>
+      </c>
+      <c r="J105" t="b">
+        <v>0</v>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>['alking9882']</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 7:30 AM UTC</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>2026-03-22T07:30:00Z</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="n">
+        <v>1</v>
+      </c>
+      <c r="S105" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" t="n">
+        <v>34</v>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2035618875723661469</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>https://x.com/ghadeerb1977/status/2035618875723661469</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://x.com/ghadeerb1977</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ghadeerb1977</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Her majesty 💖غدير🦚💎blsh المتقاعده الصغيره</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2035662655374213120/YbNNVN8m_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>حاول تخلي العلاقه شوي محدوده🎶💦خلاص</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>حاول تخلي العلاقه شوي محدوده🎶💦خلاص</t>
+        </is>
+      </c>
+      <c r="J106" t="b">
+        <v>0</v>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'Turki_alalshikh', 'RabehSaqer', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 7:25 AM UTC</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>2026-03-22T07:25:00Z</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" t="n">
+        <v>29</v>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2035613821310558693</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://x.com/xl111u/status/2035613821310558693</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>https://x.com/xl111u</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>xl111u</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>رَ</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2032992919221829632/yCQ5aVTg_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>والله اح</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>والله اح</t>
+        </is>
+      </c>
+      <c r="J107" t="b">
+        <v>0</v>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'Turki_alalshikh', 'RabehSaqer', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 7:05 AM UTC</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>2026-03-22T07:05:00Z</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" t="n">
+        <v>40</v>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2035612442487661044</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2035612442487661044</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Spot the red flags before it’s too late. Fake jobs ask for fees, transfers or banking information. Always verify, stay alert and protect yourself. #UnitedAgainstFraud</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Spot the red flags before it’s too late. Fake jobs ask for fees, transfers or banking information. Always verify, stay alert and protect yourself. &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J108" t="b">
+        <v>0</v>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 7:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>2026-03-22T07:00:00Z</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud']</t>
+        </is>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="n">
+        <v>1</v>
+      </c>
+      <c r="T108" t="n">
+        <v>5</v>
+      </c>
+      <c r="U108" t="n">
+        <v>761</v>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2035612442235998644</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2035612442235998644</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>انتبه إلى الإشارات التحذيرية قبل فوات الأوان. تطلب الوظائف الوهمية عادةً رسومًا أو تحويلات مالية أو معلومات مصرفية. +احرص دائمًا على التحقق، وابقَ يقظًا لحماية نفسك.
+#متحدون_ضد_الاحتيال</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>انتبه إلى الإشارات التحذيرية قبل فوات الأوان. تطلب الوظائف الوهمية عادةً رسومًا أو تحويلات مالية أو معلومات مصرفية. +احرص دائمًا على التحقق، وابقَ يقظًا لحماية نفسك.
+&lt;a href="/search?f=tweets&amp;amp;q=%23متحدون_ضد_الاحتيال"&gt;#متحدون_ضد_الاحتيال&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J109" t="b">
+        <v>0</v>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 7:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>2026-03-22T07:00:00Z</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23متحدون_ضد_الاحتيال']</t>
+        </is>
+      </c>
+      <c r="R109" t="n">
+        <v>1</v>
+      </c>
+      <c r="S109" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" t="n">
+        <v>4</v>
+      </c>
+      <c r="U109" t="n">
+        <v>694</v>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2035603678409732156</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>https://x.com/alking9882/status/2035603678409732156</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>https://x.com/alking9882</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>alking9882</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>aDm</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/3753963142/492b1380cad1cc1340b94dcf1542b024_bigger.jpeg</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>المملكة</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>المملكة</t>
+        </is>
+      </c>
+      <c r="J110" t="b">
+        <v>0</v>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 6:25 AM UTC</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>2026-03-22T06:25:00Z</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="n">
+        <v>1</v>
+      </c>
+      <c r="S110" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" t="n">
+        <v>34</v>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2035601453960618151</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2035601453960618151</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>يرجى تأكيد اذا كان طلبك لفتح حساب في بنك الامارات دبي الوطني فرع الامارات أو المملكة.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>يرجى تأكيد اذا كان طلبك لفتح حساب في بنك الامارات دبي الوطني فرع الامارات أو المملكة.</t>
+        </is>
+      </c>
+      <c r="J111" t="b">
+        <v>0</v>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>['alking9882']</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 6:16 AM UTC</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>2026-03-22T06:16:00Z</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="n">
+        <v>1</v>
+      </c>
+      <c r="S111" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" t="n">
+        <v>71</v>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2035599627253342599</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>https://x.com/ZahidanMuhamma/status/2035599627253342599</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>https://x.com/ZahidanMuhamma</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>ZahidanMuhamma</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Muhammad Zahidan</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1827047486680137728/R86Fb-lT_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>this bank is crappy I have withdrawal for 300 USD at 5 March but still not receiving my funds and still going on internal validation</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>this bank is crappy I have withdrawal for 300 USD at 5 March but still not receiving my funds and still going on internal validation</t>
+        </is>
+      </c>
+      <c r="J112" t="b">
+        <v>0</v>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 6:09 AM UTC</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>2026-03-22T06:09:00Z</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="n">
+        <v>1</v>
+      </c>
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" t="n">
+        <v>26</v>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2035579487899783553</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>https://x.com/alking9882/status/2035579487899783553</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>https://x.com/alking9882</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>alking9882</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>aDm</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/3753963142/492b1380cad1cc1340b94dcf1542b024_bigger.jpeg</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>انا فالسعودية واريد فتح حساب والرقم يطلب الحساب ولم يصلني حتى الان</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>انا فالسعودية واريد فتح حساب والرقم يطلب الحساب ولم يصلني حتى الان</t>
+        </is>
+      </c>
+      <c r="J113" t="b">
+        <v>0</v>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 4:49 AM UTC</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>2026-03-22T04:49:00Z</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="n">
+        <v>1</v>
+      </c>
+      <c r="S113" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" t="n">
+        <v>0</v>
+      </c>
+      <c r="U113" t="n">
+        <v>27</v>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2035574389006049758</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2035574389006049758</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>مرحباً بك، شكراً لتواصلك معنا. لضمان تجربة مصرفية سلسة وآمنة، يرجى التواصل مع دعم العملاء على مدار الساعة عبر الهاتف أو واتساب على الرقم 971600540000 لمساعدتك في استفسارك.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>مرحباً بك، شكراً لتواصلك معنا. لضمان تجربة مصرفية سلسة وآمنة، يرجى التواصل مع دعم العملاء على مدار الساعة عبر الهاتف أو واتساب على الرقم 971600540000 لمساعدتك في استفسارك.</t>
+        </is>
+      </c>
+      <c r="J114" t="b">
+        <v>0</v>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>['alking9882']</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 4:28 AM UTC</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>2026-03-22T04:28:00Z</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="n">
+        <v>1</v>
+      </c>
+      <c r="S114" t="n">
+        <v>0</v>
+      </c>
+      <c r="T114" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" t="n">
+        <v>31</v>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2035571064231596092</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2035571064231596092</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>مرحباً, يرجى الاتصال بخدمة العملاء لدينا على الرقم  المجاني 8007547777 و من خارج المملكة على 009660112122333 وسيتمكن أحد موظفينا من مساعدتك بهذا الأمر.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>مرحباً, يرجى الاتصال بخدمة العملاء لدينا على الرقم  المجاني 8007547777 و من خارج المملكة على 009660112122333 وسيتمكن أحد موظفينا من مساعدتك بهذا الأمر.</t>
+        </is>
+      </c>
+      <c r="J115" t="b">
+        <v>0</v>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>['Me_s79']</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 4:15 AM UTC</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>2026-03-22T04:15:00Z</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="n">
+        <v>0</v>
+      </c>
+      <c r="T115" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" t="n">
+        <v>17</v>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2035559087719469163</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>https://x.com/19_xm/status/2035559087719469163</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>https://x.com/19_xm</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>19_xm</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>‏𝙰𝙼</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1865952902507851776/eAessk0J_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>شوفوا كيف طلع من المحادثه😭😭😭😭</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>شوفوا كيف طلع من المحادثه😭😭😭😭</t>
+        </is>
+      </c>
+      <c r="J116" t="b">
+        <v>0</v>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 3:28 AM UTC</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>2026-03-22T03:28:00Z</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="n">
+        <v>4</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="n">
+        <v>200</v>
+      </c>
+      <c r="U116" t="n">
+        <v>20502</v>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2035556057171251530</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>https://x.com/Intuitioneis/status/2035556057171251530</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>https://x.com/Intuitioneis</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Intuitioneis</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>اداري</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2035953447535583232/4BeV2m0b_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>☹️☹️☹️☹️☹️☹️☹️☹️☹️☹️☹️😭😭😭😭😭💔💔💔💔💔💔💔</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>☹️☹️☹️☹️☹️☹️☹️☹️☹️☹️☹️😭😭😭😭😭💔💔💔💔💔💔💔</t>
+        </is>
+      </c>
+      <c r="J117" t="b">
+        <v>0</v>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'Turki_alalshikh', 'RashedTV', 'walidfayed', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 3:15 AM UTC</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>2026-03-22T03:15:00Z</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0</v>
+      </c>
+      <c r="U117" t="n">
+        <v>76</v>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2035548360187294058</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>https://x.com/Dt___mona/status/2035548360187294058</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>https://x.com/Dt___mona</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Dt___mona</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Dt.MĂ</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034814710974210048/fa3jfJBq_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>🎶🤍🤍🤍</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>🎶🤍🤍🤍</t>
+        </is>
+      </c>
+      <c r="J118" t="b">
+        <v>0</v>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'Turki_alalshikh', 'RabehSaqer', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 2:45 AM UTC</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>2026-03-22T02:45:00Z</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0</v>
+      </c>
+      <c r="U118" t="n">
+        <v>45</v>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2035547614117065127</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>https://x.com/AbuSultan_89/status/2035547614117065127</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>https://x.com/AbuSultan_89</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>AbuSultan_89</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>وليد</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1700727338990800896/wqkYZfIK_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>خل عندك شخصيه يا عديم الشخصيه لن تصبح حتى ربعه 😏</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>خل عندك شخصيه يا عديم الشخصيه لن تصبح حتى ربعه 😏</t>
+        </is>
+      </c>
+      <c r="J119" t="b">
+        <v>0</v>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'Turki_alalshikh', 'RabehSaqer', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 2:42 AM UTC</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>2026-03-22T02:42:00Z</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0</v>
+      </c>
+      <c r="U119" t="n">
+        <v>28</v>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2035546969079206263</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>https://x.com/Salman_Saad89/status/2035546969079206263</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>https://x.com/Salman_Saad89</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Salman_Saad89</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>ســـلمان</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1798816256188899328/wcuv-9Uk_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>ههههههههه يقلد والله ماتسوى حتى اصبع رجله</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>ههههههههه يقلد والله ماتسوى حتى اصبع رجله</t>
+        </is>
+      </c>
+      <c r="J120" t="b">
+        <v>0</v>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'Turki_alalshikh', 'RabehSaqer', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 2:39 AM UTC</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>2026-03-22T02:39:00Z</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" t="n">
+        <v>35</v>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2035546566807699754</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>https://x.com/AbuSultan_89/status/2035546566807699754</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://x.com/AbuSultan_89</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>AbuSultan_89</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>وليد</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1700727338990800896/wqkYZfIK_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>يا ساتر يالتقليد المعفن
+ندري انكم ما تسوين بس مو لدرجه تقلدونه بكل حركاته</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>يا ساتر يالتقليد المعفن
+ندري انكم ما تسوين بس مو لدرجه تقلدونه بكل حركاته</t>
+        </is>
+      </c>
+      <c r="J121" t="b">
+        <v>0</v>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'Turki_alalshikh', 'RabehSaqer', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 2:38 AM UTC</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>2026-03-22T02:38:00Z</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="n">
+        <v>29</v>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2036045570406535456</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036045570406535456</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>الحين وقتك مع الإمارات الإسلامي.
+احصل على مزايا خاصة واسترداد نقدي مضمون عند تحويل الراتب واستمتع بمعدلات أرباح تنافسية مع تمويل السيارات. وفر واحصل على أرباح متوقعة تصل إلى %6.00 سنوياً.
+عروض حصرية للإماراتيين.
+العرض ساري حتى 31 مارس 2026.
+تُطبق الشروط والأحكام.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>الحين وقتك مع الإمارات الإسلامي.
+احصل على مزايا خاصة واسترداد نقدي مضمون عند تحويل الراتب واستمتع بمعدلات أرباح تنافسية مع تمويل السيارات. وفر واحصل على أرباح متوقعة تصل إلى %6.00 سنوياً.
+عروض حصرية للإماراتيين.
+العرض ساري حتى 31 مارس 2026.
+تُطبق الشروط والأحكام.</t>
+        </is>
+      </c>
+      <c r="J122" t="b">
+        <v>0</v>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2h</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 11:41 AM UTC</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>2026-03-23T11:41:00Z</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="n">
+        <v>61</v>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2035996471896449306</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2035996471896449306</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J123" t="b">
+        <v>0</v>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>['Ben252024']</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 8:26 AM UTC</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>2026-03-23T08:26:00Z</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" t="n">
+        <v>6</v>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2035989928291488100</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2035989928291488100</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
+You just received a subscription renewal email with spelling mistakes. What would you do?</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
+You just received a subscription renewal email with spelling mistakes. What would you do?</t>
+        </is>
+      </c>
+      <c r="J124" t="b">
+        <v>0</v>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>2026-03-23T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" t="n">
+        <v>192</v>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2035989927905693845</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2035989927905693845</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
+Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
+Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
+        </is>
+      </c>
+      <c r="J125" t="b">
+        <v>0</v>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>2026-03-23T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" t="n">
+        <v>124</v>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2035627541164077389</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2035627541164077389</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>إذا طلب منك عرض تجاري بيانات بطاقتك ورمز التحقق، ما خطواتك التالية؟
+What if a brand offer asks for your card details and CVV?</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>إذا طلب منك عرض تجاري بيانات بطاقتك ورمز التحقق، ما خطواتك التالية؟
+What if a brand offer asks for your card details and CVV?</t>
+        </is>
+      </c>
+      <c r="J126" t="b">
+        <v>0</v>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Mar 22, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>2026-03-22T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="n">
+        <v>131</v>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>EI</t>
         </is>
       </c>
     </row>

--- a/EI_ENBD_3post.xlsx
+++ b/EI_ENBD_3post.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>40m</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -624,7 +624,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>59m</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -710,7 +710,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>2h</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>2h</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>2h</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2h</t>
+          <t>3h</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1062,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2h</t>
+          <t>3h</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1147,10 +1147,10 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U8" t="n">
-        <v>327</v>
+        <v>388</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>5h</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1236,7 +1236,7 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>5h</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>5h</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1426,7 +1426,7 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>5h</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1516,7 +1516,7 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>5h</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1692,7 +1692,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1778,7 +1778,7 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1864,7 +1864,7 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2204,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2294,7 +2294,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2384,7 +2384,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2474,7 +2474,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2564,7 +2564,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2744,7 +2744,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2834,7 +2834,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2924,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3014,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3104,7 +3104,7 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3194,7 +3194,7 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3374,7 +3374,7 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3464,7 +3464,7 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3644,7 +3644,7 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3734,7 +3734,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3824,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3914,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4004,7 +4004,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4184,7 +4184,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4274,7 +4274,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4362,7 +4362,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4454,7 +4454,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4540,7 +4540,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4689,7 +4689,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4718,7 +4718,7 @@
         <v>2</v>
       </c>
       <c r="U48" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4796,7 +4796,7 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4882,7 +4882,7 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4968,7 +4968,7 @@
         <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="U52" t="n">
-        <v>2309</v>
+        <v>2411</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -5227,7 +5227,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -5243,16 +5243,16 @@
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="S54" t="n">
         <v>153</v>
       </c>
       <c r="T54" t="n">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="U54" t="n">
-        <v>1779930</v>
+        <v>1789959</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5338,7 +5338,7 @@
         <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5424,7 +5424,7 @@
         <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>Mar 22</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -5510,7 +5510,7 @@
         <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>3242</v>
+        <v>3245</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -5805,10 +5805,10 @@
         <v>7</v>
       </c>
       <c r="T60" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="U60" t="n">
-        <v>12761</v>
+        <v>12847</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>41</v>
       </c>
       <c r="U61" t="n">
-        <v>9642</v>
+        <v>9705</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>139</v>
       </c>
       <c r="U62" t="n">
-        <v>27272</v>
+        <v>27713</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>0</v>
       </c>
       <c r="U71" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>0</v>
       </c>
       <c r="U73" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>0</v>
       </c>
       <c r="U74" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>0</v>
       </c>
       <c r="U76" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>0</v>
       </c>
       <c r="U77" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>0</v>
       </c>
       <c r="U79" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>1</v>
       </c>
       <c r="U80" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>0</v>
       </c>
       <c r="U82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>0</v>
       </c>
       <c r="U83" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>0</v>
       </c>
       <c r="U85" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>0</v>
       </c>
       <c r="U87" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>0</v>
       </c>
       <c r="U89" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>0</v>
       </c>
       <c r="U90" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>0</v>
       </c>
       <c r="U91" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>0</v>
       </c>
       <c r="U93" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="V93" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>0</v>
       </c>
       <c r="U96" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="V96" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>0</v>
       </c>
       <c r="U97" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>0</v>
       </c>
       <c r="U98" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="V98" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>0</v>
       </c>
       <c r="U99" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V99" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>0</v>
       </c>
       <c r="U100" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="V100" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>0</v>
       </c>
       <c r="U101" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="V101" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>0</v>
       </c>
       <c r="U102" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="V102" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>0</v>
       </c>
       <c r="U103" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="V103" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>1</v>
       </c>
       <c r="U104" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>0</v>
       </c>
       <c r="U105" t="n">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="V105" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>0</v>
       </c>
       <c r="U106" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V106" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>1</v>
       </c>
       <c r="U107" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V107" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>5</v>
       </c>
       <c r="U108" t="n">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="V108" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>0</v>
       </c>
       <c r="U109" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="V109" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>0</v>
       </c>
       <c r="U110" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="V110" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>0</v>
       </c>
       <c r="U111" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V111" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>0</v>
       </c>
       <c r="U112" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="V112" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>5</v>
       </c>
       <c r="U113" t="n">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="V113" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>4</v>
       </c>
       <c r="U114" t="n">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="V114" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>0</v>
       </c>
       <c r="U115" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="V115" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>0</v>
       </c>
       <c r="U116" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="V116" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>0</v>
       </c>
       <c r="U117" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>0</v>
       </c>
       <c r="U118" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="V118" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>0</v>
       </c>
       <c r="U119" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V119" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>0</v>
       </c>
       <c r="U120" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V120" t="inlineStr">
         <is>
@@ -11221,10 +11221,10 @@
         <v>10</v>
       </c>
       <c r="T121" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="U121" t="n">
-        <v>20615</v>
+        <v>20725</v>
       </c>
       <c r="V121" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>0</v>
       </c>
       <c r="U122" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="V122" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>0</v>
       </c>
       <c r="U123" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V123" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>0</v>
       </c>
       <c r="U124" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="V124" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>0</v>
       </c>
       <c r="U125" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V125" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>0</v>
       </c>
       <c r="U126" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V126" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>0</v>
       </c>
       <c r="U127" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="V127" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>0</v>
       </c>
       <c r="U128" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="V128" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>0</v>
       </c>
       <c r="U129" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V129" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr">
         <is>
-          <t>3h</t>
+          <t>4h</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -12010,7 +12010,7 @@
         <v>0</v>
       </c>
       <c r="U130" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="V130" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -12096,7 +12096,7 @@
         <v>0</v>
       </c>
       <c r="U131" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V131" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -12180,7 +12180,7 @@
         <v>0</v>
       </c>
       <c r="U132" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="V132" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -12264,7 +12264,7 @@
         <v>0</v>
       </c>
       <c r="U133" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="V133" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>0</v>
       </c>
       <c r="U134" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="V134" t="inlineStr">
         <is>

--- a/EI_ENBD_3post.xlsx
+++ b/EI_ENBD_3post.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>2h</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -624,7 +624,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>3h</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -710,7 +710,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -773,7 +773,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2h</t>
+          <t>3h</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2h</t>
+          <t>3h</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2h</t>
+          <t>3h</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>3h</t>
+          <t>4h</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1062,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3h</t>
+          <t>4h</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1150,7 +1150,7 @@
         <v>5</v>
       </c>
       <c r="U8" t="n">
-        <v>388</v>
+        <v>439</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>5h</t>
+          <t>6h</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1236,7 +1236,7 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>5h</t>
+          <t>6h</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>5h</t>
+          <t>6h</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1426,7 +1426,7 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>5h</t>
+          <t>6h</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1516,7 +1516,7 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>5h</t>
+          <t>6h</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1692,7 +1692,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1778,7 +1778,7 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1864,7 +1864,7 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1950,7 +1950,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2036,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2118,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2204,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2294,7 +2294,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2384,7 +2384,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2474,7 +2474,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2564,7 +2564,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2744,7 +2744,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2834,7 +2834,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3104,7 +3104,7 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3284,7 +3284,7 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3374,7 +3374,7 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3464,7 +3464,7 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3554,7 +3554,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3644,7 +3644,7 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3734,7 +3734,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3824,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3914,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4004,7 +4004,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4094,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4184,7 +4184,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4274,7 +4274,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4362,7 +4362,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4454,7 +4454,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4540,7 +4540,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4630,7 +4630,7 @@
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -4689,7 +4689,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4718,7 +4718,7 @@
         <v>2</v>
       </c>
       <c r="U48" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4882,7 +4882,7 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4968,7 +4968,7 @@
         <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="U52" t="n">
-        <v>2411</v>
+        <v>2481</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -5160,7 +5160,7 @@
         <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -5243,16 +5243,16 @@
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="n">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="S54" t="n">
         <v>153</v>
       </c>
       <c r="T54" t="n">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="U54" t="n">
-        <v>1789959</v>
+        <v>1804589</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>Mar 22</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5338,7 +5338,7 @@
         <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>Mar 22</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5424,7 +5424,7 @@
         <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>3245</v>
+        <v>3248</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -5805,10 +5805,10 @@
         <v>7</v>
       </c>
       <c r="T60" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U60" t="n">
-        <v>12847</v>
+        <v>12921</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>41</v>
       </c>
       <c r="U61" t="n">
-        <v>9705</v>
+        <v>9745</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>139</v>
       </c>
       <c r="U62" t="n">
-        <v>27713</v>
+        <v>27925</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
         <v>0</v>
       </c>
       <c r="U70" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>0</v>
       </c>
       <c r="U71" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>0</v>
       </c>
       <c r="U72" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>0</v>
       </c>
       <c r="U73" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>0</v>
       </c>
       <c r="U74" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>0</v>
       </c>
       <c r="U75" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>0</v>
       </c>
       <c r="U76" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>0</v>
       </c>
       <c r="U77" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>0</v>
       </c>
       <c r="U78" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>0</v>
       </c>
       <c r="U79" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>1</v>
       </c>
       <c r="U80" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>0</v>
       </c>
       <c r="U81" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>0</v>
       </c>
       <c r="U82" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>0</v>
       </c>
       <c r="U83" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>0</v>
       </c>
       <c r="U84" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="V84" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         <v>0</v>
       </c>
       <c r="U85" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>0</v>
       </c>
       <c r="U86" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>0</v>
       </c>
       <c r="U87" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>0</v>
       </c>
       <c r="U88" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>0</v>
       </c>
       <c r="U89" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>0</v>
       </c>
       <c r="U90" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>0</v>
       </c>
       <c r="U91" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>0</v>
       </c>
       <c r="U92" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V92" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>0</v>
       </c>
       <c r="U93" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="V93" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>0</v>
       </c>
       <c r="U94" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="V94" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>0</v>
       </c>
       <c r="U95" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>0</v>
       </c>
       <c r="U96" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="V96" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>0</v>
       </c>
       <c r="U97" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>0</v>
       </c>
       <c r="U98" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="V98" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>0</v>
       </c>
       <c r="U99" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="V99" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>0</v>
       </c>
       <c r="U100" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="V100" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>0</v>
       </c>
       <c r="U101" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="V101" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>0</v>
       </c>
       <c r="U103" t="n">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="V103" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>1</v>
       </c>
       <c r="U104" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>0</v>
       </c>
       <c r="U105" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="V105" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>0</v>
       </c>
       <c r="U106" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V106" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>5</v>
       </c>
       <c r="U108" t="n">
-        <v>950</v>
+        <v>961</v>
       </c>
       <c r="V108" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         <v>0</v>
       </c>
       <c r="U109" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="V109" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>0</v>
       </c>
       <c r="U110" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="V110" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>0</v>
       </c>
       <c r="U111" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="V111" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>0</v>
       </c>
       <c r="U112" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="V112" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>5</v>
       </c>
       <c r="U113" t="n">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="V113" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>4</v>
       </c>
       <c r="U114" t="n">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="V114" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>0</v>
       </c>
       <c r="U115" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="V115" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>0</v>
       </c>
       <c r="U116" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="V116" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>0</v>
       </c>
       <c r="U117" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>0</v>
       </c>
       <c r="U118" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V118" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>0</v>
       </c>
       <c r="U119" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V119" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>0</v>
       </c>
       <c r="U120" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V120" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>202</v>
       </c>
       <c r="U121" t="n">
-        <v>20725</v>
+        <v>20854</v>
       </c>
       <c r="V121" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>0</v>
       </c>
       <c r="U122" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V122" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>0</v>
       </c>
       <c r="U123" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="V123" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>0</v>
       </c>
       <c r="U125" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V125" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>0</v>
       </c>
       <c r="U126" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="V126" t="inlineStr">
         <is>
@@ -11744,7 +11744,7 @@
         <v>0</v>
       </c>
       <c r="U127" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="V127" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>0</v>
       </c>
       <c r="U128" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V128" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>0</v>
       </c>
       <c r="U129" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="V129" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>5h</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -12010,7 +12010,7 @@
         <v>0</v>
       </c>
       <c r="U130" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="V130" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -12096,7 +12096,7 @@
         <v>0</v>
       </c>
       <c r="U131" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V131" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -12180,7 +12180,7 @@
         <v>0</v>
       </c>
       <c r="U132" t="n">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="V132" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>8h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -12264,7 +12264,7 @@
         <v>0</v>
       </c>
       <c r="U133" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="V133" t="inlineStr">
         <is>
@@ -12348,7 +12348,7 @@
         <v>0</v>
       </c>
       <c r="U134" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="V134" t="inlineStr">
         <is>

--- a/EI_ENBD_3post.xlsx
+++ b/EI_ENBD_3post.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V57"/>
+  <dimension ref="A1:V58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,43 +543,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2036269961057018273</t>
+          <t>2036300027933433945</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://x.com/saimas89/status/2036269961057018273</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036300027933433945</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/saimas89</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>saimas89</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Saima | صائمہ</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1613505962098282497/lNPa9Or8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Can you not take another 7 days and give me the refund sooner? FYI I have paid using my ENBD card.</t>
+          <t>مرحباً بك, شكراً لتواصلك معنا, يرجى العلم اننا غير قادرين على التواصل معك على الرسائل, يمكنك الاتصال بنا على 600540000 
+أو عن طريق التحدث معنا من خلال الواتساب البنكي على 600540000 من الساعة 9 صباحا الى 7 مساء</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Can you not take another 7 days and give me the refund sooner? FYI I have paid using my ENBD card.</t>
+          <t>مرحباً بك, شكراً لتواصلك معنا, يرجى العلم اننا غير قادرين على التواصل معك على الرسائل, يمكنك الاتصال بنا على 600540000 
+أو عن طريق التحدث معنا من خلال الواتساب البنكي على 600540000 من الساعة 9 صباحا الى 7 مساء</t>
         </is>
       </c>
       <c r="J2" t="b">
@@ -588,28 +590,28 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['flyspicejet']</t>
+          <t>['AlyahiaMoh']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>46m</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 2:32 AM UTC</t>
+          <t>Mar 24, 2026 · 4:32 AM UTC</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-03-24T02:32:00Z</t>
+          <t>2026-03-24T04:32:00Z</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -618,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -629,73 +631,73 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2036181530364489860</t>
+          <t>2036269961057018273</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://x.com/AlyahiaMoh/status/2036181530364489860</t>
+          <t>https://x.com/saimas89/status/2036269961057018273</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/AlyahiaMoh</t>
+          <t>https://x.com/saimas89</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AlyahiaMoh</t>
+          <t>saimas89</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Mohammed Alyahia</t>
+          <t>Saima | صائمہ</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1959335410070409216/2YvWCgCy_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1613505962098282497/lNPa9Or8_bigger.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE ممكن احد يتواصل معي عن طريق الخاص للمساعدة؟؟</t>
+          <t>Can you not take another 7 days and give me the refund sooner? FYI I have paid using my ENBD card.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; ممكن احد يتواصل معي عن طريق الخاص للمساعدة؟؟</t>
+          <t>Can you not take another 7 days and give me the refund sooner? FYI I have paid using my ENBD card.</t>
         </is>
       </c>
       <c r="J3" t="b">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>['flyspicejet']</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>2h</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 8:41 PM UTC</t>
+          <t>Mar 24, 2026 · 2:32 AM UTC</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-03-23T20:41:00Z</t>
+          <t>2026-03-24T02:32:00Z</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -704,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -715,12 +717,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2036176545543266757</t>
+          <t>2036181530364489860</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://x.com/AlyahiaMoh/status/2036176545543266757</t>
+          <t>https://x.com/AlyahiaMoh/status/2036181530364489860</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -746,109 +748,109 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
+          <t>@EmiratesNBD_AE ممكن احد يتواصل معي عن طريق الخاص للمساعدة؟؟</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; ممكن احد يتواصل معي عن طريق الخاص للمساعدة؟؟</t>
+        </is>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>8h</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 8:41 PM UTC</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-03-23T20:41:00Z</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2036176545543266757</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://x.com/AlyahiaMoh/status/2036176545543266757</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://x.com/AlyahiaMoh</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AlyahiaMoh</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Mohammed Alyahia</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1959335410070409216/2YvWCgCy_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>ما اقدر ارسلك شي ع الخاص لان حسابي مو موثق
 فيه احد يتواصل معي؟</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>ما اقدر ارسلك شي ع الخاص لان حسابي مو موثق
 فيه احد يتواصل معي؟</t>
         </is>
       </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>7h</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Mar 23, 2026 · 8:21 PM UTC</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2026-03-23T20:21:00Z</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>13</v>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2036171018964713797</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://x.com/Pjnw0/status/2036171018964713797</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://x.com/Pjnw0</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Pjnw0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>ًً</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1917726644028014592/_A_c0Mka_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>ما الومه يسال بيكمل سنه من الاعلان</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>ما الومه يسال بيكمل سنه من الاعلان</t>
-        </is>
-      </c>
       <c r="J5" t="b">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>['Sadziz13', 'RotanaLive', 'Turki_alalshikh', 'RabehSaqer', 'salhendi', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -858,12 +860,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 7:59 PM UTC</t>
+          <t>Mar 23, 2026 · 8:21 PM UTC</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-03-23T19:59:00Z</t>
+          <t>2026-03-23T20:21:00Z</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -878,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -889,43 +891,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2036140802057896269</t>
+          <t>2036171018964713797</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036140802057896269</t>
+          <t>https://x.com/Pjnw0/status/2036171018964713797</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/Pjnw0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>Pjnw0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>ًً</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1917726644028014592/_A_c0Mka_bigger.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>مرحبا محمد شكرا لتواصلك معنا برجاء إرسال تفاصيل إستفسارك عبر رسائل الخاص</t>
+          <t>ما الومه يسال بيكمل سنه من الاعلان</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مرحبا محمد شكرا لتواصلك معنا برجاء إرسال تفاصيل إستفسارك عبر رسائل الخاص</t>
+          <t>ما الومه يسال بيكمل سنه من الاعلان</t>
         </is>
       </c>
       <c r="J6" t="b">
@@ -934,28 +936,28 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>['AlyahiaMoh']</t>
+          <t>['Sadziz13', 'RotanaLive', 'Turki_alalshikh', 'RabehSaqer', 'salhendi', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 5:59 PM UTC</t>
+          <t>Mar 23, 2026 · 7:59 PM UTC</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-03-23T17:59:00Z</t>
+          <t>2026-03-23T19:59:00Z</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -964,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -975,36 +977,122 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2036136587390533632</t>
+          <t>2036140802057896269</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://x.com/cas_2050001283/status/2036136587390533632</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036140802057896269</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/cas_2050001283</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>cas_2050001283</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CASTest2050001283</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
+        <is>
+          <t>مرحبا محمد شكرا لتواصلك معنا برجاء إرسال تفاصيل إستفسارك عبر رسائل الخاص</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>مرحبا محمد شكرا لتواصلك معنا برجاء إرسال تفاصيل إستفسارك عبر رسائل الخاص</t>
+        </is>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>['AlyahiaMoh']</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>11h</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 5:59 PM UTC</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2026-03-23T17:59:00Z</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>23</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2036136587390533632</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://x.com/cas_2050001283/status/2036136587390533632</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://x.com/cas_2050001283</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>cas_2050001283</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CASTest2050001283</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
         <is>
           <t>EnbD Uv6DtrmP Á7iLiMÁBpÁ
 0m&gt;T⃑h&gt;ÁE
@@ -1013,7 +1101,7 @@
 qpo🧑🏼‍❤️‍💋‍🧑🏾1A🧙🏿‍♂️7o💅🏿B👇🏻</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>EnbD Uv6DtrmP Á7iLiMÁBpÁ
 0m&amp;gt;T⃑h&amp;gt;ÁE
@@ -1022,90 +1110,6 @@
 qpo🧑🏼‍❤️‍💋‍🧑🏾1A🧙🏿‍♂️7o💅🏿B👇🏻</t>
         </is>
       </c>
-      <c r="J7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>10h</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Mar 23, 2026 · 5:42 PM UTC</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2026-03-23T17:42:00Z</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>5</v>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2036130140510449946</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>https://x.com/AlyahiaMoh/status/2036130140510449946</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://x.com/AlyahiaMoh</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>AlyahiaMoh</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Mohammed Alyahia</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1959335410070409216/2YvWCgCy_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE 
-يعطيكم العافية ايش ال swift code الخاص بفرع طريق الشيخ زايد "رحمه الله" نفس اللي بالصورة</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
-يعطيكم العافية ايش ال swift code الخاص بفرع طريق الشيخ زايد &amp;#34;رحمه الله&amp;#34; نفس اللي بالصورة</t>
-        </is>
-      </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
@@ -1113,27 +1117,23 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 5:17 PM UTC</t>
+          <t>Mar 23, 2026 · 5:42 PM UTC</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-03-23T17:17:00Z</t>
+          <t>2026-03-23T17:42:00Z</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1142,7 +1142,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1153,36 +1153,124 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2036086151656636693</t>
+          <t>2036130140510449946</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036086151656636693</t>
+          <t>https://x.com/AlyahiaMoh/status/2036130140510449946</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/AlyahiaMoh</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>AlyahiaMoh</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Mohammed Alyahia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1959335410070409216/2YvWCgCy_bigger.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE 
+يعطيكم العافية ايش ال swift code الخاص بفرع طريق الشيخ زايد "رحمه الله" نفس اللي بالصورة</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
+يعطيكم العافية ايش ال swift code الخاص بفرع طريق الشيخ زايد &amp;#34;رحمه الله&amp;#34; نفس اللي بالصورة</t>
+        </is>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>12h</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 5:17 PM UTC</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2026-03-23T17:17:00Z</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>19</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2036086151656636693</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2036086151656636693</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
         <is>
           <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to
 social@emiratesnbd.com
@@ -1190,7 +1278,7 @@
  We will make every effort to address the matter</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to
 social@emiratesnbd.com
@@ -1198,120 +1286,34 @@
  We will make every effort to address the matter</t>
         </is>
       </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>['mridulrb']</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>13h</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 2:22 PM UTC</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>2026-03-23T14:22:00Z</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>29</v>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2036081518607749454</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://x.com/mridulrb/status/2036081518607749454</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://x.com/mridulrb</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>mridulrb</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Mridul Bhandari</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1260543244464787456/hi1vRK1o_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Money transfers on ENBD X don't support SWIFT-only beneficiaries for Indian accounts like GIFT City — the app forces an IFSC lookup, but GIFT City IBUs have no IFSC code, completely hindering transfers. Please allow manual SWIFT entry. #GIFTCITY #NRI</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; Money transfers on ENBD X don&amp;#39;t support SWIFT-only beneficiaries for Indian accounts like GIFT City — the app forces an IFSC lookup, but GIFT City IBUs have no IFSC code, completely hindering transfers. Please allow manual SWIFT entry. &lt;a href="/search?f=tweets&amp;amp;q=%23GIFTCITY"&gt;#GIFTCITY&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NRI"&gt;#NRI&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Mar 23, 2026 · 2:03 PM UTC</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2026-03-23T14:03:00Z</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE', 'https://x.com/search?f=tweets&amp;q=%23GIFTCITY', 'https://x.com/search?f=tweets&amp;q=%23NRI']</t>
-        </is>
-      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1320,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1331,36 +1333,122 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2036080525308252666</t>
+          <t>2036081518607749454</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2036080525308252666</t>
+          <t>https://x.com/mridulrb/status/2036081518607749454</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY</t>
+          <t>https://x.com/mridulrb</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EmiratesNBD_EGY</t>
+          <t>mridulrb</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Mridul Bhandari</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1260543244464787456/hi1vRK1o_bigger.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Money transfers on ENBD X don't support SWIFT-only beneficiaries for Indian accounts like GIFT City — the app forces an IFSC lookup, but GIFT City IBUs have no IFSC code, completely hindering transfers. Please allow manual SWIFT entry. #GIFTCITY #NRI</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; Money transfers on ENBD X don&amp;#39;t support SWIFT-only beneficiaries for Indian accounts like GIFT City — the app forces an IFSC lookup, but GIFT City IBUs have no IFSC code, completely hindering transfers. Please allow manual SWIFT entry. &lt;a href="/search?f=tweets&amp;amp;q=%23GIFTCITY"&gt;#GIFTCITY&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NRI"&gt;#NRI&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 2:03 PM UTC</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2026-03-23T14:03:00Z</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE', 'https://x.com/search?f=tweets&amp;q=%23GIFTCITY', 'https://x.com/search?f=tweets&amp;q=%23NRI']</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>64</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2036080525308252666</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_EGY/status/2036080525308252666</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_EGY</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_EGY</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
         <is>
           <t>Double click and instantly.
 Use Apple Pay with your Emirates NBD Cards for fast, secure payments in your iPhone or Apple Watch wherever contactless payments are accepted.
@@ -1368,7 +1456,7 @@
 Tax registration number: 204-897-319</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Double click and instantly.
 Use Apple Pay with your Emirates NBD Cards for fast, secure payments in your iPhone or Apple Watch wherever contactless payments are accepted.
@@ -1376,79 +1464,79 @@
 Tax registration number: 204-897-319</t>
         </is>
       </c>
-      <c r="J11" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 2:00 PM UTC</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>2026-03-23T14:00:00Z</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>48</v>
-      </c>
-      <c r="V11" t="inlineStr">
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>50</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>2036080525299925460</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_EGY/status/2036080525299925460</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_EGY</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>EmiratesNBD_EGY</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
         <is>
           <t>اضغط مرتين وادفع فورًا.
 استخدم Apple Pay مع بطاقات بنك الإمارات دبي الوطني وادفع بسهولة وأمان من خلال Apple Wallet أو iPhone 
@@ -1456,7 +1544,7 @@
 رقم التسجيل الضريبي: 319-897-204</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>اضغط مرتين وادفع فورًا.
 استخدم Apple Pay مع بطاقات بنك الإمارات دبي الوطني وادفع بسهولة وأمان من خلال Apple Wallet أو iPhone 
@@ -1464,185 +1552,99 @@
 رقم التسجيل الضريبي: 319-897-204</t>
         </is>
       </c>
-      <c r="J12" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 2:00 PM UTC</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>2026-03-23T14:00:00Z</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>65</v>
-      </c>
-      <c r="V12" t="inlineStr">
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>67</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>2036079925136949553</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>https://x.com/Sadziz13/status/2036079925136949553</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>https://x.com/Sadziz13</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Sadziz13</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>مَ. سعـد عبدالعزيز</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1711030291840577537/3X1cIUsy_bigger.jpg</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
         <is>
           <t>حبيبنا بو شليل والله 
 كل ما مسك المايك سأل بوصقر متى الالبوم ؟ 😂
 خلووو بوصقر على كيفه وبراحته 🦅😍</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>حبيبنا بو شليل والله 
 كل ما مسك المايك سأل بوصقر متى الالبوم ؟ 😂
 خلووو بوصقر على كيفه وبراحته 🦅😍</t>
         </is>
       </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>['RotanaLive', 'Turki_alalshikh', 'RabehSaqer', 'salhendi', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Mar 23, 2026 · 1:57 PM UTC</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2026-03-23T13:57:00Z</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>98</v>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2036058390850654260</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>https://x.com/soviergn/status/2036058390850654260</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>https://x.com/soviergn</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>soviergn</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Sovereign Alpha</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2027700895899914242/dNUJuxkf_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Brought 17 Pro Max with discount for 1,14,000 in Virgin Megastore. Also got cashback of 8% with ENBD share card.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Brought 17 Pro Max with discount for 1,14,000 in Virgin Megastore. Also got cashback of 8% with ENBD share card.</t>
-        </is>
-      </c>
       <c r="J14" t="b">
         <v>0</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>['NalinisKitchen']</t>
+          <t>['RotanaLive', 'Turki_alalshikh', 'RabehSaqer', 'salhendi', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1652,27 +1654,27 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 12:32 PM UTC</t>
+          <t>Mar 23, 2026 · 1:57 PM UTC</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-03-23T12:32:00Z</t>
+          <t>2026-03-23T13:57:00Z</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1683,170 +1685,170 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2036055087643042221</t>
+          <t>2036058390850654260</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036055087643042221</t>
+          <t>https://x.com/soviergn/status/2036058390850654260</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/soviergn</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>soviergn</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Sovereign Alpha</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2027700895899914242/dNUJuxkf_bigger.jpg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
+          <t>Brought 17 Pro Max with discount for 1,14,000 in Virgin Megastore. Also got cashback of 8% with ENBD share card.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Brought 17 Pro Max with discount for 1,14,000 in Virgin Megastore. Also got cashback of 8% with ENBD share card.</t>
+        </is>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>['NalinisKitchen']</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 12:32 PM UTC</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2026-03-23T12:32:00Z</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>39</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2036055087643042221</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2036055087643042221</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>Apply for an Emirates NBD Visa Credit Card for a chance to watch FIFA World Cup 26™ live with Pep.
 emiratesnbd.com/en/campaigns…</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Apply for an Emirates NBD Visa Credit Card for a chance to watch FIFA World Cup 26™ live with Pep.
 &lt;a href="https://www.emiratesnbd.com/en/campaigns/visa-pep-promotion"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J15" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 12:18 PM UTC</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>2026-03-23T12:18:00Z</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>['https://www.emiratesnbd.com/en/campaigns/visa-pep-promotion']</t>
         </is>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
         <v>5</v>
       </c>
-      <c r="U15" t="n">
-        <v>644</v>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2036035724667974026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>https://x.com/li_yxe/status/2036035724667974026</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>https://x.com/li_yxe</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>li_yxe</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>محب موسس نادي الجاليات احمد البربري💛💙</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2002729561453203456/9mjw63eM_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>غلطة العمر دخولك على الفن</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>غلطة العمر دخولك على الفن</t>
-        </is>
-      </c>
-      <c r="J16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>['RotanaLive', 'Turki_alalshikh', 'RabehSaqer', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Mar 23, 2026 · 11:01 AM UTC</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2026-03-23T11:01:00Z</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
       <c r="U16" t="n">
-        <v>25</v>
+        <v>662</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1857,43 +1859,43 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2036034615769518550</t>
+          <t>2036035724667974026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036034615769518550</t>
+          <t>https://x.com/li_yxe/status/2036035724667974026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/li_yxe</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>li_yxe</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>محب موسس نادي الجاليات احمد البربري💛💙</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2002729561453203456/9mjw63eM_bigger.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #987474 in the subject line.</t>
+          <t>غلطة العمر دخولك على الفن</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #987474 in the subject line.</t>
+          <t>غلطة العمر دخولك على الفن</t>
         </is>
       </c>
       <c r="J17" t="b">
@@ -1902,22 +1904,22 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>['Nightowl263']</t>
+          <t>['RotanaLive', 'Turki_alalshikh', 'RabehSaqer', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 10:57 AM UTC</t>
+          <t>Mar 23, 2026 · 11:01 AM UTC</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-03-23T10:57:00Z</t>
+          <t>2026-03-23T11:01:00Z</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -1932,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -1943,36 +1945,122 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2036029459585781847</t>
+          <t>2036034615769518550</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://x.com/Prahmatic17/status/2036029459585781847</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036034615769518550</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/Prahmatic17</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Prahmatic17</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PragmaticWatcher</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2005896675047403521/VCdF3HFl_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
+        <is>
+          <t>We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #987474 in the subject line.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #987474 in the subject line.</t>
+        </is>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>['Nightowl263']</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 10:57 AM UTC</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2026-03-23T10:57:00Z</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>37</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2036029459585781847</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://x.com/Prahmatic17/status/2036029459585781847</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://x.com/Prahmatic17</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Prahmatic17</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>PragmaticWatcher</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2005896675047403521/VCdF3HFl_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
         <is>
           <t>UAE equities — Monday open.
 🔴 #Dubai DFM: -2.5%
@@ -1986,7 +2074,7 @@
 #UAE #DFM #Iran #Markets</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>UAE equities — Monday open.
 🔴 &lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt; DFM: -2.5%
@@ -2000,124 +2088,34 @@
 &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DFM"&gt;#DFM&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Iran"&gt;#Iran&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Markets"&gt;#Markets&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 10:37 AM UTC</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>2026-03-23T10:37:00Z</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23Dubai', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23DFM', 'https://x.com/search?f=tweets&amp;q=%23Iran', 'https://x.com/search?f=tweets&amp;q=%23Markets']</t>
-        </is>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>416</v>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2036027630722617585</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>https://x.com/Nightowl263/status/2036027630722617585</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://x.com/Nightowl263</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Nightowl263</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Priya George</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1718237295055433728/mRkQyUDb_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>I’ve been waiting a month for this bank to process account application. Every day I follow up, they say “wait 5 more days.” And yet, they’re busy educating customers on small delivery fees. Can I trust them with my money? 😕 what would you do in this case ? #UnitedAgainstFraud</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>I’ve been waiting a month for this bank to process account application. Every day I follow up, they say “wait 5 more days.” And yet, they’re busy educating customers on small delivery fees. Can I trust them with my money? 😕 what would you do in this case ? &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Mar 23, 2026 · 10:29 AM UTC</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2026-03-23T10:29:00Z</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23Dubai', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23DFM', 'https://x.com/search?f=tweets&amp;q=%23Iran', 'https://x.com/search?f=tweets&amp;q=%23Markets']</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2126,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>36</v>
+        <v>422</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -2137,43 +2135,43 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2036024666901668316</t>
+          <t>2036027630722617585</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://x.com/coolmomdxb/status/2036024666901668316</t>
+          <t>https://x.com/Nightowl263/status/2036027630722617585</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/coolmomdxb</t>
+          <t>https://x.com/Nightowl263</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>coolmomdxb</t>
+          <t>Nightowl263</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Anuradha</t>
+          <t>Priya George</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1576510705481678850/3vJsydFv_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1718237295055433728/mRkQyUDb_bigger.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.89% @fatema_painter @SelmaRomola @Harshabhatia2</t>
+          <t>I’ve been waiting a month for this bank to process account application. Every day I follow up, they say “wait 5 more days.” And yet, they’re busy educating customers on small delivery fees. Can I trust them with my money? 😕 what would you do in this case ? #UnitedAgainstFraud</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.89% &lt;a href="/fatema_painter" title="FATEMA"&gt;@fatema_painter&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Harshabhatia2" title="Harsha bhatia"&gt;@Harshabhatia2&lt;/a&gt;</t>
+          <t>I’ve been waiting a month for this bank to process account application. Every day I follow up, they say “wait 5 more days.” And yet, they’re busy educating customers on small delivery fees. Can I trust them with my money? 😕 what would you do in this case ? &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J20" t="b">
@@ -2187,27 +2185,27 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 10:18 AM UTC</t>
+          <t>Mar 23, 2026 · 10:29 AM UTC</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-03-23T10:18:00Z</t>
+          <t>2026-03-23T10:29:00Z</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>['https://x.com/fatema_painter', 'https://x.com/SelmaRomola', 'https://x.com/Harshabhatia2']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud']</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -2216,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -2227,43 +2225,43 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2035995575489909048</t>
+          <t>2036024666901668316</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2035995575489909048</t>
+          <t>https://x.com/coolmomdxb/status/2036024666901668316</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA</t>
+          <t>https://x.com/coolmomdxb</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA</t>
+          <t>coolmomdxb</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EmiratesNBD KSA</t>
+          <t>Anuradha</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1576510705481678850/3vJsydFv_bigger.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>we understand your concern, and we have already escalated it, you will be contacted as soon as possible.</t>
+          <t>1.89% @fatema_painter @SelmaRomola @Harshabhatia2</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>we understand your concern, and we have already escalated it, you will be contacted as soon as possible.</t>
+          <t>1.89% &lt;a href="/fatema_painter" title="FATEMA"&gt;@fatema_painter&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Harshabhatia2" title="Harsha bhatia"&gt;@Harshabhatia2&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J21" t="b">
@@ -2272,7 +2270,7 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['netdiscussion']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2282,16 +2280,20 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 8:22 AM UTC</t>
+          <t>Mar 23, 2026 · 10:18 AM UTC</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-03-23T08:22:00Z</t>
+          <t>2026-03-23T10:18:00Z</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>['https://x.com/fatema_painter', 'https://x.com/SelmaRomola', 'https://x.com/Harshabhatia2']</t>
+        </is>
+      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -2302,7 +2304,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -2313,43 +2315,43 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2035990013700157483</t>
+          <t>2035995575489909048</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://x.com/netdiscussion/status/2035990013700157483</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2035995575489909048</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://x.com/netdiscussion</t>
+          <t>https://x.com/EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>netdiscussion</t>
+          <t>EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Muhammad Kashif Ashraf</t>
+          <t>EmiratesNBD KSA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Same message receiving multiple times with zero response</t>
+          <t>we understand your concern, and we have already escalated it, you will be contacted as soon as possible.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Same message receiving multiple times with zero response</t>
+          <t>we understand your concern, and we have already escalated it, you will be contacted as soon as possible.</t>
         </is>
       </c>
       <c r="J22" t="b">
@@ -2358,7 +2360,7 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_KSA']</t>
+          <t>['netdiscussion']</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2368,18 +2370,18 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 8:00 AM UTC</t>
+          <t>Mar 23, 2026 · 8:22 AM UTC</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-03-23T08:00:00Z</t>
+          <t>2026-03-23T08:22:00Z</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2388,7 +2390,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2399,43 +2401,43 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2035984966622879907</t>
+          <t>2035990013700157483</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2035984966622879907</t>
+          <t>https://x.com/netdiscussion/status/2035990013700157483</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA</t>
+          <t>https://x.com/netdiscussion</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA</t>
+          <t>netdiscussion</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>EmiratesNBD KSA</t>
+          <t>Muhammad Kashif Ashraf</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Hi Muhammad, thanks for reaching us, and we are extremely sorry for the delay, and we have asked our team to contact you as soon as possible. Thanks</t>
+          <t>Same message receiving multiple times with zero response</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Hi Muhammad, thanks for reaching us, and we are extremely sorry for the delay, and we have asked our team to contact you as soon as possible. Thanks</t>
+          <t>Same message receiving multiple times with zero response</t>
         </is>
       </c>
       <c r="J23" t="b">
@@ -2444,22 +2446,22 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>['netdiscussion']</t>
+          <t>['EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 7:40 AM UTC</t>
+          <t>Mar 23, 2026 · 8:00 AM UTC</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-03-23T07:40:00Z</t>
+          <t>2026-03-23T08:00:00Z</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2474,7 +2476,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -2485,71 +2487,71 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2035983374574059838</t>
+          <t>2035984966622879907</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://x.com/netdiscussion/status/2035983374574059838</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2035984966622879907</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://x.com/netdiscussion</t>
+          <t>https://x.com/EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>netdiscussion</t>
+          <t>EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Muhammad Kashif Ashraf</t>
+          <t>EmiratesNBD KSA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA I don't understand, why no response/update on any official Channel by phone, email, Twitter??, since 8 of March, dispute case is registered.</t>
+          <t>Hi Muhammad, thanks for reaching us, and we are extremely sorry for the delay, and we have asked our team to contact you as soon as possible. Thanks</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; I don&amp;#39;t understand, why no response/update on any official Channel by phone, email, Twitter??, since 8 of March, dispute case is registered.</t>
+          <t>Hi Muhammad, thanks for reaching us, and we are extremely sorry for the delay, and we have asked our team to contact you as soon as possible. Thanks</t>
         </is>
       </c>
       <c r="J24" t="b">
         <v>0</v>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>['netdiscussion']</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 7:33 AM UTC</t>
+          <t>Mar 23, 2026 · 7:40 AM UTC</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-03-23T07:33:00Z</t>
+          <t>2026-03-23T07:40:00Z</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="n">
         <v>1</v>
       </c>
@@ -2560,7 +2562,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -2571,73 +2573,73 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2035976151764549748</t>
+          <t>2035983374574059838</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2035976151764549748</t>
+          <t>https://x.com/netdiscussion/status/2035983374574059838</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA</t>
+          <t>https://x.com/netdiscussion</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA</t>
+          <t>netdiscussion</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>EmiratesNBD KSA</t>
+          <t>Muhammad Kashif Ashraf</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Hi Rakshit, our team tried to contact you, but there was no answer from your side, we have asked our team to contact you again as soon as possible.</t>
+          <t>@EmiratesNBD_KSA I don't understand, why no response/update on any official Channel by phone, email, Twitter??, since 8 of March, dispute case is registered.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Hi Rakshit, our team tried to contact you, but there was no answer from your side, we have asked our team to contact you again as soon as possible.</t>
+          <t>&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; I don&amp;#39;t understand, why no response/update on any official Channel by phone, email, Twitter??, since 8 of March, dispute case is registered.</t>
         </is>
       </c>
       <c r="J25" t="b">
         <v>0</v>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>['RakshtVaghasiya']</t>
-        </is>
-      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 7:05 AM UTC</t>
+          <t>Mar 23, 2026 · 7:33 AM UTC</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-03-23T07:05:00Z</t>
+          <t>2026-03-23T07:33:00Z</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_KSA']</t>
+        </is>
+      </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2657,63 +2659,67 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2035964468413493475</t>
+          <t>2035976151764549748</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://x.com/Mr__Krabs___/status/2035964468413493475</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2035976151764549748</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://x.com/Mr__Krabs___</t>
+          <t>https://x.com/EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mr__Krabs___</t>
+          <t>EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Eugene H Krabs</t>
+          <t>EmiratesNBD KSA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1439693335644487683/C-FPyRyf_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Operation epic bimbo has been closed for a small profit; too many significant threats to GCC key infrastructure and honestly had thought this would be wrap</t>
+          <t>Hi Rakshit, our team tried to contact you, but there was no answer from your side, we have asked our team to contact you again as soon as possible.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Operation epic bimbo has been closed for a small profit; too many significant threats to GCC key infrastructure and honestly had thought this would be wrap</t>
+          <t>Hi Rakshit, our team tried to contact you, but there was no answer from your side, we have asked our team to contact you again as soon as possible.</t>
         </is>
       </c>
       <c r="J26" t="b">
         <v>0</v>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>['RakshtVaghasiya']</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 6:18 AM UTC</t>
+          <t>Mar 23, 2026 · 7:05 AM UTC</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-03-23T06:18:00Z</t>
+          <t>2026-03-23T07:05:00Z</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -2728,7 +2734,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -2739,54 +2745,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2035957508989444417</t>
+          <t>2035964468413493475</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://x.com/parulghalout/status/2035957508989444417</t>
+          <t>https://x.com/Mr__Krabs___/status/2035964468413493475</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://x.com/parulghalout</t>
+          <t>https://x.com/Mr__Krabs___</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>parulghalout</t>
+          <t>Mr__Krabs___</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>parul ghalout</t>
+          <t>Eugene H Krabs</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/589412760515031040/ehckyrV3_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1439693335644487683/C-FPyRyf_bigger.jpg</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @skrana111 @krahman_4 @Shilpa4669</t>
+          <t>Operation epic bimbo has been closed for a small profit; too many significant threats to GCC key infrastructure and honestly had thought this would be wrap</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/skrana111" title="sandeep kumar"&gt;@skrana111&lt;/a&gt; &lt;a href="/krahman_4" title="Kinza Rehman"&gt;@krahman_4&lt;/a&gt; &lt;a href="/Shilpa4669" title="Shilpa Jain"&gt;@Shilpa4669&lt;/a&gt;</t>
+          <t>Operation epic bimbo has been closed for a small profit; too many significant threats to GCC key infrastructure and honestly had thought this would be wrap</t>
         </is>
       </c>
       <c r="J27" t="b">
         <v>0</v>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>22h</t>
@@ -2794,20 +2796,16 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 5:51 AM UTC</t>
+          <t>Mar 23, 2026 · 6:18 AM UTC</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-03-23T05:51:00Z</t>
+          <t>2026-03-23T06:18:00Z</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>['https://x.com/skrana111', 'https://x.com/krahman_4', 'https://x.com/Shilpa4669']</t>
-        </is>
-      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -2818,7 +2816,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -2829,12 +2827,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2035957290990498203</t>
+          <t>2035957508989444417</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://x.com/parulghalout/status/2035957290990498203</t>
+          <t>https://x.com/parulghalout/status/2035957508989444417</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2860,12 +2858,12 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App.  @Shilpa4669 @mnsadiq84 @FazilAnas</t>
+          <t>Exchanger volunteer program @skrana111 @krahman_4 @Shilpa4669</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App.  &lt;a href="/Shilpa4669" title="Shilpa Jain"&gt;@Shilpa4669&lt;/a&gt; &lt;a href="/mnsadiq84" title="naveed sadiq"&gt;@mnsadiq84&lt;/a&gt; &lt;a href="/FazilAnas" title="Tosifmuhammad 🇦🇪"&gt;@FazilAnas&lt;/a&gt;</t>
+          <t>Exchanger volunteer program &lt;a href="/skrana111" title="sandeep kumar"&gt;@skrana111&lt;/a&gt; &lt;a href="/krahman_4" title="Kinza Rehman"&gt;@krahman_4&lt;/a&gt; &lt;a href="/Shilpa4669" title="Shilpa Jain"&gt;@Shilpa4669&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J28" t="b">
@@ -2879,23 +2877,23 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 5:50 AM UTC</t>
+          <t>Mar 23, 2026 · 5:51 AM UTC</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-03-23T05:50:00Z</t>
+          <t>2026-03-23T05:51:00Z</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>['https://x.com/Shilpa4669', 'https://x.com/mnsadiq84', 'https://x.com/FazilAnas']</t>
+          <t>['https://x.com/skrana111', 'https://x.com/krahman_4', 'https://x.com/Shilpa4669']</t>
         </is>
       </c>
       <c r="R28" t="n">
@@ -2908,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -2919,43 +2917,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2035957091601657909</t>
+          <t>2035957290990498203</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035957091601657909</t>
+          <t>https://x.com/parulghalout/status/2035957290990498203</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/parulghalout</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>parulghalout</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>parul ghalout</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/589412760515031040/ehckyrV3_bigger.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>B- 1.89% @Emy191990 @parulghalout @Salma2232019</t>
+          <t>Via the ENBD X Mobile App.  @Shilpa4669 @mnsadiq84 @FazilAnas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>B- 1.89% &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+          <t>Via the ENBD X Mobile App.  &lt;a href="/Shilpa4669" title="Shilpa Jain"&gt;@Shilpa4669&lt;/a&gt; &lt;a href="/mnsadiq84" title="naveed sadiq"&gt;@mnsadiq84&lt;/a&gt; &lt;a href="/FazilAnas" title="Tosifmuhammad 🇦🇪"&gt;@FazilAnas&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J29" t="b">
@@ -2969,23 +2967,23 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 5:49 AM UTC</t>
+          <t>Mar 23, 2026 · 5:50 AM UTC</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-03-23T05:49:00Z</t>
+          <t>2026-03-23T05:50:00Z</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/Shilpa4669', 'https://x.com/mnsadiq84', 'https://x.com/FazilAnas']</t>
         </is>
       </c>
       <c r="R29" t="n">
@@ -2998,7 +2996,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -3009,12 +3007,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2035956997238165721</t>
+          <t>2035957091601657909</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956997238165721</t>
+          <t>https://x.com/Sosomostafa729S/status/2035957091601657909</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3040,12 +3038,12 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>B- 1.89% @ibushra_03 @parulghalout @Salma2232019</t>
+          <t>B- 1.89% @Emy191990 @parulghalout @Salma2232019</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>B- 1.89% &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+          <t>B- 1.89% &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J30" t="b">
@@ -3059,7 +3057,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3075,7 +3073,7 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>['https://x.com/ibushra_03', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
       <c r="R30" t="n">
@@ -3088,7 +3086,7 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -3099,12 +3097,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2035956939956642179</t>
+          <t>2035956997238165721</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956939956642179</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956997238165721</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3130,12 +3128,12 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>B- 1.89% @semeet @SelmaRomola @Emy191990</t>
+          <t>B- 1.89% @ibushra_03 @parulghalout @Salma2232019</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>B- 1.89% &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt;</t>
+          <t>B- 1.89% &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J31" t="b">
@@ -3149,23 +3147,23 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 5:48 AM UTC</t>
+          <t>Mar 23, 2026 · 5:49 AM UTC</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-03-23T05:48:00Z</t>
+          <t>2026-03-23T05:49:00Z</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/Emy191990']</t>
+          <t>['https://x.com/ibushra_03', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
       <c r="R31" t="n">
@@ -3178,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -3189,12 +3187,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2035956878518460827</t>
+          <t>2035956939956642179</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956878518460827</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956939956642179</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3220,12 +3218,12 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>B- 1.89% @Emy191990 @parulghalout @SelmaRomola</t>
+          <t>B- 1.89% @semeet @SelmaRomola @Emy191990</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>B- 1.89% &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
+          <t>B- 1.89% &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J32" t="b">
@@ -3239,7 +3237,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3255,7 +3253,7 @@
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/SelmaRomola']</t>
+          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/Emy191990']</t>
         </is>
       </c>
       <c r="R32" t="n">
@@ -3268,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -3279,12 +3277,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2035956707604705316</t>
+          <t>2035956878518460827</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956707604705316</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956878518460827</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3310,12 +3308,12 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @parulghalout @semeet @SelmaRomola</t>
+          <t>B- 1.89% @Emy191990 @parulghalout @SelmaRomola</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
+          <t>B- 1.89% &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J33" t="b">
@@ -3329,23 +3327,23 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 5:47 AM UTC</t>
+          <t>Mar 23, 2026 · 5:48 AM UTC</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-03-23T05:47:00Z</t>
+          <t>2026-03-23T05:48:00Z</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>['https://x.com/parulghalout', 'https://x.com/semeet', 'https://x.com/SelmaRomola']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/SelmaRomola']</t>
         </is>
       </c>
       <c r="R33" t="n">
@@ -3358,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -3369,43 +3367,43 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2035956681939828984</t>
+          <t>2035956707604705316</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://x.com/parulghalout/status/2035956681939828984</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956707604705316</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://x.com/parulghalout</t>
+          <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>parulghalout</t>
+          <t>Sosomostafa729S</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>parul ghalout</t>
+          <t>Soha.mostafa77</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/589412760515031040/ehckyrV3_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>B. 1.89%  @skrana111 @sehar_beg @semeet</t>
+          <t>Exchanger volunteer program @parulghalout @semeet @SelmaRomola</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>B. 1.89%  &lt;a href="/skrana111" title="sandeep kumar"&gt;@skrana111&lt;/a&gt; &lt;a href="/sehar_beg" title="Sehar Umar Beg"&gt;@sehar_beg&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt;</t>
+          <t>Exchanger volunteer program &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J34" t="b">
@@ -3419,7 +3417,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3435,7 +3433,7 @@
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>['https://x.com/skrana111', 'https://x.com/sehar_beg', 'https://x.com/semeet']</t>
+          <t>['https://x.com/parulghalout', 'https://x.com/semeet', 'https://x.com/SelmaRomola']</t>
         </is>
       </c>
       <c r="R34" t="n">
@@ -3448,7 +3446,7 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -3459,43 +3457,43 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2035956637853421634</t>
+          <t>2035956681939828984</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956637853421634</t>
+          <t>https://x.com/parulghalout/status/2035956681939828984</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/parulghalout</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>parulghalout</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>parul ghalout</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/589412760515031040/ehckyrV3_bigger.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @semeet @ibushra_03 @Salma2232019</t>
+          <t>B. 1.89%  @skrana111 @sehar_beg @semeet</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+          <t>B. 1.89%  &lt;a href="/skrana111" title="sandeep kumar"&gt;@skrana111&lt;/a&gt; &lt;a href="/sehar_beg" title="Sehar Umar Beg"&gt;@sehar_beg&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J35" t="b">
@@ -3509,7 +3507,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3525,7 +3523,7 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/ibushra_03', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/skrana111', 'https://x.com/sehar_beg', 'https://x.com/semeet']</t>
         </is>
       </c>
       <c r="R35" t="n">
@@ -3549,12 +3547,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2035956572711710976</t>
+          <t>2035956637853421634</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956572711710976</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956637853421634</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3580,12 +3578,12 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @Emy191990 @Salma2232019 @SelmaRomola</t>
+          <t>Exchanger volunteer program @semeet @ibushra_03 @Salma2232019</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
+          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J36" t="b">
@@ -3599,7 +3597,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3615,7 +3613,7 @@
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/Salma2232019', 'https://x.com/SelmaRomola']</t>
+          <t>['https://x.com/semeet', 'https://x.com/ibushra_03', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
       <c r="R36" t="n">
@@ -3628,7 +3626,7 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -3639,12 +3637,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2035956477169631536</t>
+          <t>2035956572711710976</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956477169631536</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956572711710976</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3670,12 +3668,12 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @Salma2232019 @Emy191990 @parulghalout</t>
+          <t>Exchanger volunteer program @Emy191990 @Salma2232019 @SelmaRomola</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
+          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J37" t="b">
@@ -3689,7 +3687,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3705,7 +3703,7 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>['https://x.com/Salma2232019', 'https://x.com/Emy191990', 'https://x.com/parulghalout']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/Salma2232019', 'https://x.com/SelmaRomola']</t>
         </is>
       </c>
       <c r="R37" t="n">
@@ -3718,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -3729,43 +3727,43 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2035956416520069280</t>
+          <t>2035956477169631536</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://x.com/parulghalout/status/2035956416520069280</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956477169631536</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://x.com/parulghalout</t>
+          <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>parulghalout</t>
+          <t>Sosomostafa729S</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>parul ghalout</t>
+          <t>Soha.mostafa77</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/589412760515031040/ehckyrV3_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD  @mnsadiq84 @skrana111 @dxb_sknj</t>
+          <t>Exchanger volunteer program @Salma2232019 @Emy191990 @parulghalout</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD  &lt;a href="/mnsadiq84" title="naveed sadiq"&gt;@mnsadiq84&lt;/a&gt; &lt;a href="/skrana111" title="sandeep kumar"&gt;@skrana111&lt;/a&gt; &lt;a href="/dxb_sknj" title="dxb_sknj"&gt;@dxb_sknj&lt;/a&gt;</t>
+          <t>Exchanger volunteer program &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J38" t="b">
@@ -3779,23 +3777,23 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 5:46 AM UTC</t>
+          <t>Mar 23, 2026 · 5:47 AM UTC</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-03-23T05:46:00Z</t>
+          <t>2026-03-23T05:47:00Z</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>['https://x.com/mnsadiq84', 'https://x.com/skrana111', 'https://x.com/dxb_sknj']</t>
+          <t>['https://x.com/Salma2232019', 'https://x.com/Emy191990', 'https://x.com/parulghalout']</t>
         </is>
       </c>
       <c r="R38" t="n">
@@ -3808,7 +3806,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -3819,43 +3817,43 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2035956407212925393</t>
+          <t>2035956416520069280</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956407212925393</t>
+          <t>https://x.com/parulghalout/status/2035956416520069280</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/parulghalout</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>parulghalout</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>parul ghalout</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/589412760515031040/ehckyrV3_bigger.jpg</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @semeet @SelmaRomola @ibushra_03</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD  @mnsadiq84 @skrana111 @dxb_sknj</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD  &lt;a href="/mnsadiq84" title="naveed sadiq"&gt;@mnsadiq84&lt;/a&gt; &lt;a href="/skrana111" title="sandeep kumar"&gt;@skrana111&lt;/a&gt; &lt;a href="/dxb_sknj" title="dxb_sknj"&gt;@dxb_sknj&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J39" t="b">
@@ -3869,7 +3867,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3885,7 +3883,7 @@
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/ibushra_03']</t>
+          <t>['https://x.com/mnsadiq84', 'https://x.com/skrana111', 'https://x.com/dxb_sknj']</t>
         </is>
       </c>
       <c r="R39" t="n">
@@ -3898,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -3909,12 +3907,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2035956342763258332</t>
+          <t>2035956407212925393</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956342763258332</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956407212925393</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3940,12 +3938,12 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout</t>
+          <t>Exchanger volunteer program @semeet @SelmaRomola @ibushra_03</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
+          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J40" t="b">
@@ -3959,7 +3957,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3975,7 +3973,7 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
+          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/ibushra_03']</t>
         </is>
       </c>
       <c r="R40" t="n">
@@ -3999,12 +3997,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2035956152442449955</t>
+          <t>2035956342763258332</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956152442449955</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956342763258332</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4030,12 +4028,12 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD @parulghalout @Emy191990 @Salma2232019</t>
+          <t>Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J41" t="b">
@@ -4049,23 +4047,23 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 5:45 AM UTC</t>
+          <t>Mar 23, 2026 · 5:46 AM UTC</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-03-23T05:45:00Z</t>
+          <t>2026-03-23T05:46:00Z</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>['https://x.com/parulghalout', 'https://x.com/Emy191990', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
         </is>
       </c>
       <c r="R41" t="n">
@@ -4078,7 +4076,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -4089,12 +4087,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2035956075355361747</t>
+          <t>2035956152442449955</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956075355361747</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956152442449955</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4120,12 +4118,12 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Salma2232019 @semeet</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD @parulghalout @Emy191990 @Salma2232019</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt;</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J42" t="b">
@@ -4139,7 +4137,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4155,7 +4153,7 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>['https://x.com/SelmaRomola', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
+          <t>['https://x.com/parulghalout', 'https://x.com/Emy191990', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
       <c r="R42" t="n">
@@ -4168,7 +4166,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -4179,12 +4177,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2035956001279775104</t>
+          <t>2035956075355361747</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035956001279775104</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956075355361747</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4210,12 +4208,12 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD @Emy191990 @parulghalout @ibushra_03</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Salma2232019 @semeet</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J43" t="b">
@@ -4229,7 +4227,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4245,7 +4243,7 @@
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/ibushra_03']</t>
+          <t>['https://x.com/SelmaRomola', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
         </is>
       </c>
       <c r="R43" t="n">
@@ -4258,7 +4256,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -4269,12 +4267,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2035955834002501721</t>
+          <t>2035956001279775104</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035955834002501721</t>
+          <t>https://x.com/Sosomostafa729S/status/2035956001279775104</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4300,12 +4298,12 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @Emy191990 @Salma2232019 @Salma2232019</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD @Emy191990 @parulghalout @ibushra_03</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J44" t="b">
@@ -4319,23 +4317,23 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 5:44 AM UTC</t>
+          <t>Mar 23, 2026 · 5:45 AM UTC</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-03-23T05:44:00Z</t>
+          <t>2026-03-23T05:45:00Z</t>
         </is>
       </c>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/Salma2232019', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/ibushra_03']</t>
         </is>
       </c>
       <c r="R44" t="n">
@@ -4348,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -4359,12 +4357,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2035955759859834985</t>
+          <t>2035955834002501721</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035955759859834985</t>
+          <t>https://x.com/Sosomostafa729S/status/2035955834002501721</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4390,12 +4388,12 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @SelmaRomola @semeet @ibushra_03</t>
+          <t>Via the ENBD X Mobile App. @Emy191990 @Salma2232019 @Salma2232019</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
+          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J45" t="b">
@@ -4409,7 +4407,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4425,7 +4423,7 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>['https://x.com/SelmaRomola', 'https://x.com/semeet', 'https://x.com/ibushra_03']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/Salma2232019', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
       <c r="R45" t="n">
@@ -4438,7 +4436,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -4449,12 +4447,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2035955684098163029</t>
+          <t>2035955759859834985</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035955684098163029</t>
+          <t>https://x.com/Sosomostafa729S/status/2035955759859834985</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4480,12 +4478,12 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @Emy191990 @parulghalout @Salma2232019</t>
+          <t>Via the ENBD X Mobile App. @SelmaRomola @semeet @ibushra_03</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+          <t>Via the ENBD X Mobile App. &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J46" t="b">
@@ -4499,23 +4497,23 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 5:43 AM UTC</t>
+          <t>Mar 23, 2026 · 5:44 AM UTC</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-03-23T05:43:00Z</t>
+          <t>2026-03-23T05:44:00Z</t>
         </is>
       </c>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/SelmaRomola', 'https://x.com/semeet', 'https://x.com/ibushra_03']</t>
         </is>
       </c>
       <c r="R46" t="n">
@@ -4539,12 +4537,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2035955579966173454</t>
+          <t>2035955684098163029</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035955579966173454</t>
+          <t>https://x.com/Sosomostafa729S/status/2035955684098163029</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4570,12 +4568,12 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @semeet @SelmaRomola @Salma2232019</t>
+          <t>Via the ENBD X Mobile App. @Emy191990 @parulghalout @Salma2232019</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J47" t="b">
@@ -4589,7 +4587,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4605,7 +4603,7 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
       <c r="R47" t="n">
@@ -4618,7 +4616,7 @@
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -4629,12 +4627,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2035955485564936537</t>
+          <t>2035955579966173454</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035955485564936537</t>
+          <t>https://x.com/Sosomostafa729S/status/2035955579966173454</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4660,12 +4658,12 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @SelmaRomola @Emy191990 @parulghalout</t>
+          <t>Via the ENBD X Mobile App. @semeet @SelmaRomola @Salma2232019</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
+          <t>Via the ENBD X Mobile App. &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J48" t="b">
@@ -4679,7 +4677,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4695,7 +4693,7 @@
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>['https://x.com/SelmaRomola', 'https://x.com/Emy191990', 'https://x.com/parulghalout']</t>
+          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
       <c r="R48" t="n">
@@ -4708,7 +4706,7 @@
         <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -4719,12 +4717,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2035955401255235904</t>
+          <t>2035955485564936537</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2035955401255235904</t>
+          <t>https://x.com/Sosomostafa729S/status/2035955485564936537</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4750,12 +4748,12 @@
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @Emy191990 @Salma2232019 @semeet</t>
+          <t>Via the ENBD X Mobile App. @SelmaRomola @Emy191990 @parulghalout</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt;</t>
+          <t>Via the ENBD X Mobile App. &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J49" t="b">
@@ -4769,23 +4767,23 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 5:42 AM UTC</t>
+          <t>Mar 23, 2026 · 5:43 AM UTC</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-03-23T05:42:00Z</t>
+          <t>2026-03-23T05:43:00Z</t>
         </is>
       </c>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
+          <t>['https://x.com/SelmaRomola', 'https://x.com/Emy191990', 'https://x.com/parulghalout']</t>
         </is>
       </c>
       <c r="R49" t="n">
@@ -4798,7 +4796,7 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -4809,232 +4807,232 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2035947184114344234</t>
+          <t>2035955401255235904</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2035947184114344234</t>
+          <t>https://x.com/Sosomostafa729S/status/2035955401255235904</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>Sosomostafa729S</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Soha.mostafa77</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
+          <t>Via the ENBD X Mobile App. @Emy191990 @Salma2232019 @semeet</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 5:42 AM UTC</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>2026-03-23T05:42:00Z</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
+        </is>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>21</v>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2035947184114344234</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2035947184114344234</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
           <t>Thank you for reaching out to us. To ensure a seamless and secure banking experience, please reach out to our customer support on call 24/7.
 Or WhatsApp banking services from 9AM to 7PM at 971600540000 to assist, this helps us maintain the highest security standards for your account. Thank you for your understanding.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>Thank you for reaching out to us. To ensure a seamless and secure banking experience, please reach out to our customer support on call 24/7.
 Or WhatsApp banking services from 9AM to 7PM at 971600540000 to assist, this helps us maintain the highest security standards for your account. Thank you for your understanding.</t>
         </is>
       </c>
-      <c r="J50" t="b">
-        <v>0</v>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
         <is>
           <t>['ShagilShams']</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Mar 23</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 5:10 AM UTC</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>2026-03-23T05:10:00Z</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>35</v>
-      </c>
-      <c r="V50" t="inlineStr">
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>38</v>
+      </c>
+      <c r="V51" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>2035937800336384350</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_KSA/status/2035937800336384350</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_KSA</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>EmiratesNBD_KSA</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>EmiratesNBD KSA</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
         <is>
           <t>مرحباً بك, يمكنك الأن معرفة المزيد عن اماكن الفروع و أوقات العمل من خلال الضغط على الرابط ادناه.
 ms.spr.ly/6016Qszsr</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>مرحباً بك, يمكنك الأن معرفة المزيد عن اماكن الفروع و أوقات العمل من خلال الضغط على الرابط ادناه.
 &lt;a href="http://ms.spr.ly/6016Qszsr"&gt;ms.spr.ly/6016Qszsr&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J51" t="b">
-        <v>0</v>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>['c65kg']</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>Mar 23, 2026 · 4:32 AM UTC</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>2026-03-23T04:32:00Z</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>['http://ms.spr.ly/6016Qszsr']</t>
-        </is>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>35</v>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2035887867075948831</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>https://x.com/ahmd_4050/status/2035887867075948831</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>https://x.com/ahmd_4050</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>ahmd_4050</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>ahmd</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1686557037948276736/wZXFbO-o_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>كم تعطون قروض</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>كم تعطون قروض</t>
-        </is>
-      </c>
       <c r="J52" t="b">
         <v>0</v>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['c65kg']</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5044,16 +5042,20 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 1:14 AM UTC</t>
+          <t>Mar 23, 2026 · 4:32 AM UTC</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-03-23T01:14:00Z</t>
+          <t>2026-03-23T04:32:00Z</t>
         </is>
       </c>
       <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>['http://ms.spr.ly/6016Qszsr']</t>
+        </is>
+      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -5064,7 +5066,7 @@
         <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -5075,126 +5077,212 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2035879255176093818</t>
+          <t>2035887867075948831</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://x.com/ShagilShams/status/2035879255176093818</t>
+          <t>https://x.com/ahmd_4050/status/2035887867075948831</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://x.com/ShagilShams</t>
+          <t>https://x.com/ahmd_4050</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ShagilShams</t>
+          <t>ahmd_4050</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Shagil Shams</t>
+          <t>ahmd</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1618258890503901184/GcGIQNmE_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1686557037948276736/wZXFbO-o_bigger.jpg</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
+        <is>
+          <t>كم تعطون قروض</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>كم تعطون قروض</t>
+        </is>
+      </c>
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Mar 23</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 1:14 AM UTC</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2026-03-23T01:14:00Z</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>17</v>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2035879255176093818</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://x.com/ShagilShams/status/2035879255176093818</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://x.com/ShagilShams</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ShagilShams</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Shagil Shams</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1618258890503901184/GcGIQNmE_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE Hi Team , 
 I'm in India , Unable to transfer money to myself. Payment getting declined . 
 Please check .</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; Hi Team , 
 I&amp;#39;m in India , Unable to transfer money to myself. Payment getting declined . 
 Please check .</t>
         </is>
       </c>
-      <c r="J53" t="b">
-        <v>0</v>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
+      <c r="J54" t="b">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
         <is>
           <t>Mar 23</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 12:40 AM UTC</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>2026-03-23T00:40:00Z</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr">
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
         <is>
           <t>['https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="R53" t="n">
+      <c r="R54" t="n">
         <v>1</v>
       </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>31</v>
-      </c>
-      <c r="V53" t="inlineStr">
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>33</v>
+      </c>
+      <c r="V54" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>2036045570406535456</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2036045570406535456</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
         <is>
           <t>الحين وقتك مع الإمارات الإسلامي.
 احصل على مزايا خاصة واسترداد نقدي مضمون عند تحويل الراتب واستمتع بمعدلات أرباح تنافسية مع تمويل السيارات. وفر واحصل على أرباح متوقعة تصل إلى %6.00 سنوياً.
@@ -5203,7 +5291,7 @@
 تُطبق الشروط والأحكام.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>الحين وقتك مع الإمارات الإسلامي.
 احصل على مزايا خاصة واسترداد نقدي مضمون عند تحويل الراتب واستمتع بمعدلات أرباح تنافسية مع تمويل السيارات. وفر واحصل على أرباح متوقعة تصل إلى %6.00 سنوياً.
@@ -5212,125 +5300,39 @@
 تُطبق الشروط والأحكام.</t>
         </is>
       </c>
-      <c r="J54" t="b">
-        <v>0</v>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>16h</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
+      <c r="J55" t="b">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
         <is>
           <t>Mar 23, 2026 · 11:41 AM UTC</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>2026-03-23T11:41:00Z</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>1</v>
-      </c>
-      <c r="U54" t="n">
-        <v>135</v>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2035996471896449306</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2035996471896449306</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
-      <c r="J55" t="b">
-        <v>0</v>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>['Ben252024']</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>Mar 23, 2026 · 8:26 AM UTC</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>2026-03-23T08:26:00Z</t>
         </is>
       </c>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U55" t="n">
-        <v>11</v>
+        <v>149</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -5341,12 +5343,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2035989928291488100</t>
+          <t>2035996471896449306</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2035989928291488100</t>
+          <t>https://x.com/emiratesislamic/status/2035996471896449306</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5372,21 +5374,23 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
-You just received a subscription renewal email with spelling mistakes. What would you do?</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
-You just received a subscription renewal email with spelling mistakes. What would you do?</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="J56" t="b">
         <v>0</v>
       </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>['Ben252024']</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
           <t>20h</t>
@@ -5394,12 +5398,12 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Mar 23, 2026 · 8:00 AM UTC</t>
+          <t>Mar 23, 2026 · 8:26 AM UTC</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-03-23T08:00:00Z</t>
+          <t>2026-03-23T08:26:00Z</t>
         </is>
       </c>
       <c r="P56" t="inlineStr"/>
@@ -5414,7 +5418,7 @@
         <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>253</v>
+        <v>13</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -5425,12 +5429,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2035989927905693845</t>
+          <t>2035989928291488100</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2035989927905693845</t>
+          <t>https://x.com/emiratesislamic/status/2035989928291488100</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5456,14 +5460,14 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
-Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
+          <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
+You just received a subscription renewal email with spelling mistakes. What would you do?</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
-Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
+          <t>وصلتك رسالة بريد إلكتروني لتجديد اشتراك تحتوي على أخطاء إملائية، ماذا تفعل؟
+You just received a subscription renewal email with spelling mistakes. What would you do?</t>
         </is>
       </c>
       <c r="J57" t="b">
@@ -5473,7 +5477,7 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -5498,9 +5502,93 @@
         <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>163</v>
+        <v>258</v>
       </c>
       <c r="V57" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2035989927905693845</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2035989927905693845</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
+Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>احذر الاحتيال. وصلتك رسالة تجديد من بريد جي ميل أو ياهو، ماذا تفعل؟
+Stay alert to scams. Received a renewal email from a Gmail/Yahoo address?</t>
+        </is>
+      </c>
+      <c r="J58" t="b">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Mar 23, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>2026-03-23T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>168</v>
+      </c>
+      <c r="V58" t="inlineStr">
         <is>
           <t>EI</t>
         </is>

--- a/EI_ENBD_3post.xlsx
+++ b/EI_ENBD_3post.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V69"/>
+  <dimension ref="A1:V70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,12 +543,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2036654307596992707</t>
+          <t>2036665227840803080</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036654307596992707</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036665227840803080</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -574,102 +574,100 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
+          <t>Thanks for writing to us, kindly note that we have replied to your email</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Thanks for writing to us, kindly note that we have replied to your email</t>
+        </is>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>['ZahidanMuhamma']</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>37m</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Mar 25, 2026 · 4:43 AM UTC</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2026-03-25T04:43:00Z</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2036654307596992707</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2036654307596992707</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>Your financial tip of the week
 #FinancialWellbeing #EmiratesNBDTips #SmartMoney #FinWell</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Your financial tip of the week
 &lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBDTips"&gt;#EmiratesNBDTips&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoney"&gt;#SmartMoney&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinWell"&gt;#FinWell&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>4m</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 · 4:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2026-03-25T04:00:00Z</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBDTips', 'https://x.com/search?f=tweets&amp;q=%23SmartMoney', 'https://x.com/search?f=tweets&amp;q=%23FinWell']</t>
-        </is>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>40</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2036654307383111761</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036654307383111761</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Emirates NBD</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>نصيحتك المالية لهذا الأسبوع
-#FinancialWellbeing #EmiratesNBDTips #FinWell #SmartMoney</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>نصيحتك المالية لهذا الأسبوع
-&lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBDTips"&gt;#EmiratesNBDTips&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinWell"&gt;#FinWell&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoney"&gt;#SmartMoney&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J3" t="b">
@@ -679,7 +677,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>4m</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -695,7 +693,7 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBDTips', 'https://x.com/search?f=tweets&amp;q=%23FinWell', 'https://x.com/search?f=tweets&amp;q=%23SmartMoney']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBDTips', 'https://x.com/search?f=tweets&amp;q=%23SmartMoney', 'https://x.com/search?f=tweets&amp;q=%23FinWell']</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -708,7 +706,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>42</v>
+        <v>227</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -719,71 +717,73 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2036586113079328797</t>
+          <t>2036654307383111761</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://x.com/semeet/status/2036586113079328797</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036654307383111761</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/semeet</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>semeet</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>seema shelat</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1376978771538898945/X-iaSTLK_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Congratulations 🎊</t>
+          <t>نصيحتك المالية لهذا الأسبوع
+#FinancialWellbeing #EmiratesNBDTips #FinWell #SmartMoney</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Congratulations 🎊</t>
+          <t>نصيحتك المالية لهذا الأسبوع
+&lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBDTips"&gt;#EmiratesNBDTips&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinWell"&gt;#FinWell&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoney"&gt;#SmartMoney&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J4" t="b">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>4h</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 11:29 PM UTC</t>
+          <t>Mar 25, 2026 · 4:00 AM UTC</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-03-24T23:29:00Z</t>
+          <t>2026-03-25T04:00:00Z</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBDTips', 'https://x.com/search?f=tweets&amp;q=%23FinWell', 'https://x.com/search?f=tweets&amp;q=%23SmartMoney']</t>
+        </is>
+      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>210</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -805,161 +805,161 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2036561511594991637</t>
+          <t>2036586113079328797</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://x.com/Ridvan_Dayanc/status/2036561511594991637</t>
+          <t>https://x.com/semeet/status/2036586113079328797</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/Ridvan_Dayanc</t>
+          <t>https://x.com/semeet</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ridvan_Dayanc</t>
+          <t>semeet</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rıdvan Dayanç</t>
+          <t>seema shelat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/891319667645702144/MaGwpQS6_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1376978771538898945/X-iaSTLK_bigger.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>Congratulations 🎊</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Congratulations 🎊</t>
+        </is>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 11:29 PM UTC</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-03-24T23:29:00Z</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>5</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2036561511594991637</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://x.com/Ridvan_Dayanc/status/2036561511594991637</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://x.com/Ridvan_Dayanc</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ridvan_Dayanc</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Rıdvan Dayanç</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/891319667645702144/MaGwpQS6_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
         <is>
           <t>General Information ⚠️
 All clear 🤲
 #dubai #attack #besafe</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>General Information ⚠️
 All clear 🤲
 &lt;a href="/search?f=tweets&amp;amp;q=%23dubai"&gt;#dubai&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23attack"&gt;#attack&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23besafe"&gt;#besafe&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>6h</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>7h</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>Mar 24, 2026 · 9:51 PM UTC</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>2026-03-24T21:51:00Z</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23dubai', 'https://x.com/search?f=tweets&amp;q=%23attack', 'https://x.com/search?f=tweets&amp;q=%23besafe']</t>
         </is>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>218</v>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2036558462906409266</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://x.com/ZahidanMuhamma/status/2036558462906409266</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://x.com/ZahidanMuhamma</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ZahidanMuhamma</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Muhammad Zahidan</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1827047486680137728/R86Fb-lT_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>It's a joke I will wait for 90 days to receive my fund what a joke</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>It&amp;#39;s a joke I will wait for 90 days to receive my fund what a joke</t>
-        </is>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>6h</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Mar 24, 2026 · 9:39 PM UTC</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2026-03-24T21:39:00Z</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -970,7 +970,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>5</v>
+        <v>244</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -981,63 +981,67 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2036555909082534200</t>
+          <t>2036558462906409266</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://x.com/islamchann86950/status/2036555909082534200</t>
+          <t>https://x.com/ZahidanMuhamma/status/2036558462906409266</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/islamchann86950</t>
+          <t>https://x.com/ZahidanMuhamma</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>islamchann86950</t>
+          <t>ZahidanMuhamma</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>islam channel</t>
+          <t>Muhammad Zahidan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2024383226257588224/NOAuj7I0_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1827047486680137728/R86Fb-lT_bigger.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Doing good doesn't require much ..🫱🫲</t>
+          <t>It's a joke I will wait for 90 days to receive my fund what a joke</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Doing good doesn&amp;#39;t require much ..🫱🫲</t>
+          <t>It&amp;#39;s a joke I will wait for 90 days to receive my fund what a joke</t>
         </is>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 9:29 PM UTC</t>
+          <t>Mar 24, 2026 · 9:39 PM UTC</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-03-24T21:29:00Z</t>
+          <t>2026-03-24T21:39:00Z</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1049,10 +1053,10 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1063,36 +1067,118 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2036498571747532999</t>
+          <t>2036555909082534200</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://x.com/axerock2024/status/2036498571747532999</t>
+          <t>https://x.com/islamchann86950/status/2036555909082534200</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/axerock2024</t>
+          <t>https://x.com/islamchann86950</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>axerock2024</t>
+          <t>islamchann86950</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Axe</t>
+          <t>islam channel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/2024383226257588224/NOAuj7I0_bigger.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
+        <is>
+          <t>Doing good doesn't require much ..🫱🫲</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Doing good doesn&amp;#39;t require much ..🫱🫲</t>
+        </is>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>7h</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 9:29 PM UTC</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2026-03-24T21:29:00Z</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2036498571747532999</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://x.com/axerock2024/status/2036498571747532999</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://x.com/axerock2024</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>axerock2024</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Axe</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
         <is>
           <t>Disastrous!!! Avoid.
 @FinMinIndia
@@ -1110,7 +1196,7 @@
 cnbctv18.com/business/financ…</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Disastrous!!! Avoid.
 &lt;a href="/FinMinIndia" title="Ministry of Finance"&gt;@FinMinIndia&lt;/a&gt;
@@ -1128,87 +1214,87 @@
 &lt;a href="https://www.cnbctv18.com/business/finance/emirates-nbd-says-rbl-bank-deal-on-track-despite-geopolitical-tensions-ws-l-19869449.htm"&gt;cnbctv18.com/business/financ…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J8" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>['axerock2024', 'EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>10h</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>11h</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>Mar 24, 2026 · 5:41 PM UTC</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>2026-03-24T17:41:00Z</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>['https://x.com/FinMinIndia', 'https://x.com/nsitharaman', 'https://x.com/CimGOI', 'https://x.com/PiyushGoyal', 'https://x.com/HMOIndia', 'https://x.com/RBI', 'https://x.com/SmalhotraRBI', 'https://x.com/AmitShah', 'https://x.com/DrSJaishankar', 'https://x.com/MEAIndia', 'https://x.com/PMOIndia', 'https://x.com/narendramodi', 'https://www.cnbctv18.com/business/finance/emirates-nbd-says-rbl-bank-deal-on-track-despite-geopolitical-tensions-ws-l-19869449.htm']</t>
         </is>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>16</v>
-      </c>
-      <c r="V8" t="inlineStr">
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>19</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>2036488212902731999</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_EGY/status/2036488212902731999</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_EGY</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>EmiratesNBD_EGY</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
         <is>
           <t>Buy your hair essentials with 0% down payment, 0% interest, and 0% processing fees on 6 months from CH&amp;BE through their website using Emirates NBD credit cards.
 Offer is valid till 15th of April 2026.
@@ -1216,7 +1302,7 @@
 Tax registration number: 204-897-319</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Buy your hair essentials with 0% down payment, 0% interest, and 0% processing fees on 6 months from CH&amp;amp;BE through their website using Emirates NBD credit cards.
 Offer is valid till 15th of April 2026.
@@ -1224,79 +1310,79 @@
 Tax registration number: 204-897-319</t>
         </is>
       </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>11h</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>12h</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>Mar 24, 2026 · 5:00 PM UTC</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>2026-03-24T17:00:00Z</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>37</v>
-      </c>
-      <c r="V9" t="inlineStr">
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>39</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>2036488212877648052</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_EGY/status/2036488212877648052</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_EGY</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>EmiratesNBD_EGY</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
         <is>
           <t>استعدي لإطلالة جديدة واشتري منتاجات العناية بالشعر من CH&amp;BE ب0% مقدم، 0% فوائد، و 0% مصاريف إدارية على 6 أشهر من خلال الموقع الإلكتروني باستخدام بطاقات بنك الإمارات دبي الوطني الائتمانية.
 العرض سارى حتى 15 أبريل 2026
@@ -1304,7 +1390,7 @@
 رقم التسجيل الضريبي: 319-897-204</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>استعدي لإطلالة جديدة واشتري منتاجات العناية بالشعر من CH&amp;amp;BE ب0% مقدم، 0% فوائد، و 0% مصاريف إدارية على 6 أشهر من خلال الموقع الإلكتروني باستخدام بطاقات بنك الإمارات دبي الوطني الائتمانية.
 العرض سارى حتى 15 أبريل 2026
@@ -1312,79 +1398,79 @@
 رقم التسجيل الضريبي: 319-897-204</t>
         </is>
       </c>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>11h</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>12h</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>Mar 24, 2026 · 5:00 PM UTC</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>2026-03-24T17:00:00Z</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>52</v>
-      </c>
-      <c r="V10" t="inlineStr">
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>55</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2036472567389716544</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2036472567389716544</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
         <is>
           <t>لحظة اعتزاز. وتجسيد للثقة.
 نفخر بحصولنا على هذا التكريم في جوائز يوروموني للخدمات المصرفية الخاصة 2026:
@@ -1394,7 +1480,7 @@
 #جوائز_يوروموني #التميز_في_الخدمات_المصرفية_الخاصة</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>لحظة اعتزاز. وتجسيد للثقة.
 نفخر بحصولنا على هذا التكريم في جوائز يوروموني للخدمات المصرفية الخاصة 2026:
@@ -1404,83 +1490,83 @@
 &lt;a href="/search?f=tweets&amp;amp;q=%23جوائز_يوروموني"&gt;#جوائز_يوروموني&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التميز_في_الخدمات_المصرفية_الخاصة"&gt;#التميز_في_الخدمات_المصرفية_الخاصة&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J11" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>12h</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>Mar 24, 2026 · 3:57 PM UTC</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>2026-03-24T15:57:00Z</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23جوائز_يوروموني', 'https://x.com/search?f=tweets&amp;q=%23التميز_في_الخدمات_المصرفية_الخاصة']</t>
         </is>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
         <v>1</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" t="n">
         <v>4</v>
       </c>
-      <c r="U11" t="n">
-        <v>407</v>
-      </c>
-      <c r="V11" t="inlineStr">
+      <c r="U12" t="n">
+        <v>424</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>2036472534812512442</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2036472534812512442</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
         <is>
           <t>A moment of pride. A reflection of trust.
 We are pleased to be recognised at the Euromoney Private Banking Awards 2026 as:
@@ -1491,7 +1577,7 @@
 #EuromoneyAwards #PrivateBankingExcellence</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>A moment of pride. A reflection of trust.
 We are pleased to be recognised at the Euromoney Private Banking Awards 2026 as:
@@ -1502,92 +1588,6 @@
 &lt;a href="/search?f=tweets&amp;amp;q=%23EuromoneyAwards"&gt;#EuromoneyAwards&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23PrivateBankingExcellence"&gt;#PrivateBankingExcellence&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J12" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>12h</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Mar 24, 2026 · 3:57 PM UTC</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2026-03-24T15:57:00Z</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EuromoneyAwards', 'https://x.com/search?f=tweets&amp;q=%23PrivateBankingExcellence']</t>
-        </is>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>351</v>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2036459552041046257</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>https://x.com/vcdxnz001/status/2036459552041046257</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>https://x.com/vcdxnz001</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>vcdxnz001</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Lord WebScale Webster</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1157827121282072581/YmPuMRvh_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>I really love @EmiratesNBD_AE and their payment systems. International transfers received in 10 minutes from UAE to USA. Nothing else like this. Would take a day in New Zealand. Just incredible. The UAE banking system is really great.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>I really love &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; and their payment systems. International transfers received in 10 minutes from UAE to USA. Nothing else like this. Would take a day in New Zealand. Just incredible. The UAE banking system is really great.</t>
-        </is>
-      </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
@@ -1595,36 +1595,36 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 3:06 PM UTC</t>
+          <t>Mar 24, 2026 · 3:57 PM UTC</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-03-24T15:06:00Z</t>
+          <t>2026-03-24T15:57:00Z</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EuromoneyAwards', 'https://x.com/search?f=tweets&amp;q=%23PrivateBankingExcellence']</t>
         </is>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U13" t="n">
-        <v>37</v>
+        <v>366</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1635,54 +1635,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2036439106700607823</t>
+          <t>2036459552041046257</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://x.com/HimanshuMotiyan/status/2036439106700607823</t>
+          <t>https://x.com/vcdxnz001/status/2036459552041046257</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/HimanshuMotiyan</t>
+          <t>https://x.com/vcdxnz001</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>HimanshuMotiyan</t>
+          <t>vcdxnz001</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Himanshu Motiyani</t>
+          <t>Lord WebScale Webster</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2032072703134613504/JzErzVWc_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1157827121282072581/YmPuMRvh_bigger.jpg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Again its same we are following up and we will update how many times team said this kindly release my funds as this is an emergency or provide me an date for releasing funds ?</t>
+          <t>I really love @EmiratesNBD_AE and their payment systems. International transfers received in 10 minutes from UAE to USA. Nothing else like this. Would take a day in New Zealand. Just incredible. The UAE banking system is really great.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Again its same we are following up and we will update how many times team said this kindly release my funds as this is an emergency or provide me an date for releasing funds ?</t>
+          <t>I really love &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; and their payment systems. International transfers received in 10 minutes from UAE to USA. Nothing else like this. Would take a day in New Zealand. Just incredible. The UAE banking system is really great.</t>
         </is>
       </c>
       <c r="J14" t="b">
         <v>0</v>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>14h</t>
@@ -1690,16 +1686,20 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 1:44 PM UTC</t>
+          <t>Mar 24, 2026 · 3:06 PM UTC</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-03-24T13:44:00Z</t>
+          <t>2026-03-24T15:06:00Z</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -1707,10 +1707,10 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1721,43 +1721,43 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2036438860737982775</t>
+          <t>2036439106700607823</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036438860737982775</t>
+          <t>https://x.com/HimanshuMotiyan/status/2036439106700607823</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/HimanshuMotiyan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>HimanshuMotiyan</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Himanshu Motiyani</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2032072703134613504/JzErzVWc_bigger.jpg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>We sincerely regret for the inconvenience, kindly note that we have replied to your email</t>
+          <t>Again its same we are following up and we will update how many times team said this kindly release my funds as this is an emergency or provide me an date for releasing funds ?</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>We sincerely regret for the inconvenience, kindly note that we have replied to your email</t>
+          <t>Again its same we are following up and we will update how many times team said this kindly release my funds as this is an emergency or provide me an date for releasing funds ?</t>
         </is>
       </c>
       <c r="J15" t="b">
@@ -1766,28 +1766,28 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>['HimanshuMotiyan']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 1:43 PM UTC</t>
+          <t>Mar 24, 2026 · 1:44 PM UTC</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-03-24T13:43:00Z</t>
+          <t>2026-03-24T13:44:00Z</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1807,12 +1807,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2036434154506649672</t>
+          <t>2036438860737982775</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036434154506649672</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036438860737982775</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1837,6 +1837,92 @@
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
+        <is>
+          <t>We sincerely regret for the inconvenience, kindly note that we have replied to your email</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>We sincerely regret for the inconvenience, kindly note that we have replied to your email</t>
+        </is>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>['HimanshuMotiyan']</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 1:43 PM UTC</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2026-03-24T13:43:00Z</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>23</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2036434154506649672</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2036434154506649672</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
         <is>
           <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to us at
 social@emiratesnbd.coml@emiratesnbd.com 
@@ -1844,7 +1930,7 @@
 We will make every effort to address the</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to us at
 social@emiratesnbd.coml@emiratesnbd.com 
@@ -1852,267 +1938,267 @@
 We will make every effort to address the</t>
         </is>
       </c>
-      <c r="J16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
         <is>
           <t>['TariqMa18773899']</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>Mar 24, 2026 · 1:25 PM UTC</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>2026-03-24T13:25:00Z</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>11</v>
-      </c>
-      <c r="V16" t="inlineStr">
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>16</v>
+      </c>
+      <c r="V17" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>2036430572923609589</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>https://x.com/HimanshuMotiyan/status/2036430572923609589</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>https://x.com/HimanshuMotiyan</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>HimanshuMotiyan</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Himanshu Motiyani</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2032072703134613504/JzErzVWc_bigger.jpg</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
         <is>
           <t>Hello @EmiratesNBD_AE 
 URGENT: Resolution Required for Case #983058 - Medical Emergency &amp; Travel Restrictions case no : #983058
 Its been more then a month bank is not releasing my funds in emergency situation also this case has been registered on 12th march today is 24th march</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Hello &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
 URGENT: Resolution Required for Case #983058 - Medical Emergency &amp;amp; Travel Restrictions case no : #983058
 Its been more then a month bank is not releasing my funds in emergency situation also this case has been registered on 12th march today is 24th march</t>
         </is>
       </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>Mar 24, 2026 · 1:10 PM UTC</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>2026-03-24T13:10:00Z</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>['https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="R17" t="n">
+      <c r="R18" t="n">
         <v>1</v>
       </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>11</v>
-      </c>
-      <c r="V17" t="inlineStr">
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>14</v>
+      </c>
+      <c r="V18" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>2036430430883414274</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>https://x.com/HimanshuMotiyan/status/2036430430883414274</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>https://x.com/HimanshuMotiyan</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>HimanshuMotiyan</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Himanshu Motiyani</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2032072703134613504/JzErzVWc_bigger.jpg</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
         <is>
           <t>Hello @EmiratesNBD_AE 
 URGENT: Resolution Required for Case #983058 - Medical Emergency &amp; Travel Restrictions case no : #983058
 Its been more then a month bank is not releasing my funds in emergency situation also this case has been registered on 12th march today is 24th march</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Hello &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
 URGENT: Resolution Required for Case #983058 - Medical Emergency &amp;amp; Travel Restrictions case no : #983058
 Its been more then a month bank is not releasing my funds in emergency situation also this case has been registered on 12th march today is 24th march</t>
         </is>
       </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>Mar 24, 2026 · 1:10 PM UTC</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>2026-03-24T13:10:00Z</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>['https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>3</v>
-      </c>
-      <c r="V18" t="inlineStr">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4</v>
+      </c>
+      <c r="V19" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>2036427479733432465</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>https://x.com/TariqMa18773899/status/2036427479733432465</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>https://x.com/TariqMa18773899</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>TariqMa18773899</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Tariq Malik</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1507617364636049410/VGpC-lFO_bigger.jpg</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
         <is>
           <t>I request to cancel the card ,it was told to me that I will receive the call for confirmation but due to current situation I was about to withdraw my rejection .
 No call but card was cancelled.
@@ -2120,7 +2206,7 @@
 Thank you NBD</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>I request to cancel the card ,it was told to me that I will receive the call for confirmation but due to current situation I was about to withdraw my rejection .
 No call but card was cancelled.
@@ -2128,83 +2214,83 @@
 Thank you NBD</t>
         </is>
       </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>Mar 24, 2026 · 12:58 PM UTC</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>2026-03-24T12:58:00Z</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="n">
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="n">
         <v>1</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>4</v>
-      </c>
-      <c r="V19" t="inlineStr">
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>7</v>
+      </c>
+      <c r="V20" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>2036419599017673090</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>https://x.com/Almalchannel/status/2036419599017673090</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>https://x.com/Almalchannel</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Almalchannel</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>قناة المال | Almal Channel</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1522466082388426752/G7GbO5MC_bigger.jpg</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
         <is>
           <t>أصول القطاع المصرفي +5.4 تريليون درهم … 🇦🇪
 مؤشرات تعكس قوة الاقتصاد 📊💰
@@ -2217,7 +2303,7 @@
 1/2</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>أصول القطاع المصرفي +5.4 تريليون درهم … 🇦🇪
 مؤشرات تعكس قوة الاقتصاد 📊💰
@@ -2230,79 +2316,79 @@
 1/2</t>
         </is>
       </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>Mar 24, 2026 · 12:27 PM UTC</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>2026-03-24T12:27:00Z</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="n">
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="n">
         <v>1</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S21" t="n">
         <v>10</v>
       </c>
-      <c r="T20" t="n">
-        <v>20</v>
-      </c>
-      <c r="U20" t="n">
-        <v>923</v>
-      </c>
-      <c r="V20" t="inlineStr">
+      <c r="T21" t="n">
+        <v>21</v>
+      </c>
+      <c r="U21" t="n">
+        <v>945</v>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>2036419006157168802</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>https://x.com/nasnews_ar/status/2036419006157168802</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>https://x.com/nasnews_ar</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>nasnews_ar</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>ناس نيوز- الإمارات</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2034402372802482176/xcCIp6EK_bigger.jpg</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
         <is>
           <t>🔵5.41 تريليونات درهم بنسبة نمو 1.4%
 🔵واصلت المؤشرات النقدية والمصرفية في دولة الإمارات، تسجيل أداء إيجابي مع بداية 2026، حيث ارتفع إجمالي الأصول المصرفية 1.4% ليتجاوز 5.413 تريليونات درهم في نهاية يناير 2026 مقارنة مع نحو 5.339 تريليونات درهم في نهاية ديسمبر 2025
@@ -2315,7 +2401,7 @@
 @nasnews_ar</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>🔵5.41 تريليونات درهم بنسبة نمو 1.4%
 🔵واصلت المؤشرات النقدية والمصرفية في دولة الإمارات، تسجيل أداء إيجابي مع بداية 2026، حيث ارتفع إجمالي الأصول المصرفية 1.4% ليتجاوز 5.413 تريليونات درهم في نهاية يناير 2026 مقارنة مع نحو 5.339 تريليونات درهم في نهاية ديسمبر 2025
@@ -2328,129 +2414,43 @@
 &lt;a href="/nasnews_ar" title="ناس نيوز- الإمارات"&gt;@nasnews_ar&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>Mar 24, 2026 · 12:25 PM UTC</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>2026-03-24T12:25:00Z</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23الإمارات', 'https://x.com/search?f=tweets&amp;q=%23عام_الأسرة', 'https://x.com/search?f=tweets&amp;q=%23ناس_نيوز_الإمارات', 'https://x.com/nasnews_ar']</t>
         </is>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
         <v>2</v>
       </c>
-      <c r="U21" t="n">
-        <v>475</v>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2036417775510442457</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2036417775510442457</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_KSA</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_KSA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>EmiratesNBD KSA</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل الخاصه بشكواك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل الخاصه بشكواك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
-        </is>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>['motsafeh057']</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Mar 24, 2026 · 12:20 PM UTC</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2026-03-24T12:20:00Z</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
       <c r="U22" t="n">
-        <v>26</v>
+        <v>483</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2461,73 +2461,73 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2036414919394971981</t>
+          <t>2036417775510442457</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://x.com/motsafeh057/status/2036414919394971981</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2036417775510442457</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://x.com/motsafeh057</t>
+          <t>https://x.com/EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>motsafeh057</t>
+          <t>EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>متصفح وقارئ للأخبار</t>
+          <t>EmiratesNBD KSA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1996323967443881984/qDVGWeO0_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA البنك رافض قطعيا يفتح لي حساب حاولت عن طريق خدمة العملاء رفض</t>
+          <t>مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل الخاصه بشكواك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; البنك رافض قطعيا يفتح لي حساب حاولت عن طريق خدمة العملاء رفض</t>
+          <t>مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل الخاصه بشكواك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
       <c r="J23" t="b">
         <v>0</v>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>['motsafeh057']</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 12:08 PM UTC</t>
+          <t>Mar 24, 2026 · 12:20 PM UTC</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-03-24T12:08:00Z</t>
+          <t>2026-03-24T12:20:00Z</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -2536,7 +2536,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -2547,43 +2547,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2036405523604709887</t>
+          <t>2036414919394971981</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://x.com/DFMalerts/status/2036405523604709887</t>
+          <t>https://x.com/motsafeh057/status/2036414919394971981</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://x.com/DFMalerts</t>
+          <t>https://x.com/motsafeh057</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DFMalerts</t>
+          <t>motsafeh057</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dubai Financial Market</t>
+          <t>متصفح وقارئ للأخبار</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1517441998717956098/e_tgPkVx_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1996323967443881984/qDVGWeO0_bigger.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>#DFM Top Gainers of the day: CHAE up 7.50%, EMIRATESNBD up 7.25%, DSI up 5.29%</t>
+          <t>@EmiratesNBD_KSA البنك رافض قطعيا يفتح لي حساب حاولت عن طريق خدمة العملاء رفض</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23DFM"&gt;#DFM&lt;/a&gt; Top Gainers of the day: CHAE up 7.50%, EMIRATESNBD up 7.25%, DSI up 5.29%</t>
+          <t>&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; البنك رافض قطعيا يفتح لي حساب حاولت عن طريق خدمة العملاء رفض</t>
         </is>
       </c>
       <c r="J24" t="b">
@@ -2593,36 +2593,36 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 11:31 AM UTC</t>
+          <t>Mar 24, 2026 · 12:08 PM UTC</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-03-24T11:31:00Z</t>
+          <t>2026-03-24T12:08:00Z</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23DFM']</t>
+          <t>['https://x.com/EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>267</v>
+        <v>63</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -2633,12 +2633,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2036402467106390175</t>
+          <t>2036405523604709887</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://x.com/DFMalerts/status/2036402467106390175</t>
+          <t>https://x.com/DFMalerts/status/2036405523604709887</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2664,12 +2664,12 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>الشركات الأكثر إرتفاعا لليوم في سوق دبي المالي: CHAE ارتفع 7.50%، EMIRATESNBD ارتفع 7.25%، DSI ارتفع 5.29%</t>
+          <t>#DFM Top Gainers of the day: CHAE up 7.50%, EMIRATESNBD up 7.25%, DSI up 5.29%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>الشركات الأكثر إرتفاعا لليوم في سوق دبي المالي: CHAE ارتفع 7.50%، EMIRATESNBD ارتفع 7.25%، DSI ارتفع 5.29%</t>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23DFM"&gt;#DFM&lt;/a&gt; Top Gainers of the day: CHAE up 7.50%, EMIRATESNBD up 7.25%, DSI up 5.29%</t>
         </is>
       </c>
       <c r="J25" t="b">
@@ -2679,21 +2679,25 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 11:19 AM UTC</t>
+          <t>Mar 24, 2026 · 11:31 AM UTC</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-03-24T11:19:00Z</t>
+          <t>2026-03-24T11:31:00Z</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23DFM']</t>
+        </is>
+      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -2701,10 +2705,10 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2715,69 +2719,63 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2036400751896043863</t>
+          <t>2036402467106390175</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://x.com/koko_isa8/status/2036400751896043863</t>
+          <t>https://x.com/DFMalerts/status/2036402467106390175</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://x.com/koko_isa8</t>
+          <t>https://x.com/DFMalerts</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>koko_isa8</t>
+          <t>DFMalerts</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>κoκo мadeмöıseιιe⁸ 💅🏽</t>
+          <t>Dubai Financial Market</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2035262775103242240/J6m7iJmF_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1517441998717956098/e_tgPkVx_bigger.png</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>So? 
-Am i expecting any call from your side?</t>
+          <t>الشركات الأكثر إرتفاعا لليوم في سوق دبي المالي: CHAE ارتفع 7.50%، EMIRATESNBD ارتفع 7.25%، DSI ارتفع 5.29%</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>So? 
-Am i expecting any call from your side?</t>
+          <t>الشركات الأكثر إرتفاعا لليوم في سوق دبي المالي: CHAE ارتفع 7.50%، EMIRATESNBD ارتفع 7.25%، DSI ارتفع 5.29%</t>
         </is>
       </c>
       <c r="J26" t="b">
         <v>0</v>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 11:12 AM UTC</t>
+          <t>Mar 24, 2026 · 11:19 AM UTC</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-03-24T11:12:00Z</t>
+          <t>2026-03-24T11:19:00Z</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -2792,7 +2790,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>6</v>
+        <v>285</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -2803,43 +2801,45 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2036389317132583041</t>
+          <t>2036400751896043863</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://x.com/netdiscussion/status/2036389317132583041</t>
+          <t>https://x.com/koko_isa8/status/2036400751896043863</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://x.com/netdiscussion</t>
+          <t>https://x.com/koko_isa8</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>netdiscussion</t>
+          <t>koko_isa8</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Muhammad Kashif Ashraf</t>
+          <t>κoκo мadeмöıseιιe⁸ 💅🏽</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/2035262775103242240/J6m7iJmF_bigger.jpg</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>@SAMAcares There's no response on the dispute query for the wrong/back dated fee applied, pending since 8 March</t>
+          <t>So? 
+Am i expecting any call from your side?</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>&lt;a href="/SAMAcares" title="SAMACares | ساما تهتم"&gt;@SAMAcares&lt;/a&gt; There&amp;#39;s no response on the dispute query for the wrong/back dated fee applied, pending since 8 March</t>
+          <t>So? 
+Am i expecting any call from your side?</t>
         </is>
       </c>
       <c r="J27" t="b">
@@ -2848,30 +2848,26 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_KSA']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 10:27 AM UTC</t>
+          <t>Mar 24, 2026 · 11:12 AM UTC</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-03-24T10:27:00Z</t>
+          <t>2026-03-24T11:12:00Z</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>['https://x.com/SAMAcares']</t>
-        </is>
-      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -2882,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -2893,43 +2889,43 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2036378422146932854</t>
+          <t>2036389317132583041</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036378422146932854</t>
+          <t>https://x.com/netdiscussion/status/2036389317132583041</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/netdiscussion</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>netdiscussion</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Muhammad Kashif Ashraf</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>You can find the winners list on the same page till January 2026, the rest will be updated shortly. we appreciate your patience.</t>
+          <t>@SAMAcares There's no response on the dispute query for the wrong/back dated fee applied, pending since 8 March</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>You can find the winners list on the same page till January 2026, the rest will be updated shortly. we appreciate your patience.</t>
+          <t>&lt;a href="/SAMAcares" title="SAMACares | ساما تهتم"&gt;@SAMAcares&lt;/a&gt; There&amp;#39;s no response on the dispute query for the wrong/back dated fee applied, pending since 8 March</t>
         </is>
       </c>
       <c r="J28" t="b">
@@ -2938,7 +2934,7 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>['FarazKhan11228']</t>
+          <t>['EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2948,16 +2944,20 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 9:43 AM UTC</t>
+          <t>Mar 24, 2026 · 10:27 AM UTC</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-03-24T09:43:00Z</t>
+          <t>2026-03-24T10:27:00Z</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>['https://x.com/SAMAcares']</t>
+        </is>
+      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -2968,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -2979,43 +2979,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2036368098593480939</t>
+          <t>2036378422146932854</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036368098593480939</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036378422146932854</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>B- 1.89% @Emy191990 @ibushra_03 @semeet</t>
+          <t>You can find the winners list on the same page till January 2026, the rest will be updated shortly. we appreciate your patience.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>B- 1.89% &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt;</t>
+          <t>You can find the winners list on the same page till January 2026, the rest will be updated shortly. we appreciate your patience.</t>
         </is>
       </c>
       <c r="J29" t="b">
@@ -3024,7 +3024,7 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['FarazKhan11228']</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3034,20 +3034,16 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 9:02 AM UTC</t>
+          <t>Mar 24, 2026 · 9:43 AM UTC</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-03-24T09:02:00Z</t>
+          <t>2026-03-24T09:43:00Z</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/semeet']</t>
-        </is>
-      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -3058,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -3069,12 +3065,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2036368044075966644</t>
+          <t>2036368098593480939</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036368044075966644</t>
+          <t>https://x.com/Sosomostafa729S/status/2036368098593480939</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3100,12 +3096,12 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>B- 1.89% @semeet @SelmaRomola @ibushra_03</t>
+          <t>B- 1.89% @Emy191990 @ibushra_03 @semeet</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>B- 1.89% &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
+          <t>B- 1.89% &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J30" t="b">
@@ -3119,7 +3115,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3135,7 +3131,7 @@
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/ibushra_03']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/semeet']</t>
         </is>
       </c>
       <c r="R30" t="n">
@@ -3159,12 +3155,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2036367982033768789</t>
+          <t>2036368044075966644</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036367982033768789</t>
+          <t>https://x.com/Sosomostafa729S/status/2036368044075966644</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3190,12 +3186,12 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>B- 1.89% @Emy191990 @ibushra_03 @Salma2232019</t>
+          <t>B- 1.89% @semeet @SelmaRomola @ibushra_03</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>B- 1.89% &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+          <t>B- 1.89% &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J31" t="b">
@@ -3209,7 +3205,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3225,7 +3221,7 @@
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/ibushra_03']</t>
         </is>
       </c>
       <c r="R31" t="n">
@@ -3238,7 +3234,7 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -3249,12 +3245,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2036367792195379613</t>
+          <t>2036367982033768789</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036367792195379613</t>
+          <t>https://x.com/Sosomostafa729S/status/2036367982033768789</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3280,12 +3276,12 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @parulghalout @parulghalout @Salma2232019</t>
+          <t>B- 1.89% @Emy191990 @ibushra_03 @Salma2232019</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+          <t>B- 1.89% &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J32" t="b">
@@ -3299,23 +3295,23 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 9:01 AM UTC</t>
+          <t>Mar 24, 2026 · 9:02 AM UTC</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-03-24T09:01:00Z</t>
+          <t>2026-03-24T09:02:00Z</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>['https://x.com/parulghalout', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
       <c r="R32" t="n">
@@ -3328,7 +3324,7 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -3339,12 +3335,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2036367691980873799</t>
+          <t>2036367792195379613</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036367691980873799</t>
+          <t>https://x.com/Sosomostafa729S/status/2036367792195379613</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3370,12 +3366,12 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @semeet @Salma2232019 @SelmaRomola</t>
+          <t>Exchanger volunteer program @parulghalout @parulghalout @Salma2232019</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
+          <t>Exchanger volunteer program &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J33" t="b">
@@ -3389,7 +3385,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3405,7 +3401,7 @@
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/Salma2232019', 'https://x.com/SelmaRomola']</t>
+          <t>['https://x.com/parulghalout', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
       <c r="R33" t="n">
@@ -3418,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -3429,12 +3425,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2036367634590212403</t>
+          <t>2036367691980873799</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036367634590212403</t>
+          <t>https://x.com/Sosomostafa729S/status/2036367691980873799</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3460,12 +3456,12 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @Emy191990 @parulghalout @parulghalout</t>
+          <t>Exchanger volunteer program @semeet @Salma2232019 @SelmaRomola</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
+          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J34" t="b">
@@ -3479,23 +3475,23 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 9:00 AM UTC</t>
+          <t>Mar 24, 2026 · 9:01 AM UTC</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-03-24T09:00:00Z</t>
+          <t>2026-03-24T09:01:00Z</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/parulghalout']</t>
+          <t>['https://x.com/semeet', 'https://x.com/Salma2232019', 'https://x.com/SelmaRomola']</t>
         </is>
       </c>
       <c r="R34" t="n">
@@ -3508,7 +3504,7 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -3519,12 +3515,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2036367508480098434</t>
+          <t>2036367634590212403</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036367508480098434</t>
+          <t>https://x.com/Sosomostafa729S/status/2036367634590212403</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3550,12 +3546,12 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @semeet @Emy191990 @ibushra_03</t>
+          <t>Exchanger volunteer program @Emy191990 @parulghalout @parulghalout</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
+          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J35" t="b">
@@ -3569,7 +3565,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3585,7 +3581,7 @@
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/Emy191990', 'https://x.com/ibushra_03']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/parulghalout']</t>
         </is>
       </c>
       <c r="R35" t="n">
@@ -3598,7 +3594,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -3609,12 +3605,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2036367351269171519</t>
+          <t>2036367508480098434</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036367351269171519</t>
+          <t>https://x.com/Sosomostafa729S/status/2036367508480098434</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3640,12 +3636,12 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @Salma2232019 @Emy191990 @SelmaRomola</t>
+          <t>Exchanger volunteer program @semeet @Emy191990 @ibushra_03</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
+          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J36" t="b">
@@ -3659,23 +3655,23 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 8:59 AM UTC</t>
+          <t>Mar 24, 2026 · 9:00 AM UTC</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-03-24T08:59:00Z</t>
+          <t>2026-03-24T09:00:00Z</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>['https://x.com/Salma2232019', 'https://x.com/Emy191990', 'https://x.com/SelmaRomola']</t>
+          <t>['https://x.com/semeet', 'https://x.com/Emy191990', 'https://x.com/ibushra_03']</t>
         </is>
       </c>
       <c r="R36" t="n">
@@ -3688,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -3699,12 +3695,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2036367170549195036</t>
+          <t>2036367351269171519</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036367170549195036</t>
+          <t>https://x.com/Sosomostafa729S/status/2036367351269171519</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3730,12 +3726,12 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @parulghalout @ibushra_03 @semeet</t>
+          <t>Exchanger volunteer program @Salma2232019 @Emy191990 @SelmaRomola</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt;</t>
+          <t>Exchanger volunteer program &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J37" t="b">
@@ -3749,7 +3745,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3765,7 +3761,7 @@
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>['https://x.com/parulghalout', 'https://x.com/ibushra_03', 'https://x.com/semeet']</t>
+          <t>['https://x.com/Salma2232019', 'https://x.com/Emy191990', 'https://x.com/SelmaRomola']</t>
         </is>
       </c>
       <c r="R37" t="n">
@@ -3778,7 +3774,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -3789,12 +3785,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2036366933784928624</t>
+          <t>2036367170549195036</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036366933784928624</t>
+          <t>https://x.com/Sosomostafa729S/status/2036367170549195036</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3820,12 +3816,12 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD @semeet @Emy191990 @Salma2232019</t>
+          <t>Exchanger volunteer program @parulghalout @ibushra_03 @semeet</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+          <t>Exchanger volunteer program &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J38" t="b">
@@ -3839,23 +3835,23 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 8:58 AM UTC</t>
+          <t>Mar 24, 2026 · 8:59 AM UTC</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-03-24T08:58:00Z</t>
+          <t>2026-03-24T08:59:00Z</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/Emy191990', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/parulghalout', 'https://x.com/ibushra_03', 'https://x.com/semeet']</t>
         </is>
       </c>
       <c r="R38" t="n">
@@ -3868,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -3879,12 +3875,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2036366860195909907</t>
+          <t>2036366933784928624</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036366860195909907</t>
+          <t>https://x.com/Sosomostafa729S/status/2036366933784928624</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3910,12 +3906,12 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD @semeet @SelmaRomola @parulghalout</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD @semeet @Emy191990 @Salma2232019</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J39" t="b">
@@ -3929,23 +3925,23 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 8:57 AM UTC</t>
+          <t>Mar 24, 2026 · 8:58 AM UTC</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-03-24T08:57:00Z</t>
+          <t>2026-03-24T08:58:00Z</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/parulghalout']</t>
+          <t>['https://x.com/semeet', 'https://x.com/Emy191990', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
       <c r="R39" t="n">
@@ -3958,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -3969,12 +3965,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2036366755782914242</t>
+          <t>2036366860195909907</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036366755782914242</t>
+          <t>https://x.com/Sosomostafa729S/status/2036366860195909907</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4000,12 +3996,12 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD @Emy191990 @ibushra_03 @parulghalout</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD @semeet @SelmaRomola @parulghalout</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J40" t="b">
@@ -4019,7 +4015,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4035,7 +4031,7 @@
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
+          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/parulghalout']</t>
         </is>
       </c>
       <c r="R40" t="n">
@@ -4048,7 +4044,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -4059,12 +4055,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2036366520943816783</t>
+          <t>2036366755782914242</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036366520943816783</t>
+          <t>https://x.com/Sosomostafa729S/status/2036366755782914242</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4090,12 +4086,12 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @Emy191990 @parulghalout @ibushra_03</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD @Emy191990 @ibushra_03 @parulghalout</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J41" t="b">
@@ -4109,23 +4105,23 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 8:56 AM UTC</t>
+          <t>Mar 24, 2026 · 8:57 AM UTC</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-03-24T08:56:00Z</t>
+          <t>2026-03-24T08:57:00Z</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/ibushra_03']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
         </is>
       </c>
       <c r="R41" t="n">
@@ -4138,7 +4134,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -4149,12 +4145,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2036366461179212172</t>
+          <t>2036366520943816783</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036366461179212172</t>
+          <t>https://x.com/Sosomostafa729S/status/2036366520943816783</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4180,12 +4176,12 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @semeet @SelmaRomola @Salma2232019</t>
+          <t>Via the ENBD X Mobile App. @Emy191990 @parulghalout @ibushra_03</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J42" t="b">
@@ -4199,7 +4195,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4215,7 +4211,7 @@
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/ibushra_03']</t>
         </is>
       </c>
       <c r="R42" t="n">
@@ -4228,7 +4224,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -4239,12 +4235,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2036366352638996520</t>
+          <t>2036366461179212172</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036366352638996520</t>
+          <t>https://x.com/Sosomostafa729S/status/2036366461179212172</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4270,12 +4266,12 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @Emy191990 @parulghalout @Salma2232019</t>
+          <t>Via the ENBD X Mobile App. @semeet @SelmaRomola @Salma2232019</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+          <t>Via the ENBD X Mobile App. &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J43" t="b">
@@ -4289,23 +4285,23 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 8:55 AM UTC</t>
+          <t>Mar 24, 2026 · 8:56 AM UTC</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-03-24T08:55:00Z</t>
+          <t>2026-03-24T08:56:00Z</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
       <c r="R43" t="n">
@@ -4318,7 +4314,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -4329,12 +4325,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2036366238046363821</t>
+          <t>2036366352638996520</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036366238046363821</t>
+          <t>https://x.com/Sosomostafa729S/status/2036366352638996520</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4360,12 +4356,12 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @Emy191990 @parulghalout @SelmaRomola</t>
+          <t>Via the ENBD X Mobile App. @Emy191990 @parulghalout @Salma2232019</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
+          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J44" t="b">
@@ -4379,7 +4375,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4395,7 +4391,7 @@
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/SelmaRomola']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
       <c r="R44" t="n">
@@ -4408,7 +4404,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -4419,12 +4415,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2036366176520118773</t>
+          <t>2036366238046363821</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036366176520118773</t>
+          <t>https://x.com/Sosomostafa729S/status/2036366238046363821</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4450,12 +4446,12 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @semeet @ibushra_03 @SelmaRomola</t>
+          <t>Via the ENBD X Mobile App. @Emy191990 @parulghalout @SelmaRomola</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
+          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J45" t="b">
@@ -4469,7 +4465,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4485,7 +4481,7 @@
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/ibushra_03', 'https://x.com/SelmaRomola']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/SelmaRomola']</t>
         </is>
       </c>
       <c r="R45" t="n">
@@ -4509,12 +4505,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2036366036120076489</t>
+          <t>2036366176520118773</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036366036120076489</t>
+          <t>https://x.com/Sosomostafa729S/status/2036366176520118773</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4540,12 +4536,12 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @Emy191990 @semeet @parulghalout</t>
+          <t>Via the ENBD X Mobile App. @semeet @ibushra_03 @SelmaRomola</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
+          <t>Via the ENBD X Mobile App. &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J46" t="b">
@@ -4559,23 +4555,23 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 8:54 AM UTC</t>
+          <t>Mar 24, 2026 · 8:55 AM UTC</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-03-24T08:54:00Z</t>
+          <t>2026-03-24T08:55:00Z</t>
         </is>
       </c>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/semeet', 'https://x.com/parulghalout']</t>
+          <t>['https://x.com/semeet', 'https://x.com/ibushra_03', 'https://x.com/SelmaRomola']</t>
         </is>
       </c>
       <c r="R46" t="n">
@@ -4588,7 +4584,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -4599,43 +4595,43 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2036364005779124312</t>
+          <t>2036366036120076489</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://x.com/FarazKhan11228/status/2036364005779124312</t>
+          <t>https://x.com/Sosomostafa729S/status/2036366036120076489</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://x.com/FarazKhan11228</t>
+          <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>FarazKhan11228</t>
+          <t>Sosomostafa729S</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Faraz Khan</t>
+          <t>Soha.mostafa77</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1758877091154583552/adAHM2jR_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>I am asking for the winners list, which is not being published</t>
+          <t>Via the ENBD X Mobile App. @Emy191990 @semeet @parulghalout</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>I am asking for the winners list, which is not being published</t>
+          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J47" t="b">
@@ -4649,23 +4645,27 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 8:46 AM UTC</t>
+          <t>Mar 24, 2026 · 8:54 AM UTC</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-03-24T08:46:00Z</t>
+          <t>2026-03-24T08:54:00Z</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/semeet', 'https://x.com/parulghalout']</t>
+        </is>
+      </c>
       <c r="R47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -4674,7 +4674,7 @@
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -4685,165 +4685,165 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2036353860705395115</t>
+          <t>2036364005779124312</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036353860705395115</t>
+          <t>https://x.com/FarazKhan11228/status/2036364005779124312</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/FarazKhan11228</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>FarazKhan11228</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Faraz Khan</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1758877091154583552/adAHM2jR_bigger.png</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
+          <t>I am asking for the winners list, which is not being published</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>I am asking for the winners list, which is not being published</t>
+        </is>
+      </c>
+      <c r="J48" t="b">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 8:46 AM UTC</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>2026-03-24T08:46:00Z</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>20</v>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2036353860705395115</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2036353860705395115</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
           <t>Hi, please click the link below to know more about the winners.
 ms.spr.ly/6014Qs768</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>Hi, please click the link below to know more about the winners.
 &lt;a href="http://ms.spr.ly/6014Qs768"&gt;ms.spr.ly/6014Qs768&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J48" t="b">
-        <v>0</v>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>['FarazKhan11228']</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Mar 24, 2026 · 8:06 AM UTC</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>2026-03-24T08:06:00Z</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>['http://ms.spr.ly/6014Qs768']</t>
-        </is>
-      </c>
-      <c r="R48" t="n">
-        <v>1</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>27</v>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2036345221831905561</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>https://x.com/msafrh79/status/2036345221831905561</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>https://x.com/msafrh79</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>msafrh79</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>mervet foad</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2027681283045003266/D4AYhe6v_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>مرحبا اين يتم اعلان الفائزين في مسابقة مواقع التواصل الاجتماعي؟؟ راسلتكم كثيرا على الخاص ومافي اي رد</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>مرحبا اين يتم اعلان الفائزين في مسابقة مواقع التواصل الاجتماعي؟؟ راسلتكم كثيرا على الخاص ومافي اي رد</t>
-        </is>
-      </c>
       <c r="J49" t="b">
         <v>0</v>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['FarazKhan11228']</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 7:31 AM UTC</t>
+          <t>Mar 24, 2026 · 8:06 AM UTC</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-03-24T07:31:00Z</t>
+          <t>2026-03-24T08:06:00Z</t>
         </is>
       </c>
       <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>['http://ms.spr.ly/6014Qs768']</t>
+        </is>
+      </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -4852,7 +4852,7 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -4863,43 +4863,43 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2036339891978793210</t>
+          <t>2036345221831905561</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://x.com/FarazKhan11228/status/2036339891978793210</t>
+          <t>https://x.com/msafrh79/status/2036345221831905561</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://x.com/FarazKhan11228</t>
+          <t>https://x.com/msafrh79</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>FarazKhan11228</t>
+          <t>msafrh79</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Faraz Khan</t>
+          <t>mervet foad</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1758877091154583552/adAHM2jR_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/2027681283045003266/D4AYhe6v_bigger.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>What about millionaire account winners, i dont get any updates on that!!!</t>
+          <t>مرحبا اين يتم اعلان الفائزين في مسابقة مواقع التواصل الاجتماعي؟؟ راسلتكم كثيرا على الخاص ومافي اي رد</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>What about millionaire account winners, i dont get any updates on that!!!</t>
+          <t>مرحبا اين يتم اعلان الفائزين في مسابقة مواقع التواصل الاجتماعي؟؟ راسلتكم كثيرا على الخاص ومافي اي رد</t>
         </is>
       </c>
       <c r="J50" t="b">
@@ -4913,23 +4913,23 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 7:10 AM UTC</t>
+          <t>Mar 24, 2026 · 7:31 AM UTC</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-03-24T07:10:00Z</t>
+          <t>2026-03-24T07:31:00Z</t>
         </is>
       </c>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -4938,7 +4938,7 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -4949,36 +4949,122 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2036328892919685283</t>
+          <t>2036339891978793210</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036328892919685283</t>
+          <t>https://x.com/FarazKhan11228/status/2036339891978793210</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/FarazKhan11228</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>FarazKhan11228</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Faraz Khan</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1758877091154583552/adAHM2jR_bigger.png</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
+        <is>
+          <t>What about millionaire account winners, i dont get any updates on that!!!</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>What about millionaire account winners, i dont get any updates on that!!!</t>
+        </is>
+      </c>
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 7:10 AM UTC</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>2026-03-24T07:10:00Z</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>31</v>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2036328892919685283</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2036328892919685283</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
         <is>
           <t>شهر جديد مع المزيد من الفائزين.
 تهانينا للفائز بالجائزة الكبرى وهي سيارة ROX 01، وللفائزين أيضًا بجائزة القطعة الذهبية بوزن 10 غرامات وذلك لاشتراكهم في حملة "حان وقت ربح جوائز كبرى" المقدمة من الخدمات المصرفية للأعمال لشهر يناير 2026.
@@ -4986,7 +5072,7 @@
 يسري العرض حتى 31 مارس 2026.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>شهر جديد مع المزيد من الفائزين.
 تهانينا للفائز بالجائزة الكبرى وهي سيارة ROX 01، وللفائزين أيضًا بجائزة القطعة الذهبية بوزن 10 غرامات وذلك لاشتراكهم في حملة &amp;#34;حان وقت ربح جوائز كبرى&amp;#34; المقدمة من الخدمات المصرفية للأعمال لشهر يناير 2026.
@@ -4994,79 +5080,79 @@
 يسري العرض حتى 31 مارس 2026.</t>
         </is>
       </c>
-      <c r="J51" t="b">
-        <v>0</v>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
         <is>
           <t>Mar 24, 2026 · 6:26 AM UTC</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>2026-03-24T06:26:00Z</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="n">
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="n">
         <v>2</v>
       </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
         <v>8</v>
       </c>
-      <c r="U51" t="n">
-        <v>871</v>
-      </c>
-      <c r="V51" t="inlineStr">
+      <c r="U52" t="n">
+        <v>890</v>
+      </c>
+      <c r="V52" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>2036328801429336479</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2036328801429336479</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr">
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
         <is>
           <t>Another month. More winners.
 Congratulations to the ROX 01 grand prize winner and 10-gram gold winners from our Business Banking ‘Time to Win Big’ January 2026 draw.
@@ -5074,7 +5160,7 @@
 Offer is valid until 31 March 2026.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>Another month. More winners.
 Congratulations to the ROX 01 grand prize winner and 10-gram gold winners from our Business Banking ‘Time to Win Big’ January 2026 draw.
@@ -5082,88 +5168,6 @@
 Offer is valid until 31 March 2026.</t>
         </is>
       </c>
-      <c r="J52" t="b">
-        <v>0</v>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>Mar 24, 2026 · 6:26 AM UTC</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>2026-03-24T06:26:00Z</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="n">
-        <v>2</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>8</v>
-      </c>
-      <c r="U52" t="n">
-        <v>679</v>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2036322118611169669</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036322118611169669</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Emirates NBD</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>We are together against Fraud. @UAEBF #FightFraud #UAEBF #togetheragainstfraud #UnitedAgainstFraud</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>We are together against Fraud. &lt;a href="/UAEBF" title="UAE Banks Federation"&gt;@UAEBF&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FightFraud"&gt;#FightFraud&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAEBF"&gt;#UAEBF&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23togetheragainstfraud"&gt;#togetheragainstfraud&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;</t>
-        </is>
-      </c>
       <c r="J53" t="b">
         <v>0</v>
       </c>
@@ -5176,31 +5180,27 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 6:00 AM UTC</t>
+          <t>Mar 24, 2026 · 6:26 AM UTC</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-03-24T06:00:00Z</t>
+          <t>2026-03-24T06:26:00Z</t>
         </is>
       </c>
       <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>['https://x.com/UAEBF', 'https://x.com/search?f=tweets&amp;q=%23FightFraud', 'https://x.com/search?f=tweets&amp;q=%23UAEBF', 'https://x.com/search?f=tweets&amp;q=%23togetheragainstfraud', 'https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud']</t>
-        </is>
-      </c>
+      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U53" t="n">
-        <v>583</v>
+        <v>701</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -5211,12 +5211,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2036300027933433945</t>
+          <t>2036322118611169669</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036300027933433945</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036322118611169669</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5242,109 +5242,109 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
+          <t>We are together against Fraud. @UAEBF #FightFraud #UAEBF #togetheragainstfraud #UnitedAgainstFraud</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>We are together against Fraud. &lt;a href="/UAEBF" title="UAE Banks Federation"&gt;@UAEBF&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FightFraud"&gt;#FightFraud&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAEBF"&gt;#UAEBF&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23togetheragainstfraud"&gt;#togetheragainstfraud&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J54" t="b">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 6:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2026-03-24T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>['https://x.com/UAEBF', 'https://x.com/search?f=tweets&amp;q=%23FightFraud', 'https://x.com/search?f=tweets&amp;q=%23UAEBF', 'https://x.com/search?f=tweets&amp;q=%23togetheragainstfraud', 'https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud']</t>
+        </is>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>5</v>
+      </c>
+      <c r="U54" t="n">
+        <v>591</v>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2036300027933433945</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2036300027933433945</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
           <t>مرحباً بك, شكراً لتواصلك معنا, يرجى العلم اننا غير قادرين على التواصل معك على الرسائل, يمكنك الاتصال بنا على 600540000 
 أو عن طريق التحدث معنا من خلال الواتساب البنكي على 600540000 من الساعة 9 صباحا الى 7 مساء</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>مرحباً بك, شكراً لتواصلك معنا, يرجى العلم اننا غير قادرين على التواصل معك على الرسائل, يمكنك الاتصال بنا على 600540000 
 أو عن طريق التحدث معنا من خلال الواتساب البنكي على 600540000 من الساعة 9 صباحا الى 7 مساء</t>
         </is>
       </c>
-      <c r="J54" t="b">
-        <v>0</v>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>['AlyahiaMoh']</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>Mar 24, 2026 · 4:32 AM UTC</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>2026-03-24T04:32:00Z</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>24</v>
-      </c>
-      <c r="V54" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2036269961057018273</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>https://x.com/saimas89/status/2036269961057018273</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>https://x.com/saimas89</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>saimas89</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Saima | صائمہ</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1613505962098282497/lNPa9Or8_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Can you not take another 7 days and give me the refund sooner? FYI I have paid using my ENBD card.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>Can you not take another 7 days and give me the refund sooner? FYI I have paid using my ENBD card.</t>
-        </is>
-      </c>
       <c r="J55" t="b">
         <v>0</v>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['flyspicejet']</t>
+          <t>['AlyahiaMoh']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5354,18 +5354,18 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 2:32 AM UTC</t>
+          <t>Mar 24, 2026 · 4:32 AM UTC</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-03-24T02:32:00Z</t>
+          <t>2026-03-24T04:32:00Z</t>
         </is>
       </c>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -5374,7 +5374,7 @@
         <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -5385,43 +5385,43 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2036410734163247450</t>
+          <t>2036269961057018273</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036410734163247450</t>
+          <t>https://x.com/saimas89/status/2036269961057018273</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/saimas89</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>saimas89</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Saima | صائمہ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1613505962098282497/lNPa9Or8_bigger.jpg</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+          <t>Can you not take another 7 days and give me the refund sooner? FYI I have paid using my ENBD card.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+          <t>Can you not take another 7 days and give me the refund sooner? FYI I have paid using my ENBD card.</t>
         </is>
       </c>
       <c r="J56" t="b">
@@ -5430,28 +5430,28 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['Abdulla40446316']</t>
+          <t>['flyspicejet']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>Mar 24</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 11:52 AM UTC</t>
+          <t>Mar 24, 2026 · 2:32 AM UTC</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-03-24T11:52:00Z</t>
+          <t>2026-03-24T02:32:00Z</t>
         </is>
       </c>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -5460,23 +5460,23 @@
         <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2036399322183442876</t>
+          <t>2036410734163247450</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036399322183442876</t>
+          <t>https://x.com/emiratesislamic/status/2036410734163247450</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5502,12 +5502,12 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
         </is>
       </c>
       <c r="J57" t="b">
@@ -5516,22 +5516,22 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>['acroboatic']</t>
+          <t>['Abdulla40446316']</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 11:06 AM UTC</t>
+          <t>Mar 24, 2026 · 11:52 AM UTC</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-03-24T11:06:00Z</t>
+          <t>2026-03-24T11:52:00Z</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
@@ -5546,7 +5546,7 @@
         <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -5557,12 +5557,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2036399290717704546</t>
+          <t>2036399322183442876</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036399290717704546</t>
+          <t>https://x.com/emiratesislamic/status/2036399322183442876</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -5632,7 +5632,7 @@
         <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -5643,12 +5643,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2036385610118623239</t>
+          <t>2036399290717704546</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036385610118623239</t>
+          <t>https://x.com/emiratesislamic/status/2036399290717704546</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5673,6 +5673,92 @@
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J59" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>['acroboatic']</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 11:06 AM UTC</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>2026-03-24T11:06:00Z</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>14</v>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2036385610118623239</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036385610118623239</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
         <is>
           <t>💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships
 📅Offer valid till 31 March 2026.
@@ -5680,7 +5766,7 @@
 emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships
 📅Offer valid till 31 March 2026.
@@ -5688,169 +5774,169 @@
 &lt;a href="https://www.emiratesislamic.ae/en/offers/auto-finance-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=af"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J59" t="b">
-        <v>0</v>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
+      <c r="J60" t="b">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
         <is>
           <t>Mar 24, 2026 · 10:12 AM UTC</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>2026-03-24T10:12:00Z</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr">
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
         <is>
           <t>['https://www.emiratesislamic.ae/en/offers/auto-finance-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=af']</t>
         </is>
       </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>50</v>
-      </c>
-      <c r="V59" t="inlineStr">
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>55</v>
+      </c>
+      <c r="V60" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>2036385607883034826</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2036385607883034826</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr">
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
         <is>
           <t>Drive home your dream car with Emirates Islamic Auto Finance!
 📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)
 📅Payment holiday of up to 6 months</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>Drive home your dream car with Emirates Islamic Auto Finance!
 📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)
 📅Payment holiday of up to 6 months</t>
         </is>
       </c>
-      <c r="J60" t="b">
-        <v>0</v>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
+      <c r="J61" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
         <is>
           <t>Mar 24, 2026 · 10:12 AM UTC</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>2026-03-24T10:12:00Z</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="n">
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="n">
         <v>1</v>
       </c>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" t="n">
-        <v>79</v>
-      </c>
-      <c r="V60" t="inlineStr">
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>88</v>
+      </c>
+      <c r="V61" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>2036382130784047605</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2036382130784047605</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr">
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
         <is>
           <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
 📅يسري لغاية 31 مارس 2026.
@@ -5858,7 +5944,7 @@
 emiratesislamic.ae/ar/offers…</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
 📅يسري لغاية 31 مارس 2026.
@@ -5866,202 +5952,114 @@
 &lt;a href="https://www.emiratesislamic.ae/ar/offers/auto-finance-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=af"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J61" t="b">
-        <v>0</v>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
         <is>
           <t>Mar 24, 2026 · 9:58 AM UTC</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>2026-03-24T09:58:00Z</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr">
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
         <is>
           <t>['https://www.emiratesislamic.ae/ar/offers/auto-finance-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=af']</t>
         </is>
       </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>51</v>
-      </c>
-      <c r="V61" t="inlineStr">
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>56</v>
+      </c>
+      <c r="V62" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>2036382128359751773</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2036382128359751773</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr">
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
         <is>
           <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
 📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً)
 📅فترة سماح السداد تصل إلى 6 أشهر</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
 📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً)
 📅فترة سماح السداد تصل إلى 6 أشهر</t>
         </is>
       </c>
-      <c r="J62" t="b">
-        <v>0</v>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
+      <c r="J63" t="b">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
         <is>
           <t>Mar 24, 2026 · 9:58 AM UTC</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>2026-03-24T09:58:00Z</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="n">
-        <v>1</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="n">
-        <v>67</v>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2036353357435248836</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>https://x.com/acroboatic/status/2036353357435248836</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>https://x.com/acroboatic</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>acroboatic</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>saudaaaas</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/536089004978884608/PVIgXDs5_bigger.jpeg</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Thanks
-I have followed your page now</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Thanks
-I have followed your page now</t>
-        </is>
-      </c>
-      <c r="J63" t="b">
-        <v>0</v>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>Mar 24, 2026 · 8:04 AM UTC</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>2026-03-24T08:04:00Z</t>
         </is>
       </c>
       <c r="P63" t="inlineStr"/>
@@ -6076,7 +6074,7 @@
         <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -6087,12 +6085,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2036352538568802661</t>
+          <t>2036353357435248836</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://x.com/acroboatic/status/2036352538568802661</t>
+          <t>https://x.com/acroboatic/status/2036353357435248836</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -6118,16 +6116,14 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Hi, happy to connect.
-I didn’t receive your DM, and my replies don’t seem to be going through either. Not sure if there’s a technical issue.
-I’m available now, please feel free to message</t>
+          <t>Thanks
+I have followed your page now</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Hi, happy to connect.
-I didn’t receive your DM, and my replies don’t seem to be going through either. Not sure if there’s a technical issue.
-I’m available now, please feel free to message</t>
+          <t>Thanks
+I have followed your page now</t>
         </is>
       </c>
       <c r="J64" t="b">
@@ -6141,17 +6137,17 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 8:00 AM UTC</t>
+          <t>Mar 24, 2026 · 8:04 AM UTC</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>2026-03-24T08:00:00Z</t>
+          <t>2026-03-24T08:04:00Z</t>
         </is>
       </c>
       <c r="P64" t="inlineStr"/>
@@ -6166,7 +6162,7 @@
         <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -6177,43 +6173,47 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2036331891541127358</t>
+          <t>2036352538568802661</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://x.com/Ben252024/status/2036331891541127358</t>
+          <t>https://x.com/acroboatic/status/2036352538568802661</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://x.com/Ben252024</t>
+          <t>https://x.com/acroboatic</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Ben252024</t>
+          <t>acroboatic</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>saudaaaas</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/536089004978884608/PVIgXDs5_bigger.jpeg</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>When ?</t>
+          <t>Hi, happy to connect.
+I didn’t receive your DM, and my replies don’t seem to be going through either. Not sure if there’s a technical issue.
+I’m available now, please feel free to message</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>When ?</t>
+          <t>Hi, happy to connect.
+I didn’t receive your DM, and my replies don’t seem to be going through either. Not sure if there’s a technical issue.
+I’m available now, please feel free to message</t>
         </is>
       </c>
       <c r="J65" t="b">
@@ -6232,18 +6232,18 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 6:38 AM UTC</t>
+          <t>Mar 24, 2026 · 8:00 AM UTC</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-03-24T06:38:00Z</t>
+          <t>2026-03-24T08:00:00Z</t>
         </is>
       </c>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -6252,7 +6252,7 @@
         <v>0</v>
       </c>
       <c r="U65" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
@@ -6263,43 +6263,43 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2036319304132473271</t>
+          <t>2036331891541127358</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036319304132473271</t>
+          <t>https://x.com/Ben252024/status/2036331891541127358</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/Ben252024</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Ben252024</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>When ?</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>When ?</t>
         </is>
       </c>
       <c r="J66" t="b">
@@ -6308,7 +6308,7 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>['wasishion']</t>
+          <t>['emiratesislamic']</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6318,12 +6318,12 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 5:48 AM UTC</t>
+          <t>Mar 24, 2026 · 6:38 AM UTC</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2026-03-24T05:48:00Z</t>
+          <t>2026-03-24T06:38:00Z</t>
         </is>
       </c>
       <c r="P66" t="inlineStr"/>
@@ -6338,7 +6338,7 @@
         <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
@@ -6349,12 +6349,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2036313897985020336</t>
+          <t>2036319304132473271</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036313897985020336</t>
+          <t>https://x.com/emiratesislamic/status/2036319304132473271</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -6380,12 +6380,12 @@
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message rule (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message rule (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
         </is>
       </c>
       <c r="J67" t="b">
@@ -6394,28 +6394,28 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>['acroboatic']</t>
+          <t>['wasishion']</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 5:27 AM UTC</t>
+          <t>Mar 24, 2026 · 5:48 AM UTC</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-03-24T05:27:00Z</t>
+          <t>2026-03-24T05:48:00Z</t>
         </is>
       </c>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="U67" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
@@ -6435,12 +6435,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2036313593797288395</t>
+          <t>2036313897985020336</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036313593797288395</t>
+          <t>https://x.com/emiratesislamic/status/2036313897985020336</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -6466,12 +6466,12 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message rule (Not Following our page). Please DM us back in order to assist you better.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message rule (Not Following our page). Please DM us back in order to assist you better.</t>
         </is>
       </c>
       <c r="J68" t="b">
@@ -6485,23 +6485,23 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 5:26 AM UTC</t>
+          <t>Mar 24, 2026 · 5:27 AM UTC</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-03-24T05:26:00Z</t>
+          <t>2026-03-24T05:27:00Z</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -6510,7 +6510,7 @@
         <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
@@ -6521,12 +6521,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2036313549929107798</t>
+          <t>2036313593797288395</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036313549929107798</t>
+          <t>https://x.com/emiratesislamic/status/2036313593797288395</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -6571,34 +6571,120 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 5:25 AM UTC</t>
+          <t>Mar 24, 2026 · 5:26 AM UTC</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-03-24T05:25:00Z</t>
+          <t>2026-03-24T05:26:00Z</t>
         </is>
       </c>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>16</v>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2036313549929107798</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036313549929107798</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="J70" t="b">
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>['acroboatic']</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Mar 24, 2026 · 5:25 AM UTC</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>2026-03-24T05:25:00Z</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="n">
         <v>1</v>
       </c>
-      <c r="S69" t="n">
-        <v>0</v>
-      </c>
-      <c r="T69" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" t="n">
-        <v>19</v>
-      </c>
-      <c r="V69" t="inlineStr">
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>22</v>
+      </c>
+      <c r="V70" t="inlineStr">
         <is>
           <t>EI</t>
         </is>

--- a/EI_ENBD_3post.xlsx
+++ b/EI_ENBD_3post.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V70"/>
+  <dimension ref="A1:V81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,67 +543,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2036665227840803080</t>
+          <t>2037012056881180890</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036665227840803080</t>
+          <t>https://x.com/kamal_Zamalek/status/2037012056881180890</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/kamal_Zamalek</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>kamal_Zamalek</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>محمد_صبري</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1989277397472972800/0TJHAbxy_bigger.jpg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Thanks for writing to us, kindly note that we have replied to your email</t>
+          <t>غريبه ان بنك زي ده بيرعي فريق محدش بيتفرج عاليه وف نفس الوقت مفيش اي بنك مسموح ليه يرعي الزمالك ولا الاسماعيلي ولا اي فريق جماهيري 
+والكلام عن شركه WE اللي كانت هترعي الاسماعيلي وبعدين الموضوع اتلغي نادي الإسماعيلي بيشحت وهينزل درجه تانيه</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Thanks for writing to us, kindly note that we have replied to your email</t>
+          <t>غريبه ان بنك زي ده بيرعي فريق محدش بيتفرج عاليه وف نفس الوقت مفيش اي بنك مسموح ليه يرعي الزمالك ولا الاسماعيلي ولا اي فريق جماهيري 
+والكلام عن شركه WE اللي كانت هترعي الاسماعيلي وبعدين الموضوع اتلغي نادي الإسماعيلي بيشحت وهينزل درجه تانيه</t>
         </is>
       </c>
       <c r="J2" t="b">
         <v>0</v>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>['ZahidanMuhamma']</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>37m</t>
+          <t>21m</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 4:43 AM UTC</t>
+          <t>Mar 26, 2026 · 3:41 AM UTC</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-03-25T04:43:00Z</t>
+          <t>2026-03-26T03:41:00Z</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -618,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -629,45 +627,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2036654307596992707</t>
+          <t>2036918641149829234</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036654307596992707</t>
+          <t>https://x.com/MultibaggAI/status/2036918641149829234</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/MultibaggAI</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>MultibaggAI</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>multibagg.ai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2017665342756294656/o62zwaRv_bigger.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Your financial tip of the week
-#FinancialWellbeing #EmiratesNBDTips #SmartMoney #FinWell</t>
+          <t>RBLBANK: EMIRATES NBD INFORMED RBL BANK THAT UAE CENTRAL BANK HAS APPROVED ITS PROPOSED ACQUISITION OF A MAJORITY STAKE IN RBL AND AMALGAMATION OF EMIRATES NBD'S INDIA OPERATIONS INTO RBL, SUBJECT TO REQUISITE APPROVALS.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Your financial tip of the week
-&lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBDTips"&gt;#EmiratesNBDTips&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoney"&gt;#SmartMoney&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinWell"&gt;#FinWell&lt;/a&gt;</t>
+          <t>RBLBANK: EMIRATES NBD INFORMED RBL BANK THAT UAE CENTRAL BANK HAS APPROVED ITS PROPOSED ACQUISITION OF A MAJORITY STAKE IN RBL AND AMALGAMATION OF EMIRATES NBD&amp;#39;S INDIA OPERATIONS INTO RBL, SUBJECT TO REQUISITE APPROVALS.</t>
         </is>
       </c>
       <c r="J3" t="b">
@@ -677,25 +673,21 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>6h</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 4:00 AM UTC</t>
+          <t>Mar 25, 2026 · 9:30 PM UTC</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-03-25T04:00:00Z</t>
+          <t>2026-03-25T21:30:00Z</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBDTips', 'https://x.com/search?f=tweets&amp;q=%23SmartMoney', 'https://x.com/search?f=tweets&amp;q=%23FinWell']</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -706,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>227</v>
+        <v>41</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -717,45 +709,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2036654307383111761</t>
+          <t>2036913676490281251</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036654307383111761</t>
+          <t>https://x.com/TradeInZoneIN/status/2036913676490281251</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/TradeInZoneIN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>TradeInZoneIN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Trade in Zone</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1907808051697950720/gAd-nJZ__bigger.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>نصيحتك المالية لهذا الأسبوع
-#FinancialWellbeing #EmiratesNBDTips #FinWell #SmartMoney</t>
+          <t>Major banking move: Emirates NBD has received UAE Central Bank approval to acquire a majority stake in RBL Bank. The deal involves merging Indian operations and a significant share issue. A huge shift for private sector banking in India. 📈🚀</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>نصيحتك المالية لهذا الأسبوع
-&lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBDTips"&gt;#EmiratesNBDTips&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinWell"&gt;#FinWell&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoney"&gt;#SmartMoney&lt;/a&gt;</t>
+          <t>Major banking move: Emirates NBD has received UAE Central Bank approval to acquire a majority stake in RBL Bank. The deal involves merging Indian operations and a significant share issue. A huge shift for private sector banking in India. 📈🚀</t>
         </is>
       </c>
       <c r="J4" t="b">
@@ -765,25 +755,21 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>6h</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 4:00 AM UTC</t>
+          <t>Mar 25, 2026 · 9:10 PM UTC</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-03-25T04:00:00Z</t>
+          <t>2026-03-25T21:10:00Z</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBDTips', 'https://x.com/search?f=tweets&amp;q=%23FinWell', 'https://x.com/search?f=tweets&amp;q=%23SmartMoney']</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -794,7 +780,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>210</v>
+        <v>12</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -805,43 +791,45 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2036586113079328797</t>
+          <t>2036907649933951454</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://x.com/semeet/status/2036586113079328797</t>
+          <t>https://x.com/theshivrao/status/2036907649933951454</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/semeet</t>
+          <t>https://x.com/theshivrao</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>semeet</t>
+          <t>theshivrao</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>seema shelat</t>
+          <t>Shiv Rao</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1376978771538898945/X-iaSTLK_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1537059258826895362/aTalVMrH_bigger.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Congratulations 🎊</t>
+          <t>@grok what’s the investment amount. How much is going to be the post money valuation of RBL, and who exactly is exiting.
+What’s the profile of this Emirates NBD?</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Congratulations 🎊</t>
+          <t>&lt;a href="/grok" title="Grok"&gt;@grok&lt;/a&gt; what’s the investment amount. How much is going to be the post money valuation of RBL, and who exactly is exiting.
+What’s the profile of this Emirates NBD?</t>
         </is>
       </c>
       <c r="J5" t="b">
@@ -850,28 +838,32 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['moneycontrolcom']</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>5h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 11:29 PM UTC</t>
+          <t>Mar 25, 2026 · 8:46 PM UTC</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-03-24T23:29:00Z</t>
+          <t>2026-03-25T20:46:00Z</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>['https://x.com/grok']</t>
+        </is>
+      </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -880,7 +872,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -891,47 +883,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2036561511594991637</t>
+          <t>2036906970095964494</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://x.com/Ridvan_Dayanc/status/2036561511594991637</t>
+          <t>https://x.com/saif_aldareei/status/2036906970095964494</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/Ridvan_Dayanc</t>
+          <t>https://x.com/saif_aldareei</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ridvan_Dayanc</t>
+          <t>saif_aldareei</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rıdvan Dayanç</t>
+          <t>سيف الدرعي| Saif alderei</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/891319667645702144/MaGwpQS6_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1597913616363257856/PitDyJR6_bigger.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>General Information ⚠️
-All clear 🤲
-#dubai #attack #besafe</t>
+          <t>الإمارات : الأصول تتخطى 5.4 تريليون درهم خلال يناير 2026، مع توسع الائتمان المدعوم بنمو الودائع المحلية وزيادة التمويل الموجه للاقتصاد.
+بنمو شهري 1.4%، وإجمالي 5.3% مقارنة بالعام الماضي.
+القطاع المصرفي الإماراتي.. يواصل التألق والريادة.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>General Information ⚠️
-All clear 🤲
-&lt;a href="/search?f=tweets&amp;amp;q=%23dubai"&gt;#dubai&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23attack"&gt;#attack&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23besafe"&gt;#besafe&lt;/a&gt;</t>
+          <t>الإمارات : الأصول تتخطى 5.4 تريليون درهم خلال يناير 2026، مع توسع الائتمان المدعوم بنمو الودائع المحلية وزيادة التمويل الموجه للاقتصاد.
+بنمو شهري 1.4%، وإجمالي 5.3% مقارنة بالعام الماضي.
+القطاع المصرفي الإماراتي.. يواصل التألق والريادة.</t>
         </is>
       </c>
       <c r="J6" t="b">
@@ -946,31 +938,27 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 9:51 PM UTC</t>
+          <t>Mar 25, 2026 · 8:44 PM UTC</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-03-24T21:51:00Z</t>
+          <t>2026-03-25T20:44:00Z</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23dubai', 'https://x.com/search?f=tweets&amp;q=%23attack', 'https://x.com/search?f=tweets&amp;q=%23besafe']</t>
-        </is>
-      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="U6" t="n">
-        <v>244</v>
+        <v>5737</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -981,43 +969,45 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2036558462906409266</t>
+          <t>2036862365786845591</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://x.com/ZahidanMuhamma/status/2036558462906409266</t>
+          <t>https://x.com/EmiratesNBD_EGY/status/2036862365786845591</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/ZahidanMuhamma</t>
+          <t>https://x.com/EmiratesNBD_EGY</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ZahidanMuhamma</t>
+          <t>EmiratesNBD_EGY</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Muhammad Zahidan</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1827047486680137728/R86Fb-lT_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>It's a joke I will wait for 90 days to receive my fund what a joke</t>
+          <t>شكرًا لاهتمامكم بمنتجنا. يُرجى الاطلاع على الرابط أدناه لمزيد من التفاصيل والنموذج المطلوب تعبئته، وسيتواصل فريقنا معكم في أقرب وقت ممكن. شكرًا - زبير
+emiratesnbd.com.eg/ar/standa…</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>It&amp;#39;s a joke I will wait for 90 days to receive my fund what a joke</t>
+          <t>شكرًا لاهتمامكم بمنتجنا. يُرجى الاطلاع على الرابط أدناه لمزيد من التفاصيل والنموذج المطلوب تعبئته، وسيتواصل فريقنا معكم في أقرب وقت ممكن. شكرًا - زبير
+&lt;a href="https://www.emiratesnbd.com.eg/ar/standard-banking/cards/debit-cards/foreign-currency-card"&gt;emiratesnbd.com.eg/ar/standa…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J7" t="b">
@@ -1026,26 +1016,30 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['SafwatTools']</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 9:39 PM UTC</t>
+          <t>Mar 25, 2026 · 5:46 PM UTC</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-03-24T21:39:00Z</t>
+          <t>2026-03-25T17:46:00Z</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesnbd.com.eg/ar/standard-banking/cards/debit-cards/foreign-currency-card']</t>
+        </is>
+      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1056,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1067,43 +1061,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2036555909082534200</t>
+          <t>2036861658321346594</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://x.com/islamchann86950/status/2036555909082534200</t>
+          <t>https://x.com/MultibaggAI/status/2036861658321346594</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/islamchann86950</t>
+          <t>https://x.com/MultibaggAI</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>islamchann86950</t>
+          <t>MultibaggAI</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>islam channel</t>
+          <t>multibagg.ai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2024383226257588224/NOAuj7I0_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2017665342756294656/o62zwaRv_bigger.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Doing good doesn't require much ..🫱🫲</t>
+          <t>EMIRATES NBD TO ACQUIRE ~60% OF RBL BANK; UAE CENTRAL BANK APPROVED ON 24 MAR 2026, LETTER RECEIVED 25 MAR 2026 || CCI CLEARED DEAL, MANDATORY OPEN OFFER UP TO 26% PLANNED.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Doing good doesn&amp;#39;t require much ..🫱🫲</t>
+          <t>EMIRATES NBD TO ACQUIRE ~60% OF RBL BANK; UAE CENTRAL BANK APPROVED ON 24 MAR 2026, LETTER RECEIVED 25 MAR 2026 || CCI CLEARED DEAL, MANDATORY OPEN OFFER UP TO 26% PLANNED.</t>
         </is>
       </c>
       <c r="J8" t="b">
@@ -1113,17 +1107,17 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 9:29 PM UTC</t>
+          <t>Mar 25, 2026 · 5:43 PM UTC</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-03-24T21:29:00Z</t>
+          <t>2026-03-25T17:43:00Z</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1135,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1149,112 +1143,86 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2036498571747532999</t>
+          <t>2036857393393680584</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://x.com/axerock2024/status/2036498571747532999</t>
+          <t>https://x.com/moneycontrolcom/status/2036857393393680584</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/axerock2024</t>
+          <t>https://x.com/moneycontrolcom</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>axerock2024</t>
+          <t>moneycontrolcom</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Axe</t>
+          <t>Moneycontrol</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/841519699632447488/ea4043nJ_bigger.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Disastrous!!! Avoid.
-@FinMinIndia
-@nsitharaman
-@CimGOI
-@PiyushGoyal
-@HMOIndia
-@RBI
-@SmalhotraRBI
-@AmitShah
-@DrSJaishankar
-@MEAIndia
-@PMOIndia
-@narendramodi 
-cnbctv18.com/business/financ…</t>
+          <t>#Business | Emirates NBD gets UAE central bank nod for majority stake in RBL Bank
+More details👇
+moneycontrol.com/news/busine…</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Disastrous!!! Avoid.
-&lt;a href="/FinMinIndia" title="Ministry of Finance"&gt;@FinMinIndia&lt;/a&gt;
-&lt;a href="/nsitharaman" title="Nirmala Sitharaman"&gt;@nsitharaman&lt;/a&gt;
-&lt;a href="/CimGOI" title="Minister of Commerce and Industry"&gt;@CimGOI&lt;/a&gt;
-&lt;a href="/PiyushGoyal" title="Piyush Goyal"&gt;@PiyushGoyal&lt;/a&gt;
-&lt;a href="/HMOIndia" title="गृहमंत्री कार्यालय, HMO India"&gt;@HMOIndia&lt;/a&gt;
-&lt;a href="/RBI" title="ReserveBankOfIndia"&gt;@RBI&lt;/a&gt;
-&lt;a href="/SmalhotraRBI" title="Sanjay Malhotra RBI 🇮🇳"&gt;@SmalhotraRBI&lt;/a&gt;
-&lt;a href="/AmitShah" title="Amit Shah"&gt;@AmitShah&lt;/a&gt;
-&lt;a href="/DrSJaishankar" title="Dr. S. Jaishankar"&gt;@DrSJaishankar&lt;/a&gt;
-&lt;a href="/MEAIndia" title="Randhir Jaiswal"&gt;@MEAIndia&lt;/a&gt;
-&lt;a href="/PMOIndia" title="PMO India"&gt;@PMOIndia&lt;/a&gt;
-&lt;a href="/narendramodi" title="Narendra Modi"&gt;@narendramodi&lt;/a&gt; 
-&lt;a href="https://www.cnbctv18.com/business/finance/emirates-nbd-says-rbl-bank-deal-on-track-despite-geopolitical-tensions-ws-l-19869449.htm"&gt;cnbctv18.com/business/financ…&lt;/a&gt;</t>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23Business"&gt;#Business&lt;/a&gt; | Emirates NBD gets UAE central bank nod for majority stake in RBL Bank
+More details👇
+&lt;a href="https://www.moneycontrol.com/news/business/banks/emirates-nbd-gets-uae-central-bank-nod-for-majority-stake-in-rbl-bank-13870833.html"&gt;moneycontrol.com/news/busine…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>['axerock2024', 'EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 5:41 PM UTC</t>
+          <t>Mar 25, 2026 · 5:27 PM UTC</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-03-24T17:41:00Z</t>
+          <t>2026-03-25T17:27:00Z</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>['https://x.com/FinMinIndia', 'https://x.com/nsitharaman', 'https://x.com/CimGOI', 'https://x.com/PiyushGoyal', 'https://x.com/HMOIndia', 'https://x.com/RBI', 'https://x.com/SmalhotraRBI', 'https://x.com/AmitShah', 'https://x.com/DrSJaishankar', 'https://x.com/MEAIndia', 'https://x.com/PMOIndia', 'https://x.com/narendramodi', 'https://www.cnbctv18.com/business/finance/emirates-nbd-says-rbl-bank-deal-on-track-despite-geopolitical-tensions-ws-l-19869449.htm']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23Business', 'https://www.moneycontrol.com/news/business/banks/emirates-nbd-gets-uae-central-bank-nod-for-majority-stake-in-rbl-bank-13870833.html']</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="U9" t="n">
-        <v>19</v>
+        <v>3111</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1265,49 +1233,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2036488212902731999</t>
+          <t>2036856277721075840</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2036488212902731999</t>
+          <t>https://x.com/CNBCTV18News/status/2036856277721075840</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY</t>
+          <t>https://x.com/CNBCTV18News</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EmiratesNBD_EGY</t>
+          <t>CNBCTV18News</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>CNBC-TV18</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1926678193345273856/OxMqCV6J_bigger.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Buy your hair essentials with 0% down payment, 0% interest, and 0% processing fees on 6 months from CH&amp;BE through their website using Emirates NBD credit cards.
-Offer is valid till 15th of April 2026.
-Terms and conditions apply.
-Tax registration number: 204-897-319</t>
+          <t>#UAECentralBank approves #EmiratesNBD's proposed stake acquisition in #RBLBank
+@jpullokaran
+buff.ly/XJ1NhVr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Buy your hair essentials with 0% down payment, 0% interest, and 0% processing fees on 6 months from CH&amp;amp;BE through their website using Emirates NBD credit cards.
-Offer is valid till 15th of April 2026.
-Terms and conditions apply.
-Tax registration number: 204-897-319</t>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23UAECentralBank"&gt;#UAECentralBank&lt;/a&gt; approves &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt;&amp;#39;s proposed stake acquisition in &lt;a href="/search?f=tweets&amp;amp;q=%23RBLBank"&gt;#RBLBank&lt;/a&gt;
+&lt;a href="/jpullokaran" title="Jomy Jos Pullokaran"&gt;@jpullokaran&lt;/a&gt;
+&lt;a href="https://buff.ly/XJ1NhVr"&gt;buff.ly/XJ1NhVr&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J10" t="b">
@@ -1317,32 +1283,36 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 5:00 PM UTC</t>
+          <t>Mar 25, 2026 · 5:22 PM UTC</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-03-24T17:00:00Z</t>
+          <t>2026-03-25T17:22:00Z</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23UAECentralBank', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23RBLBank', 'https://x.com/jpullokaran', 'https://buff.ly/XJ1NhVr']</t>
+        </is>
+      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U10" t="n">
-        <v>39</v>
+        <v>3184</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1353,49 +1323,43 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2036488212877648052</t>
+          <t>2036852664009711914</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2036488212877648052</t>
+          <t>https://x.com/MultibaggAI/status/2036852664009711914</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY</t>
+          <t>https://x.com/MultibaggAI</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EmiratesNBD_EGY</t>
+          <t>MultibaggAI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>multibagg.ai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2017665342756294656/o62zwaRv_bigger.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>استعدي لإطلالة جديدة واشتري منتاجات العناية بالشعر من CH&amp;BE ب0% مقدم، 0% فوائد، و 0% مصاريف إدارية على 6 أشهر من خلال الموقع الإلكتروني باستخدام بطاقات بنك الإمارات دبي الوطني الائتمانية.
-العرض سارى حتى 15 أبريل 2026
-تطبق الشروط والأحكام.
-رقم التسجيل الضريبي: 319-897-204</t>
+          <t>UAE CENTRAL BANK APPROVED EMIRATES NBD'S ACQUISITION OF A MAJORITY STAKE IN RBL BANK, REGULATOR'S NOD ANNOUNCED ON 25 MAR 2026 || PAVES WAY FOR CHANGE OF CONTROL AT RBL</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>استعدي لإطلالة جديدة واشتري منتاجات العناية بالشعر من CH&amp;amp;BE ب0% مقدم، 0% فوائد، و 0% مصاريف إدارية على 6 أشهر من خلال الموقع الإلكتروني باستخدام بطاقات بنك الإمارات دبي الوطني الائتمانية.
-العرض سارى حتى 15 أبريل 2026
-تطبق الشروط والأحكام.
-رقم التسجيل الضريبي: 319-897-204</t>
+          <t>UAE CENTRAL BANK APPROVED EMIRATES NBD&amp;#39;S ACQUISITION OF A MAJORITY STAKE IN RBL BANK, REGULATOR&amp;#39;S NOD ANNOUNCED ON 25 MAR 2026 || PAVES WAY FOR CHANGE OF CONTROL AT RBL</t>
         </is>
       </c>
       <c r="J11" t="b">
@@ -1405,17 +1369,17 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>10h</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 5:00 PM UTC</t>
+          <t>Mar 25, 2026 · 5:08 PM UTC</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-03-24T17:00:00Z</t>
+          <t>2026-03-25T17:08:00Z</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1427,10 +1391,10 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1441,53 +1405,45 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2036472567389716544</t>
+          <t>2036850996706762863</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036472567389716544</t>
+          <t>https://x.com/ETNOWlive/status/2036850996706762863</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/ETNOWlive</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>ETNOWlive</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>ET NOW</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1863866767027933184/hC9WqRl-_bigger.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>لحظة اعتزاز. وتجسيد للثقة.
-نفخر بحصولنا على هذا التكريم في جوائز يوروموني للخدمات المصرفية الخاصة 2026:
-• أفضل بنك للخدمات المصرفية الخاصة في الشرق الأوسط
-• أفضل بنك لخدمات المكاتب العائلية في الشرق الأوسط
-نتقدم بخالص الشكر لعملائنا على ثقتهم المستمرة وشراكتهم الدائمة. ويُعد هذا الإنجاز تأكيدًا على التزامنا الراسخ بالتميّز.
-#جوائز_يوروموني #التميز_في_الخدمات_المصرفية_الخاصة</t>
+          <t>#StockInNews | RBL Bank: UAE Central Bank approves NBD takeover of RBL majority stake
+@rblbank @centralbankuae @EmiratesNBD_AE #StockMarket</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>لحظة اعتزاز. وتجسيد للثقة.
-نفخر بحصولنا على هذا التكريم في جوائز يوروموني للخدمات المصرفية الخاصة 2026:
-• أفضل بنك للخدمات المصرفية الخاصة في الشرق الأوسط
-• أفضل بنك لخدمات المكاتب العائلية في الشرق الأوسط
-نتقدم بخالص الشكر لعملائنا على ثقتهم المستمرة وشراكتهم الدائمة. ويُعد هذا الإنجاز تأكيدًا على التزامنا الراسخ بالتميّز.
-&lt;a href="/search?f=tweets&amp;amp;q=%23جوائز_يوروموني"&gt;#جوائز_يوروموني&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23التميز_في_الخدمات_المصرفية_الخاصة"&gt;#التميز_في_الخدمات_المصرفية_الخاصة&lt;/a&gt;</t>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23StockInNews"&gt;#StockInNews&lt;/a&gt; | RBL Bank: UAE Central Bank approves NBD takeover of RBL majority stake
+&lt;a href="/rblbank" title="RBL Bank"&gt;@rblbank&lt;/a&gt; &lt;a href="/centralbankuae" title="Central Bank of the UAE"&gt;@centralbankuae&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23StockMarket"&gt;#StockMarket&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J12" t="b">
@@ -1497,36 +1453,36 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 3:57 PM UTC</t>
+          <t>Mar 25, 2026 · 5:01 PM UTC</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-03-24T15:57:00Z</t>
+          <t>2026-03-25T17:01:00Z</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23جوائز_يوروموني', 'https://x.com/search?f=tweets&amp;q=%23التميز_في_الخدمات_المصرفية_الخاصة']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23StockInNews', 'https://x.com/rblbank', 'https://x.com/centralbankuae', 'https://x.com/EmiratesNBD_AE', 'https://x.com/search?f=tweets&amp;q=%23StockMarket']</t>
         </is>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="U12" t="n">
-        <v>424</v>
+        <v>1850</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1537,55 +1493,45 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2036472534812512442</t>
+          <t>2036850685946597634</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036472534812512442</t>
+          <t>https://x.com/_RituSingh/status/2036850685946597634</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/_RituSingh</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>_RituSingh</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Ritu Singh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2020720836177764352/eHyjmdvb_bigger.jpg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>A moment of pride. A reflection of trust.
-We are pleased to be recognised at the Euromoney Private Banking Awards 2026 as:
-• Middle East’s Best Private Bank
-&amp;
-• Middle East’s Best Bank for Family Office Services
-This recognition is a testament to the enduring trust of our clients, partners, and our unwavering commitment to excellence.
-#EuromoneyAwards #PrivateBankingExcellence</t>
+          <t>🚨 Emirates NBD Gets UAE Central Bank Nod For Acquisition of Majority Stake In RBL Bank
+@rblbank @EmiratesNBD_AE @CNBCTV18Live</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>A moment of pride. A reflection of trust.
-We are pleased to be recognised at the Euromoney Private Banking Awards 2026 as:
-• Middle East’s Best Private Bank
-&amp;amp;
-• Middle East’s Best Bank for Family Office Services
-This recognition is a testament to the enduring trust of our clients, partners, and our unwavering commitment to excellence.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EuromoneyAwards"&gt;#EuromoneyAwards&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23PrivateBankingExcellence"&gt;#PrivateBankingExcellence&lt;/a&gt;</t>
+          <t>🚨 Emirates NBD Gets UAE Central Bank Nod For Acquisition of Majority Stake In RBL Bank
+&lt;a href="/rblbank" title="RBL Bank"&gt;@rblbank&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; &lt;a href="/CNBCTV18Live" title="CNBC-TV18"&gt;@CNBCTV18Live&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J13" t="b">
@@ -1595,36 +1541,36 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 3:57 PM UTC</t>
+          <t>Mar 25, 2026 · 5:00 PM UTC</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-03-24T15:57:00Z</t>
+          <t>2026-03-25T17:00:00Z</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EuromoneyAwards', 'https://x.com/search?f=tweets&amp;q=%23PrivateBankingExcellence']</t>
+          <t>['https://x.com/rblbank', 'https://x.com/EmiratesNBD_AE', 'https://x.com/CNBCTV18Live']</t>
         </is>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T13" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="U13" t="n">
-        <v>366</v>
+        <v>947</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1635,43 +1581,43 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2036459552041046257</t>
+          <t>2036850314364834133</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://x.com/vcdxnz001/status/2036459552041046257</t>
+          <t>https://x.com/shunto0823/status/2036850314364834133</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/vcdxnz001</t>
+          <t>https://x.com/shunto0823</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>vcdxnz001</t>
+          <t>shunto0823</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lord WebScale Webster</t>
+          <t>しゅんと/ドバイ在住不動産エージェント【UAE不動産】</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1157827121282072581/YmPuMRvh_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1885182332878954496/ejkcHMnq_bigger.jpg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>I really love @EmiratesNBD_AE and their payment systems. International transfers received in 10 minutes from UAE to USA. Nothing else like this. Would take a day in New Zealand. Just incredible. The UAE banking system is really great.</t>
+          <t>【ドバイ銀行口座の凍結？】現地の銀行でデマを調査してみた / 3月25日午後5時30分</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>I really love &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; and their payment systems. International transfers received in 10 minutes from UAE to USA. Nothing else like this. Would take a day in New Zealand. Just incredible. The UAE banking system is really great.</t>
+          <t>【ドバイ銀行口座の凍結？】現地の銀行でデマを調査してみた / 3月25日午後5時30分</t>
         </is>
       </c>
       <c r="J14" t="b">
@@ -1681,25 +1627,21 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 3:06 PM UTC</t>
+          <t>Mar 25, 2026 · 4:58 PM UTC</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-03-24T15:06:00Z</t>
+          <t>2026-03-25T16:58:00Z</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -1707,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U14" t="n">
-        <v>41</v>
+        <v>1028</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1721,43 +1663,43 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2036439106700607823</t>
+          <t>2036841622822883698</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://x.com/HimanshuMotiyan/status/2036439106700607823</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036841622822883698</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/HimanshuMotiyan</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>HimanshuMotiyan</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Himanshu Motiyani</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2032072703134613504/JzErzVWc_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Again its same we are following up and we will update how many times team said this kindly release my funds as this is an emergency or provide me an date for releasing funds ?</t>
+          <t>Please mention in the email subject social media case #988468.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Again its same we are following up and we will update how many times team said this kindly release my funds as this is an emergency or provide me an date for releasing funds ?</t>
+          <t>Please mention in the email subject social media case #988468.</t>
         </is>
       </c>
       <c r="J15" t="b">
@@ -1766,22 +1708,22 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['GidwaniHero']</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 1:44 PM UTC</t>
+          <t>Mar 25, 2026 · 4:24 PM UTC</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-03-24T13:44:00Z</t>
+          <t>2026-03-25T16:24:00Z</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -1796,7 +1738,7 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1807,12 +1749,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2036438860737982775</t>
+          <t>2036841585950756910</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036438860737982775</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036841585950756910</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1838,12 +1780,12 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>We sincerely regret for the inconvenience, kindly note that we have replied to your email</t>
+          <t>Hi , we’re sorry to hear that you’re having unpleasant experience. We will be glad to assist you and have it fixed. Kindly send us the details at social@EmiratesNBD.com from your registered email address so we can review and assist.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>We sincerely regret for the inconvenience, kindly note that we have replied to your email</t>
+          <t>Hi , we’re sorry to hear that you’re having unpleasant experience. We will be glad to assist you and have it fixed. Kindly send us the details at social@EmiratesNBD.com from your registered email address so we can review and assist.</t>
         </is>
       </c>
       <c r="J16" t="b">
@@ -1852,28 +1794,28 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>['HimanshuMotiyan']</t>
+          <t>['GidwaniHero']</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 1:43 PM UTC</t>
+          <t>Mar 25, 2026 · 4:24 PM UTC</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-03-24T13:43:00Z</t>
+          <t>2026-03-25T16:24:00Z</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1882,7 +1824,7 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1893,79 +1835,77 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2036434154506649672</t>
+          <t>2036841067778363615</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036434154506649672</t>
+          <t>https://x.com/GidwaniHero/status/2036841067778363615</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/GidwaniHero</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>GidwaniHero</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Hero Gidwani</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1924556859526283267/UcvezR38_bigger.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to us at
-social@emiratesnbd.coml@emiratesnbd.com 
-Quoting case #987912 in the subject line of the email from your registered email address 
-We will make every effort to address the</t>
+          <t>@HHShkMohd @MohamedBinZayed 
+@FABConnects @MashreqTweets @EmiratesNBD_AE 
+Dear UAE Government Request You To Keep Security Guards Inside ATM AND BRANCHS AT NIGHT TIME MANY POEPLE ARE MISS USING OF MACHINES 1 customer do 10 trns and they show attitude what type of services inside</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to us at
-social@emiratesnbd.coml@emiratesnbd.com 
-Quoting case #987912 in the subject line of the email from your registered email address 
-We will make every effort to address the</t>
+          <t>&lt;a href="/HHShkMohd" title="HH Sheikh Mohammed"&gt;@HHShkMohd&lt;/a&gt; &lt;a href="/MohamedBinZayed" title="محمد بن زايد"&gt;@MohamedBinZayed&lt;/a&gt; 
+&lt;a href="/FABConnects" title="FAB Connects"&gt;@FABConnects&lt;/a&gt; &lt;a href="/MashreqTweets" title="Mashreq"&gt;@MashreqTweets&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
+Dear UAE Government Request You To Keep Security Guards Inside ATM AND BRANCHS AT NIGHT TIME MANY POEPLE ARE MISS USING OF MACHINES 1 customer do 10 trns and they show attitude what type of services inside</t>
         </is>
       </c>
       <c r="J17" t="b">
         <v>0</v>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>['TariqMa18773899']</t>
-        </is>
-      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 1:25 PM UTC</t>
+          <t>Mar 25, 2026 · 4:22 PM UTC</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-03-24T13:25:00Z</t>
+          <t>2026-03-25T16:22:00Z</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>['https://x.com/HHShkMohd', 'https://x.com/MohamedBinZayed', 'https://x.com/FABConnects', 'https://x.com/MashreqTweets', 'https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -1974,7 +1914,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -1985,81 +1925,73 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2036430572923609589</t>
+          <t>2036823583914365348</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://x.com/HimanshuMotiyan/status/2036430572923609589</t>
+          <t>https://x.com/stockwatch_live/status/2036823583914365348</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/HimanshuMotiyan</t>
+          <t>https://x.com/stockwatch_live</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>HimanshuMotiyan</t>
+          <t>stockwatch_live</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Himanshu Motiyani</t>
+          <t>Stockwatch.live</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2032072703134613504/JzErzVWc_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1922756599971708929/IhP9CXt7_bigger.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Hello @EmiratesNBD_AE 
-URGENT: Resolution Required for Case #983058 - Medical Emergency &amp; Travel Restrictions case no : #983058
-Its been more then a month bank is not releasing my funds in emergency situation also this case has been registered on 12th march today is 24th march</t>
+          <t>$RBLBANK.NSE RBL Bank Receives Approval from Central Bank of UAE for Majority Stake Acquisition by Emirates NBD Bank stockwatch.live/news?name=RB… #stock #nse #bse #market #RBLBANK #RBLBankLtd</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Hello &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
-URGENT: Resolution Required for Case #983058 - Medical Emergency &amp;amp; Travel Restrictions case no : #983058
-Its been more then a month bank is not releasing my funds in emergency situation also this case has been registered on 12th march today is 24th march</t>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23RBLBANK"&gt;$RBLBANK&lt;/a&gt;.NSE RBL Bank Receives Approval from Central Bank of UAE for Majority Stake Acquisition by Emirates NBD Bank &lt;a href="https://www.stockwatch.live/news?name=RBL+Bank+Ltd&amp;amp;showModal=true&amp;amp;title=RBL+Bank+Receives+Approval+from+Central+Bank+of+UAE+for+Majority+Stake+Acquisition+by+Emirates+NBD+Bank&amp;amp;newsId=fb36b797-76cb-4e5b-af51-5f06aebb98fd"&gt;stockwatch.live/news?name=RB…&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23stock"&gt;#stock&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23nse"&gt;#nse&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23bse"&gt;#bse&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23market"&gt;#market&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23RBLBANK"&gt;#RBLBANK&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23RBLBankLtd"&gt;#RBLBankLtd&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J18" t="b">
         <v>0</v>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 1:10 PM UTC</t>
+          <t>Mar 25, 2026 · 3:12 PM UTC</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-03-24T13:10:00Z</t>
+          <t>2026-03-25T15:12:00Z</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23RBLBANK', 'https://www.stockwatch.live/news?name=RBL+Bank+Ltd&amp;showModal=true&amp;title=RBL+Bank+Receives+Approval+from+Central+Bank+of+UAE+for+Majority+Stake+Acquisition+by+Emirates+NBD+Bank&amp;newsId=fb36b797-76cb-4e5b-af51-5f06aebb98fd', 'https://x.com/search?f=tweets&amp;q=%23stock', 'https://x.com/search?f=tweets&amp;q=%23nse', 'https://x.com/search?f=tweets&amp;q=%23bse', 'https://x.com/search?f=tweets&amp;q=%23market', 'https://x.com/search?f=tweets&amp;q=%23RBLBANK', 'https://x.com/search?f=tweets&amp;q=%23RBLBankLtd']</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -2068,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -2079,47 +2011,51 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2036430430883414274</t>
+          <t>2036821360086069616</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://x.com/HimanshuMotiyan/status/2036430430883414274</t>
+          <t>https://x.com/_Investor_Feed_/status/2036821360086069616</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/HimanshuMotiyan</t>
+          <t>https://x.com/_Investor_Feed_</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HimanshuMotiyan</t>
+          <t>_Investor_Feed_</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Himanshu Motiyani</t>
+          <t>Investor Feed</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2032072703134613504/JzErzVWc_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1897853077535047680/p8b9Zv5P_bigger.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Hello @EmiratesNBD_AE 
-URGENT: Resolution Required for Case #983058 - Medical Emergency &amp; Travel Restrictions case no : #983058
-Its been more then a month bank is not releasing my funds in emergency situation also this case has been registered on 12th march today is 24th march</t>
+          <t>🏦 Emirates NBD Secures UAE Central Bank Approval for Majority Stake in RBL Bank | MCap 20,197.23 Cr
+• UAE Central Bank approved Emirates NBD's majority stake acquisition in RBL Bank on March 24, 2026
+• Approval includes amalgamation of Emirates NBD's existing Indian operations into RBL Bank
+Complete Source: bseindia.com/xml-data/corpfi…
+Disc: Information provided in this tweet can be inaccurate, verify through the source before making any investment decision.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Hello &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
-URGENT: Resolution Required for Case #983058 - Medical Emergency &amp;amp; Travel Restrictions case no : #983058
-Its been more then a month bank is not releasing my funds in emergency situation also this case has been registered on 12th march today is 24th march</t>
+          <t>🏦 Emirates NBD Secures UAE Central Bank Approval for Majority Stake in RBL Bank | MCap 20,197.23 Cr
+• UAE Central Bank approved Emirates NBD&amp;#39;s majority stake acquisition in RBL Bank on March 24, 2026
+• Approval includes amalgamation of Emirates NBD&amp;#39;s existing Indian operations into RBL Bank
+Complete Source: &lt;a href="https://www.bseindia.com/xml-data/corpfiling/AttachLive/16d12839-deaa-4f3e-acd1-b6184ab87abc.pdf"&gt;bseindia.com/xml-data/corpfi…&lt;/a&gt;
+Disc: Information provided in this tweet can be inaccurate, verify through the source before making any investment decision.</t>
         </is>
       </c>
       <c r="J19" t="b">
@@ -2129,23 +2065,23 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 1:10 PM UTC</t>
+          <t>Mar 25, 2026 · 3:03 PM UTC</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-03-24T13:10:00Z</t>
+          <t>2026-03-25T15:03:00Z</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
+          <t>['https://www.bseindia.com/xml-data/corpfiling/AttachLive/16d12839-deaa-4f3e-acd1-b6184ab87abc.pdf']</t>
         </is>
       </c>
       <c r="R19" t="n">
@@ -2155,10 +2091,10 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>4</v>
+        <v>287</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -2169,79 +2105,79 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2036427479733432465</t>
+          <t>2036821223116845234</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://x.com/TariqMa18773899/status/2036427479733432465</t>
+          <t>https://x.com/wegro_app/status/2036821223116845234</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/TariqMa18773899</t>
+          <t>https://x.com/wegro_app</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TariqMa18773899</t>
+          <t>wegro_app</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tariq Malik</t>
+          <t>Wegro App</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1507617364636049410/VGpC-lFO_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1793658188497117184/T9pfyA67_bigger.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>I request to cancel the card ,it was told to me that I will receive the call for confirmation but due to current situation I was about to withdraw my rejection .
-No call but card was cancelled.
-As a customer since more than 5 year. I am really disappointed.
-Thank you NBD</t>
+          <t>RBL Bank announced that Emirates NBD Bank has received approval from the Central Bank of UAE for its proposed acquisition of a majority stake in RBL Bank &amp; amalgamation of Emirates NBD's India operations into RBL Bank. This is subject to receipt of all necessary regulatory approvals. The information is hosted on RBL Bank's website.
+📊 RBL BANK LTD | 🏷️ General
+🌐 Details: wegro.app/UWJL50
+⚡️Instant stock alerts on WhatsApp - Try FREE 👉 wegro.app/go</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>I request to cancel the card ,it was told to me that I will receive the call for confirmation but due to current situation I was about to withdraw my rejection .
-No call but card was cancelled.
-As a customer since more than 5 year. I am really disappointed.
-Thank you NBD</t>
+          <t>RBL Bank announced that Emirates NBD Bank has received approval from the Central Bank of UAE for its proposed acquisition of a majority stake in RBL Bank &amp;amp; amalgamation of Emirates NBD&amp;#39;s India operations into RBL Bank. This is subject to receipt of all necessary regulatory approvals. The information is hosted on RBL Bank&amp;#39;s website.
+📊 RBL BANK LTD | 🏷️ General
+🌐 Details: &lt;a href="https://www.wegro.app/UWJL50"&gt;wegro.app/UWJL50&lt;/a&gt;
+⚡️Instant stock alerts on WhatsApp - Try FREE 👉 &lt;a href="https://www.wegro.app/go"&gt;wegro.app/go&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J20" t="b">
         <v>0</v>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 12:58 PM UTC</t>
+          <t>Mar 25, 2026 · 3:03 PM UTC</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-03-24T12:58:00Z</t>
+          <t>2026-03-25T15:03:00Z</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>['https://www.wegro.app/UWJL50', 'https://www.wegro.app/go']</t>
+        </is>
+      </c>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -2250,7 +2186,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -2261,59 +2197,53 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2036419599017673090</t>
+          <t>2036821129726501170</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://x.com/Almalchannel/status/2036419599017673090</t>
+          <t>https://x.com/SpeedyStox45552/status/2036821129726501170</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://x.com/Almalchannel</t>
+          <t>https://x.com/SpeedyStox45552</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Almalchannel</t>
+          <t>SpeedyStox45552</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>قناة المال | Almal Channel</t>
+          <t>Speedy Stox</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1522466082388426752/G7GbO5MC_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2026633232603893760/w3Lqscnz_bigger.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>أصول القطاع المصرفي +5.4 تريليون درهم … 🇦🇪
-مؤشرات تعكس قوة الاقتصاد 📊💰
-مع نمو مستمر في الائتمان والودائع
-الأرقام بنهاية يناير:📊
-▪️ الأصول: 5.41 تريليون درهم (+1.4%)
-▪️ الائتمان: 2.59 تريليون درهم (+1.1%)
-▪️ الودائع: 3.33 تريليون درهم (+0.9%)
-💡 ما وراء الأرقام؟ 🤔
-1/2</t>
+          <t>📊 RBL BANK LTD - 540065 | 🏷️ General
+Emirates NBD Bank (P.J.S.C) received approval from the Central Bank of UAE on March 24, 2026, for the proposed acquisition of a majority stake and amalgamation of its operations in India, pending necessary regulatory approvals.
+💰 CMP: ₹303.80 (+2.51%)
+🏢 MCap: ₹18,778 Cr
+🌐 Details: tinyurl.com/2bbt3ha2
+⚡️Instant stock alerts on WhatsApp - Try FREE 👉 speedystox.com</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>أصول القطاع المصرفي +5.4 تريليون درهم … 🇦🇪
-مؤشرات تعكس قوة الاقتصاد 📊💰
-مع نمو مستمر في الائتمان والودائع
-الأرقام بنهاية يناير:📊
-▪️ الأصول: 5.41 تريليون درهم (+1.4%)
-▪️ الائتمان: 2.59 تريليون درهم (+1.1%)
-▪️ الودائع: 3.33 تريليون درهم (+0.9%)
-💡 ما وراء الأرقام؟ 🤔
-1/2</t>
+          <t>📊 RBL BANK LTD - 540065 | 🏷️ General
+Emirates NBD Bank (P.J.S.C) received approval from the Central Bank of UAE on March 24, 2026, for the proposed acquisition of a majority stake and amalgamation of its operations in India, pending necessary regulatory approvals.
+💰 CMP: ₹303.80 (+2.51%)
+🏢 MCap: ₹18,778 Cr
+🌐 Details: &lt;a href="https://tinyurl.com/2bbt3ha2"&gt;tinyurl.com/2bbt3ha2&lt;/a&gt;
+⚡️Instant stock alerts on WhatsApp - Try FREE 👉 &lt;a href="http://speedystox.com"&gt;speedystox.com&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J21" t="b">
@@ -2323,32 +2253,36 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 12:27 PM UTC</t>
+          <t>Mar 25, 2026 · 3:02 PM UTC</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-03-24T12:27:00Z</t>
+          <t>2026-03-25T15:02:00Z</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>['https://tinyurl.com/2bbt3ha2', 'http://speedystox.com']</t>
+        </is>
+      </c>
       <c r="R21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>945</v>
+        <v>38</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -2359,59 +2293,51 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2036419006157168802</t>
+          <t>2036820403755037156</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://x.com/nasnews_ar/status/2036419006157168802</t>
+          <t>https://x.com/EmiratesNBD_EGY/status/2036820403755037156</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://x.com/nasnews_ar</t>
+          <t>https://x.com/EmiratesNBD_EGY</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>nasnews_ar</t>
+          <t>EmiratesNBD_EGY</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ناس نيوز- الإمارات</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034402372802482176/xcCIp6EK_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>🔵5.41 تريليونات درهم بنسبة نمو 1.4%
-🔵واصلت المؤشرات النقدية والمصرفية في دولة الإمارات، تسجيل أداء إيجابي مع بداية 2026، حيث ارتفع إجمالي الأصول المصرفية 1.4% ليتجاوز 5.413 تريليونات درهم في نهاية يناير 2026 مقارنة مع نحو 5.339 تريليونات درهم في نهاية ديسمبر 2025
-🔵 وارتفع إجمالي الائتمان 1.1%، من نحو 2.57 تريليون درهم في نهاية ديسمبر، ليتجاوز 2.598 تريليون درهم بنهاية يناير 2026، مدعوماً بزيادة الائتمان المحلي بقيمة 27.9 مليار درهم.
-🔵ويعود نمو الائتمان المحلي إلى ارتفاع الائتمان الممنوح للقطاع الحكومي بنسبة 2.5%، والقطاع الخاص بنسبة 0.6%، والذي أسهم بنحو 0.4 نقطة مئوية من إجمالي النمو
-🔵وارتفع إجمالي الودائع المصرفية 0.9% ليصل إلى نحو 3.337 تريليون درهم في نهاية يناير 2026، مقارنة مع 3.307 تريليون درهم في نهاية ديسمبر، مدعوماً بزيادة ودائع المقيمين بنسبة 1.2% لتصل إلى 3.046 تريليون درهم
-#الإمارات
-#عام_الأسرة 
-#ناس_نيوز_الإمارات
-@nasnews_ar</t>
+          <t>From All Seasons Park to Open Air Mall ENBD Mastercard x TMG credit cardholders enjoyed surprises and rewards across Ilo Specialty, Stereo, Breadfast, and Tabali.
+And this was just the beginning…
+More Happy Hours are coming your way.
+Stay ready.
+Tax registration number: 204-897-319</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>🔵5.41 تريليونات درهم بنسبة نمو 1.4%
-🔵واصلت المؤشرات النقدية والمصرفية في دولة الإمارات، تسجيل أداء إيجابي مع بداية 2026، حيث ارتفع إجمالي الأصول المصرفية 1.4% ليتجاوز 5.413 تريليونات درهم في نهاية يناير 2026 مقارنة مع نحو 5.339 تريليونات درهم في نهاية ديسمبر 2025
-🔵 وارتفع إجمالي الائتمان 1.1%، من نحو 2.57 تريليون درهم في نهاية ديسمبر، ليتجاوز 2.598 تريليون درهم بنهاية يناير 2026، مدعوماً بزيادة الائتمان المحلي بقيمة 27.9 مليار درهم.
-🔵ويعود نمو الائتمان المحلي إلى ارتفاع الائتمان الممنوح للقطاع الحكومي بنسبة 2.5%، والقطاع الخاص بنسبة 0.6%، والذي أسهم بنحو 0.4 نقطة مئوية من إجمالي النمو
-🔵وارتفع إجمالي الودائع المصرفية 0.9% ليصل إلى نحو 3.337 تريليون درهم في نهاية يناير 2026، مقارنة مع 3.307 تريليون درهم في نهاية ديسمبر، مدعوماً بزيادة ودائع المقيمين بنسبة 1.2% لتصل إلى 3.046 تريليون درهم
-&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات"&gt;#الإمارات&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23عام_الأسرة"&gt;#عام_الأسرة&lt;/a&gt; 
-&lt;a href="/search?f=tweets&amp;amp;q=%23ناس_نيوز_الإمارات"&gt;#ناس_نيوز_الإمارات&lt;/a&gt;
-&lt;a href="/nasnews_ar" title="ناس نيوز- الإمارات"&gt;@nasnews_ar&lt;/a&gt;</t>
+          <t>From All Seasons Park to Open Air Mall ENBD Mastercard x TMG credit cardholders enjoyed surprises and rewards across Ilo Specialty, Stereo, Breadfast, and Tabali.
+And this was just the beginning…
+More Happy Hours are coming your way.
+Stay ready.
+Tax registration number: 204-897-319</t>
         </is>
       </c>
       <c r="J22" t="b">
@@ -2421,25 +2347,21 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 12:25 PM UTC</t>
+          <t>Mar 25, 2026 · 3:00 PM UTC</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-03-24T12:25:00Z</t>
+          <t>2026-03-25T15:00:00Z</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23الإمارات', 'https://x.com/search?f=tweets&amp;q=%23عام_الأسرة', 'https://x.com/search?f=tweets&amp;q=%23ناس_نيوز_الإمارات', 'https://x.com/nasnews_ar']</t>
-        </is>
-      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -2447,10 +2369,10 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>483</v>
+        <v>49</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2461,67 +2383,69 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2036417775510442457</t>
+          <t>2036820403234979999</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2036417775510442457</t>
+          <t>https://x.com/EmiratesNBD_EGY/status/2036820403234979999</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA</t>
+          <t>https://x.com/EmiratesNBD_EGY</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA</t>
+          <t>EmiratesNBD_EGY</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>EmiratesNBD KSA</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل الخاصه بشكواك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
+          <t>من All Seasons Park إلى Open Air Mall ، استمتع حاملي بطاقة بنك الإمارات دبي الوطني ماستركارد الائتمانية بالتعاون مع مجموعة طلعت مصطفى بمفاجآت وجوائز في Ilo Specialty، Stereo، Breadfast، وTabali.
+و دي مجرد البداية...
+استنونا في مفاجآت ومكافآت أكتر.
+رقم التسجيل الضريبي: 319-897-204</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل الخاصه بشكواك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
+          <t>من All Seasons Park إلى Open Air Mall ، استمتع حاملي بطاقة بنك الإمارات دبي الوطني ماستركارد الائتمانية بالتعاون مع مجموعة طلعت مصطفى بمفاجآت وجوائز في Ilo Specialty، Stereo، Breadfast، وTabali.
+و دي مجرد البداية...
+استنونا في مفاجآت ومكافآت أكتر.
+رقم التسجيل الضريبي: 319-897-204</t>
         </is>
       </c>
       <c r="J23" t="b">
         <v>0</v>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>['motsafeh057']</t>
-        </is>
-      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 12:20 PM UTC</t>
+          <t>Mar 25, 2026 · 3:00 PM UTC</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-03-24T12:20:00Z</t>
+          <t>2026-03-25T15:00:00Z</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2536,7 +2460,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -2547,43 +2471,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2036414919394971981</t>
+          <t>2036810456203952345</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://x.com/motsafeh057/status/2036414919394971981</t>
+          <t>https://x.com/Kevin_Carey_WB/status/2036810456203952345</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://x.com/motsafeh057</t>
+          <t>https://x.com/Kevin_Carey_WB</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>motsafeh057</t>
+          <t>Kevin_Carey_WB</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>متصفح وقارئ للأخبار</t>
+          <t>Kevin Carey</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1996323967443881984/qDVGWeO0_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1471236762265600011/Py_QxqOf_bigger.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA البنك رافض قطعيا يفتح لي حساب حاولت عن طريق خدمة العملاء رفض</t>
+          <t>Don't have a good sense of the normal flow but noticing a couple of redemptions of Additional Tier 1 securities by UAE banks today (First Abu Dhabi Bank, Emirates NBD).</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; البنك رافض قطعيا يفتح لي حساب حاولت عن طريق خدمة العملاء رفض</t>
+          <t>Don&amp;#39;t have a good sense of the normal flow but noticing a couple of redemptions of Additional Tier 1 securities by UAE banks today (First Abu Dhabi Bank, Emirates NBD).</t>
         </is>
       </c>
       <c r="J24" t="b">
@@ -2593,36 +2517,32 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 12:08 PM UTC</t>
+          <t>Mar 25, 2026 · 2:20 PM UTC</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-03-24T12:08:00Z</t>
+          <t>2026-03-25T14:20:00Z</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
         <v>1</v>
       </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
       <c r="U24" t="n">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -2633,71 +2553,71 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2036405523604709887</t>
+          <t>2036804187833401607</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://x.com/DFMalerts/status/2036405523604709887</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036804187833401607</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://x.com/DFMalerts</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DFMalerts</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dubai Financial Market</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1517441998717956098/e_tgPkVx_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>#DFM Top Gainers of the day: CHAE up 7.50%, EMIRATESNBD up 7.25%, DSI up 5.29%</t>
+          <t>نأسف بشدة، وقد طلبنا من فريقنا الاتصال بك في أقرب وقت ممكن لمساعدتك. شكرًا لك.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23DFM"&gt;#DFM&lt;/a&gt; Top Gainers of the day: CHAE up 7.50%, EMIRATESNBD up 7.25%, DSI up 5.29%</t>
+          <t>نأسف بشدة، وقد طلبنا من فريقنا الاتصال بك في أقرب وقت ممكن لمساعدتك. شكرًا لك.</t>
         </is>
       </c>
       <c r="J25" t="b">
         <v>0</v>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>['hamzzah99']</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 11:31 AM UTC</t>
+          <t>Mar 25, 2026 · 1:55 PM UTC</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-03-24T11:31:00Z</t>
+          <t>2026-03-25T13:55:00Z</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23DFM']</t>
-        </is>
-      </c>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -2705,10 +2625,10 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>274</v>
+        <v>12</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2719,69 +2639,73 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2036402467106390175</t>
+          <t>2036803846417039482</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://x.com/DFMalerts/status/2036402467106390175</t>
+          <t>https://x.com/hamzzah99/status/2036803846417039482</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://x.com/DFMalerts</t>
+          <t>https://x.com/hamzzah99</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DFMalerts</t>
+          <t>hamzzah99</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dubai Financial Market</t>
+          <t>Hamza 💙🤍</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1517441998717956098/e_tgPkVx_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1628569116847087616/77YITtTX_bigger.jpg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>الشركات الأكثر إرتفاعا لليوم في سوق دبي المالي: CHAE ارتفع 7.50%، EMIRATESNBD ارتفع 7.25%، DSI ارتفع 5.29%</t>
+          <t>تواصلت خاص قبل فترة ونفس الرد ويتصلون في اوقات غير مناسبة</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>الشركات الأكثر إرتفاعا لليوم في سوق دبي المالي: CHAE ارتفع 7.50%، EMIRATESNBD ارتفع 7.25%، DSI ارتفع 5.29%</t>
+          <t>تواصلت خاص قبل فترة ونفس الرد ويتصلون في اوقات غير مناسبة</t>
         </is>
       </c>
       <c r="J26" t="b">
         <v>0</v>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 11:19 AM UTC</t>
+          <t>Mar 25, 2026 · 1:54 PM UTC</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-03-24T11:19:00Z</t>
+          <t>2026-03-25T13:54:00Z</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2790,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>285</v>
+        <v>9</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -2801,45 +2725,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2036400751896043863</t>
+          <t>2036803555248513519</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://x.com/koko_isa8/status/2036400751896043863</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036803555248513519</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://x.com/koko_isa8</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>koko_isa8</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>κoκo мadeмöıseιιe⁸ 💅🏽</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2035262775103242240/J6m7iJmF_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>So? 
-Am i expecting any call from your side?</t>
+          <t>نشكركم على تواصلكم معنا، ونعتذر بشدة عن التأخير، وقد طلبنا من فريقنا التواصل معكم لإطلاعكم على آخر المستجدات في أقرب وقت ممكن. شكرًا.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>So? 
-Am i expecting any call from your side?</t>
+          <t>نشكركم على تواصلكم معنا، ونعتذر بشدة عن التأخير، وقد طلبنا من فريقنا التواصل معكم لإطلاعكم على آخر المستجدات في أقرب وقت ممكن. شكرًا.</t>
         </is>
       </c>
       <c r="J27" t="b">
@@ -2848,37 +2770,37 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['hamzzah99']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 11:12 AM UTC</t>
+          <t>Mar 25, 2026 · 1:53 PM UTC</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-03-24T11:12:00Z</t>
+          <t>2026-03-25T13:53:00Z</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -2889,43 +2811,43 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2036389317132583041</t>
+          <t>2036803479503609971</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://x.com/netdiscussion/status/2036389317132583041</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036803479503609971</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://x.com/netdiscussion</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>netdiscussion</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Muhammad Kashif Ashraf</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>@SAMAcares There's no response on the dispute query for the wrong/back dated fee applied, pending since 8 March</t>
+          <t>Thanks for reaching us and we are extremely sorry for the delay and we have asked our team to contact you with an update as soon as possible. Thanks</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>&lt;a href="/SAMAcares" title="SAMACares | ساما تهتم"&gt;@SAMAcares&lt;/a&gt; There&amp;#39;s no response on the dispute query for the wrong/back dated fee applied, pending since 8 March</t>
+          <t>Thanks for reaching us and we are extremely sorry for the delay and we have asked our team to contact you with an update as soon as possible. Thanks</t>
         </is>
       </c>
       <c r="J28" t="b">
@@ -2934,30 +2856,26 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_KSA']</t>
+          <t>['hamzzah99']</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 10:27 AM UTC</t>
+          <t>Mar 25, 2026 · 1:52 PM UTC</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-03-24T10:27:00Z</t>
+          <t>2026-03-25T13:52:00Z</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>['https://x.com/SAMAcares']</t>
-        </is>
-      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -2968,7 +2886,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -2979,43 +2897,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2036378422146932854</t>
+          <t>2036802785895678272</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036378422146932854</t>
+          <t>https://x.com/hamzzah99/status/2036802785895678272</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/hamzzah99</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>hamzzah99</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Hamza 💙🤍</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1628569116847087616/77YITtTX_bigger.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>You can find the winners list on the same page till January 2026, the rest will be updated shortly. we appreciate your patience.</t>
+          <t>It's been over 18 days for a service that was supposed to be 3 days, and it hasn't been completed. When we called, they said it would be escalated and our request would be processed, but nothing has been done.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>You can find the winners list on the same page till January 2026, the rest will be updated shortly. we appreciate your patience.</t>
+          <t>It&amp;#39;s been over 18 days for a service that was supposed to be 3 days, and it hasn&amp;#39;t been completed. When we called, they said it would be escalated and our request would be processed, but nothing has been done.</t>
         </is>
       </c>
       <c r="J29" t="b">
@@ -3024,28 +2942,28 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>['FarazKhan11228']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 9:43 AM UTC</t>
+          <t>Mar 25, 2026 · 1:50 PM UTC</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-03-24T09:43:00Z</t>
+          <t>2026-03-25T13:50:00Z</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -3054,7 +2972,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -3065,43 +2983,43 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2036368098593480939</t>
+          <t>2036802694979969378</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036368098593480939</t>
+          <t>https://x.com/hamzzah99/status/2036802694979969378</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/hamzzah99</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>hamzzah99</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>Hamza 💙🤍</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1628569116847087616/77YITtTX_bigger.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>B- 1.89% @Emy191990 @ibushra_03 @semeet</t>
+          <t>اكثر من 18 يوم عشان خدمة مدتها 3 ايام لم تنفذ واذا اتصلنا قالو سوف يتم التصعيد وسيتم تفيد طلبك دون جدوى</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>B- 1.89% &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt;</t>
+          <t>اكثر من 18 يوم عشان خدمة مدتها 3 ايام لم تنفذ واذا اتصلنا قالو سوف يتم التصعيد وسيتم تفيد طلبك دون جدوى</t>
         </is>
       </c>
       <c r="J30" t="b">
@@ -3115,27 +3033,23 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 9:02 AM UTC</t>
+          <t>Mar 25, 2026 · 1:49 PM UTC</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-03-24T09:02:00Z</t>
+          <t>2026-03-25T13:49:00Z</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/semeet']</t>
-        </is>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -3144,7 +3058,7 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -3155,77 +3069,77 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2036368044075966644</t>
+          <t>2036796926939578566</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036368044075966644</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036796926939578566</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>B- 1.89% @semeet @SelmaRomola @ibushra_03</t>
+          <t>Get guaranteed vouchers worth of AED750
+Apply for Emirates NBD SHARE Visa Credit Card and receive a guaranteed Majid Al Futtaim voucher worth AED 750.
+Apply Now: apply.emiratesnbd.com/en/cre…</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>B- 1.89% &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
+          <t>Get guaranteed vouchers worth of AED750
+Apply for Emirates NBD SHARE Visa Credit Card and receive a guaranteed Majid Al Futtaim voucher worth AED 750.
+Apply Now: &lt;a href="https://apply.emiratesnbd.com/en/credit-card/maf"&gt;apply.emiratesnbd.com/en/cre…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J31" t="b">
         <v>0</v>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 9:02 AM UTC</t>
+          <t>Mar 25, 2026 · 1:26 PM UTC</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-03-24T09:02:00Z</t>
+          <t>2026-03-25T13:26:00Z</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/ibushra_03']</t>
+          <t>['https://apply.emiratesnbd.com/en/credit-card/maf']</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3234,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>9</v>
+        <v>468</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -3245,73 +3159,151 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2036367982033768789</t>
+          <t>2036791503868281341</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036367982033768789</t>
+          <t>https://x.com/adisatrader/status/2036791503868281341</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/adisatrader</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>adisatrader</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>AD.Trader</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1848073601280573440/NI8qeR5q_bigger.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>B- 1.89% @Emy191990 @ibushra_03 @Salma2232019</t>
+          <t>AWS機房被炸之後：加密貨幣在戰爭裡是什麼角色
+帳戶裡有錢、卻動不了它。這才是現代戰爭最殘忍的一刀
+你以為分散配置了。但你有沒有想過，那些資產在你最需要的時候，根本不在你身邊？
+伊朗無人機炸了 AWS 在阿聯酋與巴林的三座機房。
+Emirates NBD、ADCB 當機。POS 刷不了。叫車 App 開不了。
+你的錢還在帳戶裡。
+你就是碰不到它。
+▋ AWS 事件炸出來的，其實是傳統金融的地基
+很多人看到這則新聞的第一反應：「連雲端都能被炸，加密貨幣一樣沒用。」
+這句話差一點就說對了。差在哪裡，很重要。
+網路中斷，確實讓你暫時無法動用鏈上資產。但你的 BTC 仍然鎖在那個 address 裡，一點都沒少。比特幣這條鏈的節點跑在全球數萬台機器上，沒有一個「總機房」能被定點清除。
+真正的問題從來不是「資產消失了」，而是「你能不能到達一個有網路的地方」。
+一旦你跨出戰區，帶著助記詞，錢包打開，一切立刻回來。銀行存款在當地系統裡動不了，房地產你帶不走，保管箱的黃金你扛不動。加密資產在這個維度上的優勢，不是靠敘事支撐的，是架構決定的。
+▋ 黃金的硬傷，沒有人在牛市裡願意正視
+黃金的長期避險邏輯無法反駁，幾千年的數據擺在那裡。
+但戰爭場景不是理論題。
+你能帶多少重量過邊境？邊境稽查時，金條比什麼都顯眼。部分政權對黃金的態度是：看到就沒收，找個理由很容易。就算你帶出去了，到了一個陌生的國家，你要找誰換？用什麼匯率？這中間的摩擦成本，在你最需要流動性的那一刻，會大到出乎你意料。
+黃金的問題不是「沒有價值」，是它的價值在你最需要「帶著跑」的那個當下，幾乎無法被你實際兌現。
+▋ 三種資產在戰場上真正的樣子
+本地現金在秩序還在的時候最好用，POS 能刷、找零沒問題。但銀行關門、ATM 停擺之後，那疊紙鈔接下來值多少，是另一回事。出了境，戰亂國家的法幣通常只剩紀念價值。
+黃金跨境有摩擦，兌現有摩擦，在極端情境下甚至有被沒收的風險。作為長期儲值它是對的，但當你需要它動起來的時候，它太重、太慢、太顯眼。
+加密資產短期支付確實依賴網路，這點不用美化。但一旦你能到有網路的地方，它的跨境流動性是其他資產比不上的。12個字的助記詞，可以穿過任何邊境，沒有重量，沒有顯眼的體積，沒有任何政府能在你腦子裡搜查什麼。
+沒有完美資產。但「帶著跑」這件事，結構上就是加密資產的主場。
+▋ 集中式基礎設施的脆弱，這次只是預演
+這次中斷的根本原因很簡單：多數銀行和支付公司把核心系統壓在幾個雲端區域，某個地理位置出事，整個區域的金融服務就一起倒。
+公鏈不是這個架構。沒有單一攻擊點，局部斷網只影響你此刻的接取，不影響資產本身的存在。在真實的地緣衝突裡，這種去中心化的基礎設施反而比很多人想像中的「國家級關鍵基礎設施」更難被完整打趴。
+這次是預演，不是終局。
+▋ 如果換成是你的城市，現在能怎麼做
+資產配置上，實體現金留夠應付短期停網下的本地消費，但別把所有流動資金壓在單一法幣。黃金作為長期儲值是合理的，只是要對攜帶和過境的實際成本有清醒認識。主流加密資產和穩定幣，要有一部分在自託管狀態。硬體錢包、助記詞離線備份，缺一不可。
+工具面，助記詞不能只存在手機備忘錄或雲端。想清楚一個問題：如果手機壞掉、SIM 卡同時失效，你靠什麼打開你的錢包？
+出場路徑，想像一個具體場景：你帶著護照和一組助記詞，抵達一個陌生國家，國內的帳戶全部碰不到。
+這時你需要的，是一個在多國都有法幣出入金管道、P2P 市場夠深、KYC 流程不會在最糟糕的時機卡住你的平台。
+像 @binancezh 這類全球性交易所，在這個場景裡的價值不是廣告詞。是當某個地區的銀行系統已經失能，你還能透過其他司法轄區的出入金管道或 P2P 市場，把鏈上資產換成當地能用的現金。這個路徑平時看起來是備用選項，到了那個時刻，它是唯一選項。
+前提一樣：身份驗證要早做，介面要熟，不是等事情發生了才去摸索。戰爭爆發那天才臨時下載 App，已經太慢了。
+你讀完這篇，心裡有個聲音說「有道理，改天認真研究一下」。我知道，因為大多數人的反應都是這樣，然後他們繼續維持現在的配置，繼續做一樣的決策。
+問題不在於你懂不懂這些道理。
+問題在於：你的配置裡有沒有覆蓋到「尾部」。
+過去十年，COVID、烏俄戰爭、中東升溫、銀行擠兌、穩
+定幣脫鉤。每一次事件發生前，都有人說這種事不會發生，機率很低，不值得為它調整策略。他們說的沒有錯。機率確實低。但期望值是機率乘以損失幅度，不是只算機率。
+倖存者偏差的運作方式很安靜：在你遇到那個尾部事件之前，你的系統看起來一直都是對的。你活著，所以策略有效。直到有一天它突然無效。那天你才會明白這道數學是怎麼對你生效的。
+市場從不需要你相信它。
+它只需要時間。</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>B- 1.89% &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+          <t>AWS機房被炸之後：加密貨幣在戰爭裡是什麼角色
+帳戶裡有錢、卻動不了它。這才是現代戰爭最殘忍的一刀
+你以為分散配置了。但你有沒有想過，那些資產在你最需要的時候，根本不在你身邊？
+伊朗無人機炸了 AWS 在阿聯酋與巴林的三座機房。
+Emirates NBD、ADCB 當機。POS 刷不了。叫車 App 開不了。
+你的錢還在帳戶裡。
+你就是碰不到它。
+▋ AWS 事件炸出來的，其實是傳統金融的地基
+很多人看到這則新聞的第一反應：「連雲端都能被炸，加密貨幣一樣沒用。」
+這句話差一點就說對了。差在哪裡，很重要。
+網路中斷，確實讓你暫時無法動用鏈上資產。但你的 BTC 仍然鎖在那個 address 裡，一點都沒少。比特幣這條鏈的節點跑在全球數萬台機器上，沒有一個「總機房」能被定點清除。
+真正的問題從來不是「資產消失了」，而是「你能不能到達一個有網路的地方」。
+一旦你跨出戰區，帶著助記詞，錢包打開，一切立刻回來。銀行存款在當地系統裡動不了，房地產你帶不走，保管箱的黃金你扛不動。加密資產在這個維度上的優勢，不是靠敘事支撐的，是架構決定的。
+▋ 黃金的硬傷，沒有人在牛市裡願意正視
+黃金的長期避險邏輯無法反駁，幾千年的數據擺在那裡。
+但戰爭場景不是理論題。
+你能帶多少重量過邊境？邊境稽查時，金條比什麼都顯眼。部分政權對黃金的態度是：看到就沒收，找個理由很容易。就算你帶出去了，到了一個陌生的國家，你要找誰換？用什麼匯率？這中間的摩擦成本，在你最需要流動性的那一刻，會大到出乎你意料。
+黃金的問題不是「沒有價值」，是它的價值在你最需要「帶著跑」的那個當下，幾乎無法被你實際兌現。
+▋ 三種資產在戰場上真正的樣子
+本地現金在秩序還在的時候最好用，POS 能刷、找零沒問題。但銀行關門、ATM 停擺之後，那疊紙鈔接下來值多少，是另一回事。出了境，戰亂國家的法幣通常只剩紀念價值。
+黃金跨境有摩擦，兌現有摩擦，在極端情境下甚至有被沒收的風險。作為長期儲值它是對的，但當你需要它動起來的時候，它太重、太慢、太顯眼。
+加密資產短期支付確實依賴網路，這點不用美化。但一旦你能到有網路的地方，它的跨境流動性是其他資產比不上的。12個字的助記詞，可以穿過任何邊境，沒有重量，沒有顯眼的體積，沒有任何政府能在你腦子裡搜查什麼。
+沒有完美資產。但「帶著跑」這件事，結構上就是加密資產的主場。
+▋ 集中式基礎設施的脆弱，這次只是預演
+這次中斷的根本原因很簡單：多數銀行和支付公司把核心系統壓在幾個雲端區域，某個地理位置出事，整個區域的金融服務就一起倒。
+公鏈不是這個架構。沒有單一攻擊點，局部斷網只影響你此刻的接取，不影響資產本身的存在。在真實的地緣衝突裡，這種去中心化的基礎設施反而比很多人想像中的「國家級關鍵基礎設施」更難被完整打趴。
+這次是預演，不是終局。
+▋ 如果換成是你的城市，現在能怎麼做
+資產配置上，實體現金留夠應付短期停網下的本地消費，但別把所有流動資金壓在單一法幣。黃金作為長期儲值是合理的，只是要對攜帶和過境的實際成本有清醒認識。主流加密資產和穩定幣，要有一部分在自託管狀態。硬體錢包、助記詞離線備份，缺一不可。
+工具面，助記詞不能只存在手機備忘錄或雲端。想清楚一個問題：如果手機壞掉、SIM 卡同時失效，你靠什麼打開你的錢包？
+出場路徑，想像一個具體場景：你帶著護照和一組助記詞，抵達一個陌生國家，國內的帳戶全部碰不到。
+這時你需要的，是一個在多國都有法幣出入金管道、P2P 市場夠深、KYC 流程不會在最糟糕的時機卡住你的平台。
+像 &lt;a href="/binancezh" title="币安Binance华语"&gt;@binancezh&lt;/a&gt; 這類全球性交易所，在這個場景裡的價值不是廣告詞。是當某個地區的銀行系統已經失能，你還能透過其他司法轄區的出入金管道或 P2P 市場，把鏈上資產換成當地能用的現金。這個路徑平時看起來是備用選項，到了那個時刻，它是唯一選項。
+前提一樣：身份驗證要早做，介面要熟，不是等事情發生了才去摸索。戰爭爆發那天才臨時下載 App，已經太慢了。
+你讀完這篇，心裡有個聲音說「有道理，改天認真研究一下」。我知道，因為大多數人的反應都是這樣，然後他們繼續維持現在的配置，繼續做一樣的決策。
+問題不在於你懂不懂這些道理。
+問題在於：你的配置裡有沒有覆蓋到「尾部」。
+過去十年，COVID、烏俄戰爭、中東升溫、銀行擠兌、穩
+定幣脫鉤。每一次事件發生前，都有人說這種事不會發生，機率很低，不值得為它調整策略。他們說的沒有錯。機率確實低。但期望值是機率乘以損失幅度，不是只算機率。
+倖存者偏差的運作方式很安靜：在你遇到那個尾部事件之前，你的系統看起來一直都是對的。你活著，所以策略有效。直到有一天它突然無效。那天你才會明白這道數學是怎麼對你生效的。
+市場從不需要你相信它。
+它只需要時間。</t>
         </is>
       </c>
       <c r="J32" t="b">
         <v>0</v>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 9:02 AM UTC</t>
+          <t>Mar 25, 2026 · 1:05 PM UTC</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-03-24T09:02:00Z</t>
+          <t>2026-03-25T13:05:00Z</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/binancezh']</t>
         </is>
       </c>
       <c r="R32" t="n">
@@ -3324,7 +3316,7 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -3335,12 +3327,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2036367792195379613</t>
+          <t>2036789515558543658</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036367792195379613</t>
+          <t>https://x.com/Sosomostafa729S/status/2036789515558543658</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3366,12 +3358,12 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @parulghalout @parulghalout @Salma2232019</t>
+          <t>B- 1.89% @parulghalout @semeet @SelmaRomola</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+          <t>B- 1.89% &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J33" t="b">
@@ -3385,23 +3377,23 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 9:01 AM UTC</t>
+          <t>Mar 25, 2026 · 12:57 PM UTC</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-03-24T09:01:00Z</t>
+          <t>2026-03-25T12:57:00Z</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>['https://x.com/parulghalout', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/parulghalout', 'https://x.com/semeet', 'https://x.com/SelmaRomola']</t>
         </is>
       </c>
       <c r="R33" t="n">
@@ -3414,7 +3406,7 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -3425,12 +3417,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2036367691980873799</t>
+          <t>2036789451557609902</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036367691980873799</t>
+          <t>https://x.com/Sosomostafa729S/status/2036789451557609902</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3456,12 +3448,12 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @semeet @Salma2232019 @SelmaRomola</t>
+          <t>B- 1.89% @semeet @SelmaRomola @Emy191990</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
+          <t>B- 1.89% &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J34" t="b">
@@ -3475,23 +3467,23 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 9:01 AM UTC</t>
+          <t>Mar 25, 2026 · 12:57 PM UTC</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-03-24T09:01:00Z</t>
+          <t>2026-03-25T12:57:00Z</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/Salma2232019', 'https://x.com/SelmaRomola']</t>
+          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/Emy191990']</t>
         </is>
       </c>
       <c r="R34" t="n">
@@ -3504,7 +3496,7 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -3515,12 +3507,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2036367634590212403</t>
+          <t>2036789382523523230</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036367634590212403</t>
+          <t>https://x.com/Sosomostafa729S/status/2036789382523523230</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3546,12 +3538,12 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @Emy191990 @parulghalout @parulghalout</t>
+          <t>B- 1.89% @ibushra_03 @Emy191990 @Salma2232019</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
+          <t>B- 1.89% &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J35" t="b">
@@ -3565,23 +3557,23 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 9:00 AM UTC</t>
+          <t>Mar 25, 2026 · 12:56 PM UTC</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-03-24T09:00:00Z</t>
+          <t>2026-03-25T12:56:00Z</t>
         </is>
       </c>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/parulghalout']</t>
+          <t>['https://x.com/ibushra_03', 'https://x.com/Emy191990', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
       <c r="R35" t="n">
@@ -3594,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -3605,12 +3597,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2036367508480098434</t>
+          <t>2036789305784586495</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036367508480098434</t>
+          <t>https://x.com/Sosomostafa729S/status/2036789305784586495</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3636,12 +3628,12 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @semeet @Emy191990 @ibushra_03</t>
+          <t>B- 1.89% @Salma2232019 @SelmaRomola @Emy191990</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
+          <t>B- 1.89% &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J36" t="b">
@@ -3655,23 +3647,23 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 9:00 AM UTC</t>
+          <t>Mar 25, 2026 · 12:56 PM UTC</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-03-24T09:00:00Z</t>
+          <t>2026-03-25T12:56:00Z</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/Emy191990', 'https://x.com/ibushra_03']</t>
+          <t>['https://x.com/Salma2232019', 'https://x.com/SelmaRomola', 'https://x.com/Emy191990']</t>
         </is>
       </c>
       <c r="R36" t="n">
@@ -3684,7 +3676,7 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -3695,12 +3687,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2036367351269171519</t>
+          <t>2036789246493851944</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036367351269171519</t>
+          <t>https://x.com/Sosomostafa729S/status/2036789246493851944</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3726,12 +3718,12 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @Salma2232019 @Emy191990 @SelmaRomola</t>
+          <t>B- 1.89% @semeet @SelmaRomola @ibushra_03</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
+          <t>B- 1.89% &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J37" t="b">
@@ -3745,23 +3737,23 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 8:59 AM UTC</t>
+          <t>Mar 25, 2026 · 12:56 PM UTC</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-03-24T08:59:00Z</t>
+          <t>2026-03-25T12:56:00Z</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>['https://x.com/Salma2232019', 'https://x.com/Emy191990', 'https://x.com/SelmaRomola']</t>
+          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/ibushra_03']</t>
         </is>
       </c>
       <c r="R37" t="n">
@@ -3774,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -3785,12 +3777,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2036367170549195036</t>
+          <t>2036789179338920208</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036367170549195036</t>
+          <t>https://x.com/Sosomostafa729S/status/2036789179338920208</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3816,12 +3808,12 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @parulghalout @ibushra_03 @semeet</t>
+          <t>B- 1.89% @Emy191990 @ibushra_03 @parulghalout</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt;</t>
+          <t>B- 1.89% &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J38" t="b">
@@ -3835,23 +3827,23 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 8:59 AM UTC</t>
+          <t>Mar 25, 2026 · 12:55 PM UTC</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-03-24T08:59:00Z</t>
+          <t>2026-03-25T12:55:00Z</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>['https://x.com/parulghalout', 'https://x.com/ibushra_03', 'https://x.com/semeet']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
         </is>
       </c>
       <c r="R38" t="n">
@@ -3864,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -3875,12 +3867,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2036366933784928624</t>
+          <t>2036789007674482934</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036366933784928624</t>
+          <t>https://x.com/Sosomostafa729S/status/2036789007674482934</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3906,12 +3898,12 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD @semeet @Emy191990 @Salma2232019</t>
+          <t>Exchanger volunteer program @Emy191990 @Salma2232019 @semeet</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J39" t="b">
@@ -3925,23 +3917,23 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 8:58 AM UTC</t>
+          <t>Mar 25, 2026 · 12:55 PM UTC</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-03-24T08:58:00Z</t>
+          <t>2026-03-25T12:55:00Z</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/Emy191990', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
         </is>
       </c>
       <c r="R39" t="n">
@@ -3954,7 +3946,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -3965,12 +3957,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2036366860195909907</t>
+          <t>2036788941731577874</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036366860195909907</t>
+          <t>https://x.com/Sosomostafa729S/status/2036788941731577874</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3996,12 +3988,12 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD @semeet @SelmaRomola @parulghalout</t>
+          <t>Exchanger volunteer program @semeet @SelmaRomola @ibushra_03</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
+          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J40" t="b">
@@ -4015,23 +4007,23 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 8:57 AM UTC</t>
+          <t>Mar 25, 2026 · 12:55 PM UTC</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-03-24T08:57:00Z</t>
+          <t>2026-03-25T12:55:00Z</t>
         </is>
       </c>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/parulghalout']</t>
+          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/ibushra_03']</t>
         </is>
       </c>
       <c r="R40" t="n">
@@ -4044,7 +4036,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -4055,12 +4047,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2036366755782914242</t>
+          <t>2036788876954812619</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036366755782914242</t>
+          <t>https://x.com/Sosomostafa729S/status/2036788876954812619</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4086,12 +4078,12 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD @Emy191990 @ibushra_03 @parulghalout</t>
+          <t>Exchanger volunteer program @Emy191990 @parulghalout @ibushra_03</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
+          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J41" t="b">
@@ -4105,23 +4097,23 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 8:57 AM UTC</t>
+          <t>Mar 25, 2026 · 12:54 PM UTC</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-03-24T08:57:00Z</t>
+          <t>2026-03-25T12:54:00Z</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/ibushra_03']</t>
         </is>
       </c>
       <c r="R41" t="n">
@@ -4134,7 +4126,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -4145,12 +4137,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2036366520943816783</t>
+          <t>2036788786441629924</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036366520943816783</t>
+          <t>https://x.com/Sosomostafa729S/status/2036788786441629924</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4176,12 +4168,12 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @Emy191990 @parulghalout @ibushra_03</t>
+          <t>Exchanger volunteer program @semeet @Emy191990 @ibushra_03</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
+          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J42" t="b">
@@ -4195,23 +4187,23 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 8:56 AM UTC</t>
+          <t>Mar 25, 2026 · 12:54 PM UTC</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-03-24T08:56:00Z</t>
+          <t>2026-03-25T12:54:00Z</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/ibushra_03']</t>
+          <t>['https://x.com/semeet', 'https://x.com/Emy191990', 'https://x.com/ibushra_03']</t>
         </is>
       </c>
       <c r="R42" t="n">
@@ -4224,7 +4216,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -4235,12 +4227,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2036366461179212172</t>
+          <t>2036788720435962160</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036366461179212172</t>
+          <t>https://x.com/Sosomostafa729S/status/2036788720435962160</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4266,12 +4258,12 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @semeet @SelmaRomola @Salma2232019</t>
+          <t>Exchanger volunteer program @Salma2232019 @parulghalout @SelmaRomola</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+          <t>Exchanger volunteer program &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J43" t="b">
@@ -4285,23 +4277,23 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 8:56 AM UTC</t>
+          <t>Mar 25, 2026 · 12:54 PM UTC</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-03-24T08:56:00Z</t>
+          <t>2026-03-25T12:54:00Z</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/Salma2232019', 'https://x.com/parulghalout', 'https://x.com/SelmaRomola']</t>
         </is>
       </c>
       <c r="R43" t="n">
@@ -4314,7 +4306,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -4325,12 +4317,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2036366352638996520</t>
+          <t>2036788631269171518</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036366352638996520</t>
+          <t>https://x.com/Sosomostafa729S/status/2036788631269171518</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4356,12 +4348,12 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @Emy191990 @parulghalout @Salma2232019</t>
+          <t>Exchanger volunteer program @Emy191990 @parulghalout @SelmaRomola</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J44" t="b">
@@ -4375,23 +4367,23 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 8:55 AM UTC</t>
+          <t>Mar 25, 2026 · 12:53 PM UTC</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-03-24T08:55:00Z</t>
+          <t>2026-03-25T12:53:00Z</t>
         </is>
       </c>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/SelmaRomola']</t>
         </is>
       </c>
       <c r="R44" t="n">
@@ -4404,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -4415,12 +4407,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2036366238046363821</t>
+          <t>2036788436074631193</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036366238046363821</t>
+          <t>https://x.com/Sosomostafa729S/status/2036788436074631193</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4446,12 +4438,12 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @Emy191990 @parulghalout @SelmaRomola</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD @Salma2232019 @SelmaRomola @semeet</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J45" t="b">
@@ -4465,23 +4457,23 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 8:55 AM UTC</t>
+          <t>Mar 25, 2026 · 12:52 PM UTC</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-03-24T08:55:00Z</t>
+          <t>2026-03-25T12:52:00Z</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/SelmaRomola']</t>
+          <t>['https://x.com/Salma2232019', 'https://x.com/SelmaRomola', 'https://x.com/semeet']</t>
         </is>
       </c>
       <c r="R45" t="n">
@@ -4494,7 +4486,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -4505,12 +4497,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2036366176520118773</t>
+          <t>2036788367770435626</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036366176520118773</t>
+          <t>https://x.com/Sosomostafa729S/status/2036788367770435626</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4536,12 +4528,12 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @semeet @ibushra_03 @SelmaRomola</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD @semeet @SelmaRomola @Emy191990</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J46" t="b">
@@ -4555,23 +4547,23 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 8:55 AM UTC</t>
+          <t>Mar 25, 2026 · 12:52 PM UTC</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-03-24T08:55:00Z</t>
+          <t>2026-03-25T12:52:00Z</t>
         </is>
       </c>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/ibushra_03', 'https://x.com/SelmaRomola']</t>
+          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/Emy191990']</t>
         </is>
       </c>
       <c r="R46" t="n">
@@ -4584,7 +4576,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -4595,12 +4587,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2036366036120076489</t>
+          <t>2036788302997754337</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036366036120076489</t>
+          <t>https://x.com/Sosomostafa729S/status/2036788302997754337</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4626,12 +4618,12 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. @Emy191990 @semeet @parulghalout</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD @ibushra_03 @Emy191990 @Salma2232019</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Via the ENBD X Mobile App. &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J47" t="b">
@@ -4645,23 +4637,23 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 8:54 AM UTC</t>
+          <t>Mar 25, 2026 · 12:52 PM UTC</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-03-24T08:54:00Z</t>
+          <t>2026-03-25T12:52:00Z</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/semeet', 'https://x.com/parulghalout']</t>
+          <t>['https://x.com/ibushra_03', 'https://x.com/Emy191990', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
       <c r="R47" t="n">
@@ -4674,7 +4666,7 @@
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -4685,43 +4677,43 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2036364005779124312</t>
+          <t>2036788148525797451</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://x.com/FarazKhan11228/status/2036364005779124312</t>
+          <t>https://x.com/Sosomostafa729S/status/2036788148525797451</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://x.com/FarazKhan11228</t>
+          <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>FarazKhan11228</t>
+          <t>Sosomostafa729S</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Faraz Khan</t>
+          <t>Soha.mostafa77</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1758877091154583552/adAHM2jR_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>I am asking for the winners list, which is not being published</t>
+          <t>Through ENBD X Mobile Banking's App @SelmaRomola @semeet @parulghalout</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>I am asking for the winners list, which is not being published</t>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J48" t="b">
@@ -4735,23 +4727,27 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 8:46 AM UTC</t>
+          <t>Mar 25, 2026 · 12:51 PM UTC</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-03-24T08:46:00Z</t>
+          <t>2026-03-25T12:51:00Z</t>
         </is>
       </c>
       <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>['https://x.com/SelmaRomola', 'https://x.com/semeet', 'https://x.com/parulghalout']</t>
+        </is>
+      </c>
       <c r="R48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -4760,7 +4756,7 @@
         <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -4771,45 +4767,43 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2036353860705395115</t>
+          <t>2036788078598336738</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036353860705395115</t>
+          <t>https://x.com/Sosomostafa729S/status/2036788078598336738</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>Sosomostafa729S</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Soha.mostafa77</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Hi, please click the link below to know more about the winners.
-ms.spr.ly/6014Qs768</t>
+          <t>Through ENBD X Mobile Banking's App @Emy191990 @ibushra_03 @parulghalout</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Hi, please click the link below to know more about the winners.
-&lt;a href="http://ms.spr.ly/6014Qs768"&gt;ms.spr.ly/6014Qs768&lt;/a&gt;</t>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J49" t="b">
@@ -4818,32 +4812,32 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>['FarazKhan11228']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 8:06 AM UTC</t>
+          <t>Mar 25, 2026 · 12:51 PM UTC</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-03-24T08:06:00Z</t>
+          <t>2026-03-25T12:51:00Z</t>
         </is>
       </c>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>['http://ms.spr.ly/6014Qs768']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
         </is>
       </c>
       <c r="R49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -4852,7 +4846,7 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -4863,43 +4857,43 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2036345221831905561</t>
+          <t>2036787984134242571</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://x.com/msafrh79/status/2036345221831905561</t>
+          <t>https://x.com/Sosomostafa729S/status/2036787984134242571</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://x.com/msafrh79</t>
+          <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>msafrh79</t>
+          <t>Sosomostafa729S</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>mervet foad</t>
+          <t>Soha.mostafa77</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2027681283045003266/D4AYhe6v_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>مرحبا اين يتم اعلان الفائزين في مسابقة مواقع التواصل الاجتماعي؟؟ راسلتكم كثيرا على الخاص ومافي اي رد</t>
+          <t>Through ENBD X Mobile Banking's App @ibushra_03 @parulghalout @Salma2232019</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>مرحبا اين يتم اعلان الفائزين في مسابقة مواقع التواصل الاجتماعي؟؟ راسلتكم كثيرا على الخاص ومافي اي رد</t>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J50" t="b">
@@ -4913,21 +4907,25 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 7:31 AM UTC</t>
+          <t>Mar 25, 2026 · 12:51 PM UTC</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-03-24T07:31:00Z</t>
+          <t>2026-03-25T12:51:00Z</t>
         </is>
       </c>
       <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>['https://x.com/ibushra_03', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
+        </is>
+      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -4938,7 +4936,7 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -4949,43 +4947,43 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2036339891978793210</t>
+          <t>2036787923086106992</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://x.com/FarazKhan11228/status/2036339891978793210</t>
+          <t>https://x.com/Sosomostafa729S/status/2036787923086106992</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://x.com/FarazKhan11228</t>
+          <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>FarazKhan11228</t>
+          <t>Sosomostafa729S</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Faraz Khan</t>
+          <t>Soha.mostafa77</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1758877091154583552/adAHM2jR_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>What about millionaire account winners, i dont get any updates on that!!!</t>
+          <t>Through ENBD X Mobile Banking's App @semeet @SelmaRomola @Salma2232019</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>What about millionaire account winners, i dont get any updates on that!!!</t>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J51" t="b">
@@ -4999,23 +4997,27 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 7:10 AM UTC</t>
+          <t>Mar 25, 2026 · 12:50 PM UTC</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-03-24T07:10:00Z</t>
+          <t>2026-03-25T12:50:00Z</t>
         </is>
       </c>
       <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/Salma2232019']</t>
+        </is>
+      </c>
       <c r="R51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -5024,7 +5026,7 @@
         <v>0</v>
       </c>
       <c r="U51" t="n">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
@@ -5035,84 +5037,88 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2036328892919685283</t>
+          <t>2036787833776857213</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036328892919685283</t>
+          <t>https://x.com/Sosomostafa729S/status/2036787833776857213</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>Sosomostafa729S</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Soha.mostafa77</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>شهر جديد مع المزيد من الفائزين.
-تهانينا للفائز بالجائزة الكبرى وهي سيارة ROX 01، وللفائزين أيضًا بجائزة القطعة الذهبية بوزن 10 غرامات وذلك لاشتراكهم في حملة "حان وقت ربح جوائز كبرى" المقدمة من الخدمات المصرفية للأعمال لشهر يناير 2026.
-تابع استخدام حساب الأعمال الخاص بك لتنفيذ معاملات الصرف بالعملات الأجنبية وعمليات التمويل التجاري، لترفع فرص شركتك في الفوز.
-يسري العرض حتى 31 مارس 2026.</t>
+          <t>Through ENBD X Mobile Banking's App 
+@Emy191990 @ibushra_03 @parulghalout</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>شهر جديد مع المزيد من الفائزين.
-تهانينا للفائز بالجائزة الكبرى وهي سيارة ROX 01، وللفائزين أيضًا بجائزة القطعة الذهبية بوزن 10 غرامات وذلك لاشتراكهم في حملة &amp;#34;حان وقت ربح جوائز كبرى&amp;#34; المقدمة من الخدمات المصرفية للأعمال لشهر يناير 2026.
-تابع استخدام حساب الأعمال الخاص بك لتنفيذ معاملات الصرف بالعملات الأجنبية وعمليات التمويل التجاري، لترفع فرص شركتك في الفوز.
-يسري العرض حتى 31 مارس 2026.</t>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App 
+&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J52" t="b">
         <v>0</v>
       </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 6:26 AM UTC</t>
+          <t>Mar 25, 2026 · 12:50 PM UTC</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-03-24T06:26:00Z</t>
+          <t>2026-03-25T12:50:00Z</t>
         </is>
       </c>
       <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
+        </is>
+      </c>
       <c r="R52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>890</v>
+        <v>6</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -5123,49 +5129,43 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2036328801429336479</t>
+          <t>2036784089479741604</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036328801429336479</t>
+          <t>https://x.com/ay_140/status/2036784089479741604</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/ay_140</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>ay_140</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2027750913017094144/OvTR8OgR_bigger.jpg</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Another month. More winners.
-Congratulations to the ROX 01 grand prize winner and 10-gram gold winners from our Business Banking ‘Time to Win Big’ January 2026 draw.
-Continue using your Business Account for all your foreign exchange and trade finance transactions for a chance to win in the next draw.
-Offer is valid until 31 March 2026.</t>
+          <t>ما يحتاج تقرا التقرير بس تشوف اداء سهم ENBD واديب وبتعرف</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Another month. More winners.
-Congratulations to the ROX 01 grand prize winner and 10-gram gold winners from our Business Banking ‘Time to Win Big’ January 2026 draw.
-Continue using your Business Account for all your foreign exchange and trade finance transactions for a chance to win in the next draw.
-Offer is valid until 31 March 2026.</t>
+          <t>ما يحتاج تقرا التقرير بس تشوف اداء سهم ENBD واديب وبتعرف</t>
         </is>
       </c>
       <c r="J53" t="b">
@@ -5175,32 +5175,32 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 6:26 AM UTC</t>
+          <t>Mar 25, 2026 · 12:35 PM UTC</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-03-24T06:26:00Z</t>
+          <t>2026-03-25T12:35:00Z</t>
         </is>
       </c>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T53" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U53" t="n">
-        <v>701</v>
+        <v>980</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -5211,43 +5211,43 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2036322118611169669</t>
+          <t>2036777554435363023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036322118611169669</t>
+          <t>https://x.com/bno_cos21/status/2036777554435363023</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/bno_cos21</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>bno_cos21</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>紅尾</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1978076947768041472/SJW8V_vN_bigger.jpg</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>We are together against Fraud. @UAEBF #FightFraud #UAEBF #togetheragainstfraud #UnitedAgainstFraud</t>
+          <t>私のMBTI？はENBDチューブみたいなやつ</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>We are together against Fraud. &lt;a href="/UAEBF" title="UAE Banks Federation"&gt;@UAEBF&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FightFraud"&gt;#FightFraud&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAEBF"&gt;#UAEBF&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23togetheragainstfraud"&gt;#togetheragainstfraud&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;</t>
+          <t>私のMBTI？はENBDチューブみたいなやつ</t>
         </is>
       </c>
       <c r="J54" t="b">
@@ -5257,36 +5257,32 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 6:00 AM UTC</t>
+          <t>Mar 25, 2026 · 12:09 PM UTC</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-03-24T06:00:00Z</t>
+          <t>2026-03-25T12:09:00Z</t>
         </is>
       </c>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>['https://x.com/UAEBF', 'https://x.com/search?f=tweets&amp;q=%23FightFraud', 'https://x.com/search?f=tweets&amp;q=%23UAEBF', 'https://x.com/search?f=tweets&amp;q=%23togetheragainstfraud', 'https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud']</t>
-        </is>
-      </c>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="n">
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>591</v>
+        <v>60</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -5297,12 +5293,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2036300027933433945</t>
+          <t>2036765481072218459</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036300027933433945</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036765481072218459</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5328,14 +5324,18 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>مرحباً بك, شكراً لتواصلك معنا, يرجى العلم اننا غير قادرين على التواصل معك على الرسائل, يمكنك الاتصال بنا على 600540000 
-أو عن طريق التحدث معنا من خلال الواتساب البنكي على 600540000 من الساعة 9 صباحا الى 7 مساء</t>
+          <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach to us at 
+social@emiratesnbd.com
+Quoting case #988352 in the subject line of the email from your registered email address
+ We will make every effort to address the matter</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>مرحباً بك, شكراً لتواصلك معنا, يرجى العلم اننا غير قادرين على التواصل معك على الرسائل, يمكنك الاتصال بنا على 600540000 
-أو عن طريق التحدث معنا من خلال الواتساب البنكي على 600540000 من الساعة 9 صباحا الى 7 مساء</t>
+          <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach to us at 
+social@emiratesnbd.com
+Quoting case #988352 in the subject line of the email from your registered email address
+ We will make every effort to address the matter</t>
         </is>
       </c>
       <c r="J55" t="b">
@@ -5344,22 +5344,22 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>['AlyahiaMoh']</t>
+          <t>['Aamir44530491']</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Mar 24</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 4:32 AM UTC</t>
+          <t>Mar 25, 2026 · 11:21 AM UTC</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-03-24T04:32:00Z</t>
+          <t>2026-03-25T11:21:00Z</t>
         </is>
       </c>
       <c r="P55" t="inlineStr"/>
@@ -5374,7 +5374,7 @@
         <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -5385,43 +5385,43 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2036269961057018273</t>
+          <t>2036764114912268547</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://x.com/saimas89/status/2036269961057018273</t>
+          <t>https://x.com/Aamir44530491/status/2036764114912268547</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://x.com/saimas89</t>
+          <t>https://x.com/Aamir44530491</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>saimas89</t>
+          <t>Aamir44530491</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saima | صائمہ</t>
+          <t>Aamir</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1613505962098282497/lNPa9Or8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Can you not take another 7 days and give me the refund sooner? FYI I have paid using my ENBD card.</t>
+          <t>Dear My Enbd x app is not working I am not able to access my funds or not able to TRANSFER funds. Can you check and reply. Dubai</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Can you not take another 7 days and give me the refund sooner? FYI I have paid using my ENBD card.</t>
+          <t>Dear My Enbd x app is not working I am not able to access my funds or not able to TRANSFER funds. Can you check and reply. Dubai</t>
         </is>
       </c>
       <c r="J56" t="b">
@@ -5430,22 +5430,22 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>['flyspicejet']</t>
+          <t>['EmiratesNBD_AE', 'rihandagarwal']</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Mar 24</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 2:32 AM UTC</t>
+          <t>Mar 25, 2026 · 11:16 AM UTC</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-03-24T02:32:00Z</t>
+          <t>2026-03-25T11:16:00Z</t>
         </is>
       </c>
       <c r="P56" t="inlineStr"/>
@@ -5460,7 +5460,7 @@
         <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>31</v>
+        <v>92</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -5471,54 +5471,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2036410734163247450</t>
+          <t>2036751437909119306</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036410734163247450</t>
+          <t>https://x.com/ForbesME/status/2036751437909119306</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/ForbesME</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>ForbesME</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>فوربس الشرق الأوسط</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2033871674752339968/4leVeNHQ_bigger.jpg</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+          <t>الأصول المصرفية في #الإمارات تتخطى 5.4 تريليون درهم خلال يناير 2026، مع توسع الائتمان مدفوعًا بنمو الودائع المحلية وزيادة التمويل الموجه للاقتصاد.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+          <t>الأصول المصرفية في &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات"&gt;#الإمارات&lt;/a&gt; تتخطى 5.4 تريليون درهم خلال يناير 2026، مع توسع الائتمان مدفوعًا بنمو الودائع المحلية وزيادة التمويل الموجه للاقتصاد.</t>
         </is>
       </c>
       <c r="J57" t="b">
         <v>0</v>
       </c>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>['Abdulla40446316']</t>
-        </is>
-      </c>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>17h</t>
@@ -5526,74 +5522,80 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 11:52 AM UTC</t>
+          <t>Mar 25, 2026 · 10:25 AM UTC</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-03-24T11:52:00Z</t>
+          <t>2026-03-25T10:25:00Z</t>
         </is>
       </c>
       <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23الإمارات']</t>
+        </is>
+      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="U57" t="n">
-        <v>13</v>
+        <v>4363</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2036399322183442876</t>
+          <t>2036744671699804303</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036399322183442876</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036744671699804303</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>نشكركم على اهتمامكم بمنتجاتنا، يرجى زيارة الرابط أدناه وتعبئة بياناتكم، وسيتواصل معكم فريق المبيعات لدينا خلال يومي عمل. الحد الأدنى للراتب المطلوب هو 5000 درهم إماراتي. شكرًا - زبير
+beta.emiratesnbd.com/en/Camp…</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>نشكركم على اهتمامكم بمنتجاتنا، يرجى زيارة الرابط أدناه وتعبئة بياناتكم، وسيتواصل معكم فريق المبيعات لدينا خلال يومي عمل. الحد الأدنى للراتب المطلوب هو 5000 درهم إماراتي. شكرًا - زبير
+&lt;a href="https://beta.emiratesnbd.com/en/Campaigns/social-media-apply?SOURCE=&amp;amp;REF&amp;amp;ref=legacy&amp;amp;legacy_redirect=true"&gt;beta.emiratesnbd.com/en/Camp…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J58" t="b">
@@ -5602,7 +5604,7 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>['acroboatic']</t>
+          <t>['saudigamdi07']</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5612,16 +5614,20 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 11:06 AM UTC</t>
+          <t>Mar 25, 2026 · 9:59 AM UTC</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-03-24T11:06:00Z</t>
+          <t>2026-03-25T09:59:00Z</t>
         </is>
       </c>
       <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>['https://beta.emiratesnbd.com/en/Campaigns/social-media-apply?SOURCE=&amp;REF&amp;ref=legacy&amp;legacy_redirect=true']</t>
+        </is>
+      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -5632,65 +5638,63 @@
         <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2036399290717704546</t>
+          <t>2036743492840423459</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036399290717704546</t>
+          <t>https://x.com/Bnok24/status/2036743492840423459</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/Bnok24</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Bnok24</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>bnok 24</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2035297929708113920/61ymWMLp_bigger.jpg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>خدمة #Apple_Pay من #بنك_الإمارات_دبي الوطني تتيح الدفع بسهولة وأمان من خلال #Apple_Wallet أو #iPhone 
+التفاصيل|  bnok24.com/?p=255133</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>خدمة &lt;a href="/search?f=tweets&amp;amp;q=%23Apple_Pay"&gt;#Apple_Pay&lt;/a&gt; من &lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_دبي"&gt;#بنك_الإمارات_دبي&lt;/a&gt; الوطني تتيح الدفع بسهولة وأمان من خلال &lt;a href="/search?f=tweets&amp;amp;q=%23Apple_Wallet"&gt;#Apple_Wallet&lt;/a&gt; أو &lt;a href="/search?f=tweets&amp;amp;q=%23iPhone"&gt;#iPhone&lt;/a&gt; 
+التفاصيل|  &lt;a href="https://www.bnok24.com/?p=255133"&gt;bnok24.com/?p=255133&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J59" t="b">
         <v>0</v>
       </c>
       <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>['acroboatic']</t>
-        </is>
-      </c>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
           <t>18h</t>
@@ -5698,16 +5702,20 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 11:06 AM UTC</t>
+          <t>Mar 25, 2026 · 9:54 AM UTC</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-03-24T11:06:00Z</t>
+          <t>2026-03-25T09:54:00Z</t>
         </is>
       </c>
       <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23Apple_Pay', 'https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_دبي', 'https://x.com/search?f=tweets&amp;q=%23Apple_Wallet', 'https://x.com/search?f=tweets&amp;q=%23iPhone', 'https://www.bnok24.com/?p=255133']</t>
+        </is>
+      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -5718,90 +5726,86 @@
         <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2036385610118623239</t>
+          <t>2036731298304196880</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036385610118623239</t>
+          <t>https://x.com/saudigamdi07/status/2036731298304196880</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/saudigamdi07</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>saudigamdi07</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>ملاكي</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships
-📅Offer valid till 31 March 2026.
-Terms &amp; Conditions apply.
-emiratesislamic.ae/en/offers…</t>
+          <t>يقولو نسبكم في الامويل الشخصي ممتازة وتصل الى واحد ونصف لبعض الجهات 
+ابي استفسر عن كيف احصل ع خدمة شراء المديونية لمنتج البناء ذاتي القرض مدعوم</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships
-📅Offer valid till 31 March 2026.
-Terms &amp;amp; Conditions apply.
-&lt;a href="https://www.emiratesislamic.ae/en/offers/auto-finance-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=af"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
+          <t>يقولو نسبكم في الامويل الشخصي ممتازة وتصل الى واحد ونصف لبعض الجهات 
+ابي استفسر عن كيف احصل ع خدمة شراء المديونية لمنتج البناء ذاتي القرض مدعوم</t>
         </is>
       </c>
       <c r="J60" t="b">
         <v>0</v>
       </c>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 10:12 AM UTC</t>
+          <t>Mar 25, 2026 · 9:05 AM UTC</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2026-03-24T10:12:00Z</t>
+          <t>2026-03-25T09:05:00Z</t>
         </is>
       </c>
       <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesislamic.ae/en/offers/auto-finance-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=af']</t>
-        </is>
-      </c>
+      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -5810,58 +5814,58 @@
         <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>55</v>
+        <v>179</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2036385607883034826</t>
+          <t>2036730808556490908</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036385607883034826</t>
+          <t>https://x.com/omarzooqi/status/2036730808556490908</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/omarzooqi</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>omarzooqi</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Omar Almarzooqi</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2035997907485429760/QlpL3FpP_bigger.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Drive home your dream car with Emirates Islamic Auto Finance!
-📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)
-📅Payment holiday of up to 6 months</t>
+          <t>Connections are the real currency in Dubai 💼✨
+Had a great meeting at Emirates NBD – Al Satwa branch with Sameer Mohammed Al Bastaki.
+#DubaiBusiness #UAEBanking #NetworkingDubai #EmiratesNBD #dubailife</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Drive home your dream car with Emirates Islamic Auto Finance!
-📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.)
-📅Payment holiday of up to 6 months</t>
+          <t>Connections are the real currency in Dubai 💼✨
+Had a great meeting at Emirates NBD – Al Satwa branch with Sameer Mohammed Al Bastaki.
+&lt;a href="/search?f=tweets&amp;amp;q=%23DubaiBusiness"&gt;#DubaiBusiness&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAEBanking"&gt;#UAEBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NetworkingDubai"&gt;#NetworkingDubai&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23dubailife"&gt;#dubailife&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J61" t="b">
@@ -5871,92 +5875,102 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 10:12 AM UTC</t>
+          <t>Mar 25, 2026 · 9:04 AM UTC</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-03-24T10:12:00Z</t>
+          <t>2026-03-25T09:04:00Z</t>
         </is>
       </c>
       <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23DubaiBusiness', 'https://x.com/search?f=tweets&amp;q=%23UAEBanking', 'https://x.com/search?f=tweets&amp;q=%23NetworkingDubai', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23dubailife']</t>
+        </is>
+      </c>
       <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
         <v>1</v>
       </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
       <c r="U61" t="n">
-        <v>88</v>
+        <v>35</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2036382130784047605</t>
+          <t>2036727881976484208</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036382130784047605</t>
+          <t>https://x.com/hashim_fahmawi/status/2036727881976484208</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/hashim_fahmawi</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>hashim_fahmawi</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>المحلل الاقتصادي / هاشم الفحماوي</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1626339625345114112/dFHYINOP_bigger.jpg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
-📅يسري لغاية 31 مارس 2026.
-تطبق الشروط والأحكام.
-emiratesislamic.ae/ar/offers…</t>
+          <t>#اعمار
+#اعمار_للتطوير
+#بنك_الامارات 
+تفرغة المؤشرات واضحه .
+ننتظر ارتفاع الشركات التى لم تتفاعل مع ارتفاع المؤشر.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
-📅يسري لغاية 31 مارس 2026.
-تطبق الشروط والأحكام.
-&lt;a href="https://www.emiratesislamic.ae/ar/offers/auto-finance-offer?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=af"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23اعمار"&gt;#اعمار&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23اعمار_للتطوير"&gt;#اعمار_للتطوير&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الامارات"&gt;#بنك_الامارات&lt;/a&gt; 
+تفرغة المؤشرات واضحه .
+ننتظر ارتفاع الشركات التى لم تتفاعل مع ارتفاع المؤشر.</t>
         </is>
       </c>
       <c r="J62" t="b">
         <v>0</v>
       </c>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>['hashim_fahmawi']</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
           <t>19h</t>
@@ -5964,18 +5978,18 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 9:58 AM UTC</t>
+          <t>Mar 25, 2026 · 8:52 AM UTC</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-03-24T09:58:00Z</t>
+          <t>2026-03-25T08:52:00Z</t>
         </is>
       </c>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>['https://www.emiratesislamic.ae/ar/offers/auto-finance-offer?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=af']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23اعمار', 'https://x.com/search?f=tweets&amp;q=%23اعمار_للتطوير', 'https://x.com/search?f=tweets&amp;q=%23بنك_الامارات']</t>
         </is>
       </c>
       <c r="R62" t="n">
@@ -5985,61 +5999,61 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U62" t="n">
-        <v>56</v>
+        <v>1531</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2036382128359751773</t>
+          <t>2036716463508291618</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036382128359751773</t>
+          <t>https://x.com/talent_folder/status/2036716463508291618</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/talent_folder</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>talent_folder</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Talentfolder</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1785222859268218880/QKe4zDoG_bigger.jpg</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
-📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً)
-📅فترة سماح السداد تصل إلى 6 أشهر</t>
+          <t>Open Your Bank Account in Dubai Easily
+Looking to open a bank account in Dubai? We make it simple, fast, and stress-free!
+Whether you're a resident, investor, or business owner, our experts help you open accounts with top UAE banks like ADCB, FAB, Emirates NBD, and more.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
-📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً)
-📅فترة سماح السداد تصل إلى 6 أشهر</t>
+          <t>Open Your Bank Account in Dubai Easily
+Looking to open a bank account in Dubai? We make it simple, fast, and stress-free!
+Whether you&amp;#39;re a resident, investor, or business owner, our experts help you open accounts with top UAE banks like ADCB, FAB, Emirates NBD, and more.</t>
         </is>
       </c>
       <c r="J63" t="b">
@@ -6054,18 +6068,18 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 9:58 AM UTC</t>
+          <t>Mar 25, 2026 · 8:06 AM UTC</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-03-24T09:58:00Z</t>
+          <t>2026-03-25T08:06:00Z</t>
         </is>
       </c>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -6074,56 +6088,58 @@
         <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2036353357435248836</t>
+          <t>2036715367096066528</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://x.com/acroboatic/status/2036353357435248836</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036715367096066528</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://x.com/acroboatic</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>acroboatic</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>saudaaaas</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/536089004978884608/PVIgXDs5_bigger.jpeg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Thanks
-I have followed your page now</t>
+          <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach to us at
+social@emiratesnbd.com
+ Quoting case 988205 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Thanks
-I have followed your page now</t>
+          <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach to us at
+social@emiratesnbd.com
+ Quoting case 988205 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
         </is>
       </c>
       <c r="J64" t="b">
@@ -6132,22 +6148,22 @@
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>['emiratesislamic']</t>
+          <t>['rihandagarwal']</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 8:04 AM UTC</t>
+          <t>Mar 25, 2026 · 8:02 AM UTC</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>2026-03-24T08:04:00Z</t>
+          <t>2026-03-25T08:02:00Z</t>
         </is>
       </c>
       <c r="P64" t="inlineStr"/>
@@ -6162,86 +6178,84 @@
         <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2036352538568802661</t>
+          <t>2036713554930491654</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://x.com/acroboatic/status/2036352538568802661</t>
+          <t>https://x.com/rihandagarwal/status/2036713554930491654</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://x.com/acroboatic</t>
+          <t>https://x.com/rihandagarwal</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>acroboatic</t>
+          <t>rihandagarwal</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>saudaaaas</t>
+          <t>Rihand Agarwal</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/536089004978884608/PVIgXDs5_bigger.jpeg</t>
+          <t>https://pbs.twimg.com/profile_images/1672415803457818624/qXizRa0Q_bigger.jpg</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Hi, happy to connect.
-I didn’t receive your DM, and my replies don’t seem to be going through either. Not sure if there’s a technical issue.
-I’m available now, please feel free to message</t>
+          <t>@EmiratesNBD_AE I have now been trying to access my ENBDX mobile app AND my funds for the past 2 weeks without success. 
+Due to a technical issue on your end, my login credentials were erased 2 weeks ago. Since then, I have tried multiple calls. This is unacceptable from you.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Hi, happy to connect.
-I didn’t receive your DM, and my replies don’t seem to be going through either. Not sure if there’s a technical issue.
-I’m available now, please feel free to message</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; I have now been trying to access my ENBDX mobile app AND my funds for the past 2 weeks without success. 
+Due to a technical issue on your end, my login credentials were erased 2 weeks ago. Since then, I have tried multiple calls. This is unacceptable from you.</t>
         </is>
       </c>
       <c r="J65" t="b">
         <v>0</v>
       </c>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 8:00 AM UTC</t>
+          <t>Mar 25, 2026 · 7:55 AM UTC</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-03-24T08:00:00Z</t>
+          <t>2026-03-25T07:55:00Z</t>
         </is>
       </c>
       <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="R65" t="n">
         <v>1</v>
       </c>
@@ -6249,57 +6263,57 @@
         <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U65" t="n">
         <v>17</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2036331891541127358</t>
+          <t>2036700769617887531</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://x.com/Ben252024/status/2036331891541127358</t>
+          <t>https://x.com/motsafeh057/status/2036700769617887531</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://x.com/Ben252024</t>
+          <t>https://x.com/motsafeh057</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Ben252024</t>
+          <t>motsafeh057</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>متصفح وقارئ للأخبار</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1996323967443881984/qDVGWeO0_bigger.jpg</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>When ?</t>
+          <t>0570500894</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>When ?</t>
+          <t>0570500894</t>
         </is>
       </c>
       <c r="J66" t="b">
@@ -6308,22 +6322,22 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>['emiratesislamic']</t>
+          <t>['EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 6:38 AM UTC</t>
+          <t>Mar 25, 2026 · 7:04 AM UTC</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2026-03-24T06:38:00Z</t>
+          <t>2026-03-25T07:04:00Z</t>
         </is>
       </c>
       <c r="P66" t="inlineStr"/>
@@ -6338,82 +6352,86 @@
         <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2036319304132473271</t>
+          <t>2036700638353191376</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036319304132473271</t>
+          <t>https://x.com/letstalkdubai/status/2036700638353191376</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/letstalkdubai</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>letstalkdubai</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Let's Talk Dubai</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526561120164921344/W-lU0fbd_bigger.png</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>#UAE Business &amp; Economy Headlines
+25 March 2026    
+#MiddleEast   Full Report:  infoblaze.com/news/details/1…</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; Business &amp;amp; Economy Headlines
+25 March 2026    
+&lt;a href="/search?f=tweets&amp;amp;q=%23MiddleEast"&gt;#MiddleEast&lt;/a&gt;   Full Report:  &lt;a href="http://infoblaze.com/news/details/117057"&gt;infoblaze.com/news/details/1…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J67" t="b">
         <v>0</v>
       </c>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>['wasishion']</t>
-        </is>
-      </c>
+      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 5:48 AM UTC</t>
+          <t>Mar 25, 2026 · 7:04 AM UTC</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-03-24T05:48:00Z</t>
+          <t>2026-03-25T07:04:00Z</t>
         </is>
       </c>
       <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23MiddleEast', 'http://infoblaze.com/news/details/117057']</t>
+        </is>
+      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -6421,57 +6439,57 @@
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2036313897985020336</t>
+          <t>2036700495067127889</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036313897985020336</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2036700495067127889</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>EmiratesNBD KSA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message rule (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال الهاتف الخاص بك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message rule (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال الهاتف الخاص بك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
       <c r="J68" t="b">
@@ -6480,22 +6498,22 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>['acroboatic']</t>
+          <t>['motsafeh057']</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 5:27 AM UTC</t>
+          <t>Mar 25, 2026 · 7:03 AM UTC</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-03-24T05:27:00Z</t>
+          <t>2026-03-25T07:03:00Z</t>
         </is>
       </c>
       <c r="P68" t="inlineStr"/>
@@ -6510,54 +6528,54 @@
         <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2036313593797288395</t>
+          <t>2036696100367704134</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036313593797288395</t>
+          <t>https://x.com/motsafeh057/status/2036696100367704134</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/motsafeh057</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>motsafeh057</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>متصفح وقارئ للأخبار</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1996323967443881984/qDVGWeO0_bigger.jpg</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>اليوم محاوله من عدة محاولات لفتح حساب من عدة طرق سواء بالمتصفح او التطبيق او عن طريق الفرع وجاتني الرساله الاخيره تحت</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>اليوم محاوله من عدة محاولات لفتح حساب من عدة طرق سواء بالمتصفح او التطبيق او عن طريق الفرع وجاتني الرساله الاخيره تحت</t>
         </is>
       </c>
       <c r="J69" t="b">
@@ -6566,28 +6584,28 @@
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>['acroboatic']</t>
+          <t>['EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Mar 24, 2026 · 5:26 AM UTC</t>
+          <t>Mar 25, 2026 · 6:46 AM UTC</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>2026-03-24T05:26:00Z</t>
+          <t>2026-03-25T06:46:00Z</t>
         </is>
       </c>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -6596,95 +6614,1101 @@
         <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>EI</t>
+          <t>ENBD</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2036313549929107798</t>
+          <t>2036684502588588270</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2036313549929107798</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2036684502588588270</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>Because Your Mornings Deserve Better
+Apply for the Emirates NBD noon One Visa Credit Card and De’Longhi LA SPECIALISTA ARTE EVO Espresso Machine could be yours.
+What’s more?
+AED 500 welcome bonus
+1-year free noon One membership &amp; 50% thereafter
+Up to 20% back as noon credits on spends across all noon platforms
+Offer is valid until 31 March 2026.
+emiratesnbd.com/en/campaigns…</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>Because Your Mornings Deserve Better
+Apply for the Emirates NBD noon One Visa Credit Card and De’Longhi LA SPECIALISTA ARTE EVO Espresso Machine could be yours.
+What’s more?
+AED 500 welcome bonus
+1-year free noon One membership &amp;amp; 50% thereafter
+Up to 20% back as noon credits on spends across all noon platforms
+Offer is valid until 31 March 2026.
+&lt;a href="https://www.emiratesnbd.com/en/campaigns/noon-one-credit-card"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J70" t="b">
         <v>0</v>
       </c>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>['acroboatic']</t>
-        </is>
-      </c>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Mar 25, 2026 · 5:59 AM UTC</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>2026-03-25T05:59:00Z</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesnbd.com/en/campaigns/noon-one-credit-card']</t>
+        </is>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3</v>
+      </c>
+      <c r="U70" t="n">
+        <v>526</v>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2036665227840803080</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2036665227840803080</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Thanks for writing to us, kindly note that we have replied to your email</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Thanks for writing to us, kindly note that we have replied to your email</t>
+        </is>
+      </c>
+      <c r="J71" t="b">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>['ZahidanMuhamma']</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
           <t>23h</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>Mar 24, 2026 · 5:25 AM UTC</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>2026-03-24T05:25:00Z</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="n">
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Mar 25, 2026 · 4:43 AM UTC</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>2026-03-25T04:43:00Z</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>21</v>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2036654307596992707</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2036654307596992707</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Your financial tip of the week
+#FinancialWellbeing #EmiratesNBDTips #SmartMoney #FinWell</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Your financial tip of the week
+&lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBDTips"&gt;#EmiratesNBDTips&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoney"&gt;#SmartMoney&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinWell"&gt;#FinWell&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J72" t="b">
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Mar 25</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Mar 25, 2026 · 4:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>2026-03-25T04:00:00Z</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBDTips', 'https://x.com/search?f=tweets&amp;q=%23SmartMoney', 'https://x.com/search?f=tweets&amp;q=%23FinWell']</t>
+        </is>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>527</v>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2036654307383111761</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2036654307383111761</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>نصيحتك المالية لهذا الأسبوع
+#FinancialWellbeing #EmiratesNBDTips #FinWell #SmartMoney</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>نصيحتك المالية لهذا الأسبوع
+&lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBDTips"&gt;#EmiratesNBDTips&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinWell"&gt;#FinWell&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoney"&gt;#SmartMoney&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Mar 25</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Mar 25, 2026 · 4:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>2026-03-25T04:00:00Z</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBDTips', 'https://x.com/search?f=tweets&amp;q=%23FinWell', 'https://x.com/search?f=tweets&amp;q=%23SmartMoney']</t>
+        </is>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>462</v>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2036879879950786787</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://x.com/centralbankuae/status/2036879879950786787</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://x.com/centralbankuae</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>centralbankuae</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Central Bank of the UAE</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2013084633873747968/H63zAIGY_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Dear Consumer
+Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
+For any information or to file a complaint, please contact @SanadakUAE, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: sanadak.gov.ae/en 
+Best regards,
+Central Bank of the UAE</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Dear Consumer
+Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
+For any information or to file a complaint, please contact &lt;a href="/SanadakUAE" title="Sanadak"&gt;@SanadakUAE&lt;/a&gt;, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: &lt;a href="https://www.sanadak.gov.ae/en"&gt;sanadak.gov.ae/en&lt;/a&gt; 
+Best regards,
+Central Bank of the UAE</t>
+        </is>
+      </c>
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>['abuzubayr1987', 'emiratesislamic', 'JamalIslamic']</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>9h</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Mar 25, 2026 · 6:56 PM UTC</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>2026-03-25T18:56:00Z</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>['https://x.com/SanadakUAE', 'https://www.sanadak.gov.ae/en']</t>
+        </is>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>14</v>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2036838112907972926</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://x.com/Tiamat531229675/status/2036838112907972926</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://x.com/Tiamat531229675</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Tiamat531229675</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Tiamat</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1650968397432373248/bTVP9Hqc_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>If you consider the Emirates Islamic cool.
+I think all muslim societies should be that way.
+I never said I disliked it.
+I advocate for it.
+I only go through muslim X and see them horrified by the Emirates allowing 'unIslamic' laws being allowed.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>If you consider the Emirates Islamic cool.
+I think all muslim societies should be that way.
+I never said I disliked it.
+I advocate for it.
+I only go through muslim X and see them horrified by the Emirates allowing &amp;#39;unIslamic&amp;#39; laws being allowed.</t>
+        </is>
+      </c>
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>['KarrDriver', 'WallStreetMav', 'EndWokeness']</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>11h</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Mar 25, 2026 · 4:10 PM UTC</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>2026-03-25T16:10:00Z</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="n">
         <v>1</v>
       </c>
-      <c r="S70" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" t="n">
-        <v>22</v>
-      </c>
-      <c r="V70" t="inlineStr">
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>7</v>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2036821858868416788</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://x.com/abuzubayr1987/status/2036821858868416788</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://x.com/abuzubayr1987</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>abuzubayr1987</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Safwan</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>@centralbankuae 
+I am left in a precarious situation having no living expenses for the coming weeks after @emiratesislamic bank deducted 100% against my credit card dues without notice. After having a call they have been inconsiderate over my situation.
+@JamalIslamic</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>&lt;a href="/centralbankuae" title="Central Bank of the UAE"&gt;@centralbankuae&lt;/a&gt; 
+I am left in a precarious situation having no living expenses for the coming weeks after &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; bank deducted 100% against my credit card dues without notice. After having a call they have been inconsiderate over my situation.
+&lt;a href="/JamalIslamic" title="JAMAL BIN GHALIATA (CEO EMIRATES ISLAMIC BANK)"&gt;@JamalIslamic&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>12h</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Mar 25, 2026 · 3:05 PM UTC</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>2026-03-25T15:05:00Z</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>['https://x.com/centralbankuae', 'https://x.com/emiratesislamic', 'https://x.com/JamalIslamic']</t>
+        </is>
+      </c>
+      <c r="R76" t="n">
+        <v>1</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>7</v>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2036796287182647587</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://x.com/dhara_katariya/status/2036796287182647587</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://x.com/dhara_katariya</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>dhara_katariya</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Dhara Katariya</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1205157338639978497/HK2x6jCp_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>@Maersk maersk kanoo emirates why dont you check with your bank why you didn't received it? Your executives saying we didnt received 100 times but atleast for once ask your bank. Your client is stressed.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>&lt;a href="/Maersk" title="Maersk"&gt;@Maersk&lt;/a&gt; maersk kanoo emirates why dont you check with your bank why you didn&amp;#39;t received it? Your executives saying we didnt received 100 times but atleast for once ask your bank. Your client is stressed.</t>
+        </is>
+      </c>
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>['dhara_katariya', 'emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Mar 25, 2026 · 1:24 PM UTC</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>2026-03-25T13:24:00Z</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>['https://x.com/Maersk']</t>
+        </is>
+      </c>
+      <c r="R77" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>13</v>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2036794106270413038</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://x.com/dhara_katariya/status/2036794106270413038</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://x.com/dhara_katariya</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>dhara_katariya</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Dhara Katariya</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1205157338639978497/HK2x6jCp_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>@emiratesislamic A transaction was made from palsun maritime LLC to MAERSK KANOO EMIRATES LLC on 19th mar 2026 of usd 30301$
+ ETE ID EPHCOP07809C8DTA
+The amount is debited but maersk kanoo didn't received it. We dont have any revert from the bank where the payment is .Resolve it</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; A transaction was made from palsun maritime LLC to MAERSK KANOO EMIRATES LLC on 19th mar 2026 of usd 30301$
+ ETE ID EPHCOP07809C8DTA
+The amount is debited but maersk kanoo didn&amp;#39;t received it. We dont have any revert from the bank where the payment is .Resolve it</t>
+        </is>
+      </c>
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>14h</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Mar 25, 2026 · 1:15 PM UTC</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>2026-03-25T13:15:00Z</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>['https://x.com/emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="R78" t="n">
+        <v>1</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="n">
+        <v>12</v>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2036783540419903727</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036783540419903727</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Flight cancelled and awaiting a refund? Fraudsters use this opportunity to scam. Pause before clicking any link, verify the source, and stay alert.
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Flight cancelled and awaiting a refund? Fraudsters use this opportunity to scam. Pause before clicking any link, verify the source, and stay alert.
+Do not fall for the traps. Stay alert to scams.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
+&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J79" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Mar 25, 2026 · 12:33 PM UTC</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>2026-03-25T12:33:00Z</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud']</t>
+        </is>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>72</v>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2036783538087850447</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2036783538087850447</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>هل تم إلغاء رحلتك وتنتظر استرداد المبلغ؟ يستغل المحتالون هذه الفرصة للاحتيال. توقف قبل الضغط على أي رابط، وتحقق من المصدر، وانتبه للإشارات التحذيرية.
+لا تقع في الفخ. احذر الاحتيال.
+#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>هل تم إلغاء رحلتك وتنتظر استرداد المبلغ؟ يستغل المحتالون هذه الفرصة للاحتيال. توقف قبل الضغط على أي رابط، وتحقق من المصدر، وانتبه للإشارات التحذيرية.
+لا تقع في الفخ. احذر الاحتيال.
+&lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.</t>
+        </is>
+      </c>
+      <c r="J80" t="b">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Mar 25, 2026 · 12:33 PM UTC</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>2026-03-25T12:33:00Z</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال']</t>
+        </is>
+      </c>
+      <c r="R80" t="n">
+        <v>1</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="n">
+        <v>140</v>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2036732548290891833</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://x.com/AirIndiaX/status/2036732548290891833</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://x.com/AirIndiaX</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AirIndiaX</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Air India Express</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1937212217578983424/vF-DUPT9_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Since the booking is done through Air India, we request you to please reach out to them for any assistance.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Since the booking is done through Air India, we request you to please reach out to them for any assistance.</t>
+        </is>
+      </c>
+      <c r="J81" t="b">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>['naanrdk', 'emiratesislamic', 'airindia']</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Mar 25, 2026 · 9:10 AM UTC</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>2026-03-25T09:10:00Z</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="n">
+        <v>1</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>0</v>
+      </c>
+      <c r="U81" t="n">
+        <v>47</v>
+      </c>
+      <c r="V81" t="inlineStr">
         <is>
           <t>EI</t>
         </is>

--- a/EI_ENBD_3post.xlsx
+++ b/EI_ENBD_3post.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V81"/>
+  <dimension ref="A1:V56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,45 +543,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2037012056881180890</t>
+          <t>2037318670750281886</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://x.com/kamal_Zamalek/status/2037012056881180890</t>
+          <t>https://x.com/babanasseralgh/status/2037318670750281886</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/kamal_Zamalek</t>
+          <t>https://x.com/babanasseralgh</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>kamal_Zamalek</t>
+          <t>babanasseralgh</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>محمد_صبري</t>
+          <t>لفقيدي والدي</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1989277397472972800/0TJHAbxy_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1645878730496114688/ejU13FCo_bigger.jpg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>غريبه ان بنك زي ده بيرعي فريق محدش بيتفرج عاليه وف نفس الوقت مفيش اي بنك مسموح ليه يرعي الزمالك ولا الاسماعيلي ولا اي فريق جماهيري 
-والكلام عن شركه WE اللي كانت هترعي الاسماعيلي وبعدين الموضوع اتلغي نادي الإسماعيلي بيشحت وهينزل درجه تانيه</t>
+          <t>@EmiratesNBD_AE السلام عليكم 
+وصلاتني رساله من شخص يقول اني فزت معاه وارسلي ايصال الحواله وقال تستغرق ٧ ايام هل صحيح ممكن اعطيكم ايصال الحواله</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>غريبه ان بنك زي ده بيرعي فريق محدش بيتفرج عاليه وف نفس الوقت مفيش اي بنك مسموح ليه يرعي الزمالك ولا الاسماعيلي ولا اي فريق جماهيري 
-والكلام عن شركه WE اللي كانت هترعي الاسماعيلي وبعدين الموضوع اتلغي نادي الإسماعيلي بيشحت وهينزل درجه تانيه</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; السلام عليكم 
+وصلاتني رساله من شخص يقول اني فزت معاه وارسلي ايصال الحواله وقال تستغرق ٧ ايام هل صحيح ممكن اعطيكم ايصال الحواله</t>
         </is>
       </c>
       <c r="J2" t="b">
@@ -591,21 +591,25 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>21m</t>
+          <t>4h</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Mar 26, 2026 · 3:41 AM UTC</t>
+          <t>Mar 26, 2026 · 11:59 PM UTC</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-03-26T03:41:00Z</t>
+          <t>2026-03-26T23:59:00Z</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -616,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -627,67 +631,79 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2036918641149829234</t>
+          <t>2037210917356921244</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://x.com/MultibaggAI/status/2036918641149829234</t>
+          <t>https://x.com/SelmaRomola/status/2037210917356921244</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/MultibaggAI</t>
+          <t>https://x.com/SelmaRomola</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MultibaggAI</t>
+          <t>SelmaRomola</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>multibagg.ai</t>
+          <t>Selma Romola</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2017665342756294656/o62zwaRv_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1118152018995105792/5fyZOTth_bigger.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>RBLBANK: EMIRATES NBD INFORMED RBL BANK THAT UAE CENTRAL BANK HAS APPROVED ITS PROPOSED ACQUISITION OF A MAJORITY STAKE IN RBL AND AMALGAMATION OF EMIRATES NBD'S INDIA OPERATIONS INTO RBL, SUBJECT TO REQUISITE APPROVALS.</t>
+          <t>Mutual fund/ Investment Fund
+#ENBDRiddleOfTheWeek 
+#financialwellbeing</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>RBLBANK: EMIRATES NBD INFORMED RBL BANK THAT UAE CENTRAL BANK HAS APPROVED ITS PROPOSED ACQUISITION OF A MAJORITY STAKE IN RBL AND AMALGAMATION OF EMIRATES NBD&amp;#39;S INDIA OPERATIONS INTO RBL, SUBJECT TO REQUISITE APPROVALS.</t>
+          <t>Mutual fund/ Investment Fund
+&lt;a href="/search?f=tweets&amp;amp;q=%23ENBDRiddleOfTheWeek"&gt;#ENBDRiddleOfTheWeek&lt;/a&gt; 
+&lt;a href="/search?f=tweets&amp;amp;q=%23financialwellbeing"&gt;#financialwellbeing&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J3" t="b">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 9:30 PM UTC</t>
+          <t>Mar 26, 2026 · 4:51 PM UTC</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-03-25T21:30:00Z</t>
+          <t>2026-03-26T16:51:00Z</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23ENBDRiddleOfTheWeek', 'https://x.com/search?f=tweets&amp;q=%23financialwellbeing']</t>
+        </is>
+      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -698,7 +714,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -709,67 +725,79 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2036913676490281251</t>
+          <t>2037210762847138137</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://x.com/TradeInZoneIN/status/2036913676490281251</t>
+          <t>https://x.com/SelmaRomola/status/2037210762847138137</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/TradeInZoneIN</t>
+          <t>https://x.com/SelmaRomola</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TradeInZoneIN</t>
+          <t>SelmaRomola</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trade in Zone</t>
+          <t>Selma Romola</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1907808051697950720/gAd-nJZ__bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1118152018995105792/5fyZOTth_bigger.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Major banking move: Emirates NBD has received UAE Central Bank approval to acquire a majority stake in RBL Bank. The deal involves merging Indian operations and a significant share issue. A huge shift for private sector banking in India. 📈🚀</t>
+          <t>Mutual fund 
+#ENBDRiddleOfTheWeek 
+#financialwellbeing</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Major banking move: Emirates NBD has received UAE Central Bank approval to acquire a majority stake in RBL Bank. The deal involves merging Indian operations and a significant share issue. A huge shift for private sector banking in India. 📈🚀</t>
+          <t>Mutual fund 
+&lt;a href="/search?f=tweets&amp;amp;q=%23ENBDRiddleOfTheWeek"&gt;#ENBDRiddleOfTheWeek&lt;/a&gt; 
+&lt;a href="/search?f=tweets&amp;amp;q=%23financialwellbeing"&gt;#financialwellbeing&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J4" t="b">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 9:10 PM UTC</t>
+          <t>Mar 26, 2026 · 4:51 PM UTC</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-03-25T21:10:00Z</t>
+          <t>2026-03-26T16:51:00Z</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23ENBDRiddleOfTheWeek', 'https://x.com/search?f=tweets&amp;q=%23financialwellbeing']</t>
+        </is>
+      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -780,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -791,45 +819,45 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2036907649933951454</t>
+          <t>2037188660789973451</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://x.com/theshivrao/status/2036907649933951454</t>
+          <t>https://x.com/khushbuag88/status/2037188660789973451</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/theshivrao</t>
+          <t>https://x.com/khushbuag88</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>theshivrao</t>
+          <t>khushbuag88</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shiv Rao</t>
+          <t>Khushbu Agarwal</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1537059258826895362/aTalVMrH_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1950530694746447872/VGZLi5fA_bigger.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>@grok what’s the investment amount. How much is going to be the post money valuation of RBL, and who exactly is exiting.
-What’s the profile of this Emirates NBD?</t>
+          <t>Mutual fund #ENBDRiddleOfTheWeek 
+#FinancialWellbeing</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>&lt;a href="/grok" title="Grok"&gt;@grok&lt;/a&gt; what’s the investment amount. How much is going to be the post money valuation of RBL, and who exactly is exiting.
-What’s the profile of this Emirates NBD?</t>
+          <t>Mutual fund &lt;a href="/search?f=tweets&amp;amp;q=%23ENBDRiddleOfTheWeek"&gt;#ENBDRiddleOfTheWeek&lt;/a&gt; 
+&lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J5" t="b">
@@ -838,32 +866,32 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>['moneycontrolcom']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 8:46 PM UTC</t>
+          <t>Mar 26, 2026 · 3:23 PM UTC</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-03-25T20:46:00Z</t>
+          <t>2026-03-26T15:23:00Z</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>['https://x.com/grok']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23ENBDRiddleOfTheWeek', 'https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing']</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -872,7 +900,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -883,82 +911,82 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2036906970095964494</t>
+          <t>2037184663228473456</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://x.com/saif_aldareei/status/2036906970095964494</t>
+          <t>https://x.com/maharsha_37/status/2037184663228473456</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/saif_aldareei</t>
+          <t>https://x.com/maharsha_37</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>saif_aldareei</t>
+          <t>maharsha_37</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سيف الدرعي| Saif alderei</t>
+          <t>mahesh patidar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1597913616363257856/PitDyJR6_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1763242358601043968/vC4TbYcN_bigger.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>الإمارات : الأصول تتخطى 5.4 تريليون درهم خلال يناير 2026، مع توسع الائتمان المدعوم بنمو الودائع المحلية وزيادة التمويل الموجه للاقتصاد.
-بنمو شهري 1.4%، وإجمالي 5.3% مقارنة بالعام الماضي.
-القطاع المصرفي الإماراتي.. يواصل التألق والريادة.</t>
+          <t>Stay away from this bank. My card details were compromised and used for fraud on Amazon KSA. I reported it within 2 minutes, but the case was closed without refund. It’s been 2 months with no response. Extremely poor service, no accountability,. Case number: 232674141616</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>الإمارات : الأصول تتخطى 5.4 تريليون درهم خلال يناير 2026، مع توسع الائتمان المدعوم بنمو الودائع المحلية وزيادة التمويل الموجه للاقتصاد.
-بنمو شهري 1.4%، وإجمالي 5.3% مقارنة بالعام الماضي.
-القطاع المصرفي الإماراتي.. يواصل التألق والريادة.</t>
+          <t>Stay away from this bank. My card details were compromised and used for fraud on Amazon KSA. I reported it within 2 minutes, but the case was closed without refund. It’s been 2 months with no response. Extremely poor service, no accountability,. Case number: 232674141616</t>
         </is>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 8:44 PM UTC</t>
+          <t>Mar 26, 2026 · 3:07 PM UTC</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-03-25T20:44:00Z</t>
+          <t>2026-03-26T15:07:00Z</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>5737</v>
+        <v>25</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -969,45 +997,51 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2036862365786845591</t>
+          <t>2037178056108839321</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2036862365786845591</t>
+          <t>https://x.com/semeet/status/2037178056108839321</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY</t>
+          <t>https://x.com/semeet</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EmiratesNBD_EGY</t>
+          <t>semeet</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>seema shelat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1376978771538898945/X-iaSTLK_bigger.jpg</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>شكرًا لاهتمامكم بمنتجنا. يُرجى الاطلاع على الرابط أدناه لمزيد من التفاصيل والنموذج المطلوب تعبئته، وسيتواصل فريقنا معكم في أقرب وقت ممكن. شكرًا - زبير
-emiratesnbd.com.eg/ar/standa…</t>
+          <t>A mutual fund or investment fund
+#ENBDRiddleOfTheWeek
+#FinancialWellbeing
+#InvestSmart
+#MoneyBasics</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>شكرًا لاهتمامكم بمنتجنا. يُرجى الاطلاع على الرابط أدناه لمزيد من التفاصيل والنموذج المطلوب تعبئته، وسيتواصل فريقنا معكم في أقرب وقت ممكن. شكرًا - زبير
-&lt;a href="https://www.emiratesnbd.com.eg/ar/standard-banking/cards/debit-cards/foreign-currency-card"&gt;emiratesnbd.com.eg/ar/standa…&lt;/a&gt;</t>
+          <t>A mutual fund or investment fund
+&lt;a href="/search?f=tweets&amp;amp;q=%23ENBDRiddleOfTheWeek"&gt;#ENBDRiddleOfTheWeek&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23InvestSmart"&gt;#InvestSmart&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23MoneyBasics"&gt;#MoneyBasics&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J7" t="b">
@@ -1016,28 +1050,28 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>['SafwatTools']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 5:46 PM UTC</t>
+          <t>Mar 26, 2026 · 2:41 PM UTC</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-03-25T17:46:00Z</t>
+          <t>2026-03-26T14:41:00Z</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>['https://www.emiratesnbd.com.eg/ar/standard-banking/cards/debit-cards/foreign-currency-card']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23ENBDRiddleOfTheWeek', 'https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23InvestSmart', 'https://x.com/search?f=tweets&amp;q=%23MoneyBasics']</t>
         </is>
       </c>
       <c r="R7" t="n">
@@ -1050,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1061,67 +1095,85 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2036861658321346594</t>
+          <t>2037177932859204023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://x.com/MultibaggAI/status/2036861658321346594</t>
+          <t>https://x.com/semeet/status/2037177932859204023</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/MultibaggAI</t>
+          <t>https://x.com/semeet</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MultibaggAI</t>
+          <t>semeet</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>multibagg.ai</t>
+          <t>seema shelat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2017665342756294656/o62zwaRv_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1376978771538898945/X-iaSTLK_bigger.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>EMIRATES NBD TO ACQUIRE ~60% OF RBL BANK; UAE CENTRAL BANK APPROVED ON 24 MAR 2026, LETTER RECEIVED 25 MAR 2026 || CCI CLEARED DEAL, MANDATORY OPEN OFFER UP TO 26% PLANNED.</t>
+          <t>A mutual fund or investment fund
+Emirates NBD بنك الإمارات دبي الوطني
+#ENBDRiddleOfTheWeek
+#FinancialWellbeing
+#InvestSmart
+#MoneyBasics</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>EMIRATES NBD TO ACQUIRE ~60% OF RBL BANK; UAE CENTRAL BANK APPROVED ON 24 MAR 2026, LETTER RECEIVED 25 MAR 2026 || CCI CLEARED DEAL, MANDATORY OPEN OFFER UP TO 26% PLANNED.</t>
+          <t>A mutual fund or investment fund
+Emirates NBD بنك الإمارات دبي الوطني
+&lt;a href="/search?f=tweets&amp;amp;q=%23ENBDRiddleOfTheWeek"&gt;#ENBDRiddleOfTheWeek&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23InvestSmart"&gt;#InvestSmart&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23MoneyBasics"&gt;#MoneyBasics&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 5:43 PM UTC</t>
+          <t>Mar 26, 2026 · 2:40 PM UTC</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-03-25T17:43:00Z</t>
+          <t>2026-03-26T14:40:00Z</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23ENBDRiddleOfTheWeek', 'https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23InvestSmart', 'https://x.com/search?f=tweets&amp;q=%23MoneyBasics']</t>
+        </is>
+      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -1132,7 +1184,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1143,86 +1195,92 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2036857393393680584</t>
+          <t>2037152117019074621</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://x.com/moneycontrolcom/status/2036857393393680584</t>
+          <t>https://x.com/metooomer/status/2037152117019074621</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/moneycontrolcom</t>
+          <t>https://x.com/metooomer</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>moneycontrolcom</t>
+          <t>metooomer</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Moneycontrol</t>
+          <t>Mutasim</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/841519699632447488/ea4043nJ_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1899186218690379776/Fu95zTWB_bigger.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>#Business | Emirates NBD gets UAE central bank nod for majority stake in RBL Bank
-More details👇
-moneycontrol.com/news/busine…</t>
+          <t>1.89% سنوياً
+@intisar_ma 
+@um_maazz 
+@Om__saad_</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23Business"&gt;#Business&lt;/a&gt; | Emirates NBD gets UAE central bank nod for majority stake in RBL Bank
-More details👇
-&lt;a href="https://www.moneycontrol.com/news/business/banks/emirates-nbd-gets-uae-central-bank-nod-for-majority-stake-in-rbl-bank-13870833.html"&gt;moneycontrol.com/news/busine…&lt;/a&gt;</t>
+          <t>1.89% سنوياً
+&lt;a href="/intisar_ma" title="إنتصار #بالعربي"&gt;@intisar_ma&lt;/a&gt; 
+&lt;a href="/um_maazz" title="um_maaz"&gt;@um_maazz&lt;/a&gt; 
+&lt;a href="/Om__saad_" title="om_saad"&gt;@Om__saad_&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 5:27 PM UTC</t>
+          <t>Mar 26, 2026 · 12:58 PM UTC</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-03-25T17:27:00Z</t>
+          <t>2026-03-26T12:58:00Z</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23Business', 'https://www.moneycontrol.com/news/business/banks/emirates-nbd-gets-uae-central-bank-nod-for-majority-stake-in-rbl-bank-13870833.html']</t>
+          <t>['https://x.com/intisar_ma', 'https://x.com/um_maazz', 'https://x.com/Om__saad_']</t>
         </is>
       </c>
       <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
         <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2</v>
-      </c>
-      <c r="T9" t="n">
-        <v>27</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3111</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1233,86 +1291,92 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2036856277721075840</t>
+          <t>2037151840035561797</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://x.com/CNBCTV18News/status/2036856277721075840</t>
+          <t>https://x.com/metooomer/status/2037151840035561797</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/CNBCTV18News</t>
+          <t>https://x.com/metooomer</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CNBCTV18News</t>
+          <t>metooomer</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CNBC-TV18</t>
+          <t>Mutasim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1926678193345273856/OxMqCV6J_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1899186218690379776/Fu95zTWB_bigger.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>#UAECentralBank approves #EmiratesNBD's proposed stake acquisition in #RBLBank
-@jpullokaran
-buff.ly/XJ1NhVr</t>
+          <t>1.89% سنوياً
+@intisar_ma 
+@um_maazz 
+@Fr638</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23UAECentralBank"&gt;#UAECentralBank&lt;/a&gt; approves &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt;&amp;#39;s proposed stake acquisition in &lt;a href="/search?f=tweets&amp;amp;q=%23RBLBank"&gt;#RBLBank&lt;/a&gt;
-&lt;a href="/jpullokaran" title="Jomy Jos Pullokaran"&gt;@jpullokaran&lt;/a&gt;
-&lt;a href="https://buff.ly/XJ1NhVr"&gt;buff.ly/XJ1NhVr&lt;/a&gt;</t>
+          <t>1.89% سنوياً
+&lt;a href="/intisar_ma" title="إنتصار #بالعربي"&gt;@intisar_ma&lt;/a&gt; 
+&lt;a href="/um_maazz" title="um_maaz"&gt;@um_maazz&lt;/a&gt; 
+&lt;a href="/Fr638" title="Faris _m"&gt;@Fr638&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 5:22 PM UTC</t>
+          <t>Mar 26, 2026 · 12:57 PM UTC</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-03-25T17:22:00Z</t>
+          <t>2026-03-26T12:57:00Z</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23UAECentralBank', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23RBLBank', 'https://x.com/jpullokaran', 'https://buff.ly/XJ1NhVr']</t>
+          <t>['https://x.com/intisar_ma', 'https://x.com/um_maazz', 'https://x.com/Fr638']</t>
         </is>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3184</v>
+        <v>1</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1323,67 +1387,81 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2036852664009711914</t>
+          <t>2037151306373337310</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://x.com/MultibaggAI/status/2036852664009711914</t>
+          <t>https://x.com/metooomer/status/2037151306373337310</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/MultibaggAI</t>
+          <t>https://x.com/metooomer</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MultibaggAI</t>
+          <t>metooomer</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>multibagg.ai</t>
+          <t>Mutasim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2017665342756294656/o62zwaRv_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1899186218690379776/Fu95zTWB_bigger.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>UAE CENTRAL BANK APPROVED EMIRATES NBD'S ACQUISITION OF A MAJORITY STAKE IN RBL BANK, REGULATOR'S NOD ANNOUNCED ON 25 MAR 2026 || PAVES WAY FOR CHANGE OF CONTROL AT RBL</t>
+          <t>Exchanger Volunteering Program 
+@intisar_ma 
+@um_maazz 
+@Fr638</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>UAE CENTRAL BANK APPROVED EMIRATES NBD&amp;#39;S ACQUISITION OF A MAJORITY STAKE IN RBL BANK, REGULATOR&amp;#39;S NOD ANNOUNCED ON 25 MAR 2026 || PAVES WAY FOR CHANGE OF CONTROL AT RBL</t>
+          <t>Exchanger Volunteering Program 
+&lt;a href="/intisar_ma" title="إنتصار #بالعربي"&gt;@intisar_ma&lt;/a&gt; 
+&lt;a href="/um_maazz" title="um_maaz"&gt;@um_maazz&lt;/a&gt; 
+&lt;a href="/Fr638" title="Faris _m"&gt;@Fr638&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J11" t="b">
         <v>0</v>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 5:08 PM UTC</t>
+          <t>Mar 26, 2026 · 12:54 PM UTC</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-03-25T17:08:00Z</t>
+          <t>2026-03-26T12:54:00Z</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>['https://x.com/intisar_ma', 'https://x.com/um_maazz', 'https://x.com/Fr638']</t>
+        </is>
+      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -1391,10 +1469,10 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
         <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>54</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1405,71 +1483,81 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2036850996706762863</t>
+          <t>2037150489595559998</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://x.com/ETNOWlive/status/2036850996706762863</t>
+          <t>https://x.com/metooomer/status/2037150489595559998</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/ETNOWlive</t>
+          <t>https://x.com/metooomer</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ETNOWlive</t>
+          <t>metooomer</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ET NOW</t>
+          <t>Mutasim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1863866767027933184/hC9WqRl-_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1899186218690379776/Fu95zTWB_bigger.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>#StockInNews | RBL Bank: UAE Central Bank approves NBD takeover of RBL majority stake
-@rblbank @centralbankuae @EmiratesNBD_AE #StockMarket</t>
+          <t>Via the ENBD X Mobile App
+@um_maazz 
+@Om__saad_ 
+@Fr638
+..</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23StockInNews"&gt;#StockInNews&lt;/a&gt; | RBL Bank: UAE Central Bank approves NBD takeover of RBL majority stake
-&lt;a href="/rblbank" title="RBL Bank"&gt;@rblbank&lt;/a&gt; &lt;a href="/centralbankuae" title="Central Bank of the UAE"&gt;@centralbankuae&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23StockMarket"&gt;#StockMarket&lt;/a&gt;</t>
+          <t>Via the ENBD X Mobile App
+&lt;a href="/um_maazz" title="um_maaz"&gt;@um_maazz&lt;/a&gt; 
+&lt;a href="/Om__saad_" title="om_saad"&gt;@Om__saad_&lt;/a&gt; 
+&lt;a href="/Fr638" title="Faris _m"&gt;@Fr638&lt;/a&gt;
+..</t>
         </is>
       </c>
       <c r="J12" t="b">
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 5:01 PM UTC</t>
+          <t>Mar 26, 2026 · 12:51 PM UTC</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-03-25T17:01:00Z</t>
+          <t>2026-03-26T12:51:00Z</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23StockInNews', 'https://x.com/rblbank', 'https://x.com/centralbankuae', 'https://x.com/EmiratesNBD_AE', 'https://x.com/search?f=tweets&amp;q=%23StockMarket']</t>
+          <t>['https://x.com/um_maazz', 'https://x.com/Om__saad_', 'https://x.com/Fr638']</t>
         </is>
       </c>
       <c r="R12" t="n">
@@ -1479,10 +1567,10 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1850</v>
+        <v>2</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1493,84 +1581,92 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2036850685946597634</t>
+          <t>2037150432142004408</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://x.com/_RituSingh/status/2036850685946597634</t>
+          <t>https://x.com/metooomer/status/2037150432142004408</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/_RituSingh</t>
+          <t>https://x.com/metooomer</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>_RituSingh</t>
+          <t>metooomer</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ritu Singh</t>
+          <t>Mutasim</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2020720836177764352/eHyjmdvb_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1899186218690379776/Fu95zTWB_bigger.jpg</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>🚨 Emirates NBD Gets UAE Central Bank Nod For Acquisition of Majority Stake In RBL Bank
-@rblbank @EmiratesNBD_AE @CNBCTV18Live</t>
+          <t>Via the ENBD X Mobile App
+@um_maazz 
+@Om__saad_ 
+@Fr638</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>🚨 Emirates NBD Gets UAE Central Bank Nod For Acquisition of Majority Stake In RBL Bank
-&lt;a href="/rblbank" title="RBL Bank"&gt;@rblbank&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; &lt;a href="/CNBCTV18Live" title="CNBC-TV18"&gt;@CNBCTV18Live&lt;/a&gt;</t>
+          <t>Via the ENBD X Mobile App
+&lt;a href="/um_maazz" title="um_maaz"&gt;@um_maazz&lt;/a&gt; 
+&lt;a href="/Om__saad_" title="om_saad"&gt;@Om__saad_&lt;/a&gt; 
+&lt;a href="/Fr638" title="Faris _m"&gt;@Fr638&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 5:00 PM UTC</t>
+          <t>Mar 26, 2026 · 12:51 PM UTC</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-03-25T17:00:00Z</t>
+          <t>2026-03-26T12:51:00Z</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>['https://x.com/rblbank', 'https://x.com/EmiratesNBD_AE', 'https://x.com/CNBCTV18Live']</t>
+          <t>['https://x.com/um_maazz', 'https://x.com/Om__saad_', 'https://x.com/Fr638']</t>
         </is>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>947</v>
+        <v>3</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1581,67 +1677,81 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2036850314364834133</t>
+          <t>2037148310214250851</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://x.com/shunto0823/status/2036850314364834133</t>
+          <t>https://x.com/Bushrasabih2/status/2037148310214250851</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/shunto0823</t>
+          <t>https://x.com/Bushrasabih2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>shunto0823</t>
+          <t>Bushrasabih2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>しゅんと/ドバイ在住不動産エージェント【UAE不動産】</t>
+          <t>Bu_shaikh🌸❤️</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1885182332878954496/ejkcHMnq_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2037057205510574080/OEGMy7R9_bigger.jpg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>【ドバイ銀行口座の凍結？】現地の銀行でデマを調査してみた / 3月25日午後5時30分</t>
+          <t>Exchanger Volunteering Programe 
+@AyshaMoham64638 
+@Bushrasabih1 
+@noor1813371</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>【ドバイ銀行口座の凍結？】現地の銀行でデマを調査してみた / 3月25日午後5時30分</t>
+          <t>Exchanger Volunteering Programe 
+&lt;a href="/AyshaMoham64638" title="Aysha Mohammad"&gt;@AyshaMoham64638&lt;/a&gt; 
+&lt;a href="/Bushrasabih1" title="Fahood Emarati"&gt;@Bushrasabih1&lt;/a&gt; 
+&lt;a href="/noor1813371" title="noor"&gt;@noor1813371&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J14" t="b">
         <v>0</v>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 4:58 PM UTC</t>
+          <t>Mar 26, 2026 · 12:43 PM UTC</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-03-25T16:58:00Z</t>
+          <t>2026-03-26T12:43:00Z</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>['https://x.com/AyshaMoham64638', 'https://x.com/Bushrasabih1', 'https://x.com/noor1813371']</t>
+        </is>
+      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -1649,10 +1759,10 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1028</v>
+        <v>1</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1663,43 +1773,49 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2036841622822883698</t>
+          <t>2037148258775257219</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036841622822883698</t>
+          <t>https://x.com/Bushrasabih2/status/2037148258775257219</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/Bushrasabih2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>Bushrasabih2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Bu_shaikh🌸❤️</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2037057205510574080/OEGMy7R9_bigger.jpg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Please mention in the email subject social media case #988468.</t>
+          <t>Exchanger Volunteering Programe 
+@AyshaMoham64638 
+@Bushrasabih1 
+@Sarahfa40636602</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Please mention in the email subject social media case #988468.</t>
+          <t>Exchanger Volunteering Programe 
+&lt;a href="/AyshaMoham64638" title="Aysha Mohammad"&gt;@AyshaMoham64638&lt;/a&gt; 
+&lt;a href="/Bushrasabih1" title="Fahood Emarati"&gt;@Bushrasabih1&lt;/a&gt; 
+&lt;a href="/Sarahfa40636602" title="Sarah_fares"&gt;@Sarahfa40636602&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J15" t="b">
@@ -1708,26 +1824,30 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>['GidwaniHero']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 4:24 PM UTC</t>
+          <t>Mar 26, 2026 · 12:42 PM UTC</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-03-25T16:24:00Z</t>
+          <t>2026-03-26T12:42:00Z</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>['https://x.com/AyshaMoham64638', 'https://x.com/Bushrasabih1', 'https://x.com/Sarahfa40636602']</t>
+        </is>
+      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -1738,7 +1858,7 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1749,43 +1869,49 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2036841585950756910</t>
+          <t>2037148207525093610</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036841585950756910</t>
+          <t>https://x.com/Bushrasabih2/status/2037148207525093610</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/Bushrasabih2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>Bushrasabih2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Bu_shaikh🌸❤️</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2037057205510574080/OEGMy7R9_bigger.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hi , we’re sorry to hear that you’re having unpleasant experience. We will be glad to assist you and have it fixed. Kindly send us the details at social@EmiratesNBD.com from your registered email address so we can review and assist.</t>
+          <t>Exchanger Volunteering Programe 
+@AyshaMoham64638 
+@Bintt_Najd 
+@Bushrasabih2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Hi , we’re sorry to hear that you’re having unpleasant experience. We will be glad to assist you and have it fixed. Kindly send us the details at social@EmiratesNBD.com from your registered email address so we can review and assist.</t>
+          <t>Exchanger Volunteering Programe 
+&lt;a href="/AyshaMoham64638" title="Aysha Mohammad"&gt;@AyshaMoham64638&lt;/a&gt; 
+&lt;a href="/Bintt_Najd" title="بنت نجد العذية"&gt;@Bintt_Najd&lt;/a&gt; 
+&lt;a href="/Bushrasabih2" title="Bu_shaikh🌸❤️"&gt;@Bushrasabih2&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J16" t="b">
@@ -1794,26 +1920,30 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>['GidwaniHero']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 4:24 PM UTC</t>
+          <t>Mar 26, 2026 · 12:42 PM UTC</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-03-25T16:24:00Z</t>
+          <t>2026-03-26T12:42:00Z</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>['https://x.com/AyshaMoham64638', 'https://x.com/Bintt_Najd', 'https://x.com/Bushrasabih2']</t>
+        </is>
+      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -1824,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1835,77 +1965,85 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2036841067778363615</t>
+          <t>2037148045675291023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://x.com/GidwaniHero/status/2036841067778363615</t>
+          <t>https://x.com/Bushrasabih2/status/2037148045675291023</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/GidwaniHero</t>
+          <t>https://x.com/Bushrasabih2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>GidwaniHero</t>
+          <t>Bushrasabih2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hero Gidwani</t>
+          <t>Bu_shaikh🌸❤️</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1924556859526283267/UcvezR38_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2037057205510574080/OEGMy7R9_bigger.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>@HHShkMohd @MohamedBinZayed 
-@FABConnects @MashreqTweets @EmiratesNBD_AE 
-Dear UAE Government Request You To Keep Security Guards Inside ATM AND BRANCHS AT NIGHT TIME MANY POEPLE ARE MISS USING OF MACHINES 1 customer do 10 trns and they show attitude what type of services inside</t>
+          <t>Exchanger Volunteering Programe 
+@AyshaMoham64638 
+@Bushrasabih1 
+@Umehanimuhamma1
+..</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>&lt;a href="/HHShkMohd" title="HH Sheikh Mohammed"&gt;@HHShkMohd&lt;/a&gt; &lt;a href="/MohamedBinZayed" title="محمد بن زايد"&gt;@MohamedBinZayed&lt;/a&gt; 
-&lt;a href="/FABConnects" title="FAB Connects"&gt;@FABConnects&lt;/a&gt; &lt;a href="/MashreqTweets" title="Mashreq"&gt;@MashreqTweets&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
-Dear UAE Government Request You To Keep Security Guards Inside ATM AND BRANCHS AT NIGHT TIME MANY POEPLE ARE MISS USING OF MACHINES 1 customer do 10 trns and they show attitude what type of services inside</t>
+          <t>Exchanger Volunteering Programe 
+&lt;a href="/AyshaMoham64638" title="Aysha Mohammad"&gt;@AyshaMoham64638&lt;/a&gt; 
+&lt;a href="/Bushrasabih1" title="Fahood Emarati"&gt;@Bushrasabih1&lt;/a&gt; 
+&lt;a href="/Umehanimuhamma1" title="ام محمد احمد"&gt;@Umehanimuhamma1&lt;/a&gt;
+..</t>
         </is>
       </c>
       <c r="J17" t="b">
         <v>0</v>
       </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 4:22 PM UTC</t>
+          <t>Mar 26, 2026 · 12:41 PM UTC</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-03-25T16:22:00Z</t>
+          <t>2026-03-26T12:41:00Z</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>['https://x.com/HHShkMohd', 'https://x.com/MohamedBinZayed', 'https://x.com/FABConnects', 'https://x.com/MashreqTweets', 'https://x.com/EmiratesNBD_AE']</t>
+          <t>['https://x.com/AyshaMoham64638', 'https://x.com/Bushrasabih1', 'https://x.com/Umehanimuhamma1']</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -1914,7 +2052,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -1925,69 +2063,73 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2036823583914365348</t>
+          <t>2037147720503484508</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://x.com/stockwatch_live/status/2036823583914365348</t>
+          <t>https://x.com/Bushrasabih2/status/2037147720503484508</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/stockwatch_live</t>
+          <t>https://x.com/Bushrasabih2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>stockwatch_live</t>
+          <t>Bushrasabih2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stockwatch.live</t>
+          <t>Bu_shaikh🌸❤️</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1922756599971708929/IhP9CXt7_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2037057205510574080/OEGMy7R9_bigger.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>$RBLBANK.NSE RBL Bank Receives Approval from Central Bank of UAE for Majority Stake Acquisition by Emirates NBD Bank stockwatch.live/news?name=RB… #stock #nse #bse #market #RBLBANK #RBLBankLtd</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD @AyshaMoham64638 @AyshaMoham64638 @aa_ashirakorn</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23RBLBANK"&gt;$RBLBANK&lt;/a&gt;.NSE RBL Bank Receives Approval from Central Bank of UAE for Majority Stake Acquisition by Emirates NBD Bank &lt;a href="https://www.stockwatch.live/news?name=RBL+Bank+Ltd&amp;amp;showModal=true&amp;amp;title=RBL+Bank+Receives+Approval+from+Central+Bank+of+UAE+for+Majority+Stake+Acquisition+by+Emirates+NBD+Bank&amp;amp;newsId=fb36b797-76cb-4e5b-af51-5f06aebb98fd"&gt;stockwatch.live/news?name=RB…&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23stock"&gt;#stock&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23nse"&gt;#nse&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23bse"&gt;#bse&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23market"&gt;#market&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23RBLBANK"&gt;#RBLBANK&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23RBLBankLtd"&gt;#RBLBankLtd&lt;/a&gt;</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/AyshaMoham64638" title="Aysha Mohammad"&gt;@AyshaMoham64638&lt;/a&gt; &lt;a href="/AyshaMoham64638" title="Aysha Mohammad"&gt;@AyshaMoham64638&lt;/a&gt; &lt;a href="/aa_ashirakorn" title="AA"&gt;@aa_ashirakorn&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J18" t="b">
         <v>0</v>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 3:12 PM UTC</t>
+          <t>Mar 26, 2026 · 12:40 PM UTC</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-03-25T15:12:00Z</t>
+          <t>2026-03-26T12:40:00Z</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23RBLBANK', 'https://www.stockwatch.live/news?name=RBL+Bank+Ltd&amp;showModal=true&amp;title=RBL+Bank+Receives+Approval+from+Central+Bank+of+UAE+for+Majority+Stake+Acquisition+by+Emirates+NBD+Bank&amp;newsId=fb36b797-76cb-4e5b-af51-5f06aebb98fd', 'https://x.com/search?f=tweets&amp;q=%23stock', 'https://x.com/search?f=tweets&amp;q=%23nse', 'https://x.com/search?f=tweets&amp;q=%23bse', 'https://x.com/search?f=tweets&amp;q=%23market', 'https://x.com/search?f=tweets&amp;q=%23RBLBANK', 'https://x.com/search?f=tweets&amp;q=%23RBLBankLtd']</t>
+          <t>['https://x.com/AyshaMoham64638', 'https://x.com/AyshaMoham64638', 'https://x.com/aa_ashirakorn']</t>
         </is>
       </c>
       <c r="R18" t="n">
@@ -2000,7 +2142,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -2011,77 +2153,75 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2036821360086069616</t>
+          <t>2037147542937624952</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://x.com/_Investor_Feed_/status/2036821360086069616</t>
+          <t>https://x.com/Bushrasabih2/status/2037147542937624952</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/_Investor_Feed_</t>
+          <t>https://x.com/Bushrasabih2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>_Investor_Feed_</t>
+          <t>Bushrasabih2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Investor Feed</t>
+          <t>Bu_shaikh🌸❤️</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1897853077535047680/p8b9Zv5P_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2037057205510574080/OEGMy7R9_bigger.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>🏦 Emirates NBD Secures UAE Central Bank Approval for Majority Stake in RBL Bank | MCap 20,197.23 Cr
-• UAE Central Bank approved Emirates NBD's majority stake acquisition in RBL Bank on March 24, 2026
-• Approval includes amalgamation of Emirates NBD's existing Indian operations into RBL Bank
-Complete Source: bseindia.com/xml-data/corpfi…
-Disc: Information provided in this tweet can be inaccurate, verify through the source before making any investment decision.</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD @semeet @SelmaRomola @Emy191990
+..</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>🏦 Emirates NBD Secures UAE Central Bank Approval for Majority Stake in RBL Bank | MCap 20,197.23 Cr
-• UAE Central Bank approved Emirates NBD&amp;#39;s majority stake acquisition in RBL Bank on March 24, 2026
-• Approval includes amalgamation of Emirates NBD&amp;#39;s existing Indian operations into RBL Bank
-Complete Source: &lt;a href="https://www.bseindia.com/xml-data/corpfiling/AttachLive/16d12839-deaa-4f3e-acd1-b6184ab87abc.pdf"&gt;bseindia.com/xml-data/corpfi…&lt;/a&gt;
-Disc: Information provided in this tweet can be inaccurate, verify through the source before making any investment decision.</t>
+          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt;
+..</t>
         </is>
       </c>
       <c r="J19" t="b">
         <v>0</v>
       </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 3:03 PM UTC</t>
+          <t>Mar 26, 2026 · 12:39 PM UTC</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-03-25T15:03:00Z</t>
+          <t>2026-03-26T12:39:00Z</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>['https://www.bseindia.com/xml-data/corpfiling/AttachLive/16d12839-deaa-4f3e-acd1-b6184ab87abc.pdf']</t>
+          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/Emy191990']</t>
         </is>
       </c>
       <c r="R19" t="n">
@@ -2091,10 +2231,10 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>287</v>
+        <v>5</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -2105,75 +2245,73 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2036821223116845234</t>
+          <t>2037146722225508509</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://x.com/wegro_app/status/2036821223116845234</t>
+          <t>https://x.com/Bushrasabih2/status/2037146722225508509</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/wegro_app</t>
+          <t>https://x.com/Bushrasabih2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>wegro_app</t>
+          <t>Bushrasabih2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wegro App</t>
+          <t>Bu_shaikh🌸❤️</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1793658188497117184/T9pfyA67_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2037057205510574080/OEGMy7R9_bigger.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>RBL Bank announced that Emirates NBD Bank has received approval from the Central Bank of UAE for its proposed acquisition of a majority stake in RBL Bank &amp; amalgamation of Emirates NBD's India operations into RBL Bank. This is subject to receipt of all necessary regulatory approvals. The information is hosted on RBL Bank's website.
-📊 RBL BANK LTD | 🏷️ General
-🌐 Details: wegro.app/UWJL50
-⚡️Instant stock alerts on WhatsApp - Try FREE 👉 wegro.app/go</t>
+          <t>التثقيف المالي مع بنك الامارات دبي الوطني ,  @semeet @SelmaRomola @AyshaMoham64638</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>RBL Bank announced that Emirates NBD Bank has received approval from the Central Bank of UAE for its proposed acquisition of a majority stake in RBL Bank &amp;amp; amalgamation of Emirates NBD&amp;#39;s India operations into RBL Bank. This is subject to receipt of all necessary regulatory approvals. The information is hosted on RBL Bank&amp;#39;s website.
-📊 RBL BANK LTD | 🏷️ General
-🌐 Details: &lt;a href="https://www.wegro.app/UWJL50"&gt;wegro.app/UWJL50&lt;/a&gt;
-⚡️Instant stock alerts on WhatsApp - Try FREE 👉 &lt;a href="https://www.wegro.app/go"&gt;wegro.app/go&lt;/a&gt;</t>
+          <t>التثقيف المالي مع بنك الامارات دبي الوطني ,  &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/AyshaMoham64638" title="Aysha Mohammad"&gt;@AyshaMoham64638&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J20" t="b">
         <v>0</v>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 3:03 PM UTC</t>
+          <t>Mar 26, 2026 · 12:36 PM UTC</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-03-25T15:03:00Z</t>
+          <t>2026-03-26T12:36:00Z</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>['https://www.wegro.app/UWJL50', 'https://www.wegro.app/go']</t>
+          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/AyshaMoham64638']</t>
         </is>
       </c>
       <c r="R20" t="n">
@@ -2186,7 +2324,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -2197,79 +2335,73 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2036821129726501170</t>
+          <t>2037146697382715509</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://x.com/SpeedyStox45552/status/2036821129726501170</t>
+          <t>https://x.com/Bushrasabih2/status/2037146697382715509</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://x.com/SpeedyStox45552</t>
+          <t>https://x.com/Bushrasabih2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SpeedyStox45552</t>
+          <t>Bushrasabih2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Speedy Stox</t>
+          <t>Bu_shaikh🌸❤️</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2026633232603893760/w3Lqscnz_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2037057205510574080/OEGMy7R9_bigger.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>📊 RBL BANK LTD - 540065 | 🏷️ General
-Emirates NBD Bank (P.J.S.C) received approval from the Central Bank of UAE on March 24, 2026, for the proposed acquisition of a majority stake and amalgamation of its operations in India, pending necessary regulatory approvals.
-💰 CMP: ₹303.80 (+2.51%)
-🏢 MCap: ₹18,778 Cr
-🌐 Details: tinyurl.com/2bbt3ha2
-⚡️Instant stock alerts on WhatsApp - Try FREE 👉 speedystox.com</t>
+          <t>التثقيف المالي مع بنك الامارات دبي الوطني   @semeet @SelmaRomola @AyshaMoham64638</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>📊 RBL BANK LTD - 540065 | 🏷️ General
-Emirates NBD Bank (P.J.S.C) received approval from the Central Bank of UAE on March 24, 2026, for the proposed acquisition of a majority stake and amalgamation of its operations in India, pending necessary regulatory approvals.
-💰 CMP: ₹303.80 (+2.51%)
-🏢 MCap: ₹18,778 Cr
-🌐 Details: &lt;a href="https://tinyurl.com/2bbt3ha2"&gt;tinyurl.com/2bbt3ha2&lt;/a&gt;
-⚡️Instant stock alerts on WhatsApp - Try FREE 👉 &lt;a href="http://speedystox.com"&gt;speedystox.com&lt;/a&gt;</t>
+          <t>التثقيف المالي مع بنك الامارات دبي الوطني   &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/AyshaMoham64638" title="Aysha Mohammad"&gt;@AyshaMoham64638&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J21" t="b">
         <v>0</v>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 3:02 PM UTC</t>
+          <t>Mar 26, 2026 · 12:36 PM UTC</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-03-25T15:02:00Z</t>
+          <t>2026-03-26T12:36:00Z</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>['https://tinyurl.com/2bbt3ha2', 'http://speedystox.com']</t>
+          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/AyshaMoham64638']</t>
         </is>
       </c>
       <c r="R21" t="n">
@@ -2282,7 +2414,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -2293,75 +2425,75 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2036820403755037156</t>
+          <t>2037146430109081782</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2036820403755037156</t>
+          <t>https://x.com/Bushrasabih2/status/2037146430109081782</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY</t>
+          <t>https://x.com/Bushrasabih2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EmiratesNBD_EGY</t>
+          <t>Bushrasabih2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Bu_shaikh🌸❤️</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2037057205510574080/OEGMy7R9_bigger.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>From All Seasons Park to Open Air Mall ENBD Mastercard x TMG credit cardholders enjoyed surprises and rewards across Ilo Specialty, Stereo, Breadfast, and Tabali.
-And this was just the beginning…
-More Happy Hours are coming your way.
-Stay ready.
-Tax registration number: 204-897-319</t>
+          <t>through Emirates NBD, the fastest way is using the ENBD X mobile app.   @semeet @SelmaRomola @Salma22320</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>From All Seasons Park to Open Air Mall ENBD Mastercard x TMG credit cardholders enjoyed surprises and rewards across Ilo Specialty, Stereo, Breadfast, and Tabali.
-And this was just the beginning…
-More Happy Hours are coming your way.
-Stay ready.
-Tax registration number: 204-897-319</t>
+          <t>through Emirates NBD, the fastest way is using the ENBD X mobile app.   &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; @Salma22320</t>
         </is>
       </c>
       <c r="J22" t="b">
         <v>0</v>
       </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 3:00 PM UTC</t>
+          <t>Mar 26, 2026 · 12:35 PM UTC</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-03-25T15:00:00Z</t>
+          <t>2026-03-26T12:35:00Z</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola']</t>
+        </is>
+      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -2372,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2383,73 +2515,75 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2036820403234979999</t>
+          <t>2037146404259586482</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2036820403234979999</t>
+          <t>https://x.com/Bushrasabih2/status/2037146404259586482</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY</t>
+          <t>https://x.com/Bushrasabih2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EmiratesNBD_EGY</t>
+          <t>Bushrasabih2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Bu_shaikh🌸❤️</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2037057205510574080/OEGMy7R9_bigger.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>من All Seasons Park إلى Open Air Mall ، استمتع حاملي بطاقة بنك الإمارات دبي الوطني ماستركارد الائتمانية بالتعاون مع مجموعة طلعت مصطفى بمفاجآت وجوائز في Ilo Specialty، Stereo، Breadfast، وTabali.
-و دي مجرد البداية...
-استنونا في مفاجآت ومكافآت أكتر.
-رقم التسجيل الضريبي: 319-897-204</t>
+          <t>through Emirates NBD, the fastest way is using the ENBD X mobile app.   @Bushrasabih1 @AyshaMoham64638 @Bushrasabih1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>من All Seasons Park إلى Open Air Mall ، استمتع حاملي بطاقة بنك الإمارات دبي الوطني ماستركارد الائتمانية بالتعاون مع مجموعة طلعت مصطفى بمفاجآت وجوائز في Ilo Specialty، Stereo، Breadfast، وTabali.
-و دي مجرد البداية...
-استنونا في مفاجآت ومكافآت أكتر.
-رقم التسجيل الضريبي: 319-897-204</t>
+          <t>through Emirates NBD, the fastest way is using the ENBD X mobile app.   &lt;a href="/Bushrasabih1" title="Fahood Emarati"&gt;@Bushrasabih1&lt;/a&gt; &lt;a href="/AyshaMoham64638" title="Aysha Mohammad"&gt;@AyshaMoham64638&lt;/a&gt; &lt;a href="/Bushrasabih1" title="Fahood Emarati"&gt;@Bushrasabih1&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J23" t="b">
         <v>0</v>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 3:00 PM UTC</t>
+          <t>Mar 26, 2026 · 12:35 PM UTC</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-03-25T15:00:00Z</t>
+          <t>2026-03-26T12:35:00Z</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>['https://x.com/Bushrasabih1', 'https://x.com/AyshaMoham64638', 'https://x.com/Bushrasabih1']</t>
+        </is>
+      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -2460,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>74</v>
+        <v>8</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -2471,67 +2605,75 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2036810456203952345</t>
+          <t>2037146011169415506</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://x.com/Kevin_Carey_WB/status/2036810456203952345</t>
+          <t>https://x.com/Bushrasabih2/status/2037146011169415506</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://x.com/Kevin_Carey_WB</t>
+          <t>https://x.com/Bushrasabih2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Kevin_Carey_WB</t>
+          <t>Bushrasabih2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kevin Carey</t>
+          <t>Bu_shaikh🌸❤️</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1471236762265600011/Py_QxqOf_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2037057205510574080/OEGMy7R9_bigger.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Don't have a good sense of the normal flow but noticing a couple of redemptions of Additional Tier 1 securities by UAE banks today (First Abu Dhabi Bank, Emirates NBD).</t>
+          <t>Via the ENBD X Mobile App. @AyshaMoham64638  @Bushrasabih2  @Salma2232019</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Don&amp;#39;t have a good sense of the normal flow but noticing a couple of redemptions of Additional Tier 1 securities by UAE banks today (First Abu Dhabi Bank, Emirates NBD).</t>
+          <t>Via the ENBD X Mobile App. &lt;a href="/AyshaMoham64638" title="Aysha Mohammad"&gt;@AyshaMoham64638&lt;/a&gt;  &lt;a href="/Bushrasabih2" title="Bu_shaikh🌸❤️"&gt;@Bushrasabih2&lt;/a&gt;  &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J24" t="b">
         <v>0</v>
       </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 2:20 PM UTC</t>
+          <t>Mar 26, 2026 · 12:33 PM UTC</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-03-25T14:20:00Z</t>
+          <t>2026-03-26T12:33:00Z</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>['https://x.com/AyshaMoham64638', 'https://x.com/Bushrasabih2', 'https://x.com/Salma2232019']</t>
+        </is>
+      </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
@@ -2539,10 +2681,10 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>145</v>
+        <v>5</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -2553,43 +2695,43 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2036804187833401607</t>
+          <t>2037145897285673425</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036804187833401607</t>
+          <t>https://x.com/Bushrasabih2/status/2037145897285673425</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/Bushrasabih2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>Bushrasabih2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Bu_shaikh🌸❤️</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2037057205510574080/OEGMy7R9_bigger.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>نأسف بشدة، وقد طلبنا من فريقنا الاتصال بك في أقرب وقت ممكن لمساعدتك. شكرًا لك.</t>
+          <t>Via the ENBD X Mobile App. @semeet @SelmaRomola @Bushrasabih1</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>نأسف بشدة، وقد طلبنا من فريقنا الاتصال بك في أقرب وقت ممكن لمساعدتك. شكرًا لك.</t>
+          <t>Via the ENBD X Mobile App. &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Bushrasabih1" title="Fahood Emarati"&gt;@Bushrasabih1&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J25" t="b">
@@ -2598,26 +2740,30 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['hamzzah99']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 1:55 PM UTC</t>
+          <t>Mar 26, 2026 · 12:33 PM UTC</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-03-25T13:55:00Z</t>
+          <t>2026-03-26T12:33:00Z</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/Bushrasabih1']</t>
+        </is>
+      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -2628,7 +2774,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2639,43 +2785,43 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2036803846417039482</t>
+          <t>2037145867833241998</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://x.com/hamzzah99/status/2036803846417039482</t>
+          <t>https://x.com/Bushrasabih2/status/2037145867833241998</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://x.com/hamzzah99</t>
+          <t>https://x.com/Bushrasabih2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>hamzzah99</t>
+          <t>Bushrasabih2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hamza 💙🤍</t>
+          <t>Bu_shaikh🌸❤️</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1628569116847087616/77YITtTX_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2037057205510574080/OEGMy7R9_bigger.jpg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>تواصلت خاص قبل فترة ونفس الرد ويتصلون في اوقات غير مناسبة</t>
+          <t>Via the ENBD X Mobile App. @semeet @SelmaRomola @Salma2232019</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>تواصلت خاص قبل فترة ونفس الرد ويتصلون في اوقات غير مناسبة</t>
+          <t>Via the ENBD X Mobile App. &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J26" t="b">
@@ -2689,23 +2835,27 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 1:54 PM UTC</t>
+          <t>Mar 26, 2026 · 12:33 PM UTC</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-03-25T13:54:00Z</t>
+          <t>2026-03-26T12:33:00Z</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/Salma2232019']</t>
+        </is>
+      </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2714,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -2725,43 +2875,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2036803555248513519</t>
+          <t>2037133107002798119</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036803555248513519</t>
+          <t>https://x.com/Mjoode181818/status/2037133107002798119</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/Mjoode181818</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>Mjoode181818</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Mjod_126</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1778387020219400192/yJx3OY9J_bigger.jpg</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>نشكركم على تواصلكم معنا، ونعتذر بشدة عن التأخير، وقد طلبنا من فريقنا التواصل معكم لإطلاعكم على آخر المستجدات في أقرب وقت ممكن. شكرًا.</t>
+          <t>عبدالمجيد عبدالله القرشي  رقم الجوال 0566622312</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>نشكركم على تواصلكم معنا، ونعتذر بشدة عن التأخير، وقد طلبنا من فريقنا التواصل معكم لإطلاعكم على آخر المستجدات في أقرب وقت ممكن. شكرًا.</t>
+          <t>عبدالمجيد عبدالله القرشي  رقم الجوال 0566622312</t>
         </is>
       </c>
       <c r="J27" t="b">
@@ -2770,22 +2920,22 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>['hamzzah99']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 1:53 PM UTC</t>
+          <t>Mar 26, 2026 · 11:42 AM UTC</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-03-25T13:53:00Z</t>
+          <t>2026-03-26T11:42:00Z</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -2797,10 +2947,10 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -2811,73 +2961,73 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2036803479503609971</t>
+          <t>2037130316544905693</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036803479503609971</t>
+          <t>https://x.com/Mjoode181818/status/2037130316544905693</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/Mjoode181818</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>Mjoode181818</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Mjod_126</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1778387020219400192/yJx3OY9J_bigger.jpg</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Thanks for reaching us and we are extremely sorry for the delay and we have asked our team to contact you with an update as soon as possible. Thanks</t>
+          <t>@EmiratesNBD_AE  سلام عليكم شراء مدينية كم النسبة ؟</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Thanks for reaching us and we are extremely sorry for the delay and we have asked our team to contact you with an update as soon as possible. Thanks</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;  سلام عليكم شراء مدينية كم النسبة ؟</t>
         </is>
       </c>
       <c r="J28" t="b">
         <v>0</v>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>['hamzzah99']</t>
-        </is>
-      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 1:52 PM UTC</t>
+          <t>Mar 26, 2026 · 11:31 AM UTC</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-03-25T13:52:00Z</t>
+          <t>2026-03-26T11:31:00Z</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2886,7 +3036,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -2897,43 +3047,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2036802785895678272</t>
+          <t>2037130259007426571</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://x.com/hamzzah99/status/2036802785895678272</t>
+          <t>https://x.com/AliAycha9/status/2037130259007426571</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://x.com/hamzzah99</t>
+          <t>https://x.com/AliAycha9</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>hamzzah99</t>
+          <t>AliAycha9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hamza 💙🤍</t>
+          <t>Ali Aycha</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1628569116847087616/77YITtTX_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1472637599286243330/X0vFG6qG_bigger.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>It's been over 18 days for a service that was supposed to be 3 days, and it hasn't been completed. When we called, they said it would be escalated and our request would be processed, but nothing has been done.</t>
+          <t>I was told the Visa card is free, yet I was charged SAR 800 with no explanation. I filed a complaint and got no response. Misleading and unacceptable. Will escalate to SAMA if not resolved.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>It&amp;#39;s been over 18 days for a service that was supposed to be 3 days, and it hasn&amp;#39;t been completed. When we called, they said it would be escalated and our request would be processed, but nothing has been done.</t>
+          <t>I was told the Visa card is free, yet I was charged SAR 800 with no explanation. I filed a complaint and got no response. Misleading and unacceptable. Will escalate to SAMA if not resolved.</t>
         </is>
       </c>
       <c r="J29" t="b">
@@ -2947,17 +3097,17 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 1:50 PM UTC</t>
+          <t>Mar 26, 2026 · 11:31 AM UTC</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-03-25T13:50:00Z</t>
+          <t>2026-03-26T11:31:00Z</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -2972,7 +3122,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -2983,43 +3133,45 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2036802694979969378</t>
+          <t>2037129872498098414</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://x.com/hamzzah99/status/2036802694979969378</t>
+          <t>https://x.com/AliAycha9/status/2037129872498098414</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://x.com/hamzzah99</t>
+          <t>https://x.com/AliAycha9</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>hamzzah99</t>
+          <t>AliAycha9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hamza 💙🤍</t>
+          <t>Ali Aycha</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1628569116847087616/77YITtTX_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1472637599286243330/X0vFG6qG_bigger.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>اكثر من 18 يوم عشان خدمة مدتها 3 ايام لم تنفذ واذا اتصلنا قالو سوف يتم التصعيد وسيتم تفيد طلبك دون جدوى</t>
+          <t>أنا مستاء جداً من أسلوب التعامل. تم إبلاغي أن بطاقة الفيزا مجانية، وبعدها تم خصم مبلغ 800 ريال بدون توضيح. تقدمت باعتراض رسمي وحتى الآن لا يوجد أي رد. هذا غير مقبول ويضر بثقة العملاء. نرجو التوضيح والمعالجة فوراً.
+@EmiratesNBD</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>اكثر من 18 يوم عشان خدمة مدتها 3 ايام لم تنفذ واذا اتصلنا قالو سوف يتم التصعيد وسيتم تفيد طلبك دون جدوى</t>
+          <t>أنا مستاء جداً من أسلوب التعامل. تم إبلاغي أن بطاقة الفيزا مجانية، وبعدها تم خصم مبلغ 800 ريال بدون توضيح. تقدمت باعتراض رسمي وحتى الآن لا يوجد أي رد. هذا غير مقبول ويضر بثقة العملاء. نرجو التوضيح والمعالجة فوراً.
+&lt;a href="/EmiratesNBD" title="Emirates NBD"&gt;@EmiratesNBD&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J30" t="b">
@@ -3033,21 +3185,25 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 1:49 PM UTC</t>
+          <t>Mar 26, 2026 · 11:29 AM UTC</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-03-25T13:49:00Z</t>
+          <t>2026-03-26T11:29:00Z</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD']</t>
+        </is>
+      </c>
       <c r="R30" t="n">
         <v>1</v>
       </c>
@@ -3058,7 +3214,7 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -3069,77 +3225,83 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2036796926939578566</t>
+          <t>2037090046386504097</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036796926939578566</t>
+          <t>https://x.com/intisar_ma/status/2037090046386504097</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/intisar_ma</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>intisar_ma</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>إنتصار #بالعربي</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1514738234890280966/iqN82FvB_bigger.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Get guaranteed vouchers worth of AED750
-Apply for Emirates NBD SHARE Visa Credit Card and receive a guaranteed Majid Al Futtaim voucher worth AED 750.
-Apply Now: apply.emiratesnbd.com/en/cre…</t>
+          <t>B) 1.89%
+@Om__saad_ 
+@IMoakts 
+@um_maazz</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Get guaranteed vouchers worth of AED750
-Apply for Emirates NBD SHARE Visa Credit Card and receive a guaranteed Majid Al Futtaim voucher worth AED 750.
-Apply Now: &lt;a href="https://apply.emiratesnbd.com/en/credit-card/maf"&gt;apply.emiratesnbd.com/en/cre…&lt;/a&gt;</t>
+          <t>B) 1.89%
+&lt;a href="/Om__saad_" title="om_saad"&gt;@Om__saad_&lt;/a&gt; 
+&lt;a href="/IMoakts" title="ORYX Moakts"&gt;@IMoakts&lt;/a&gt; 
+&lt;a href="/um_maazz" title="um_maaz"&gt;@um_maazz&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J31" t="b">
         <v>0</v>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 1:26 PM UTC</t>
+          <t>Mar 26, 2026 · 8:51 AM UTC</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-03-25T13:26:00Z</t>
+          <t>2026-03-26T08:51:00Z</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>['https://apply.emiratesnbd.com/en/credit-card/maf']</t>
+          <t>['https://x.com/Om__saad_', 'https://x.com/IMoakts', 'https://x.com/um_maazz']</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3148,7 +3310,7 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>468</v>
+        <v>5</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -3159,151 +3321,79 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2036791503868281341</t>
+          <t>2037089704685035906</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://x.com/adisatrader/status/2036791503868281341</t>
+          <t>https://x.com/intisar_ma/status/2037089704685035906</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://x.com/adisatrader</t>
+          <t>https://x.com/intisar_ma</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>adisatrader</t>
+          <t>intisar_ma</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AD.Trader</t>
+          <t>إنتصار #بالعربي</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1848073601280573440/NI8qeR5q_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1514738234890280966/iqN82FvB_bigger.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>AWS機房被炸之後：加密貨幣在戰爭裡是什麼角色
-帳戶裡有錢、卻動不了它。這才是現代戰爭最殘忍的一刀
-你以為分散配置了。但你有沒有想過，那些資產在你最需要的時候，根本不在你身邊？
-伊朗無人機炸了 AWS 在阿聯酋與巴林的三座機房。
-Emirates NBD、ADCB 當機。POS 刷不了。叫車 App 開不了。
-你的錢還在帳戶裡。
-你就是碰不到它。
-▋ AWS 事件炸出來的，其實是傳統金融的地基
-很多人看到這則新聞的第一反應：「連雲端都能被炸，加密貨幣一樣沒用。」
-這句話差一點就說對了。差在哪裡，很重要。
-網路中斷，確實讓你暫時無法動用鏈上資產。但你的 BTC 仍然鎖在那個 address 裡，一點都沒少。比特幣這條鏈的節點跑在全球數萬台機器上，沒有一個「總機房」能被定點清除。
-真正的問題從來不是「資產消失了」，而是「你能不能到達一個有網路的地方」。
-一旦你跨出戰區，帶著助記詞，錢包打開，一切立刻回來。銀行存款在當地系統裡動不了，房地產你帶不走，保管箱的黃金你扛不動。加密資產在這個維度上的優勢，不是靠敘事支撐的，是架構決定的。
-▋ 黃金的硬傷，沒有人在牛市裡願意正視
-黃金的長期避險邏輯無法反駁，幾千年的數據擺在那裡。
-但戰爭場景不是理論題。
-你能帶多少重量過邊境？邊境稽查時，金條比什麼都顯眼。部分政權對黃金的態度是：看到就沒收，找個理由很容易。就算你帶出去了，到了一個陌生的國家，你要找誰換？用什麼匯率？這中間的摩擦成本，在你最需要流動性的那一刻，會大到出乎你意料。
-黃金的問題不是「沒有價值」，是它的價值在你最需要「帶著跑」的那個當下，幾乎無法被你實際兌現。
-▋ 三種資產在戰場上真正的樣子
-本地現金在秩序還在的時候最好用，POS 能刷、找零沒問題。但銀行關門、ATM 停擺之後，那疊紙鈔接下來值多少，是另一回事。出了境，戰亂國家的法幣通常只剩紀念價值。
-黃金跨境有摩擦，兌現有摩擦，在極端情境下甚至有被沒收的風險。作為長期儲值它是對的，但當你需要它動起來的時候，它太重、太慢、太顯眼。
-加密資產短期支付確實依賴網路，這點不用美化。但一旦你能到有網路的地方，它的跨境流動性是其他資產比不上的。12個字的助記詞，可以穿過任何邊境，沒有重量，沒有顯眼的體積，沒有任何政府能在你腦子裡搜查什麼。
-沒有完美資產。但「帶著跑」這件事，結構上就是加密資產的主場。
-▋ 集中式基礎設施的脆弱，這次只是預演
-這次中斷的根本原因很簡單：多數銀行和支付公司把核心系統壓在幾個雲端區域，某個地理位置出事，整個區域的金融服務就一起倒。
-公鏈不是這個架構。沒有單一攻擊點，局部斷網只影響你此刻的接取，不影響資產本身的存在。在真實的地緣衝突裡，這種去中心化的基礎設施反而比很多人想像中的「國家級關鍵基礎設施」更難被完整打趴。
-這次是預演，不是終局。
-▋ 如果換成是你的城市，現在能怎麼做
-資產配置上，實體現金留夠應付短期停網下的本地消費，但別把所有流動資金壓在單一法幣。黃金作為長期儲值是合理的，只是要對攜帶和過境的實際成本有清醒認識。主流加密資產和穩定幣，要有一部分在自託管狀態。硬體錢包、助記詞離線備份，缺一不可。
-工具面，助記詞不能只存在手機備忘錄或雲端。想清楚一個問題：如果手機壞掉、SIM 卡同時失效，你靠什麼打開你的錢包？
-出場路徑，想像一個具體場景：你帶著護照和一組助記詞，抵達一個陌生國家，國內的帳戶全部碰不到。
-這時你需要的，是一個在多國都有法幣出入金管道、P2P 市場夠深、KYC 流程不會在最糟糕的時機卡住你的平台。
-像 @binancezh 這類全球性交易所，在這個場景裡的價值不是廣告詞。是當某個地區的銀行系統已經失能，你還能透過其他司法轄區的出入金管道或 P2P 市場，把鏈上資產換成當地能用的現金。這個路徑平時看起來是備用選項，到了那個時刻，它是唯一選項。
-前提一樣：身份驗證要早做，介面要熟，不是等事情發生了才去摸索。戰爭爆發那天才臨時下載 App，已經太慢了。
-你讀完這篇，心裡有個聲音說「有道理，改天認真研究一下」。我知道，因為大多數人的反應都是這樣，然後他們繼續維持現在的配置，繼續做一樣的決策。
-問題不在於你懂不懂這些道理。
-問題在於：你的配置裡有沒有覆蓋到「尾部」。
-過去十年，COVID、烏俄戰爭、中東升溫、銀行擠兌、穩
-定幣脫鉤。每一次事件發生前，都有人說這種事不會發生，機率很低，不值得為它調整策略。他們說的沒有錯。機率確實低。但期望值是機率乘以損失幅度，不是只算機率。
-倖存者偏差的運作方式很安靜：在你遇到那個尾部事件之前，你的系統看起來一直都是對的。你活著，所以策略有效。直到有一天它突然無效。那天你才會明白這道數學是怎麼對你生效的。
-市場從不需要你相信它。
-它只需要時間。</t>
+          <t>Exchanger Volunteering Program
+@Om__saad_ 
+@um_fayzza 
+@um_maazz</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>AWS機房被炸之後：加密貨幣在戰爭裡是什麼角色
-帳戶裡有錢、卻動不了它。這才是現代戰爭最殘忍的一刀
-你以為分散配置了。但你有沒有想過，那些資產在你最需要的時候，根本不在你身邊？
-伊朗無人機炸了 AWS 在阿聯酋與巴林的三座機房。
-Emirates NBD、ADCB 當機。POS 刷不了。叫車 App 開不了。
-你的錢還在帳戶裡。
-你就是碰不到它。
-▋ AWS 事件炸出來的，其實是傳統金融的地基
-很多人看到這則新聞的第一反應：「連雲端都能被炸，加密貨幣一樣沒用。」
-這句話差一點就說對了。差在哪裡，很重要。
-網路中斷，確實讓你暫時無法動用鏈上資產。但你的 BTC 仍然鎖在那個 address 裡，一點都沒少。比特幣這條鏈的節點跑在全球數萬台機器上，沒有一個「總機房」能被定點清除。
-真正的問題從來不是「資產消失了」，而是「你能不能到達一個有網路的地方」。
-一旦你跨出戰區，帶著助記詞，錢包打開，一切立刻回來。銀行存款在當地系統裡動不了，房地產你帶不走，保管箱的黃金你扛不動。加密資產在這個維度上的優勢，不是靠敘事支撐的，是架構決定的。
-▋ 黃金的硬傷，沒有人在牛市裡願意正視
-黃金的長期避險邏輯無法反駁，幾千年的數據擺在那裡。
-但戰爭場景不是理論題。
-你能帶多少重量過邊境？邊境稽查時，金條比什麼都顯眼。部分政權對黃金的態度是：看到就沒收，找個理由很容易。就算你帶出去了，到了一個陌生的國家，你要找誰換？用什麼匯率？這中間的摩擦成本，在你最需要流動性的那一刻，會大到出乎你意料。
-黃金的問題不是「沒有價值」，是它的價值在你最需要「帶著跑」的那個當下，幾乎無法被你實際兌現。
-▋ 三種資產在戰場上真正的樣子
-本地現金在秩序還在的時候最好用，POS 能刷、找零沒問題。但銀行關門、ATM 停擺之後，那疊紙鈔接下來值多少，是另一回事。出了境，戰亂國家的法幣通常只剩紀念價值。
-黃金跨境有摩擦，兌現有摩擦，在極端情境下甚至有被沒收的風險。作為長期儲值它是對的，但當你需要它動起來的時候，它太重、太慢、太顯眼。
-加密資產短期支付確實依賴網路，這點不用美化。但一旦你能到有網路的地方，它的跨境流動性是其他資產比不上的。12個字的助記詞，可以穿過任何邊境，沒有重量，沒有顯眼的體積，沒有任何政府能在你腦子裡搜查什麼。
-沒有完美資產。但「帶著跑」這件事，結構上就是加密資產的主場。
-▋ 集中式基礎設施的脆弱，這次只是預演
-這次中斷的根本原因很簡單：多數銀行和支付公司把核心系統壓在幾個雲端區域，某個地理位置出事，整個區域的金融服務就一起倒。
-公鏈不是這個架構。沒有單一攻擊點，局部斷網只影響你此刻的接取，不影響資產本身的存在。在真實的地緣衝突裡，這種去中心化的基礎設施反而比很多人想像中的「國家級關鍵基礎設施」更難被完整打趴。
-這次是預演，不是終局。
-▋ 如果換成是你的城市，現在能怎麼做
-資產配置上，實體現金留夠應付短期停網下的本地消費，但別把所有流動資金壓在單一法幣。黃金作為長期儲值是合理的，只是要對攜帶和過境的實際成本有清醒認識。主流加密資產和穩定幣，要有一部分在自託管狀態。硬體錢包、助記詞離線備份，缺一不可。
-工具面，助記詞不能只存在手機備忘錄或雲端。想清楚一個問題：如果手機壞掉、SIM 卡同時失效，你靠什麼打開你的錢包？
-出場路徑，想像一個具體場景：你帶著護照和一組助記詞，抵達一個陌生國家，國內的帳戶全部碰不到。
-這時你需要的，是一個在多國都有法幣出入金管道、P2P 市場夠深、KYC 流程不會在最糟糕的時機卡住你的平台。
-像 &lt;a href="/binancezh" title="币安Binance华语"&gt;@binancezh&lt;/a&gt; 這類全球性交易所，在這個場景裡的價值不是廣告詞。是當某個地區的銀行系統已經失能，你還能透過其他司法轄區的出入金管道或 P2P 市場，把鏈上資產換成當地能用的現金。這個路徑平時看起來是備用選項，到了那個時刻，它是唯一選項。
-前提一樣：身份驗證要早做，介面要熟，不是等事情發生了才去摸索。戰爭爆發那天才臨時下載 App，已經太慢了。
-你讀完這篇，心裡有個聲音說「有道理，改天認真研究一下」。我知道，因為大多數人的反應都是這樣，然後他們繼續維持現在的配置，繼續做一樣的決策。
-問題不在於你懂不懂這些道理。
-問題在於：你的配置裡有沒有覆蓋到「尾部」。
-過去十年，COVID、烏俄戰爭、中東升溫、銀行擠兌、穩
-定幣脫鉤。每一次事件發生前，都有人說這種事不會發生，機率很低，不值得為它調整策略。他們說的沒有錯。機率確實低。但期望值是機率乘以損失幅度，不是只算機率。
-倖存者偏差的運作方式很安靜：在你遇到那個尾部事件之前，你的系統看起來一直都是對的。你活著，所以策略有效。直到有一天它突然無效。那天你才會明白這道數學是怎麼對你生效的。
-市場從不需要你相信它。
-它只需要時間。</t>
+          <t>Exchanger Volunteering Program
+&lt;a href="/Om__saad_" title="om_saad"&gt;@Om__saad_&lt;/a&gt; 
+&lt;a href="/um_fayzza" title="um_fayzza"&gt;@um_fayzza&lt;/a&gt; 
+&lt;a href="/um_maazz" title="um_maaz"&gt;@um_maazz&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J32" t="b">
         <v>0</v>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 1:05 PM UTC</t>
+          <t>Mar 26, 2026 · 8:50 AM UTC</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-03-25T13:05:00Z</t>
+          <t>2026-03-26T08:50:00Z</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>['https://x.com/binancezh']</t>
+          <t>['https://x.com/Om__saad_', 'https://x.com/um_fayzza', 'https://x.com/um_maazz']</t>
         </is>
       </c>
       <c r="R32" t="n">
@@ -3316,7 +3406,7 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -3327,43 +3417,49 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2036789515558543658</t>
+          <t>2037089460995973485</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036789515558543658</t>
+          <t>https://x.com/intisar_ma/status/2037089460995973485</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/intisar_ma</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>intisar_ma</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>إنتصار #بالعربي</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1514738234890280966/iqN82FvB_bigger.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>B- 1.89% @parulghalout @semeet @SelmaRomola</t>
+          <t>FINWELL - Financial well being program with #ENBD
+@Om__saad_ 
+@Fr638 
+@um_maazz</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>B- 1.89% &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
+          <t>FINWELL - Financial well being program with &lt;a href="/search?f=tweets&amp;amp;q=%23ENBD"&gt;#ENBD&lt;/a&gt;
+&lt;a href="/Om__saad_" title="om_saad"&gt;@Om__saad_&lt;/a&gt; 
+&lt;a href="/Fr638" title="Faris _m"&gt;@Fr638&lt;/a&gt; 
+&lt;a href="/um_maazz" title="um_maaz"&gt;@um_maazz&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J33" t="b">
@@ -3377,23 +3473,23 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:57 PM UTC</t>
+          <t>Mar 26, 2026 · 8:49 AM UTC</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-03-25T12:57:00Z</t>
+          <t>2026-03-26T08:49:00Z</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>['https://x.com/parulghalout', 'https://x.com/semeet', 'https://x.com/SelmaRomola']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23ENBD', 'https://x.com/Om__saad_', 'https://x.com/Fr638', 'https://x.com/um_maazz']</t>
         </is>
       </c>
       <c r="R33" t="n">
@@ -3406,7 +3502,7 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -3417,43 +3513,49 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2036789451557609902</t>
+          <t>2037089224999186915</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036789451557609902</t>
+          <t>https://x.com/intisar_ma/status/2037089224999186915</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/intisar_ma</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>intisar_ma</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>إنتصار #بالعربي</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1514738234890280966/iqN82FvB_bigger.jpg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>B- 1.89% @semeet @SelmaRomola @Emy191990</t>
+          <t>Via the ENBD X Mobile App.
+@um_fayzza 
+@um_maazz 
+@Om__saad_</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>B- 1.89% &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt;</t>
+          <t>Via the ENBD X Mobile App.
+&lt;a href="/um_fayzza" title="um_fayzza"&gt;@um_fayzza&lt;/a&gt; 
+&lt;a href="/um_maazz" title="um_maaz"&gt;@um_maazz&lt;/a&gt; 
+&lt;a href="/Om__saad_" title="om_saad"&gt;@Om__saad_&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J34" t="b">
@@ -3467,23 +3569,23 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:57 PM UTC</t>
+          <t>Mar 26, 2026 · 8:48 AM UTC</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-03-25T12:57:00Z</t>
+          <t>2026-03-26T08:48:00Z</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/Emy191990']</t>
+          <t>['https://x.com/um_fayzza', 'https://x.com/um_maazz', 'https://x.com/Om__saad_']</t>
         </is>
       </c>
       <c r="R34" t="n">
@@ -3507,43 +3609,49 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2036789382523523230</t>
+          <t>2037088389116420101</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036789382523523230</t>
+          <t>https://x.com/um_fayzza/status/2037088389116420101</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/um_fayzza</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>um_fayzza</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>um_fayzza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1642503113612427264/VvU4kQoo_bigger.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>B- 1.89% @ibushra_03 @Emy191990 @Salma2232019</t>
+          <t>B) 1.89% 
+@Om__saad_ 
+@intisar_ma 
+@um_maazz</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>B- 1.89% &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+          <t>B) 1.89% 
+&lt;a href="/Om__saad_" title="om_saad"&gt;@Om__saad_&lt;/a&gt; 
+&lt;a href="/intisar_ma" title="إنتصار #بالعربي"&gt;@intisar_ma&lt;/a&gt; 
+&lt;a href="/um_maazz" title="um_maaz"&gt;@um_maazz&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J35" t="b">
@@ -3557,23 +3665,23 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:56 PM UTC</t>
+          <t>Mar 26, 2026 · 8:44 AM UTC</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-03-25T12:56:00Z</t>
+          <t>2026-03-26T08:44:00Z</t>
         </is>
       </c>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>['https://x.com/ibushra_03', 'https://x.com/Emy191990', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/Om__saad_', 'https://x.com/intisar_ma', 'https://x.com/um_maazz']</t>
         </is>
       </c>
       <c r="R35" t="n">
@@ -3586,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -3597,43 +3705,49 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2036789305784586495</t>
+          <t>2037087819592851585</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036789305784586495</t>
+          <t>https://x.com/um_fayzza/status/2037087819592851585</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/um_fayzza</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>um_fayzza</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>um_fayzza</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1642503113612427264/VvU4kQoo_bigger.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>B- 1.89% @Salma2232019 @SelmaRomola @Emy191990</t>
+          <t>Exchanger Volunteering Program
+@Om__saad_ 
+@um_maazz 
+@intisar_ma</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>B- 1.89% &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt;</t>
+          <t>Exchanger Volunteering Program
+&lt;a href="/Om__saad_" title="om_saad"&gt;@Om__saad_&lt;/a&gt; 
+&lt;a href="/um_maazz" title="um_maaz"&gt;@um_maazz&lt;/a&gt; 
+&lt;a href="/intisar_ma" title="إنتصار #بالعربي"&gt;@intisar_ma&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J36" t="b">
@@ -3647,23 +3761,23 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:56 PM UTC</t>
+          <t>Mar 26, 2026 · 8:42 AM UTC</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-03-25T12:56:00Z</t>
+          <t>2026-03-26T08:42:00Z</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>['https://x.com/Salma2232019', 'https://x.com/SelmaRomola', 'https://x.com/Emy191990']</t>
+          <t>['https://x.com/Om__saad_', 'https://x.com/um_maazz', 'https://x.com/intisar_ma']</t>
         </is>
       </c>
       <c r="R36" t="n">
@@ -3676,7 +3790,7 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -3687,43 +3801,49 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2036789246493851944</t>
+          <t>2037087309808730569</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036789246493851944</t>
+          <t>https://x.com/um_fayzza/status/2037087309808730569</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/um_fayzza</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>um_fayzza</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>um_fayzza</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1642503113612427264/VvU4kQoo_bigger.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>B- 1.89% @semeet @SelmaRomola @ibushra_03</t>
+          <t>FINWELL - Financial well being program with #ENBD
+@um_maazz 
+@Om__saad_ 
+@Fr638</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>B- 1.89% &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
+          <t>FINWELL - Financial well being program with &lt;a href="/search?f=tweets&amp;amp;q=%23ENBD"&gt;#ENBD&lt;/a&gt;
+&lt;a href="/um_maazz" title="um_maaz"&gt;@um_maazz&lt;/a&gt; 
+&lt;a href="/Om__saad_" title="om_saad"&gt;@Om__saad_&lt;/a&gt; 
+&lt;a href="/Fr638" title="Faris _m"&gt;@Fr638&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J37" t="b">
@@ -3737,23 +3857,23 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:56 PM UTC</t>
+          <t>Mar 26, 2026 · 8:40 AM UTC</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-03-25T12:56:00Z</t>
+          <t>2026-03-26T08:40:00Z</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/ibushra_03']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23ENBD', 'https://x.com/um_maazz', 'https://x.com/Om__saad_', 'https://x.com/Fr638']</t>
         </is>
       </c>
       <c r="R37" t="n">
@@ -3766,7 +3886,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -3777,43 +3897,43 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2036789179338920208</t>
+          <t>2037086888473821344</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036789179338920208</t>
+          <t>https://x.com/hamzzah99/status/2037086888473821344</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/hamzzah99</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>hamzzah99</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>Hamza 💙🤍</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1628569116847087616/77YITtTX_bigger.jpg</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>B- 1.89% @Emy191990 @ibushra_03 @parulghalout</t>
+          <t>كيف انحلت المشكلة !! ولم يصلني اي اشعار من البنك لم يتواصل معي احد ولم تحل المشكلة</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>B- 1.89% &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
+          <t>كيف انحلت المشكلة !! ولم يصلني اي اشعار من البنك لم يتواصل معي احد ولم تحل المشكلة</t>
         </is>
       </c>
       <c r="J38" t="b">
@@ -3827,27 +3947,23 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:55 PM UTC</t>
+          <t>Mar 26, 2026 · 8:38 AM UTC</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-03-25T12:55:00Z</t>
+          <t>2026-03-26T08:38:00Z</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -3856,7 +3972,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -3867,43 +3983,49 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2036789007674482934</t>
+          <t>2037086283395457236</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036789007674482934</t>
+          <t>https://x.com/um_fayzza/status/2037086283395457236</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/um_fayzza</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>um_fayzza</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>um_fayzza</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1642503113612427264/VvU4kQoo_bigger.jpg</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @Emy191990 @Salma2232019 @semeet</t>
+          <t>Via the ENBD X Mobile App.
+@um_maazz 
+@Om__saad_ 
+@Fr638</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt;</t>
+          <t>Via the ENBD X Mobile App.
+&lt;a href="/um_maazz" title="um_maaz"&gt;@um_maazz&lt;/a&gt; 
+&lt;a href="/Om__saad_" title="om_saad"&gt;@Om__saad_&lt;/a&gt; 
+&lt;a href="/Fr638" title="Faris _m"&gt;@Fr638&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J39" t="b">
@@ -3917,23 +4039,23 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:55 PM UTC</t>
+          <t>Mar 26, 2026 · 8:36 AM UTC</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-03-25T12:55:00Z</t>
+          <t>2026-03-26T08:36:00Z</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
+          <t>['https://x.com/um_maazz', 'https://x.com/Om__saad_', 'https://x.com/Fr638']</t>
         </is>
       </c>
       <c r="R39" t="n">
@@ -3946,7 +4068,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -3957,43 +4079,49 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2036788941731577874</t>
+          <t>2037086066398945628</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036788941731577874</t>
+          <t>https://x.com/um_fayzza/status/2037086066398945628</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/um_fayzza</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>um_fayzza</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>um_fayzza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1642503113612427264/VvU4kQoo_bigger.jpg</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @semeet @SelmaRomola @ibushra_03</t>
+          <t>Via the ENBD X Mobile App
+@um_maazz 
+@Om__saad_ 
+@Fr638</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
+          <t>Via the ENBD X Mobile App
+&lt;a href="/um_maazz" title="um_maaz"&gt;@um_maazz&lt;/a&gt; 
+&lt;a href="/Om__saad_" title="om_saad"&gt;@Om__saad_&lt;/a&gt; 
+&lt;a href="/Fr638" title="Faris _m"&gt;@Fr638&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J40" t="b">
@@ -4007,23 +4135,23 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:55 PM UTC</t>
+          <t>Mar 26, 2026 · 8:35 AM UTC</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-03-25T12:55:00Z</t>
+          <t>2026-03-26T08:35:00Z</t>
         </is>
       </c>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/ibushra_03']</t>
+          <t>['https://x.com/um_maazz', 'https://x.com/Om__saad_', 'https://x.com/Fr638']</t>
         </is>
       </c>
       <c r="R40" t="n">
@@ -4036,7 +4164,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -4047,43 +4175,43 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2036788876954812619</t>
+          <t>2037058002759324095</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036788876954812619</t>
+          <t>https://x.com/hamzzah99/status/2037058002759324095</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/hamzzah99</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>hamzzah99</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>Hamza 💙🤍</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1628569116847087616/77YITtTX_bigger.jpg</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @Emy191990 @parulghalout @ibushra_03</t>
+          <t>لم يتواصل معي احد حتى الآن لإنهاء المشكلة</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
+          <t>لم يتواصل معي احد حتى الآن لإنهاء المشكلة</t>
         </is>
       </c>
       <c r="J41" t="b">
@@ -4097,27 +4225,23 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:54 PM UTC</t>
+          <t>Mar 26, 2026 · 6:44 AM UTC</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-03-25T12:54:00Z</t>
+          <t>2026-03-26T06:44:00Z</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/ibushra_03']</t>
-        </is>
-      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -4126,7 +4250,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -4137,54 +4261,52 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2036788786441629924</t>
+          <t>2037148064096415790</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036788786441629924</t>
+          <t>https://x.com/emiratesislamic/status/2037148064096415790</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @semeet @Emy191990 @ibushra_03</t>
+          <t>Stay safe and bank easily with EI + and businessONLINE.
+#EmiratesIslamic</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt;</t>
+          <t>Stay safe and bank easily with EI + and businessONLINE.
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J42" t="b">
         <v>0</v>
       </c>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>15h</t>
@@ -4192,18 +4314,18 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:54 PM UTC</t>
+          <t>Mar 26, 2026 · 12:42 PM UTC</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-03-25T12:54:00Z</t>
+          <t>2026-03-26T12:42:00Z</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/Emy191990', 'https://x.com/ibushra_03']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic']</t>
         </is>
       </c>
       <c r="R42" t="n">
@@ -4216,65 +4338,63 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2036788720435962160</t>
+          <t>2037148052255875186</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036788720435962160</t>
+          <t>https://x.com/emiratesislamic/status/2037148052255875186</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @Salma2232019 @parulghalout @SelmaRomola</t>
+          <t>ابقّ آمناً وأنجز معاملاتك المصرفية بسهولة مع تطبيق + EI ومنصة businessONLINE.
+#الإمارات_الإسلامي</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
+          <t>ابقّ آمناً وأنجز معاملاتك المصرفية بسهولة مع تطبيق + EI ومنصة businessONLINE.
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J43" t="b">
         <v>0</v>
       </c>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>15h</t>
@@ -4282,18 +4402,18 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:54 PM UTC</t>
+          <t>Mar 26, 2026 · 12:41 PM UTC</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-03-25T12:54:00Z</t>
+          <t>2026-03-26T12:41:00Z</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>['https://x.com/Salma2232019', 'https://x.com/parulghalout', 'https://x.com/SelmaRomola']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي']</t>
         </is>
       </c>
       <c r="R43" t="n">
@@ -4306,54 +4426,56 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2036788631269171518</t>
+          <t>2037144761212023024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036788631269171518</t>
+          <t>https://x.com/emiratesislamic/status/2037144761212023024</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program @Emy191990 @parulghalout @SelmaRomola</t>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt;</t>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
         </is>
       </c>
       <c r="J44" t="b">
@@ -4362,7 +4484,7 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['abuzubayr1987']</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4372,20 +4494,16 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:53 PM UTC</t>
+          <t>Mar 26, 2026 · 12:28 PM UTC</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2026-03-25T12:53:00Z</t>
+          <t>2026-03-26T12:28:00Z</t>
         </is>
       </c>
       <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/SelmaRomola']</t>
-        </is>
-      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -4396,54 +4514,54 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2036788436074631193</t>
+          <t>2037144700109337063</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036788436074631193</t>
+          <t>https://x.com/emiratesislamic/status/2037144700109337063</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD @Salma2232019 @SelmaRomola @semeet</t>
+          <t>Hello, we apologize for your recent experience, and we're committed to resolving the issue promptly. Kindly note that we will connect with you on private messaging to serve you better.. We appreciate your patience as we work to assist you effectively.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt;</t>
+          <t>Hello, we apologize for your recent experience, and we&amp;#39;re committed to resolving the issue promptly. Kindly note that we will connect with you on private messaging to serve you better.. We appreciate your patience as we work to assist you effectively.</t>
         </is>
       </c>
       <c r="J45" t="b">
@@ -4452,7 +4570,7 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['abuzubayr1987']</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4462,20 +4580,16 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:52 PM UTC</t>
+          <t>Mar 26, 2026 · 12:28 PM UTC</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-03-25T12:52:00Z</t>
+          <t>2026-03-26T12:28:00Z</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>['https://x.com/Salma2232019', 'https://x.com/SelmaRomola', 'https://x.com/semeet']</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -4486,84 +4600,82 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2036788367770435626</t>
+          <t>2037131478010929182</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036788367770435626</t>
+          <t>https://x.com/kdkingdongmedia/status/2037131478010929182</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/kdkingdongmedia</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>kdkingdongmedia</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>KD Kingdong Media</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1778323297215848448/5mY7zvci_bigger.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD @semeet @SelmaRomola @Emy191990</t>
+          <t>KD Media Group brought Emirates Islamic Bank to life across key retail destinations and premium malls in Dubai where strategy meets visibility and every square foot counts.
+#KDMediaGroup #EmiratesIslamicBank #RetailActivation #BrandActivation #Dubai</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt;</t>
+          <t>KD Media Group brought Emirates Islamic Bank to life across key retail destinations and premium malls in Dubai where strategy meets visibility and every square foot counts.
+&lt;a href="/search?f=tweets&amp;amp;q=%23KDMediaGroup"&gt;#KDMediaGroup&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamicBank"&gt;#EmiratesIslamicBank&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23RetailActivation"&gt;#RetailActivation&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23BrandActivation"&gt;#BrandActivation&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J46" t="b">
         <v>0</v>
       </c>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:52 PM UTC</t>
+          <t>Mar 26, 2026 · 11:36 AM UTC</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2026-03-25T12:52:00Z</t>
+          <t>2026-03-26T11:36:00Z</t>
         </is>
       </c>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/Emy191990']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23KDMediaGroup', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamicBank', 'https://x.com/search?f=tweets&amp;q=%23RetailActivation', 'https://x.com/search?f=tweets&amp;q=%23BrandActivation', 'https://x.com/search?f=tweets&amp;q=%23Dubai']</t>
         </is>
       </c>
       <c r="R46" t="n">
@@ -4576,54 +4688,56 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2036788302997754337</t>
+          <t>2037112769967731076</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036788302997754337</t>
+          <t>https://x.com/emiratesislamic/status/2037112769967731076</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD @ibushra_03 @Emy191990 @Salma2232019</t>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>FINEELL ( Financial Well-being program) with Emirates NBD &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+          <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
+better please check your private message.</t>
         </is>
       </c>
       <c r="J47" t="b">
@@ -4632,30 +4746,26 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['dhara_katariya']</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:52 PM UTC</t>
+          <t>Mar 26, 2026 · 10:21 AM UTC</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-03-25T12:52:00Z</t>
+          <t>2026-03-26T10:21:00Z</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>['https://x.com/ibushra_03', 'https://x.com/Emy191990', 'https://x.com/Salma2232019']</t>
-        </is>
-      </c>
+      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -4666,54 +4776,54 @@
         <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2036788148525797451</t>
+          <t>2037112693383967013</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036788148525797451</t>
+          <t>https://x.com/emiratesislamic/status/2037112693383967013</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App @SelmaRomola @semeet @parulghalout</t>
+          <t>Hello, we apologize for your recent experience, and we're committed to resolving the issue promptly. Kindly note that we will connect with you on private messaging to serve you better. We appreciate your patience as we work to assist you effectively.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
+          <t>Hello, we apologize for your recent experience, and we&amp;#39;re committed to resolving the issue promptly. Kindly note that we will connect with you on private messaging to serve you better. We appreciate your patience as we work to assist you effectively.</t>
         </is>
       </c>
       <c r="J48" t="b">
@@ -4722,30 +4832,26 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['dhara_katariya']</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:51 PM UTC</t>
+          <t>Mar 26, 2026 · 10:21 AM UTC</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2026-03-25T12:51:00Z</t>
+          <t>2026-03-26T10:21:00Z</t>
         </is>
       </c>
       <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>['https://x.com/SelmaRomola', 'https://x.com/semeet', 'https://x.com/parulghalout']</t>
-        </is>
-      </c>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -4756,54 +4862,54 @@
         <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2036788078598336738</t>
+          <t>2037102014832730391</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036788078598336738</t>
+          <t>https://x.com/emiratesislamic/status/2037102014832730391</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App @Emy191990 @ibushra_03 @parulghalout</t>
+          <t>Hello. Thanks for getting in touch. To ensure your privacy, please note that we will connect with you through the direct message. We're happy to assist you</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
+          <t>Hello. Thanks for getting in touch. To ensure your privacy, please note that we will connect with you through the direct message. We&amp;#39;re happy to assist you</t>
         </is>
       </c>
       <c r="J49" t="b">
@@ -4812,30 +4918,26 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['naanrdk']</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:51 PM UTC</t>
+          <t>Mar 26, 2026 · 9:39 AM UTC</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-03-25T12:51:00Z</t>
+          <t>2026-03-26T09:39:00Z</t>
         </is>
       </c>
       <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
-        </is>
-      </c>
+      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -4846,54 +4948,58 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2036787984134242571</t>
+          <t>2037094634342744234</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036787984134242571</t>
+          <t>https://x.com/abuzubayr1987/status/2037094634342744234</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/abuzubayr1987</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>abuzubayr1987</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>Safwan</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App @ibushra_03 @parulghalout @Salma2232019</t>
+          <t>I was expecting a call back from the account manager of @emiratesislamic , got no calls or messages.
+Amazing, how without a notice an unfair 100% deduction is done leaving my family in lurch. I have been a customer since 2016!!!
+@JamalIslamic</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+          <t>I was expecting a call back from the account manager of &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; , got no calls or messages.
+Amazing, how without a notice an unfair 100% deduction is done leaving my family in lurch. I have been a customer since 2016!!!
+&lt;a href="/JamalIslamic" title="JAMAL BIN GHALIATA (CEO EMIRATES ISLAMIC BANK)"&gt;@JamalIslamic&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J50" t="b">
@@ -4902,32 +5008,32 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['centralbankuae', 'SanadakUAE']</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:51 PM UTC</t>
+          <t>Mar 26, 2026 · 9:09 AM UTC</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-03-25T12:51:00Z</t>
+          <t>2026-03-26T09:09:00Z</t>
         </is>
       </c>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>['https://x.com/ibushra_03', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/emiratesislamic', 'https://x.com/JamalIslamic']</t>
         </is>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -4936,176 +5042,180 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2036787923086106992</t>
+          <t>2037079016033681601</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036787923086106992</t>
+          <t>https://x.com/emiratesislamic/status/2037079016033681601</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App @semeet @SelmaRomola @Salma2232019</t>
+          <t>Small choices can make a big difference.
+Staying aware of your spending helps you stay in control — today and tomorrow.
+#FinancialWellbeing #Finwell #Spending  #EmiratesIslamic
+To know more, Visit:
+emiratesislamic.ae/en/key-in…</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt;</t>
+          <t>Small choices can make a big difference.
+Staying aware of your spending helps you stay in control — today and tomorrow.
+&lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Finwell"&gt;#Finwell&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Spending"&gt;#Spending&lt;/a&gt;  &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesIslamic"&gt;#EmiratesIslamic&lt;/a&gt;
+To know more, Visit:
+&lt;a href="https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/en/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J51" t="b">
         <v>0</v>
       </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:50 PM UTC</t>
+          <t>Mar 26, 2026 · 8:07 AM UTC</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-03-25T12:50:00Z</t>
+          <t>2026-03-26T08:07:00Z</t>
         </is>
       </c>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>['https://x.com/semeet', 'https://x.com/SelmaRomola', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23Finwell', 'https://x.com/search?f=tweets&amp;q=%23Spending', 'https://x.com/search?f=tweets&amp;q=%23EmiratesIslamic', 'https://www.emiratesislamic.ae/en/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
         </is>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U51" t="n">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2036787833776857213</t>
+          <t>2037072193339691240</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2036787833776857213</t>
+          <t>https://x.com/emiratesislamic/status/2037072193339691240</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Sosomostafa729S</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Soha.mostafa77</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App 
-@Emy191990 @ibushra_03 @parulghalout</t>
+          <t>القرارات الصغيرة تصنع فرقاً كبيراً.
+الانتباه لإنفاقك يساعدك على الحفاظ على التوازن، اليوم وعلى المدى الطويل
+لمعرفة المزيد:
+emiratesislamic.ae/ar/key-in…</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking&amp;#39;s App 
-&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;</t>
+          <t>القرارات الصغيرة تصنع فرقاً كبيراً.
+الانتباه لإنفاقك يساعدك على الحفاظ على التوازن، اليوم وعلى المدى الطويل
+لمعرفة المزيد:
+&lt;a href="https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;amp;utm_medium=website&amp;amp;utm_content=sliding_menu_2_eng&amp;amp;utm_campaign=finliteracy_082024"&gt;emiratesislamic.ae/ar/key-in…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J52" t="b">
         <v>0</v>
       </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:50 PM UTC</t>
+          <t>Mar 26, 2026 · 7:40 AM UTC</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2026-03-25T12:50:00Z</t>
+          <t>2026-03-26T07:40:00Z</t>
         </is>
       </c>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
+          <t>['https://www.emiratesislamic.ae/ar/key-information/financial-wellbeing?utm_source=homepage&amp;utm_medium=website&amp;utm_content=sliding_menu_2_eng&amp;utm_campaign=finliteracy_082024']</t>
         </is>
       </c>
       <c r="R52" t="n">
@@ -5118,54 +5228,62 @@
         <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2036784089479741604</t>
+          <t>2037046896078856635</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://x.com/ay_140/status/2036784089479741604</t>
+          <t>https://x.com/emiratesislamic/status/2037046896078856635</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://x.com/ay_140</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ay_140</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2027750913017094144/OvTR8OgR_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>ما يحتاج تقرا التقرير بس تشوف اداء سهم ENBD واديب وبتعرف</t>
+          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
+🔒 تغطية تكافلية مجانية
+يسري العرض لغاية 31 مارس 2026
+تطبق الشروط والأحكام
+emiratesislamic.ae/ar/offers…</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ما يحتاج تقرا التقرير بس تشوف اداء سهم ENBD واديب وبتعرف</t>
+          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
+🔒 تغطية تكافلية مجانية
+يسري العرض لغاية 31 مارس 2026
+تطبق الشروط والأحكام
+&lt;a href="https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=INMU_iphone17_022026"&gt;emiratesislamic.ae/ar/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J53" t="b">
@@ -5175,79 +5293,93 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:35 PM UTC</t>
+          <t>Mar 26, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-03-25T12:35:00Z</t>
+          <t>2026-03-26T06:00:00Z</t>
         </is>
       </c>
       <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/ar/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=INMU_iphone17_022026']</t>
+        </is>
+      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U53" t="n">
-        <v>980</v>
+        <v>88</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2036777554435363023</t>
+          <t>2037046896061993278</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://x.com/bno_cos21/status/2036777554435363023</t>
+          <t>https://x.com/emiratesislamic/status/2037046896061993278</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://x.com/bno_cos21</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>bno_cos21</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>紅尾</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1978076947768041472/SJW8V_vN_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>私のMBTI？はENBDチューブみたいなやつ</t>
+          <t>🏦 Finance amount of up to AED 4,000,000
+✈️Payment holiday up to 6 months 
+🔒 Complimentary Takaful coverage
+Offer valid until 31 March 2026
+T&amp;Cs apply
+emiratesislamic.ae/en/offers…</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>私のMBTI？はENBDチューブみたいなやつ</t>
+          <t>🏦 Finance amount of up to AED 4,000,000
+✈️Payment holiday up to 6 months 
+🔒 Complimentary Takaful coverage
+Offer valid until 31 March 2026
+T&amp;amp;Cs apply
+&lt;a href="https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;amp;utm_medium=social&amp;amp;utm_campaign=INMU_iphone17_02202"&gt;emiratesislamic.ae/en/offers…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J54" t="b">
@@ -5257,21 +5389,25 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 12:09 PM UTC</t>
+          <t>Mar 26, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-03-25T12:09:00Z</t>
+          <t>2026-03-26T06:00:00Z</t>
         </is>
       </c>
       <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>['https://www.emiratesislamic.ae/en/offers/get-personal-finance-and-enjoy-iphone17?utm_source=organic-twitter&amp;utm_medium=social&amp;utm_campaign=INMU_iphone17_02202']</t>
+        </is>
+      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -5282,90 +5418,86 @@
         <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2036765481072218459</t>
+          <t>2037046893448958277</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036765481072218459</t>
+          <t>https://x.com/emiratesislamic/status/2037046893448958277</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach to us at 
-social@emiratesnbd.com
-Quoting case #988352 in the subject line of the email from your registered email address
- We will make every effort to address the matter</t>
+          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي بقيمة 750,000 درهم أو أكثر.
+استمتع أيضاً بالمزايا الحصرية:
+📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
+🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach to us at 
-social@emiratesnbd.com
-Quoting case #988352 in the subject line of the email from your registered email address
- We will make every effort to address the matter</t>
+          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي بقيمة 750,000 درهم أو أكثر.
+استمتع أيضاً بالمزايا الحصرية:
+📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
+🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم</t>
         </is>
       </c>
       <c r="J55" t="b">
         <v>0</v>
       </c>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>['Aamir44530491']</t>
-        </is>
-      </c>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 11:21 AM UTC</t>
+          <t>Mar 26, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-03-25T11:21:00Z</t>
+          <t>2026-03-26T06:00:00Z</t>
         </is>
       </c>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -5374,78 +5506,78 @@
         <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>9</v>
+        <v>133</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>ENBD</t>
+          <t>EI</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2036764114912268547</t>
+          <t>2037046893415395737</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://x.com/Aamir44530491/status/2036764114912268547</t>
+          <t>https://x.com/emiratesislamic/status/2037046893415395737</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://x.com/Aamir44530491</t>
+          <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Aamir44530491</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aamir</t>
+          <t>emiratesislamic</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Dear My Enbd x app is not working I am not able to access my funds or not able to TRANSFER funds. Can you check and reply. Dubai</t>
+          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance of AED 750,000 or more.
+Also, enjoy exclusive benefits:
+📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Dear My Enbd x app is not working I am not able to access my funds or not able to TRANSFER funds. Can you check and reply. Dubai</t>
+          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance of AED 750,000 or more.
+Also, enjoy exclusive benefits:
+📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate.</t>
         </is>
       </c>
       <c r="J56" t="b">
         <v>0</v>
       </c>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE', 'rihandagarwal']</t>
-        </is>
-      </c>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Mar 25, 2026 · 11:16 AM UTC</t>
+          <t>Mar 26, 2026 · 6:00 AM UTC</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-03-25T11:16:00Z</t>
+          <t>2026-03-26T06:00:00Z</t>
         </is>
       </c>
       <c r="P56" t="inlineStr"/>
@@ -5460,2255 +5592,9 @@
         <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="V56" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2036751437909119306</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>https://x.com/ForbesME/status/2036751437909119306</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>https://x.com/ForbesME</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>ForbesME</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>فوربس الشرق الأوسط</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2033871674752339968/4leVeNHQ_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>الأصول المصرفية في #الإمارات تتخطى 5.4 تريليون درهم خلال يناير 2026، مع توسع الائتمان مدفوعًا بنمو الودائع المحلية وزيادة التمويل الموجه للاقتصاد.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>الأصول المصرفية في &lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات"&gt;#الإمارات&lt;/a&gt; تتخطى 5.4 تريليون درهم خلال يناير 2026، مع توسع الائتمان مدفوعًا بنمو الودائع المحلية وزيادة التمويل الموجه للاقتصاد.</t>
-        </is>
-      </c>
-      <c r="J57" t="b">
-        <v>0</v>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 · 10:25 AM UTC</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>2026-03-25T10:25:00Z</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23الإمارات']</t>
-        </is>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>11</v>
-      </c>
-      <c r="T57" t="n">
-        <v>14</v>
-      </c>
-      <c r="U57" t="n">
-        <v>4363</v>
-      </c>
-      <c r="V57" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2036744671699804303</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036744671699804303</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Emirates NBD</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>نشكركم على اهتمامكم بمنتجاتنا، يرجى زيارة الرابط أدناه وتعبئة بياناتكم، وسيتواصل معكم فريق المبيعات لدينا خلال يومي عمل. الحد الأدنى للراتب المطلوب هو 5000 درهم إماراتي. شكرًا - زبير
-beta.emiratesnbd.com/en/Camp…</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>نشكركم على اهتمامكم بمنتجاتنا، يرجى زيارة الرابط أدناه وتعبئة بياناتكم، وسيتواصل معكم فريق المبيعات لدينا خلال يومي عمل. الحد الأدنى للراتب المطلوب هو 5000 درهم إماراتي. شكرًا - زبير
-&lt;a href="https://beta.emiratesnbd.com/en/Campaigns/social-media-apply?SOURCE=&amp;amp;REF&amp;amp;ref=legacy&amp;amp;legacy_redirect=true"&gt;beta.emiratesnbd.com/en/Camp…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="J58" t="b">
-        <v>0</v>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>['saudigamdi07']</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 · 9:59 AM UTC</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>2026-03-25T09:59:00Z</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>['https://beta.emiratesnbd.com/en/Campaigns/social-media-apply?SOURCE=&amp;REF&amp;ref=legacy&amp;legacy_redirect=true']</t>
-        </is>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" t="n">
-        <v>51</v>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2036743492840423459</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>https://x.com/Bnok24/status/2036743492840423459</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>https://x.com/Bnok24</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Bnok24</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>bnok 24</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2035297929708113920/61ymWMLp_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>خدمة #Apple_Pay من #بنك_الإمارات_دبي الوطني تتيح الدفع بسهولة وأمان من خلال #Apple_Wallet أو #iPhone 
-التفاصيل|  bnok24.com/?p=255133</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>خدمة &lt;a href="/search?f=tweets&amp;amp;q=%23Apple_Pay"&gt;#Apple_Pay&lt;/a&gt; من &lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_دبي"&gt;#بنك_الإمارات_دبي&lt;/a&gt; الوطني تتيح الدفع بسهولة وأمان من خلال &lt;a href="/search?f=tweets&amp;amp;q=%23Apple_Wallet"&gt;#Apple_Wallet&lt;/a&gt; أو &lt;a href="/search?f=tweets&amp;amp;q=%23iPhone"&gt;#iPhone&lt;/a&gt; 
-التفاصيل|  &lt;a href="https://www.bnok24.com/?p=255133"&gt;bnok24.com/?p=255133&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="J59" t="b">
-        <v>0</v>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 · 9:54 AM UTC</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>2026-03-25T09:54:00Z</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23Apple_Pay', 'https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_دبي', 'https://x.com/search?f=tweets&amp;q=%23Apple_Wallet', 'https://x.com/search?f=tweets&amp;q=%23iPhone', 'https://www.bnok24.com/?p=255133']</t>
-        </is>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>0</v>
-      </c>
-      <c r="U59" t="n">
-        <v>7</v>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2036731298304196880</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>https://x.com/saudigamdi07/status/2036731298304196880</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>https://x.com/saudigamdi07</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>saudigamdi07</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>ملاكي</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>يقولو نسبكم في الامويل الشخصي ممتازة وتصل الى واحد ونصف لبعض الجهات 
-ابي استفسر عن كيف احصل ع خدمة شراء المديونية لمنتج البناء ذاتي القرض مدعوم</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>يقولو نسبكم في الامويل الشخصي ممتازة وتصل الى واحد ونصف لبعض الجهات 
-ابي استفسر عن كيف احصل ع خدمة شراء المديونية لمنتج البناء ذاتي القرض مدعوم</t>
-        </is>
-      </c>
-      <c r="J60" t="b">
-        <v>0</v>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 · 9:05 AM UTC</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>2026-03-25T09:05:00Z</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="n">
-        <v>1</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" t="n">
-        <v>179</v>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2036730808556490908</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>https://x.com/omarzooqi/status/2036730808556490908</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>https://x.com/omarzooqi</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>omarzooqi</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Omar Almarzooqi</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2035997907485429760/QlpL3FpP_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Connections are the real currency in Dubai 💼✨
-Had a great meeting at Emirates NBD – Al Satwa branch with Sameer Mohammed Al Bastaki.
-#DubaiBusiness #UAEBanking #NetworkingDubai #EmiratesNBD #dubailife</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Connections are the real currency in Dubai 💼✨
-Had a great meeting at Emirates NBD – Al Satwa branch with Sameer Mohammed Al Bastaki.
-&lt;a href="/search?f=tweets&amp;amp;q=%23DubaiBusiness"&gt;#DubaiBusiness&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAEBanking"&gt;#UAEBanking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NetworkingDubai"&gt;#NetworkingDubai&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23dubailife"&gt;#dubailife&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="J61" t="b">
-        <v>0</v>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 · 9:04 AM UTC</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>2026-03-25T09:04:00Z</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23DubaiBusiness', 'https://x.com/search?f=tweets&amp;q=%23UAEBanking', 'https://x.com/search?f=tweets&amp;q=%23NetworkingDubai', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23dubailife']</t>
-        </is>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>1</v>
-      </c>
-      <c r="U61" t="n">
-        <v>35</v>
-      </c>
-      <c r="V61" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2036727881976484208</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>https://x.com/hashim_fahmawi/status/2036727881976484208</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>https://x.com/hashim_fahmawi</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>hashim_fahmawi</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>المحلل الاقتصادي / هاشم الفحماوي</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1626339625345114112/dFHYINOP_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>#اعمار
-#اعمار_للتطوير
-#بنك_الامارات 
-تفرغة المؤشرات واضحه .
-ننتظر ارتفاع الشركات التى لم تتفاعل مع ارتفاع المؤشر.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23اعمار"&gt;#اعمار&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23اعمار_للتطوير"&gt;#اعمار_للتطوير&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الامارات"&gt;#بنك_الامارات&lt;/a&gt; 
-تفرغة المؤشرات واضحه .
-ننتظر ارتفاع الشركات التى لم تتفاعل مع ارتفاع المؤشر.</t>
-        </is>
-      </c>
-      <c r="J62" t="b">
-        <v>0</v>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>['hashim_fahmawi']</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 · 8:52 AM UTC</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>2026-03-25T08:52:00Z</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23اعمار', 'https://x.com/search?f=tweets&amp;q=%23اعمار_للتطوير', 'https://x.com/search?f=tweets&amp;q=%23بنك_الامارات']</t>
-        </is>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" t="n">
-        <v>2</v>
-      </c>
-      <c r="U62" t="n">
-        <v>1531</v>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2036716463508291618</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>https://x.com/talent_folder/status/2036716463508291618</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>https://x.com/talent_folder</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>talent_folder</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Talentfolder</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1785222859268218880/QKe4zDoG_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Open Your Bank Account in Dubai Easily
-Looking to open a bank account in Dubai? We make it simple, fast, and stress-free!
-Whether you're a resident, investor, or business owner, our experts help you open accounts with top UAE banks like ADCB, FAB, Emirates NBD, and more.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Open Your Bank Account in Dubai Easily
-Looking to open a bank account in Dubai? We make it simple, fast, and stress-free!
-Whether you&amp;#39;re a resident, investor, or business owner, our experts help you open accounts with top UAE banks like ADCB, FAB, Emirates NBD, and more.</t>
-        </is>
-      </c>
-      <c r="J63" t="b">
-        <v>0</v>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 · 8:06 AM UTC</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>2026-03-25T08:06:00Z</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" t="n">
-        <v>43</v>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2036715367096066528</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036715367096066528</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Emirates NBD</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach to us at
-social@emiratesnbd.com
- Quoting case 988205 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach to us at
-social@emiratesnbd.com
- Quoting case 988205 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
-        </is>
-      </c>
-      <c r="J64" t="b">
-        <v>0</v>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>['rihandagarwal']</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 · 8:02 AM UTC</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>2026-03-25T08:02:00Z</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="n">
-        <v>1</v>
-      </c>
-      <c r="S64" t="n">
-        <v>0</v>
-      </c>
-      <c r="T64" t="n">
-        <v>0</v>
-      </c>
-      <c r="U64" t="n">
-        <v>13</v>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2036713554930491654</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>https://x.com/rihandagarwal/status/2036713554930491654</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>https://x.com/rihandagarwal</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>rihandagarwal</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Rihand Agarwal</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1672415803457818624/qXizRa0Q_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE I have now been trying to access my ENBDX mobile app AND my funds for the past 2 weeks without success. 
-Due to a technical issue on your end, my login credentials were erased 2 weeks ago. Since then, I have tried multiple calls. This is unacceptable from you.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; I have now been trying to access my ENBDX mobile app AND my funds for the past 2 weeks without success. 
-Due to a technical issue on your end, my login credentials were erased 2 weeks ago. Since then, I have tried multiple calls. This is unacceptable from you.</t>
-        </is>
-      </c>
-      <c r="J65" t="b">
-        <v>0</v>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 · 7:55 AM UTC</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>2026-03-25T07:55:00Z</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="R65" t="n">
-        <v>1</v>
-      </c>
-      <c r="S65" t="n">
-        <v>0</v>
-      </c>
-      <c r="T65" t="n">
-        <v>1</v>
-      </c>
-      <c r="U65" t="n">
-        <v>17</v>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2036700769617887531</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>https://x.com/motsafeh057/status/2036700769617887531</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>https://x.com/motsafeh057</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>motsafeh057</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>متصفح وقارئ للأخبار</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1996323967443881984/qDVGWeO0_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>0570500894</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>0570500894</t>
-        </is>
-      </c>
-      <c r="J66" t="b">
-        <v>0</v>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA']</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 · 7:04 AM UTC</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>2026-03-25T07:04:00Z</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="n">
-        <v>0</v>
-      </c>
-      <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
-        <v>16</v>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2036700638353191376</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>https://x.com/letstalkdubai/status/2036700638353191376</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>https://x.com/letstalkdubai</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>letstalkdubai</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Let's Talk Dubai</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526561120164921344/W-lU0fbd_bigger.png</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>#UAE Business &amp; Economy Headlines
-25 March 2026    
-#MiddleEast   Full Report:  infoblaze.com/news/details/1…</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; Business &amp;amp; Economy Headlines
-25 March 2026    
-&lt;a href="/search?f=tweets&amp;amp;q=%23MiddleEast"&gt;#MiddleEast&lt;/a&gt;   Full Report:  &lt;a href="http://infoblaze.com/news/details/117057"&gt;infoblaze.com/news/details/1…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="J67" t="b">
-        <v>0</v>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 · 7:04 AM UTC</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>2026-03-25T07:04:00Z</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23MiddleEast', 'http://infoblaze.com/news/details/117057']</t>
-        </is>
-      </c>
-      <c r="R67" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" t="n">
-        <v>1</v>
-      </c>
-      <c r="U67" t="n">
-        <v>69</v>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2036700495067127889</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2036700495067127889</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_KSA</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_KSA</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>EmiratesNBD KSA</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال الهاتف الخاص بك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال الهاتف الخاص بك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
-        </is>
-      </c>
-      <c r="J68" t="b">
-        <v>0</v>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>['motsafeh057']</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 · 7:03 AM UTC</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>2026-03-25T07:03:00Z</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="n">
-        <v>1</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" t="n">
-        <v>29</v>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2036696100367704134</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>https://x.com/motsafeh057/status/2036696100367704134</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>https://x.com/motsafeh057</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>motsafeh057</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>متصفح وقارئ للأخبار</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1996323967443881984/qDVGWeO0_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>اليوم محاوله من عدة محاولات لفتح حساب من عدة طرق سواء بالمتصفح او التطبيق او عن طريق الفرع وجاتني الرساله الاخيره تحت</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>اليوم محاوله من عدة محاولات لفتح حساب من عدة طرق سواء بالمتصفح او التطبيق او عن طريق الفرع وجاتني الرساله الاخيره تحت</t>
-        </is>
-      </c>
-      <c r="J69" t="b">
-        <v>0</v>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA']</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 · 6:46 AM UTC</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>2026-03-25T06:46:00Z</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="n">
-        <v>1</v>
-      </c>
-      <c r="S69" t="n">
-        <v>0</v>
-      </c>
-      <c r="T69" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" t="n">
-        <v>28</v>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2036684502588588270</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036684502588588270</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Emirates NBD</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Because Your Mornings Deserve Better
-Apply for the Emirates NBD noon One Visa Credit Card and De’Longhi LA SPECIALISTA ARTE EVO Espresso Machine could be yours.
-What’s more?
-AED 500 welcome bonus
-1-year free noon One membership &amp; 50% thereafter
-Up to 20% back as noon credits on spends across all noon platforms
-Offer is valid until 31 March 2026.
-emiratesnbd.com/en/campaigns…</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Because Your Mornings Deserve Better
-Apply for the Emirates NBD noon One Visa Credit Card and De’Longhi LA SPECIALISTA ARTE EVO Espresso Machine could be yours.
-What’s more?
-AED 500 welcome bonus
-1-year free noon One membership &amp;amp; 50% thereafter
-Up to 20% back as noon credits on spends across all noon platforms
-Offer is valid until 31 March 2026.
-&lt;a href="https://www.emiratesnbd.com/en/campaigns/noon-one-credit-card"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="J70" t="b">
-        <v>0</v>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 · 5:59 AM UTC</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>2026-03-25T05:59:00Z</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>['https://www.emiratesnbd.com/en/campaigns/noon-one-credit-card']</t>
-        </is>
-      </c>
-      <c r="R70" t="n">
-        <v>0</v>
-      </c>
-      <c r="S70" t="n">
-        <v>0</v>
-      </c>
-      <c r="T70" t="n">
-        <v>3</v>
-      </c>
-      <c r="U70" t="n">
-        <v>526</v>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2036665227840803080</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036665227840803080</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Emirates NBD</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Thanks for writing to us, kindly note that we have replied to your email</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Thanks for writing to us, kindly note that we have replied to your email</t>
-        </is>
-      </c>
-      <c r="J71" t="b">
-        <v>0</v>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>['ZahidanMuhamma']</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 · 4:43 AM UTC</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>2026-03-25T04:43:00Z</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" t="n">
-        <v>21</v>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2036654307596992707</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036654307596992707</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Emirates NBD</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Your financial tip of the week
-#FinancialWellbeing #EmiratesNBDTips #SmartMoney #FinWell</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Your financial tip of the week
-&lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBDTips"&gt;#EmiratesNBDTips&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoney"&gt;#SmartMoney&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinWell"&gt;#FinWell&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="J72" t="b">
-        <v>0</v>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>Mar 25</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 · 4:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>2026-03-25T04:00:00Z</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBDTips', 'https://x.com/search?f=tweets&amp;q=%23SmartMoney', 'https://x.com/search?f=tweets&amp;q=%23FinWell']</t>
-        </is>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" t="n">
-        <v>2</v>
-      </c>
-      <c r="U72" t="n">
-        <v>527</v>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2036654307383111761</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2036654307383111761</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Emirates NBD</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>نصيحتك المالية لهذا الأسبوع
-#FinancialWellbeing #EmiratesNBDTips #FinWell #SmartMoney</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>نصيحتك المالية لهذا الأسبوع
-&lt;a href="/search?f=tweets&amp;amp;q=%23FinancialWellbeing"&gt;#FinancialWellbeing&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBDTips"&gt;#EmiratesNBDTips&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23FinWell"&gt;#FinWell&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SmartMoney"&gt;#SmartMoney&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="J73" t="b">
-        <v>0</v>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>Mar 25</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 · 4:00 AM UTC</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>2026-03-25T04:00:00Z</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23FinancialWellbeing', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBDTips', 'https://x.com/search?f=tweets&amp;q=%23FinWell', 'https://x.com/search?f=tweets&amp;q=%23SmartMoney']</t>
-        </is>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" t="n">
-        <v>0</v>
-      </c>
-      <c r="T73" t="n">
-        <v>2</v>
-      </c>
-      <c r="U73" t="n">
-        <v>462</v>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2036879879950786787</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>https://x.com/centralbankuae/status/2036879879950786787</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>https://x.com/centralbankuae</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>centralbankuae</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Central Bank of the UAE</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2013084633873747968/H63zAIGY_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Dear Consumer
-Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
-For any information or to file a complaint, please contact @SanadakUAE, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: sanadak.gov.ae/en 
-Best regards,
-Central Bank of the UAE</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Dear Consumer
-Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
-For any information or to file a complaint, please contact &lt;a href="/SanadakUAE" title="Sanadak"&gt;@SanadakUAE&lt;/a&gt;, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: &lt;a href="https://www.sanadak.gov.ae/en"&gt;sanadak.gov.ae/en&lt;/a&gt; 
-Best regards,
-Central Bank of the UAE</t>
-        </is>
-      </c>
-      <c r="J74" t="b">
-        <v>0</v>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>['abuzubayr1987', 'emiratesislamic', 'JamalIslamic']</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>9h</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 · 6:56 PM UTC</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>2026-03-25T18:56:00Z</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>['https://x.com/SanadakUAE', 'https://www.sanadak.gov.ae/en']</t>
-        </is>
-      </c>
-      <c r="R74" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" t="n">
-        <v>0</v>
-      </c>
-      <c r="T74" t="n">
-        <v>0</v>
-      </c>
-      <c r="U74" t="n">
-        <v>14</v>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2036838112907972926</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>https://x.com/Tiamat531229675/status/2036838112907972926</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>https://x.com/Tiamat531229675</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Tiamat531229675</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Tiamat</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1650968397432373248/bTVP9Hqc_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>If you consider the Emirates Islamic cool.
-I think all muslim societies should be that way.
-I never said I disliked it.
-I advocate for it.
-I only go through muslim X and see them horrified by the Emirates allowing 'unIslamic' laws being allowed.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>If you consider the Emirates Islamic cool.
-I think all muslim societies should be that way.
-I never said I disliked it.
-I advocate for it.
-I only go through muslim X and see them horrified by the Emirates allowing &amp;#39;unIslamic&amp;#39; laws being allowed.</t>
-        </is>
-      </c>
-      <c r="J75" t="b">
-        <v>0</v>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>['KarrDriver', 'WallStreetMav', 'EndWokeness']</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>11h</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 · 4:10 PM UTC</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>2026-03-25T16:10:00Z</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="n">
-        <v>1</v>
-      </c>
-      <c r="S75" t="n">
-        <v>0</v>
-      </c>
-      <c r="T75" t="n">
-        <v>0</v>
-      </c>
-      <c r="U75" t="n">
-        <v>7</v>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2036821858868416788</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>https://x.com/abuzubayr1987/status/2036821858868416788</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>https://x.com/abuzubayr1987</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>abuzubayr1987</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Safwan</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>@centralbankuae 
-I am left in a precarious situation having no living expenses for the coming weeks after @emiratesislamic bank deducted 100% against my credit card dues without notice. After having a call they have been inconsiderate over my situation.
-@JamalIslamic</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>&lt;a href="/centralbankuae" title="Central Bank of the UAE"&gt;@centralbankuae&lt;/a&gt; 
-I am left in a precarious situation having no living expenses for the coming weeks after &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; bank deducted 100% against my credit card dues without notice. After having a call they have been inconsiderate over my situation.
-&lt;a href="/JamalIslamic" title="JAMAL BIN GHALIATA (CEO EMIRATES ISLAMIC BANK)"&gt;@JamalIslamic&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="J76" t="b">
-        <v>0</v>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>12h</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 · 3:05 PM UTC</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>2026-03-25T15:05:00Z</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>['https://x.com/centralbankuae', 'https://x.com/emiratesislamic', 'https://x.com/JamalIslamic']</t>
-        </is>
-      </c>
-      <c r="R76" t="n">
-        <v>1</v>
-      </c>
-      <c r="S76" t="n">
-        <v>0</v>
-      </c>
-      <c r="T76" t="n">
-        <v>0</v>
-      </c>
-      <c r="U76" t="n">
-        <v>7</v>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2036796287182647587</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>https://x.com/dhara_katariya/status/2036796287182647587</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>https://x.com/dhara_katariya</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>dhara_katariya</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Dhara Katariya</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1205157338639978497/HK2x6jCp_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>@Maersk maersk kanoo emirates why dont you check with your bank why you didn't received it? Your executives saying we didnt received 100 times but atleast for once ask your bank. Your client is stressed.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>&lt;a href="/Maersk" title="Maersk"&gt;@Maersk&lt;/a&gt; maersk kanoo emirates why dont you check with your bank why you didn&amp;#39;t received it? Your executives saying we didnt received 100 times but atleast for once ask your bank. Your client is stressed.</t>
-        </is>
-      </c>
-      <c r="J77" t="b">
-        <v>0</v>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>['dhara_katariya', 'emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 · 1:24 PM UTC</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>2026-03-25T13:24:00Z</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>['https://x.com/Maersk']</t>
-        </is>
-      </c>
-      <c r="R77" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" t="n">
-        <v>0</v>
-      </c>
-      <c r="T77" t="n">
-        <v>0</v>
-      </c>
-      <c r="U77" t="n">
-        <v>13</v>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2036794106270413038</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>https://x.com/dhara_katariya/status/2036794106270413038</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>https://x.com/dhara_katariya</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>dhara_katariya</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Dhara Katariya</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1205157338639978497/HK2x6jCp_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>@emiratesislamic A transaction was made from palsun maritime LLC to MAERSK KANOO EMIRATES LLC on 19th mar 2026 of usd 30301$
- ETE ID EPHCOP07809C8DTA
-The amount is debited but maersk kanoo didn't received it. We dont have any revert from the bank where the payment is .Resolve it</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>&lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; A transaction was made from palsun maritime LLC to MAERSK KANOO EMIRATES LLC on 19th mar 2026 of usd 30301$
- ETE ID EPHCOP07809C8DTA
-The amount is debited but maersk kanoo didn&amp;#39;t received it. We dont have any revert from the bank where the payment is .Resolve it</t>
-        </is>
-      </c>
-      <c r="J78" t="b">
-        <v>0</v>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 · 1:15 PM UTC</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>2026-03-25T13:15:00Z</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>['https://x.com/emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="R78" t="n">
-        <v>1</v>
-      </c>
-      <c r="S78" t="n">
-        <v>0</v>
-      </c>
-      <c r="T78" t="n">
-        <v>0</v>
-      </c>
-      <c r="U78" t="n">
-        <v>12</v>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2036783540419903727</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2036783540419903727</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Flight cancelled and awaiting a refund? Fraudsters use this opportunity to scam. Pause before clicking any link, verify the source, and stay alert.
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Flight cancelled and awaiting a refund? Fraudsters use this opportunity to scam. Pause before clicking any link, verify the source, and stay alert.
-Do not fall for the traps. Stay alert to scams.
-&lt;a href="/search?f=tweets&amp;amp;q=%23EIAgainstFraud"&gt;#EIAgainstFraud&lt;/a&gt; with Emirates Islamic.
-&lt;a href="/search?f=tweets&amp;amp;q=%23TogetherAgainstFraud"&gt;#TogetherAgainstFraud&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="J79" t="b">
-        <v>0</v>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 · 12:33 PM UTC</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>2026-03-25T12:33:00Z</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23EIAgainstFraud', 'https://x.com/search?f=tweets&amp;q=%23TogetherAgainstFraud']</t>
-        </is>
-      </c>
-      <c r="R79" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" t="n">
-        <v>72</v>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2036783538087850447</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2036783538087850447</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>هل تم إلغاء رحلتك وتنتظر استرداد المبلغ؟ يستغل المحتالون هذه الفرصة للاحتيال. توقف قبل الضغط على أي رابط، وتحقق من المصدر، وانتبه للإشارات التحذيرية.
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>هل تم إلغاء رحلتك وتنتظر استرداد المبلغ؟ يستغل المحتالون هذه الفرصة للاحتيال. توقف قبل الضغط على أي رابط، وتحقق من المصدر، وانتبه للإشارات التحذيرية.
-لا تقع في الفخ. احذر الاحتيال.
-&lt;a href="/search?f=tweets&amp;amp;q=%23متحّدون_ضد_الاحتيال"&gt;#متحّدون_ضد_الاحتيال&lt;/a&gt; مع الإمارات الإسلامي.</t>
-        </is>
-      </c>
-      <c r="J80" t="b">
-        <v>0</v>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 · 12:33 PM UTC</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>2026-03-25T12:33:00Z</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23متحّدون_ضد_الاحتيال']</t>
-        </is>
-      </c>
-      <c r="R80" t="n">
-        <v>1</v>
-      </c>
-      <c r="S80" t="n">
-        <v>0</v>
-      </c>
-      <c r="T80" t="n">
-        <v>0</v>
-      </c>
-      <c r="U80" t="n">
-        <v>140</v>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2036732548290891833</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>https://x.com/AirIndiaX/status/2036732548290891833</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>https://x.com/AirIndiaX</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>AirIndiaX</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Air India Express</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1937212217578983424/vF-DUPT9_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Since the booking is done through Air India, we request you to please reach out to them for any assistance.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Since the booking is done through Air India, we request you to please reach out to them for any assistance.</t>
-        </is>
-      </c>
-      <c r="J81" t="b">
-        <v>0</v>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>['naanrdk', 'emiratesislamic', 'airindia']</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>Mar 25, 2026 · 9:10 AM UTC</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>2026-03-25T09:10:00Z</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="n">
-        <v>1</v>
-      </c>
-      <c r="S81" t="n">
-        <v>0</v>
-      </c>
-      <c r="T81" t="n">
-        <v>0</v>
-      </c>
-      <c r="U81" t="n">
-        <v>47</v>
-      </c>
-      <c r="V81" t="inlineStr">
         <is>
           <t>EI</t>
         </is>

--- a/EI_ENBD_3post.xlsx
+++ b/EI_ENBD_3post.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V53"/>
+  <dimension ref="A1:V54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -593,7 +593,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>48m</t>
+          <t>3h</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>5h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -890,7 +890,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -980,7 +980,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1066,7 +1066,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1238,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1324,7 +1324,7 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1410,7 +1410,7 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1496,7 +1496,7 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1590,7 +1590,7 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1686,7 +1686,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1870,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1956,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2042,7 +2042,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2128,7 +2128,7 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2214,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2300,7 +2300,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2390,7 +2390,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2478,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2570,7 +2570,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2656,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2742,7 +2742,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2832,7 +2832,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2922,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3012,7 +3012,7 @@
         <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3108,7 +3108,7 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3194,7 +3194,7 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3284,7 +3284,7 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3370,7 +3370,7 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3460,7 +3460,7 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3548,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3634,7 +3634,7 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3806,7 +3806,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3900,7 +3900,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3988,7 +3988,7 @@
         <v>7</v>
       </c>
       <c r="U40" t="n">
-        <v>788</v>
+        <v>817</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -4049,7 +4049,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4074,7 +4074,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4246,7 +4246,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>Mar 27</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4338,7 +4338,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>Mar 27</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4432,7 +4432,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -4801,124 +4801,404 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2037484085459750931</t>
+          <t>2037499728318116157</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2037484085459750931</t>
+          <t>https://x.com/SanadakUAE/status/2037499728318116157</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic</t>
+          <t>https://x.com/SanadakUAE</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>SanadakUAE</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>emiratesislamic</t>
+          <t>Sanadak</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2012879499768049664/EHCzbImW_bigger.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
+          <t>Dear Safwan,
+Thank you for contacting Sanadak, Ombudsman Unit for the UAE.
+For more information about our services, please call 800SANADAK or visit our website sanadak.gov.ae/en/.  
+Best regards,
+Sanadak Team</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Dear Safwan,
+Thank you for contacting Sanadak, Ombudsman Unit for the UAE.
+For more information about our services, please call 800SANADAK or visit our website &lt;a href="https://www.sanadak.gov.ae/en/"&gt;sanadak.gov.ae/en/&lt;/a&gt;.  
+Best regards,
+Sanadak Team</t>
+        </is>
+      </c>
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>['abuzubayr1987', 'emiratesislamic', 'JamalIslamic']</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Mar 27, 2026 · 11:59 AM UTC</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>2026-03-27T11:59:00Z</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>['https://www.sanadak.gov.ae/en/']</t>
+        </is>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>14</v>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2037485522399236349</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://x.com/abuzubayr1987/status/2037485522399236349</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://x.com/abuzubayr1987</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>abuzubayr1987</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Safwan</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>All I got was a feedback form!
+No real solution, making things worse for me every passing day. No response from account manager. Now even my registered mobile number is suspended due to this 100% deduction that was done and I am unable to do payments!
+@SanadakUAE @JamalIslamic</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>All I got was a feedback form!
+No real solution, making things worse for me every passing day. No response from account manager. Now even my registered mobile number is suspended due to this 100% deduction that was done and I am unable to do payments!
+&lt;a href="/SanadakUAE" title="Sanadak"&gt;@SanadakUAE&lt;/a&gt; &lt;a href="/JamalIslamic" title="JAMAL BIN GHALIATA (CEO EMIRATES ISLAMIC BANK)"&gt;@JamalIslamic&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Mar 27, 2026 · 11:02 AM UTC</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>2026-03-27T11:02:00Z</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>['https://x.com/SanadakUAE', 'https://x.com/JamalIslamic']</t>
+        </is>
+      </c>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>14</v>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2037484085459750931</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2037484085459750931</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>emiratesislamic</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
           <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
 better please check your private message.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
 better please check your private message.</t>
         </is>
       </c>
-      <c r="J50" t="b">
-        <v>0</v>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
         <is>
           <t>['abuzubayr1987']</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 10:57 AM UTC</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>2026-03-27T10:57:00Z</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>9</v>
-      </c>
-      <c r="V50" t="inlineStr">
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>11</v>
+      </c>
+      <c r="V52" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2037480161797722518</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://x.com/abuzubayr1987/status/2037480161797722518</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://x.com/abuzubayr1987</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>abuzubayr1987</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Safwan</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Hello
+I got a call from your social media team, with no real solution because they cannot access my account from alternative number. While all other departments are quick enough to access details and deduct undue amounts without prior notice.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Hello
+I got a call from your social media team, with no real solution because they cannot access my account from alternative number. While all other departments are quick enough to access details and deduct undue amounts without prior notice.</t>
+        </is>
+      </c>
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>['emiratesislamic']</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Mar 27, 2026 · 10:41 AM UTC</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2026-03-27T10:41:00Z</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>13</v>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>EI</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>2037462241591615667</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2037462241591615667</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
         <is>
           <t>سلامتكم أولويتنا.
 نوصي باستخدام تطبيق + EI ومنصة businessONLINE لإنجاز معاملاتكم المصرفية بسهولة وأمان.
@@ -4926,7 +5206,7 @@
 Use EI + Mobile &amp; Online Banking and businessONLINE with ease and security.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>سلامتكم أولويتنا.
 نوصي باستخدام تطبيق + EI ومنصة businessONLINE لإنجاز معاملاتكم المصرفية بسهولة وأمان.
@@ -4934,223 +5214,41 @@
 Use EI + Mobile &amp;amp; Online Banking and businessONLINE with ease and security.</t>
         </is>
       </c>
-      <c r="J51" t="b">
-        <v>0</v>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
+      <c r="J54" t="b">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 9:30 AM UTC</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>2026-03-27T09:30:00Z</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
         <v>1</v>
       </c>
-      <c r="T51" t="n">
+      <c r="T54" t="n">
         <v>2</v>
       </c>
-      <c r="U51" t="n">
-        <v>88</v>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2037485522399236349</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>https://x.com/abuzubayr1987/status/2037485522399236349</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>https://x.com/abuzubayr1987</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>abuzubayr1987</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Safwan</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>All I got was a feedback form!
-No real solution, making things worse for me every passing day. No response from account manager. Now even my registered mobile number is suspended due to this 100% deduction that was done and I am unable to do payments!
-@SanadakUAE @JamalIslamic</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>All I got was a feedback form!
-No real solution, making things worse for me every passing day. No response from account manager. Now even my registered mobile number is suspended due to this 100% deduction that was done and I am unable to do payments!
-&lt;a href="/SanadakUAE" title="Sanadak"&gt;@SanadakUAE&lt;/a&gt; &lt;a href="/JamalIslamic" title="JAMAL BIN GHALIATA (CEO EMIRATES ISLAMIC BANK)"&gt;@JamalIslamic&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="J52" t="b">
-        <v>0</v>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>16h</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>Mar 27, 2026 · 11:02 AM UTC</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>2026-03-27T11:02:00Z</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>['https://x.com/SanadakUAE', 'https://x.com/JamalIslamic']</t>
-        </is>
-      </c>
-      <c r="R52" t="n">
-        <v>1</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="n">
-        <v>12</v>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>EI</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2037480161797722518</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>https://x.com/abuzubayr1987/status/2037480161797722518</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>https://x.com/abuzubayr1987</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>abuzubayr1987</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Safwan</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Hello
-I got a call from your social media team, with no real solution because they cannot access my account from alternative number. While all other departments are quick enough to access details and deduct undue amounts without prior notice.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Hello
-I got a call from your social media team, with no real solution because they cannot access my account from alternative number. While all other departments are quick enough to access details and deduct undue amounts without prior notice.</t>
-        </is>
-      </c>
-      <c r="J53" t="b">
-        <v>0</v>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>['emiratesislamic']</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>Mar 27, 2026 · 10:41 AM UTC</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>2026-03-27T10:41:00Z</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="n">
-        <v>1</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>11</v>
-      </c>
-      <c r="V53" t="inlineStr">
+      <c r="U54" t="n">
+        <v>90</v>
+      </c>
+      <c r="V54" t="inlineStr">
         <is>
           <t>EI</t>
         </is>

--- a/EI_ENBD_3post.xlsx
+++ b/EI_ENBD_3post.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V54"/>
+  <dimension ref="A1:V87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,71 +543,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2037730056920088898</t>
+          <t>2037865010320539854</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://x.com/wil3020/status/2037730056920088898</t>
+          <t>https://x.com/rated_sm/status/2037865010320539854</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/wil3020</t>
+          <t>https://x.com/rated_sm</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>wil3020</t>
+          <t>rated_sm</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>wiil</t>
+          <t>rated_sm</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1939900695018106882/lxZGZx9Y_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1870693863452524544/xTAmP9KA_bigger.jpg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
+          <t>@EmiratesNBD_AE My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
         </is>
       </c>
       <c r="J2" t="b">
         <v>0</v>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>3h</t>
+          <t>7m</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 3:14 AM UTC</t>
+          <t>Mar 28, 2026 · 12:10 PM UTC</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-03-28T03:14:00Z</t>
+          <t>2026-03-28T12:10:00Z</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -629,36 +629,3016 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2037656647238311969</t>
+          <t>2037827252075839770</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://x.com/Fr638/status/2037656647238311969</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2037827252075839770</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/Fr638</t>
+          <t>https://x.com/EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Fr638</t>
+          <t>EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Faris _m</t>
+          <t>EmiratesNBD KSA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1054834903785844737/syBa6NJV_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>نعم يمكنك تقسيط المبلغ, لطلب التقسيط وتفاصيل أكثر قبل إجراء المعاملة يرجى الاتصال بنا على الرقم المجاني 8007547777</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>نعم يمكنك تقسيط المبلغ, لطلب التقسيط وتفاصيل أكثر قبل إجراء المعاملة يرجى الاتصال بنا على الرقم المجاني 8007547777</t>
+        </is>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>['Talal_Hus']</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2h</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 9:40 AM UTC</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2026-03-28T09:40:00Z</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>10</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2037818020597215557</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://x.com/Talal_Hus/status/2037818020597215557</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://x.com/Talal_Hus</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Talal_Hus</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>T.A</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1499888329797652480/UU2JVEEj_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA بالنسبة للتقسيط بدون هامش ربح هل لو سددت من خلال الفيزا ابل باي اقدر استفيد من العرض ؟ 
+يعني ععندب في نون اشتري ابل باي وبعدها اقسطها ؟</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; بالنسبة للتقسيط بدون هامش ربح هل لو سددت من خلال الفيزا ابل باي اقدر استفيد من العرض ؟ 
+يعني ععندب في نون اشتري ابل باي وبعدها اقسطها ؟</t>
+        </is>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>3h</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 9:04 AM UTC</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-03-28T09:04:00Z</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>8</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2037804608517509572</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://x.com/eazyislit/status/2037804608517509572</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://x.com/eazyislit</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>eazyislit</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Dat Dark Rich Dude 💎🇳🇬🇬🇧</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1920377756946169857/gG-ZA10q_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>THE WOMAN DAT CARRIED YOU FOR 9 MONTHS MAY SHE LIVE LONG AND WITNESS YOU SUCCEED 🤍</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>THE WOMAN DAT CARRIED YOU FOR 9 MONTHS MAY SHE LIVE LONG AND WITNESS YOU SUCCEED 🤍</t>
+        </is>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 8:10 AM UTC</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-03-28T08:10:00Z</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>6</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2037801868244533349</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>What’s more suspicious?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+emiratesnbd.com/en/campaigns…</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>What’s more suspicious?
+Stay Safe, Stay Vigilant. &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;
+&lt;a href="https://www.emiratesnbd.com/en/campaigns/united-against-fraud"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2026-03-28T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud', 'https://www.emiratesnbd.com/en/campaigns/united-against-fraud']</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>326</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2037799000171216897</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://x.com/argosaki/status/2037799000171216897</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://x.com/argosaki</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>argosaki</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>GP Q</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1346926049532080128/AZU6mAE-_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>SOUNDS LIKE … QUANTUM 
+Emirates NBD enables instant trading account top-ups for UAE investors
+New system lets UAE investors fund trading accounts in near real time 
+gulfnews.com/business/bankin…</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>SOUNDS LIKE … QUANTUM 
+Emirates NBD enables instant trading account top-ups for UAE investors
+New system lets UAE investors fund trading accounts in near real time 
+&lt;a href="https://gulfnews.com/business/banking/emirates-nbd-enables-instant-trading-account-top-ups-for-uae-investors-1.500487960"&gt;gulfnews.com/business/bankin…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 7:48 AM UTC</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2026-03-28T07:48:00Z</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>['https://gulfnews.com/business/banking/emirates-nbd-enables-instant-trading-account-top-ups-for-uae-investors-1.500487960']</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>331</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2037796434725269639</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang/status/2037796434725269639</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ZaibKang</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Jahan Zaib Akbar Kang</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2028644994790436864/h-Avrj3s_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Thanks for your timely response.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Thanks for your timely response.</t>
+        </is>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 7:38 AM UTC</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2026-03-28T07:38:00Z</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2037796009921900610</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://x.com/MazBalushi35285/status/2037796009921900610</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://x.com/MazBalushi35285</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MazBalushi35285</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>مازن البلوشي</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2018589030322253824/-R_IX5Kh_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>🥳مزيد من النواة الفн على مسابقة رابح صقر! راحت لكم الحفل العيد في الرياض! 🎉 فوق_النهاية فقط</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>🥳مزيد من النواة الفн على مسابقة رابح صقر! راحت لكم الحفل العيد في الرياض! 🎉 فوق_النهاية فقط</t>
+        </is>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'Turki_alalshikh', 'RabehSaqer', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 7:36 AM UTC</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2026-03-28T07:36:00Z</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>14</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2037792667782824069</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #989763 in the subject line.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #989763 in the subject line.</t>
+        </is>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>['ZaibKang']</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 7:23 AM UTC</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2026-03-28T07:23:00Z</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>10</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2037790087141101872</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://x.com/SelmaRomola/status/2037790087141101872</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://x.com/SelmaRomola</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SelmaRomola</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Selma Romola</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1118152018995105792/5fyZOTth_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Fin well Financial well-being program with Emirates NBD 
+@Sabaashraff
+@Sosomostafa729S
+@Amanekhattab1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Fin well Financial well-being program with Emirates NBD 
+&lt;a href="/Sabaashraff" title="Saba Ashraf"&gt;@Sabaashraff&lt;/a&gt;
+&lt;a href="/Sosomostafa729S" title="Soha.mostafa77"&gt;@Sosomostafa729S&lt;/a&gt;
+&lt;a href="/Amanekhattab1" title="Amanekhattab"&gt;@Amanekhattab1&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 7:13 AM UTC</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2026-03-28T07:13:00Z</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>['https://x.com/Sabaashraff', 'https://x.com/Sosomostafa729S', 'https://x.com/Amanekhattab1']</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2037789707321622955</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://x.com/SelmaRomola/status/2037789707321622955</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://x.com/SelmaRomola</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SelmaRomola</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Selma Romola</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1118152018995105792/5fyZOTth_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
+Tagging 
+@FazilAnas 
+@Emy191990 
+@Bushrasabih2</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
+Tagging 
+&lt;a href="/FazilAnas" title="Tosifmuhammad 🇦🇪"&gt;@FazilAnas&lt;/a&gt; 
+&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; 
+&lt;a href="/Bushrasabih2" title="Bu_shaikh🌸❤️"&gt;@Bushrasabih2&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 7:11 AM UTC</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2026-03-28T07:11:00Z</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>['https://x.com/FazilAnas', 'https://x.com/Emy191990', 'https://x.com/Bushrasabih2']</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2037789510478843981</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://x.com/SelmaRomola/status/2037789510478843981</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://x.com/SelmaRomola</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SelmaRomola</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Selma Romola</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1118152018995105792/5fyZOTth_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
+Tagging 
+@Sosomostafa729S 
+@Nur_Munem 
+@yasar8212</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
+Tagging 
+&lt;a href="/Sosomostafa729S" title="Soha.mostafa77"&gt;@Sosomostafa729S&lt;/a&gt; 
+&lt;a href="/Nur_Munem" title="نـــور مُــنعم 🇦🇪"&gt;@Nur_Munem&lt;/a&gt; 
+&lt;a href="/yasar8212" title="shaniyadu"&gt;@yasar8212&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 7:10 AM UTC</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2026-03-28T07:10:00Z</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>['https://x.com/Sosomostafa729S', 'https://x.com/Nur_Munem', 'https://x.com/yasar8212']</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>5</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2037788447910564341</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://x.com/SelmaRomola/status/2037788447910564341</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://x.com/SelmaRomola</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SelmaRomola</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Selma Romola</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1118152018995105792/5fyZOTth_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
+Tagging 
+@Bushrasabih2 
+@AmalBeevi 
+@Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
+Tagging 
+&lt;a href="/Bushrasabih2" title="Bu_shaikh🌸❤️"&gt;@Bushrasabih2&lt;/a&gt; 
+&lt;a href="/AmalBeevi" title="Amal Beevi"&gt;@AmalBeevi&lt;/a&gt; 
+&lt;a href="/Sosomostafa729S" title="Soha.mostafa77"&gt;@Sosomostafa729S&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 7:06 AM UTC</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2026-03-28T07:06:00Z</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>['https://x.com/Bushrasabih2', 'https://x.com/AmalBeevi', 'https://x.com/Sosomostafa729S']</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>7</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2037785874474430532</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang/status/2037785874474430532</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ZaibKang</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Jahan Zaib Akbar Kang</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2028644994790436864/h-Avrj3s_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>I applied for liv X account Still not received any response 
+Reference number 
+2026038379331830</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>I applied for liv X account Still not received any response 
+Reference number 
+2026038379331830</t>
+        </is>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:56 AM UTC</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:56:00Z</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>18</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2037785071189671937</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://x.com/ZaibKang</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ZaibKang</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Jahan Zaib Akbar Kang</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2028644994790436864/h-Avrj3s_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible</t>
+        </is>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:53 AM UTC</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:53:00Z</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>9</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2037784853866029145</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784853866029145</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>B- 1.89% @zeynp_qas @Salma2232019 @semeet 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>B- 1.89% &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:52 AM UTC</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:52:00Z</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>['https://x.com/zeynp_qas', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2037784763122217375</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784763122217375</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>B- 1.89% &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:52 AM UTC</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:52:00Z</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>['https://x.com/semeet', 'https://x.com/Salma2232019', 'https://x.com/SelmaRomola']</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2037784668028985459</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>B- 1.89% @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>B- 1.89% &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:51 AM UTC</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:51:00Z</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2037784498885243377</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784498885243377</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program 
+@semeet @Emy191990 @ibushra_03 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program 
+&lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:50 AM UTC</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:50:00Z</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>['https://x.com/semeet', 'https://x.com/Emy191990', 'https://x.com/ibushra_03']</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2037784405700419683</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:50 AM UTC</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:50:00Z</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>['https://x.com/semeet', 'https://x.com/zeynp_qas', 'https://x.com/SelmaRomola']</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2037784344333275440</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Before clicking a link, what do you do?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+emiratesnbd.com/en/campaigns…</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Before clicking a link, what do you do?
+Stay Safe, Stay Vigilant. &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;
+&lt;a href="https://www.emiratesnbd.com/en/campaigns/united-against-fraud"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:50 AM UTC</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:50:00Z</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud', 'https://www.emiratesnbd.com/en/campaigns/united-against-fraud']</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>2</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>377</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2037784337337532619</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784337337532619</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:50 AM UTC</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:50:00Z</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2037784225022365938</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program @semeet @parulghalout @Salma2232019 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:49 AM UTC</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:49:00Z</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>['https://x.com/semeet', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
+        </is>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2037784141006344295</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784141006344295</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program @semeet @Salma2232019 @ibushra_03 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:49 AM UTC</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:49:00Z</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>['https://x.com/semeet', 'https://x.com/Salma2232019', 'https://x.com/ibushra_03']</t>
+        </is>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>4</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2037784038774317555</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program 
+@Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program 
+&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:49 AM UTC</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:49:00Z</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2037783859769876728</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783859769876728</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>FINWELL ( Financial Well-being program) with Emirates NBD @semeet @zeynp_qas @Emy191990 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>FINWELL ( Financial Well-being program) with Emirates NBD &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:48 AM UTC</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:48:00Z</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>['https://x.com/semeet', 'https://x.com/zeynp_qas', 'https://x.com/Emy191990']</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>4</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2037783775896313876</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783775896313876</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>FINWELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Emy191990 @parulghalout 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>FINWELL ( Financial Well-being program) with Emirates NBD &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:48 AM UTC</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:48:00Z</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>['https://x.com/SelmaRomola', 'https://x.com/Emy191990', 'https://x.com/parulghalout']</t>
+        </is>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>5</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2037783673144230370</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783673144230370</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>FINWELL ( Financial Well-being program) with Emirates NBD 
+@Emy191990 @ibushra_03 @SelmaRomola 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>FINWELL ( Financial Well-being program) with Emirates NBD 
+&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:47 AM UTC</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:47:00Z</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/SelmaRomola']</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>5</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2037783477979091314</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783477979091314</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking's App @parulghalout @semeet @Emy191990 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:46 AM UTC</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:46:00Z</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>['https://x.com/parulghalout', 'https://x.com/semeet', 'https://x.com/Emy191990']</t>
+        </is>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2037783402758508685</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:46 AM UTC</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:46:00Z</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>['https://x.com/zeynp_qas', 'https://x.com/SelmaRomola', 'https://x.com/Salma2232019']</t>
+        </is>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>7</v>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2037783335389540775</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783335389540775</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking's App @Emy191990 @parulghalout @ibushra_03 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:46 AM UTC</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:46:00Z</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/ibushra_03']</t>
+        </is>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2037783125854679453</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:45 AM UTC</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:45:00Z</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>['https://x.com/parulghalout', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
+        </is>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2037783049065390446</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking's App 
+@Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App 
+&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:45 AM UTC</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:45:00Z</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/semeet']</t>
+        </is>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2037730056920088898</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://x.com/wil3020/status/2037730056920088898</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://x.com/wil3020</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>wil3020</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>wiil</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1939900695018106882/lxZGZx9Y_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
+        </is>
+      </c>
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>9h</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 3:14 AM UTC</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>2026-03-28T03:14:00Z</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>31</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2037656647238311969</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://x.com/Fr638/status/2037656647238311969</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://x.com/Fr638</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Fr638</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Faris _m</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1054834903785844737/syBa6NJV_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
         <is>
           <t>Exchanger Volunteering Program
 @Om__saad_ 
@@ -666,7 +3646,7 @@
 @um_maazz</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>Exchanger Volunteering Program
 &lt;a href="/Om__saad_" title="om_saad"&gt;@Om__saad_&lt;/a&gt; 
@@ -674,963 +3654,963 @@
 &lt;a href="/um_maazz" title="um_maaz"&gt;@um_maazz&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="J36" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE', 'intisar_ma']</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>7h</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>13h</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 10:22 PM UTC</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>2026-03-27T22:22:00Z</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
         <is>
           <t>['https://x.com/Om__saad_', 'https://x.com/um_fayzza', 'https://x.com/um_maazz']</t>
         </is>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>5</v>
-      </c>
-      <c r="V3" t="inlineStr">
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>6</v>
+      </c>
+      <c r="V36" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>2037590379881472140</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_KSA/status/2037590379881472140</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_KSA</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>EmiratesNBD_KSA</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>EmiratesNBD KSA</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
         <is>
           <t>عليكم السلام ورحمه الله وبركاته مرحبا طلال شكرا لتواصلك معنا يرجي العلم ان شحن المحافظ الإلكترونيه لا تطبق عليه رسوم في الوقت الحالي</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>عليكم السلام ورحمه الله وبركاته مرحبا طلال شكرا لتواصلك معنا يرجي العلم ان شحن المحافظ الإلكترونيه لا تطبق عليه رسوم في الوقت الحالي</t>
         </is>
       </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="J37" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
         <is>
           <t>['Talal_Hus']</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>12h</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 5:59 PM UTC</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>2026-03-27T17:59:00Z</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>21</v>
-      </c>
-      <c r="V4" t="inlineStr">
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>31</v>
+      </c>
+      <c r="V37" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>2037585240823058713</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>https://x.com/Talal_Hus/status/2037585240823058713</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>https://x.com/Talal_Hus</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Talal_Hus</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>T.A</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1499888329797652480/UU2JVEEj_bigger.jpg</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA السلام عليكم
 هل شحن المحافظ الالكترونية عليه رسوم ؟ 
 مثل محفظة STCBANK ؟</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; السلام عليكم
 هل شحن المحافظ الالكترونية عليه رسوم ؟ 
 مثل محفظة STCBANK ؟</t>
         </is>
       </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>12h</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="J38" t="b">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 5:39 PM UTC</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>2026-03-27T17:39:00Z</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
         <is>
           <t>['https://x.com/EmiratesNBD_KSA']</t>
         </is>
       </c>
-      <c r="R5" t="n">
+      <c r="R38" t="n">
         <v>2</v>
       </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>29</v>
-      </c>
-      <c r="V5" t="inlineStr">
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>35</v>
+      </c>
+      <c r="V38" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>2037566177971667423</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>https://x.com/GCCBusinessNews/status/2037566177971667423</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>https://x.com/GCCBusinessNews</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>GCCBusinessNews</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>GCC Business News</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1253796411872862212/h2Q8-9rJ_bigger.jpg</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
         <is>
           <t>UAE-based brokerage firm International Securities has gone live on Emirates NBD Pay, utilizing Visa’s Account Funding Transaction (AFT) model.
 gccbusinessnews.com/internat…
 #EmiratesNBD #InternationalSecurities #EmiratesNBDPay  #GCCBusinessNews @EmiratesNBD_AE  @IntlSecurities</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>UAE-based brokerage firm International Securities has gone live on Emirates NBD Pay, utilizing Visa’s Account Funding Transaction (AFT) model.
 &lt;a href="https://www.gccbusinessnews.com/international-securities-emirates-nbd-pay/"&gt;gccbusinessnews.com/internat…&lt;/a&gt;
 &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23InternationalSecurities"&gt;#InternationalSecurities&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBDPay"&gt;#EmiratesNBDPay&lt;/a&gt;  &lt;a href="/search?f=tweets&amp;amp;q=%23GCCBusinessNews"&gt;#GCCBusinessNews&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;  &lt;a href="/IntlSecurities" title="International Securities"&gt;@IntlSecurities&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>13h</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="J39" t="b">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 4:23 PM UTC</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>2026-03-27T16:23:00Z</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
         <is>
           <t>['https://www.gccbusinessnews.com/international-securities-emirates-nbd-pay/', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23InternationalSecurities', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBDPay', 'https://x.com/search?f=tweets&amp;q=%23GCCBusinessNews', 'https://x.com/EmiratesNBD_AE', 'https://x.com/IntlSecurities']</t>
         </is>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>21</v>
-      </c>
-      <c r="V6" t="inlineStr">
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>22</v>
+      </c>
+      <c r="V39" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>2037562773547192591</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>https://x.com/deegrose/status/2037562773547192591</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>https://x.com/deegrose</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>deegrose</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>DeeG (Maria)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1997531422886703104/CcsIqiYF_bigger.jpg</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
         <is>
           <t>Mideast Stocks: UAE equities reverse early gains on Iran ceasefire uncertainty zawya.com/en/capital-markets…</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>Mideast Stocks: UAE equities reverse early gains on Iran ceasefire uncertainty &lt;a href="https://www.zawya.com/en/capital-markets/equities/mideast-stocks-uae-equities-reverse-early-gains-on-iran-ceasefire-uncertainty-fi25unoc"&gt;zawya.com/en/capital-markets…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="J40" t="b">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 4:09 PM UTC</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>2026-03-27T16:09:00Z</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
         <is>
           <t>['https://www.zawya.com/en/capital-markets/equities/mideast-stocks-uae-equities-reverse-early-gains-on-iran-ceasefire-uncertainty-fi25unoc']</t>
         </is>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>23</v>
-      </c>
-      <c r="V7" t="inlineStr">
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>25</v>
+      </c>
+      <c r="V40" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>2037555134797053998</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>https://x.com/s3yrah/status/2037555134797053998</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>https://x.com/s3yrah</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>s3yrah</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Sarrah Sumagang</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2012507741789577216/3SXJciWZ_bigger.jpg</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
         <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>Mutual Fund</t>
         </is>
       </c>
-      <c r="J8" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="J41" t="b">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 3:39 PM UTC</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>2026-03-27T15:39:00Z</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>5</v>
-      </c>
-      <c r="V8" t="inlineStr">
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>6</v>
+      </c>
+      <c r="V41" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>2037550756996530335</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>https://x.com/entrypointuae/status/2037550756996530335</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>https://x.com/entrypointuae</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>entrypointuae</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>نقطة دخول</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1908211270639067136/cQ01rfQa_bigger.jpg</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
         <is>
           <t>اتفق معاك .. أفضل بنك هو الامارات الوطني و أنل أحد عملائه .. و دائما أقول لمن حولي هو الأفضل .. خدماته مميزة عن البقية و تطبيقهم مختلف عن غيره .. يفوز أفضل بنك ..</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>اتفق معاك .. أفضل بنك هو الامارات الوطني و أنل أحد عملائه .. و دائما أقول لمن حولي هو الأفضل .. خدماته مميزة عن البقية و تطبيقهم مختلف عن غيره .. يفوز أفضل بنك ..</t>
         </is>
       </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="J42" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
         <is>
           <t>['abd11ulla', 'EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>20h</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 3:22 PM UTC</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>2026-03-27T15:22:00Z</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>43</v>
-      </c>
-      <c r="V9" t="inlineStr">
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>62</v>
+      </c>
+      <c r="V42" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>2037520386204500435</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037520386204500435</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
         <is>
           <t>Our team will review your email and update you accordingly</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>Our team will review your email and update you accordingly</t>
         </is>
       </c>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="J43" t="b">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
         <is>
           <t>['HashemTakriti']</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>16h</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 1:21 PM UTC</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>2026-03-27T13:21:00Z</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>10</v>
-      </c>
-      <c r="V10" t="inlineStr">
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>16</v>
+      </c>
+      <c r="V43" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>2037514481215938764</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>https://x.com/HashemTakriti/status/2037514481215938764</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>https://x.com/HashemTakriti</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>HashemTakriti</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Hashem Takriti</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1081667250761990144/23AHZt15_bigger.jpg</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
         <is>
           <t>I'm in just back and forth emails with no solutions, I really appreciate your support to close this case. this is really frustrated me</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>I&amp;#39;m in just back and forth emails with no solutions, I really appreciate your support to close this case. this is really frustrated me</t>
         </is>
       </c>
-      <c r="J11" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="J44" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 12:58 PM UTC</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>2026-03-27T12:58:00Z</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="n">
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>7</v>
-      </c>
-      <c r="V11" t="inlineStr">
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>13</v>
+      </c>
+      <c r="V44" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>2037513644066455978</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037513644066455978</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
         <is>
           <t>Thanks for writing to us, kindly note that our team have replied to your email</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>Thanks for writing to us, kindly note that our team have replied to your email</t>
         </is>
       </c>
-      <c r="J12" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
+      <c r="J45" t="b">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
         <is>
           <t>['HashemTakriti']</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 12:54 PM UTC</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>2026-03-27T12:54:00Z</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="n">
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="n">
         <v>1</v>
       </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>9</v>
-      </c>
-      <c r="V12" t="inlineStr">
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>13</v>
+      </c>
+      <c r="V45" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>2037511645971583026</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>https://x.com/HomszRami/status/2037511645971583026</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>https://x.com/HomszRami</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>HomszRami</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Rami Almsri</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1350012724135276544/b1uy5xLK_bigger.jpg</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
         <is>
           <t>Mutual fund/ Investment Fund
 #ENBDRiddleOfTheWeek 
 #financialwellbeing</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>Mutual fund/ Investment Fund
 &lt;a href="/search?f=tweets&amp;amp;q=%23ENBDRiddleOfTheWeek"&gt;#ENBDRiddleOfTheWeek&lt;/a&gt; 
 &lt;a href="/search?f=tweets&amp;amp;q=%23financialwellbeing"&gt;#financialwellbeing&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
+      <c r="J46" t="b">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 12:46 PM UTC</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>2026-03-27T12:46:00Z</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23ENBDRiddleOfTheWeek', 'https://x.com/search?f=tweets&amp;q=%23financialwellbeing']</t>
         </is>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
         <v>1</v>
       </c>
-      <c r="U13" t="n">
-        <v>9</v>
-      </c>
-      <c r="V13" t="inlineStr">
+      <c r="U46" t="n">
+        <v>10</v>
+      </c>
+      <c r="V46" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>2037507103892341213</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037507103892341213</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
         <is>
           <t>من عنوان بريده الإلكتروني المسجل، مع كتابة "طلب إغلاق الحساب" في خانة
  الموضوع.
@@ -1640,7 +4620,7 @@
 في حال عدم وجود أي مخالفات، سيتم إغلاق طلب إغلاق الحساب عبر البريد الإلكتروني خلال 7 أيام عمل</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>من عنوان بريده الإلكتروني المسجل، مع كتابة &amp;#34;طلب إغلاق الحساب&amp;#34; في خانة
  الموضوع.
@@ -1650,83 +4630,83 @@
 في حال عدم وجود أي مخالفات، سيتم إغلاق طلب إغلاق الحساب عبر البريد الإلكتروني خلال 7 أيام عمل</t>
         </is>
       </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
+      <c r="J47" t="b">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
         <is>
           <t>['Ibn_3ali']</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 12:28 PM UTC</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>2026-03-27T12:28:00Z</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>29</v>
-      </c>
-      <c r="V14" t="inlineStr">
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>32</v>
+      </c>
+      <c r="V47" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>2037507063501275362</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037507063501275362</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
         <is>
           <t>الرجاء القيام بما يلي قبل إغلاق الحساب: 
 سحب جميع الأموال من الحساب
@@ -1735,7 +4715,7 @@
  requests@emiratesnbd.com</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>الرجاء القيام بما يلي قبل إغلاق الحساب: 
 سحب جميع الأموال من الحساب
@@ -1744,1045 +4724,1045 @@
  requests@emiratesnbd.com</t>
         </is>
       </c>
-      <c r="J15" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
+      <c r="J48" t="b">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
         <is>
           <t>['Ibn_3ali']</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 12:28 PM UTC</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>2026-03-27T12:28:00Z</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>18</v>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2037506557190021420</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://x.com/HashemTakriti/status/2037506557190021420</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://x.com/HashemTakriti</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>HashemTakriti</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Hashem Takriti</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1081667250761990144/23AHZt15_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE  I’m still waiting to fix my issue, nothing happened since last week.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;  I’m still waiting to fix my issue, nothing happened since last week.</t>
+        </is>
+      </c>
+      <c r="J49" t="b">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Mar 27, 2026 · 12:26 PM UTC</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>2026-03-27T12:26:00Z</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="R49" t="n">
+        <v>1</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>8</v>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2037505623932199158</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037505623932199158</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>نأسف لسماع ذلك برجاء توضيح سبب إغلاق الحساب حتي نتمكن من مساعدتك بشكل أفضل</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>نأسف لسماع ذلك برجاء توضيح سبب إغلاق الحساب حتي نتمكن من مساعدتك بشكل أفضل</t>
+        </is>
+      </c>
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>['Ibn_3ali']</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Mar 27, 2026 · 12:22 PM UTC</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>2026-03-27T12:22:00Z</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>21</v>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2037505175750054028</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://x.com/HimanshuMotiyan/status/2037505175750054028</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://x.com/HimanshuMotiyan</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>HimanshuMotiyan</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Himanshu Motiyani</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2032072703134613504/JzErzVWc_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>I got again same response we will update you and are following up with the team its been more then 2 weeks Iam getting this same response instead of the solution</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>I got again same response we will update you and are following up with the team its been more then 2 weeks Iam getting this same response instead of the solution</t>
+        </is>
+      </c>
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Mar 27, 2026 · 12:21 PM UTC</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>2026-03-27T12:21:00Z</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>7</v>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2037502797097361735</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://x.com/Ibn_3ali/status/2037502797097361735</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://x.com/Ibn_3ali</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Ibn_3ali</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Ahmed Ali</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1836334761129721856/vSK3evXJ_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>كنت عايز أقفل حسابي</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>كنت عايز أقفل حسابي</t>
+        </is>
+      </c>
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Mar 27, 2026 · 12:11 PM UTC</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>2026-03-27T12:11:00Z</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="n">
+        <v>1</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
         <v>12</v>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2037506557190021420</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>https://x.com/HashemTakriti/status/2037506557190021420</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>https://x.com/HashemTakriti</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>HashemTakriti</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Hashem Takriti</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1081667250761990144/23AHZt15_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE  I’m still waiting to fix my issue, nothing happened since last week.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;  I’m still waiting to fix my issue, nothing happened since last week.</t>
-        </is>
-      </c>
-      <c r="J16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2037502674548015413</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037502674548015413</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>مرحبا أحمد شكرا لتواصلك معنا كيف يمكننا مساعدتك</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>مرحبا أحمد شكرا لتواصلك معنا كيف يمكننا مساعدتك</t>
+        </is>
+      </c>
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>['Ibn_3ali']</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Mar 27, 2026 · 12:11 PM UTC</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2026-03-27T12:11:00Z</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>21</v>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2037495447351087452</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037495447351087452</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>We sincerely regret for the inconvenience, please note that we have replied to your email</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>We sincerely regret for the inconvenience, please note that we have replied to your email</t>
+        </is>
+      </c>
+      <c r="J54" t="b">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>['HimanshuMotiyan']</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Mar 27, 2026 · 11:42 AM UTC</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2026-03-27T11:42:00Z</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="n">
+        <v>1</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>17</v>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2037491991504998834</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>https://x.com/HimanshuMotiyan/status/2037491991504998834</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://x.com/HimanshuMotiyan</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>HimanshuMotiyan</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Himanshu Motiyani</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2032072703134613504/JzErzVWc_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Hello still the solution has not been provided by your team its more then a month @EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Hello still the solution has not been provided by your team its more then a month &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J55" t="b">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Mar 27, 2026 · 12:26 PM UTC</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2026-03-27T12:26:00Z</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Mar 27, 2026 · 11:28 AM UTC</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2026-03-27T11:28:00Z</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
         <is>
           <t>['https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="R16" t="n">
+      <c r="R55" t="n">
         <v>1</v>
       </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>5</v>
-      </c>
-      <c r="V16" t="inlineStr">
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>12</v>
+      </c>
+      <c r="V55" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2037505623932199158</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037505623932199158</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Emirates NBD</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>نأسف لسماع ذلك برجاء توضيح سبب إغلاق الحساب حتي نتمكن من مساعدتك بشكل أفضل</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>نأسف لسماع ذلك برجاء توضيح سبب إغلاق الحساب حتي نتمكن من مساعدتك بشكل أفضل</t>
-        </is>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>['Ibn_3ali']</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Mar 27, 2026 · 12:22 PM UTC</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2026-03-27T12:22:00Z</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>17</v>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2037505175750054028</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>https://x.com/HimanshuMotiyan/status/2037505175750054028</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>https://x.com/HimanshuMotiyan</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>HimanshuMotiyan</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Himanshu Motiyani</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2032072703134613504/JzErzVWc_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>I got again same response we will update you and are following up with the team its been more then 2 weeks Iam getting this same response instead of the solution</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>I got again same response we will update you and are following up with the team its been more then 2 weeks Iam getting this same response instead of the solution</t>
-        </is>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Mar 27, 2026 · 12:21 PM UTC</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2026-03-27T12:21:00Z</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>4</v>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2037502797097361735</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>https://x.com/Ibn_3ali/status/2037502797097361735</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://x.com/Ibn_3ali</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Ibn_3ali</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Ahmed Ali</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1836334761129721856/vSK3evXJ_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>كنت عايز أقفل حسابي</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>كنت عايز أقفل حسابي</t>
-        </is>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Mar 27, 2026 · 12:11 PM UTC</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2026-03-27T12:11:00Z</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>8</v>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2037502674548015413</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037502674548015413</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Emirates NBD</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>مرحبا أحمد شكرا لتواصلك معنا كيف يمكننا مساعدتك</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>مرحبا أحمد شكرا لتواصلك معنا كيف يمكننا مساعدتك</t>
-        </is>
-      </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>['Ibn_3ali']</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Mar 27, 2026 · 12:11 PM UTC</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2026-03-27T12:11:00Z</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>20</v>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2037495447351087452</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037495447351087452</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Emirates NBD</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>We sincerely regret for the inconvenience, please note that we have replied to your email</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>We sincerely regret for the inconvenience, please note that we have replied to your email</t>
-        </is>
-      </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>['HimanshuMotiyan']</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Mar 27, 2026 · 11:42 AM UTC</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2026-03-27T11:42:00Z</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>13</v>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2037491991504998834</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>https://x.com/HimanshuMotiyan/status/2037491991504998834</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>https://x.com/HimanshuMotiyan</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>HimanshuMotiyan</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Himanshu Motiyani</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2032072703134613504/JzErzVWc_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Hello still the solution has not been provided by your team its more then a month @EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Hello still the solution has not been provided by your team its more then a month &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;</t>
-        </is>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>Mar 27, 2026 · 11:28 AM UTC</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2026-03-27T11:28:00Z</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>9</v>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>2037488851749409129</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>https://x.com/Ldyheart/status/2037488851749409129</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>https://x.com/Ldyheart</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Ldyheart</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>RV Global Reset</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2016603167585087489/50LxYE_N_bigger.jpg</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
         <is>
           <t>Emirates NBD enables instant trading account top-ups for UAE investors
 New system lets UAE investors fund trading accounts in near real time gulfnews.com/business/bankin…</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>Emirates NBD enables instant trading account top-ups for UAE investors
 New system lets UAE investors fund trading accounts in near real time &lt;a href="https://gulfnews.com/business/banking/emirates-nbd-enables-instant-trading-account-top-ups-for-uae-investors-1.500487960"&gt;gulfnews.com/business/bankin…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J23" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
+      <c r="J56" t="b">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 11:16 AM UTC</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>2026-03-27T11:16:00Z</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
         <is>
           <t>['https://gulfnews.com/business/banking/emirates-nbd-enables-instant-trading-account-top-ups-for-uae-investors-1.500487960']</t>
         </is>
       </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>14</v>
-      </c>
-      <c r="V23" t="inlineStr">
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>15</v>
+      </c>
+      <c r="V56" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>2037487764074008675</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_KSA/status/2037487764074008675</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_KSA</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>EmiratesNBD_KSA</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>EmiratesNBD KSA</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
         <is>
           <t>مرحباً بك, يمكنك الأن معرفة المزيد والتقديم من خلال الضغط على الرابط ادناه.
 ms.spr.ly/6012QvVio</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>مرحباً بك, يمكنك الأن معرفة المزيد والتقديم من خلال الضغط على الرابط ادناه.
 &lt;a href="http://ms.spr.ly/6012QvVio"&gt;ms.spr.ly/6012QvVio&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
+      <c r="J57" t="b">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
         <is>
           <t>['abumusab999']</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 11:11 AM UTC</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>2026-03-27T11:11:00Z</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
         <is>
           <t>['http://ms.spr.ly/6012QvVio']</t>
         </is>
       </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>14</v>
-      </c>
-      <c r="V24" t="inlineStr">
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>18</v>
+      </c>
+      <c r="V57" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>2037486509704761575</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>https://x.com/DubaiTradersHub/status/2037486509704761575</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>https://x.com/DubaiTradersHub</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>DubaiTradersHub</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>Dubai Traders Hub</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1961482791326986240/P5yGeqC3_bigger.jpg</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
         <is>
           <t>UAE Market: The Golden Opportunity After War Dislocation -  tradingview.com/chart/EMIRAT…</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>UAE Market: The Golden Opportunity After War Dislocation -  &lt;a href="https://www.tradingview.com/chart/EMIRATESNBD/yUTmOrSv-UAE-Market-The-Golden-Opportunity-After-War-Dislocation/"&gt;tradingview.com/chart/EMIRAT…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
+      <c r="J58" t="b">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 11:06 AM UTC</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>2026-03-27T11:06:00Z</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
         <is>
           <t>['https://www.tradingview.com/chart/EMIRATESNBD/yUTmOrSv-UAE-Market-The-Golden-Opportunity-After-War-Dislocation/']</t>
         </is>
       </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
         <v>1</v>
       </c>
-      <c r="U25" t="n">
-        <v>29</v>
-      </c>
-      <c r="V25" t="inlineStr">
+      <c r="U58" t="n">
+        <v>32</v>
+      </c>
+      <c r="V58" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>2037486145496387811</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>https://x.com/abumusab999/status/2037486145496387811</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>https://x.com/abumusab999</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>abumusab999</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>SMAMRI</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1264193297305628672/qHnW4I-2_bigger.png</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
         <is>
           <t>جديده</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>جديده</t>
         </is>
       </c>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
+      <c r="J59" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
         <is>
           <t>['EmiratesNBD_KSA']</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 11:05 AM UTC</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>2026-03-27T11:05:00Z</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="n">
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="n">
         <v>1</v>
       </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>32</v>
-      </c>
-      <c r="V26" t="inlineStr">
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>35</v>
+      </c>
+      <c r="V59" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>2037484781038862844</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_EGY/status/2037484781038862844</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_EGY</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>EmiratesNBD_EGY</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
         <is>
           <t>Every time you dine at any restaurant inside TMG, you’ll earn 5%cashback when you pay using your Emirates NBD Mastercard credit card x TMG.
 Apply now and benefit from a dedicated program for TMG clients.
@@ -2791,7 +5771,7 @@
 Tax registration number: 204-897-319</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>Every time you dine at any restaurant inside TMG, you’ll earn 5%cashback when you pay using your Emirates NBD Mastercard credit card x TMG.
 Apply now and benefit from a dedicated program for TMG clients.
@@ -2800,79 +5780,79 @@
 Tax registration number: 204-897-319</t>
         </is>
       </c>
-      <c r="J27" t="b">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
+      <c r="J60" t="b">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 11:00 AM UTC</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>2026-03-27T11:00:00Z</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>65</v>
-      </c>
-      <c r="V27" t="inlineStr">
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>67</v>
+      </c>
+      <c r="V60" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>2037484780925644991</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_EGY/status/2037484780925644991</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_EGY</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>EmiratesNBD_EGY</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
         <is>
           <t>كل مرة تدفع فيها في أي مطعم داخل مجموعة طلعت مصطفى، هيرجعلك 5% كاش باك لما تدفع ببطاقة بنك الإمارات دبي الوطني ماستركارد الائتمانية بالتعاون مع مجموعة طلعت مصطفى.
 قدم الان بتسهيلات خاصة لعملاء المجموعة.
@@ -2881,7 +5861,7 @@
 رقم التسجيل الضريبي: 319-897-204</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>كل مرة تدفع فيها في أي مطعم داخل مجموعة طلعت مصطفى، هيرجعلك 5% كاش باك لما تدفع ببطاقة بنك الإمارات دبي الوطني ماستركارد الائتمانية بالتعاون مع مجموعة طلعت مصطفى.
 قدم الان بتسهيلات خاصة لعملاء المجموعة.
@@ -2890,169 +5870,169 @@
 رقم التسجيل الضريبي: 319-897-204</t>
         </is>
       </c>
-      <c r="J28" t="b">
-        <v>0</v>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
+      <c r="J61" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 11:00 AM UTC</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>2026-03-27T11:00:00Z</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>85</v>
-      </c>
-      <c r="V28" t="inlineStr">
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>91</v>
+      </c>
+      <c r="V61" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>2037484492445848044</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>https://x.com/livemint/status/2037484492445848044</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>https://x.com/livemint</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>livemint</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Mint</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1873593204349812737/foqpUBJN_bigger.jpg</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
         <is>
           <t>#MintIIS2026 | India is predominantly family-owned. For society to accept M&amp;As, there had to be behavioural change: Alok Malpani, Emirates NBD Capital India
 Watch live 📺  youtube.com/live/WxfWSloT6X4
 @Priyamouli1812 | @JSALawIndia @SAEL_India @PFRDAOfficial @equirusgroup</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>&lt;a href="/search?f=tweets&amp;amp;q=%23MintIIS2026"&gt;#MintIIS2026&lt;/a&gt; | India is predominantly family-owned. For society to accept M&amp;amp;As, there had to be behavioural change: Alok Malpani, Emirates NBD Capital India
 Watch live 📺  &lt;a href="https://www.youtube.com/live/WxfWSloT6X4"&gt;youtube.com/live/WxfWSloT6X4&lt;/a&gt;
 &lt;a href="/Priyamouli1812" title="Priyamvada C"&gt;@Priyamouli1812&lt;/a&gt; | &lt;a href="/JSALawIndia" title="JSA Advocates &amp;amp; Solicitors"&gt;@JSALawIndia&lt;/a&gt; &lt;a href="/SAEL_India" title="SAEL"&gt;@SAEL_India&lt;/a&gt; &lt;a href="/PFRDAOfficial" title="PFRDA"&gt;@PFRDAOfficial&lt;/a&gt; &lt;a href="/equirusgroup" title="Equirus"&gt;@equirusgroup&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 10:58 AM UTC</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>2026-03-27T10:58:00Z</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23MintIIS2026', 'https://www.youtube.com/live/WxfWSloT6X4', 'https://x.com/Priyamouli1812', 'https://x.com/JSALawIndia', 'https://x.com/SAEL_India', 'https://x.com/PFRDAOfficial', 'https://x.com/equirusgroup']</t>
         </is>
       </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2</v>
-      </c>
-      <c r="U29" t="n">
-        <v>918</v>
-      </c>
-      <c r="V29" t="inlineStr">
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>929</v>
+      </c>
+      <c r="V62" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>2037483796837380338</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>https://x.com/livemint/status/2037483796837380338</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>https://x.com/livemint</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>livemint</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Mint</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1873593204349812737/foqpUBJN_bigger.jpg</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
         <is>
           <t>#MintIIS2026 | Alok Malpani, CEO, Emirates NBD Capital India Pvt Ltd: India, predominantly, is family owned. Even the conglomerates are family owned, the decision makers are individuals…for society to accept m&amp;as there has to be behavioural change. The real m&amp;a activity started in 2005 where India went on a shopping spree…Post-Covid the structural behaviour saw a change and we saw evolution in domestic deal making.
 Watch live 🔴
@@ -3060,7 +6040,7 @@
  @JSALawIndia |  @SAEL_India | @gripinvest | @PFRDAOfficial |  @equirusgroup | @MuthootIndia |  @MProfit</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>&lt;a href="/search?f=tweets&amp;amp;q=%23MintIIS2026"&gt;#MintIIS2026&lt;/a&gt; | Alok Malpani, CEO, Emirates NBD Capital India Pvt Ltd: India, predominantly, is family owned. Even the conglomerates are family owned, the decision makers are individuals…for society to accept m&amp;amp;as there has to be behavioural change. The real m&amp;amp;a activity started in 2005 where India went on a shopping spree…Post-Covid the structural behaviour saw a change and we saw evolution in domestic deal making.
 Watch live 🔴
@@ -3068,1225 +6048,1225 @@
  &lt;a href="/JSALawIndia" title="JSA Advocates &amp;amp; Solicitors"&gt;@JSALawIndia&lt;/a&gt; |  &lt;a href="/SAEL_India" title="SAEL"&gt;@SAEL_India&lt;/a&gt; | &lt;a href="/gripinvest" title="Grip Invest"&gt;@gripinvest&lt;/a&gt; | &lt;a href="/PFRDAOfficial" title="PFRDA"&gt;@PFRDAOfficial&lt;/a&gt; |  &lt;a href="/equirusgroup" title="Equirus"&gt;@equirusgroup&lt;/a&gt; | &lt;a href="/MuthootIndia" title="muthootindia"&gt;@MuthootIndia&lt;/a&gt; |  &lt;a href="/MProfit" title="MProfit"&gt;@MProfit&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J30" t="b">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
+      <c r="J63" t="b">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
         <is>
           <t>['livemint', 'kotak811', 'nikunjbiyani', 'RaymondRealtyIN', 'Avendus', 'Brookfield', 'GoldmanSachs']</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 10:56 AM UTC</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>2026-03-27T10:56:00Z</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23MintIIS2026', 'https://youtube.com/live/WxfWSloT6X4', 'https://x.com/JSALawIndia', 'https://x.com/SAEL_India', 'https://x.com/gripinvest', 'https://x.com/PFRDAOfficial', 'https://x.com/equirusgroup', 'https://x.com/MuthootIndia', 'https://x.com/MProfit']</t>
         </is>
       </c>
-      <c r="R30" t="n">
+      <c r="R63" t="n">
         <v>1</v>
       </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>457</v>
-      </c>
-      <c r="V30" t="inlineStr">
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>461</v>
+      </c>
+      <c r="V63" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>2037481371753443331</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_KSA/status/2037481371753443331</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_KSA</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>EmiratesNBD_KSA</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>EmiratesNBD KSA</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
         <is>
           <t>مرحبا شكرا لتواصلك معنا برجاء التوضيح هل ترغب في التقديم علي بطاقه جديده أو أستبدال بطاقه حاليه</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>مرحبا شكرا لتواصلك معنا برجاء التوضيح هل ترغب في التقديم علي بطاقه جديده أو أستبدال بطاقه حاليه</t>
         </is>
       </c>
-      <c r="J31" t="b">
-        <v>0</v>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
+      <c r="J64" t="b">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
         <is>
           <t>['abumusab999']</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 10:46 AM UTC</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>2026-03-27T10:46:00Z</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="n">
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="n">
         <v>1</v>
       </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>17</v>
-      </c>
-      <c r="V31" t="inlineStr">
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
+        <v>20</v>
+      </c>
+      <c r="V64" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>2037480800703086596</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037480800703086596</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
         <is>
           <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach to us at 
 social@emiratesnbd.com
 Quoting case #989304 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach to us at 
 social@emiratesnbd.com
 Quoting case #989304 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
         </is>
       </c>
-      <c r="J32" t="b">
-        <v>0</v>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
+      <c r="J65" t="b">
+        <v>0</v>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
         <is>
           <t>['harrissayoub']</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 10:44 AM UTC</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>2026-03-27T10:44:00Z</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>9</v>
-      </c>
-      <c r="V32" t="inlineStr">
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>12</v>
+      </c>
+      <c r="V65" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>2037476568159727811</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>https://x.com/abumusab999/status/2037476568159727811</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>https://x.com/abumusab999</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>abumusab999</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>SMAMRI</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1264193297305628672/qHnW4I-2_bigger.png</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA كيف طريقة استخراج بطاقة مزيد الائتمانيه ؟</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; كيف طريقة استخراج بطاقة مزيد الائتمانيه ؟</t>
         </is>
       </c>
-      <c r="J33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
+      <c r="J66" t="b">
+        <v>0</v>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 10:27 AM UTC</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>2026-03-27T10:27:00Z</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr">
         <is>
           <t>['https://x.com/EmiratesNBD_KSA']</t>
         </is>
       </c>
-      <c r="R33" t="n">
+      <c r="R66" t="n">
         <v>1</v>
       </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>37</v>
-      </c>
-      <c r="V33" t="inlineStr">
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>42</v>
+      </c>
+      <c r="V66" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>2037475105203507641</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>https://x.com/EntAlArabiya/status/2037475105203507641</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>https://x.com/EntAlArabiya</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>EntAlArabiya</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Entrepreneur العربية</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1514308412343033862/Cl9tt_tx_bigger.jpg</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
         <is>
           <t>الدولية للأوراق المالية تنضم إلى منصة بنك الإمارات دبي الوطني باي @EmiratesNBD_AE 
 #بنك_الإمارات_دبي_الوطني #الدولية_للأوراق_المالية #فيزا #المدفوعات #الاستثمار  #entalarabiya
 entrepreneuralarabiya.com/20…</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>الدولية للأوراق المالية تنضم إلى منصة بنك الإمارات دبي الوطني باي &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
 &lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_دبي_الوطني"&gt;#بنك_الإمارات_دبي_الوطني&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الدولية_للأوراق_المالية"&gt;#الدولية_للأوراق_المالية&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23فيزا"&gt;#فيزا&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23المدفوعات"&gt;#المدفوعات&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23الاستثمار"&gt;#الاستثمار&lt;/a&gt;  &lt;a href="/search?f=tweets&amp;amp;q=%23entalarabiya"&gt;#entalarabiya&lt;/a&gt;
 &lt;a href="https://entrepreneuralarabiya.com/2026/03/27/77211/%d8%a7%d9%84%d8%af%d9%88%d9%84%d9%8a%d8%a9-%d9%84%d9%84%d8%a3%d9%88%d8%b1%d8%a7%d9%82-%d8%a7%d9%84%d9%85%d8%a7%d9%84%d9%8a%d8%a9-%d8%aa%d8%a8%d8%af%d8%a3-%d8%a7%d9%84%d8%b9%d9%85%d9%84-%d9%83/"&gt;entrepreneuralarabiya.com/20…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J34" t="b">
-        <v>0</v>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
+      <c r="J67" t="b">
+        <v>0</v>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 10:21 AM UTC</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>2026-03-27T10:21:00Z</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
         <is>
           <t>['https://x.com/EmiratesNBD_AE', 'https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_دبي_الوطني', 'https://x.com/search?f=tweets&amp;q=%23الدولية_للأوراق_المالية', 'https://x.com/search?f=tweets&amp;q=%23فيزا', 'https://x.com/search?f=tweets&amp;q=%23المدفوعات', 'https://x.com/search?f=tweets&amp;q=%23الاستثمار', 'https://x.com/search?f=tweets&amp;q=%23entalarabiya', 'https://entrepreneuralarabiya.com/2026/03/27/77211/%d8%a7%d9%84%d8%af%d9%88%d9%84%d9%8a%d8%a9-%d9%84%d9%84%d8%a3%d9%88%d8%b1%d8%a7%d9%82-%d8%a7%d9%84%d9%85%d8%a7%d9%84%d9%8a%d8%a9-%d8%aa%d8%a8%d8%af%d8%a3-%d8%a7%d9%84%d8%b9%d9%85%d9%84-%d9%83/']</t>
         </is>
       </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>86</v>
-      </c>
-      <c r="V34" t="inlineStr">
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>89</v>
+      </c>
+      <c r="V67" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>2037470129664196764</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>https://x.com/ForumRemittance/status/2037470129664196764</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>https://x.com/ForumRemittance</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>ForumRemittance</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>World Remittance Action Forum</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1942959686417891328/FNdImGgE_bigger.jpg</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
         <is>
           <t>Emirates NBD has announced that UAE-based brokerage International Securities is now live on Emirates NBD Pay, enabling fast and secure trading account funding through Visa’s AFT model.
 #EmiratesNBD #Fintech #DigitalPayments #Trading #UAE #Visa #Innovation #Finance</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>Emirates NBD has announced that UAE-based brokerage International Securities is now live on Emirates NBD Pay, enabling fast and secure trading account funding through Visa’s AFT model.
 &lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Fintech"&gt;#Fintech&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23DigitalPayments"&gt;#DigitalPayments&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Trading"&gt;#Trading&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Visa"&gt;#Visa&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Innovation"&gt;#Innovation&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Finance"&gt;#Finance&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J35" t="b">
-        <v>0</v>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
+      <c r="J68" t="b">
+        <v>0</v>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 10:01 AM UTC</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>2026-03-27T10:01:00Z</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23Fintech', 'https://x.com/search?f=tweets&amp;q=%23DigitalPayments', 'https://x.com/search?f=tweets&amp;q=%23Trading', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23Visa', 'https://x.com/search?f=tweets&amp;q=%23Innovation', 'https://x.com/search?f=tweets&amp;q=%23Finance']</t>
         </is>
       </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>16</v>
-      </c>
-      <c r="V35" t="inlineStr">
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>18</v>
+      </c>
+      <c r="V68" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>2037466808576266477</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037466808576266477</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
         <is>
           <t>Kindly be informed that Liv team will be checking and responding to your email shortly, thank you for your patience.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>Kindly be informed that Liv team will be checking and responding to your email shortly, thank you for your patience.</t>
         </is>
       </c>
-      <c r="J36" t="b">
-        <v>0</v>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
+      <c r="J69" t="b">
+        <v>0</v>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
         <is>
           <t>['xlcsp']</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 9:48 AM UTC</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>2026-03-27T09:48:00Z</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>10</v>
-      </c>
-      <c r="V36" t="inlineStr">
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>12</v>
+      </c>
+      <c r="V69" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>2037465040018940100</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>https://x.com/harrissayoub/status/2037465040018940100</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>https://x.com/harrissayoub</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>harrissayoub</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>Harris</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1941456770540417024/W7CsxFZc_bigger.jpg</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
         <is>
           <t>Watch them auto-reply to this with a generic support email.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>Watch them auto-reply to this with a generic support email.</t>
         </is>
       </c>
-      <c r="J37" t="b">
-        <v>0</v>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
+      <c r="J70" t="b">
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
         <is>
           <t>['harrissayoub', 'EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 9:41 AM UTC</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>2026-03-27T09:41:00Z</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="n">
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="n">
         <v>1</v>
       </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>17</v>
-      </c>
-      <c r="V37" t="inlineStr">
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>21</v>
+      </c>
+      <c r="V70" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>2037464657695563894</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>https://x.com/harrissayoub/status/2037464657695563894</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>https://x.com/harrissayoub</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>harrissayoub</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>Harris</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1941456770540417024/W7CsxFZc_bigger.jpg</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
         <is>
           <t>Dealing with @EmiratesNBD_AE always follows the same pattern. Stage 1: Delays. Stage 2: Unclear responses. And finally Stage 3: Multiple follow-ups just to get the simplest things done. Currently at Stage 3.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>Dealing with &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; always follows the same pattern. Stage 1: Delays. Stage 2: Unclear responses. And finally Stage 3: Multiple follow-ups just to get the simplest things done. Currently at Stage 3.</t>
         </is>
       </c>
-      <c r="J38" t="b">
-        <v>0</v>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
+      <c r="J71" t="b">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 9:40 AM UTC</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>2026-03-27T09:40:00Z</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr">
         <is>
           <t>['https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="R38" t="n">
+      <c r="R71" t="n">
         <v>1</v>
       </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>12</v>
-      </c>
-      <c r="V38" t="inlineStr">
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>15</v>
+      </c>
+      <c r="V71" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>2037455548719968567</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>https://x.com/Dharmen86931771/status/2037455548719968567</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>https://x.com/Dharmen86931771</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>Dharmen86931771</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>Dharmendra</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1384832109672554500/1AdJFlb9_bigger.jpg</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
         <is>
           <t>Mutual fund 
 #ENBDRiddleOfTheWeek 
 #financialwellbeing</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>Mutual fund 
 &lt;a href="/search?f=tweets&amp;amp;q=%23ENBDRiddleOfTheWeek"&gt;#ENBDRiddleOfTheWeek&lt;/a&gt; 
 &lt;a href="/search?f=tweets&amp;amp;q=%23financialwellbeing"&gt;#financialwellbeing&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J39" t="b">
-        <v>0</v>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
+      <c r="J72" t="b">
+        <v>0</v>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 9:03 AM UTC</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>2026-03-27T09:03:00Z</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23ENBDRiddleOfTheWeek', 'https://x.com/search?f=tweets&amp;q=%23financialwellbeing']</t>
         </is>
       </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>4</v>
-      </c>
-      <c r="V39" t="inlineStr">
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>5</v>
+      </c>
+      <c r="V72" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>2037432200166277382</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037432200166277382</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
         <is>
           <t>Stay safe and bank with ease with ENBD X and businessONLINE 
 Visit emiratesnbd.com</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>Stay safe and bank with ease with ENBD X and businessONLINE 
 Visit &lt;a href="http://www.emiratesnbd.com"&gt;emiratesnbd.com&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J40" t="b">
-        <v>0</v>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 7:31 AM UTC</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>2026-03-27T07:31:00Z</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr">
         <is>
           <t>['http://www.emiratesnbd.com']</t>
         </is>
       </c>
-      <c r="R40" t="n">
+      <c r="R73" t="n">
         <v>1</v>
       </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>7</v>
-      </c>
-      <c r="U40" t="n">
-        <v>817</v>
-      </c>
-      <c r="V40" t="inlineStr">
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>8</v>
+      </c>
+      <c r="U73" t="n">
+        <v>871</v>
+      </c>
+      <c r="V73" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>2037427832348082374</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>https://x.com/jazrawia15/status/2037427832348082374</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>https://x.com/jazrawia15</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>jazrawia15</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>مريم ❤ MBZ</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1652475865333211136/KGd9uKCV_bigger.jpg</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
         <is>
           <t>صناديق الاستثمار المشتركة (Mutual Funds)</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>صناديق الاستثمار المشتركة (Mutual Funds)</t>
         </is>
       </c>
-      <c r="J41" t="b">
-        <v>0</v>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 7:13 AM UTC</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>2026-03-27T07:13:00Z</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>19</v>
-      </c>
-      <c r="V41" t="inlineStr">
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="n">
+        <v>20</v>
+      </c>
+      <c r="V74" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>2037427668879286533</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>https://x.com/jazrawia15/status/2037427668879286533</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>https://x.com/jazrawia15</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>jazrawia15</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>مريم ❤ MBZ</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1652475865333211136/KGd9uKCV_bigger.jpg</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
         <is>
           <t>صناديق الاستثمار المشتركة (Mutual Funds)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>صناديق الاستثمار المشتركة (Mutual Funds)</t>
         </is>
       </c>
-      <c r="J42" t="b">
-        <v>0</v>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 7:13 AM UTC</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>2026-03-27T07:13:00Z</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>17</v>
-      </c>
-      <c r="V42" t="inlineStr">
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>18</v>
+      </c>
+      <c r="V75" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>2037414318078120348</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>https://x.com/NovoCinemas/status/2037414318078120348</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>https://x.com/NovoCinemas</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>NovoCinemas</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>Novo Cinemas</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2008888282768429056/a3q3GqDa_bigger.jpg</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
         <is>
           <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting NovoCinemas.com or the App</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting &lt;a href="http://www.NovoCinemas.com"&gt;NovoCinemas.com&lt;/a&gt; or the App</t>
         </is>
       </c>
-      <c r="J43" t="b">
-        <v>0</v>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 6:20 AM UTC</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>2026-03-27T06:20:00Z</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr">
         <is>
           <t>['http://www.NovoCinemas.com']</t>
         </is>
       </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>53</v>
-      </c>
-      <c r="V43" t="inlineStr">
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="n">
+        <v>54</v>
+      </c>
+      <c r="V76" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>2037394759174799528</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>https://x.com/Tahoor500/status/2037394759174799528</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>https://x.com/Tahoor500</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>Tahoor500</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>Raja Tahoor Ahmad</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2035431872751382528/wMJZfEXF_bigger.jpg</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
         <is>
           <t>Great to see UAE banks like Emirates NBD waiving ATM fees due to current situation.
 ​But honestly, where are the money transfer apps?
@@ -4294,7 +7274,7 @@
 @dutweets @Botim_Official @remitly @remitlysupport @eandmoney</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>Great to see UAE banks like Emirates NBD waiving ATM fees due to current situation.
 ​But honestly, where are the money transfer apps?
@@ -4302,177 +7282,177 @@
 &lt;a href="/dutweets" title="dutweets"&gt;@dutweets&lt;/a&gt; &lt;a href="/Botim_Official" title="botim"&gt;@Botim_Official&lt;/a&gt; &lt;a href="/remitly" title="Remitly 🌎"&gt;@remitly&lt;/a&gt; &lt;a href="/remitlysupport" title="@RemitlySupport"&gt;@remitlysupport&lt;/a&gt; &lt;a href="/eandmoney" title="e&amp;amp; money"&gt;@eandmoney&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J44" t="b">
-        <v>0</v>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
         <is>
           <t>Mar 27</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 5:02 AM UTC</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>2026-03-27T05:02:00Z</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr">
         <is>
           <t>['https://x.com/dutweets', 'https://x.com/Botim_Official', 'https://x.com/remitly', 'https://x.com/remitlysupport', 'https://x.com/eandmoney']</t>
         </is>
       </c>
-      <c r="R44" t="n">
+      <c r="R77" t="n">
         <v>1</v>
       </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>101</v>
-      </c>
-      <c r="V44" t="inlineStr">
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="n">
+        <v>106</v>
+      </c>
+      <c r="V77" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>2037384139725488443</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>https://x.com/marcelraj/status/2037384139725488443</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>https://x.com/marcelraj</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>marcelraj</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>Marcel Raj</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/980770440766517248/keE9mwcw_bigger.jpg</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
         <is>
           <t>Mutual fund 
 #ENBDRiddleOfTheWeek 
 #financialwellbeing</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>Mutual fund 
 &lt;a href="/search?f=tweets&amp;amp;q=%23ENBDRiddleOfTheWeek"&gt;#ENBDRiddleOfTheWeek&lt;/a&gt; 
 &lt;a href="/search?f=tweets&amp;amp;q=%23financialwellbeing"&gt;#financialwellbeing&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J45" t="b">
-        <v>0</v>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>Mar 27</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 4:20 AM UTC</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>2026-03-27T04:20:00Z</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23ENBDRiddleOfTheWeek', 'https://x.com/search?f=tweets&amp;q=%23financialwellbeing']</t>
         </is>
       </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>15</v>
-      </c>
-      <c r="V45" t="inlineStr">
+      <c r="R78" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" t="n">
+        <v>16</v>
+      </c>
+      <c r="V78" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>2037369717959324018</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>https://x.com/wownews24x7/status/2037369717959324018</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>https://x.com/wownews24x7</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>wownews24x7</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>WOWNEWS24x7</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1928409671158697984/PhdWuhH9_bigger.jpg</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr">
         <is>
           <t>✅ Positives
 ‣ Infosys to acquire Stratus &amp; Optimum Healthcare IT
@@ -4481,7 +7461,7 @@
 #StocksToWatch #WOWNEWS24x7</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>✅ Positives
 ‣ Infosys to acquire Stratus &amp;amp; Optimum Healthcare IT
@@ -4490,347 +7470,347 @@
 &lt;a href="/search?f=tweets&amp;amp;q=%23StocksToWatch"&gt;#StocksToWatch&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23WOWNEWS24x7"&gt;#WOWNEWS24x7&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J46" t="b">
-        <v>0</v>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
+      <c r="J79" t="b">
+        <v>0</v>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
         <is>
           <t>Mar 27</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 3:22 AM UTC</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>2026-03-27T03:22:00Z</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23StocksToWatch', 'https://x.com/search?f=tweets&amp;q=%23WOWNEWS24x7']</t>
         </is>
       </c>
-      <c r="R46" t="n">
+      <c r="R79" t="n">
         <v>1</v>
       </c>
-      <c r="S46" t="n">
+      <c r="S79" t="n">
         <v>1</v>
       </c>
-      <c r="T46" t="n">
+      <c r="T79" t="n">
         <v>1</v>
       </c>
-      <c r="U46" t="n">
-        <v>66</v>
-      </c>
-      <c r="V46" t="inlineStr">
+      <c r="U79" t="n">
+        <v>67</v>
+      </c>
+      <c r="V79" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>2037368895515050154</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>https://x.com/MoneyMitra2025/status/2037368895515050154</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>https://x.com/MoneyMitra2025</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>MoneyMitra2025</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>Money Mitra</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1982277795695689728/_7ElsJLA_bigger.jpg</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
         <is>
           <t>2️⃣8️⃣ 🟢 𝗥𝗕𝗟 𝗕𝗔𝗡𝗞
 • Emirates NBD gets UAE central-bank nod for stake buy, RBI nod awaited
 #RBLBank #StakeSale #Banking</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>2️⃣8️⃣ 🟢 𝗥𝗕𝗟 𝗕𝗔𝗡𝗞
 • Emirates NBD gets UAE central-bank nod for stake buy, RBI nod awaited
 &lt;a href="/search?f=tweets&amp;amp;q=%23RBLBank"&gt;#RBLBank&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23StakeSale"&gt;#StakeSale&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J47" t="b">
-        <v>0</v>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
+      <c r="J80" t="b">
+        <v>0</v>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
         <is>
           <t>Mar 27</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 3:19 AM UTC</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>2026-03-27T03:19:00Z</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr">
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23RBLBank', 'https://x.com/search?f=tweets&amp;q=%23StakeSale', 'https://x.com/search?f=tweets&amp;q=%23Banking']</t>
         </is>
       </c>
-      <c r="R47" t="n">
+      <c r="R80" t="n">
         <v>1</v>
       </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>88</v>
-      </c>
-      <c r="V47" t="inlineStr">
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="n">
+        <v>93</v>
+      </c>
+      <c r="V80" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>2037351848236155236</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>https://x.com/BusinessTiding/status/2037351848236155236</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>https://x.com/BusinessTiding</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>BusinessTiding</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>BUSINESS TIDING</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1754469023033769984/tgDMDS68_bigger.jpg</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
         <is>
           <t>#IndoThai Securities: The Company (Indo Thai Financial Services) has increased the authorized Share Capital from Rs. 30 lakh to Rs. 15 Crores
 #RBLBank: Announced that Emirates NBD Bank has received approval from the Central Bank of UAE to acquire a majority stake in RBL Bank</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>&lt;a href="/search?f=tweets&amp;amp;q=%23IndoThai"&gt;#IndoThai&lt;/a&gt; Securities: The Company (Indo Thai Financial Services) has increased the authorized Share Capital from Rs. 30 lakh to Rs. 15 Crores
 &lt;a href="/search?f=tweets&amp;amp;q=%23RBLBank"&gt;#RBLBank&lt;/a&gt;: Announced that Emirates NBD Bank has received approval from the Central Bank of UAE to acquire a majority stake in RBL Bank</t>
         </is>
       </c>
-      <c r="J48" t="b">
-        <v>0</v>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
+      <c r="J81" t="b">
+        <v>0</v>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
         <is>
           <t>Mar 27</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 2:11 AM UTC</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>2026-03-27T02:11:00Z</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23IndoThai', 'https://x.com/search?f=tweets&amp;q=%23RBLBank']</t>
         </is>
       </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
+      <c r="R81" t="n">
+        <v>0</v>
+      </c>
+      <c r="S81" t="n">
         <v>1</v>
       </c>
-      <c r="T48" t="n">
+      <c r="T81" t="n">
         <v>1</v>
       </c>
-      <c r="U48" t="n">
-        <v>77</v>
-      </c>
-      <c r="V48" t="inlineStr">
+      <c r="U81" t="n">
+        <v>85</v>
+      </c>
+      <c r="V81" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>2037319416560402505</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>https://x.com/babanasseralgh/status/2037319416560402505</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>https://x.com/babanasseralgh</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>babanasseralgh</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>لفقيدي والدي</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1645878730496114688/ejU13FCo_bigger.jpg</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA ممكن تردون خاص</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; ممكن تردون خاص</t>
         </is>
       </c>
-      <c r="J49" t="b">
-        <v>0</v>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
+      <c r="J82" t="b">
+        <v>0</v>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
         <is>
           <t>Mar 27</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 12:02 AM UTC</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>2026-03-27T00:02:00Z</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr">
         <is>
           <t>['https://x.com/EmiratesNBD_KSA']</t>
         </is>
       </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
-        <v>7</v>
-      </c>
-      <c r="V49" t="inlineStr">
+      <c r="R82" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>0</v>
+      </c>
+      <c r="U82" t="n">
+        <v>8</v>
+      </c>
+      <c r="V82" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>2037499728318116157</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>https://x.com/SanadakUAE/status/2037499728318116157</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>https://x.com/SanadakUAE</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>SanadakUAE</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>Sanadak</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2012879499768049664/EHCzbImW_bigger.jpg</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
         <is>
           <t>Dear Safwan,
 Thank you for contacting Sanadak, Ombudsman Unit for the UAE.
@@ -4839,7 +7819,7 @@
 Sanadak Team</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>Dear Safwan,
 Thank you for contacting Sanadak, Ombudsman Unit for the UAE.
@@ -4848,357 +7828,357 @@
 Sanadak Team</t>
         </is>
       </c>
-      <c r="J50" t="b">
-        <v>0</v>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
+      <c r="J83" t="b">
+        <v>0</v>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
         <is>
           <t>['abuzubayr1987', 'emiratesislamic', 'JamalIslamic']</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 11:59 AM UTC</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>2026-03-27T11:59:00Z</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr">
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr">
         <is>
           <t>['https://www.sanadak.gov.ae/en/']</t>
         </is>
       </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>14</v>
-      </c>
-      <c r="V50" t="inlineStr">
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>0</v>
+      </c>
+      <c r="U83" t="n">
+        <v>15</v>
+      </c>
+      <c r="V83" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>2037485522399236349</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>https://x.com/abuzubayr1987/status/2037485522399236349</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>https://x.com/abuzubayr1987</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>abuzubayr1987</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>Safwan</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr">
         <is>
           <t>All I got was a feedback form!
 No real solution, making things worse for me every passing day. No response from account manager. Now even my registered mobile number is suspended due to this 100% deduction that was done and I am unable to do payments!
 @SanadakUAE @JamalIslamic</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>All I got was a feedback form!
 No real solution, making things worse for me every passing day. No response from account manager. Now even my registered mobile number is suspended due to this 100% deduction that was done and I am unable to do payments!
 &lt;a href="/SanadakUAE" title="Sanadak"&gt;@SanadakUAE&lt;/a&gt; &lt;a href="/JamalIslamic" title="JAMAL BIN GHALIATA (CEO EMIRATES ISLAMIC BANK)"&gt;@JamalIslamic&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J51" t="b">
-        <v>0</v>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
+      <c r="J84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
         <is>
           <t>['emiratesislamic']</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 11:02 AM UTC</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>2026-03-27T11:02:00Z</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr">
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr">
         <is>
           <t>['https://x.com/SanadakUAE', 'https://x.com/JamalIslamic']</t>
         </is>
       </c>
-      <c r="R51" t="n">
+      <c r="R84" t="n">
         <v>1</v>
       </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>14</v>
-      </c>
-      <c r="V51" t="inlineStr">
+      <c r="S84" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>0</v>
+      </c>
+      <c r="U84" t="n">
+        <v>15</v>
+      </c>
+      <c r="V84" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>2037484085459750931</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2037484085459750931</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr">
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
         <is>
           <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
 better please check your private message.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>Dear customer please note that we have replied to you on the same message on the previous post, to serve you 
 better please check your private message.</t>
         </is>
       </c>
-      <c r="J52" t="b">
-        <v>0</v>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
+      <c r="J85" t="b">
+        <v>0</v>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
         <is>
           <t>['abuzubayr1987']</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 10:57 AM UTC</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>2026-03-27T10:57:00Z</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="n">
-        <v>11</v>
-      </c>
-      <c r="V52" t="inlineStr">
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="n">
+        <v>0</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
+        <v>0</v>
+      </c>
+      <c r="U85" t="n">
+        <v>13</v>
+      </c>
+      <c r="V85" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>2037480161797722518</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>https://x.com/abuzubayr1987/status/2037480161797722518</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>https://x.com/abuzubayr1987</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>abuzubayr1987</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>Safwan</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
         <is>
           <t>Hello
 I got a call from your social media team, with no real solution because they cannot access my account from alternative number. While all other departments are quick enough to access details and deduct undue amounts without prior notice.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>Hello
 I got a call from your social media team, with no real solution because they cannot access my account from alternative number. While all other departments are quick enough to access details and deduct undue amounts without prior notice.</t>
         </is>
       </c>
-      <c r="J53" t="b">
-        <v>0</v>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr">
+      <c r="J86" t="b">
+        <v>0</v>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
         <is>
           <t>['emiratesislamic']</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 10:41 AM UTC</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>2026-03-27T10:41:00Z</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="n">
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="n">
         <v>1</v>
       </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>13</v>
-      </c>
-      <c r="V53" t="inlineStr">
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>0</v>
+      </c>
+      <c r="U86" t="n">
+        <v>15</v>
+      </c>
+      <c r="V86" t="inlineStr">
         <is>
           <t>EI</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>2037462241591615667</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2037462241591615667</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>emiratesislamic</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1526452318874619904/yJhExjro_bigger.jpg</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
         <is>
           <t>سلامتكم أولويتنا.
 نوصي باستخدام تطبيق + EI ومنصة businessONLINE لإنجاز معاملاتكم المصرفية بسهولة وأمان.
@@ -5206,7 +8186,7 @@
 Use EI + Mobile &amp; Online Banking and businessONLINE with ease and security.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>سلامتكم أولويتنا.
 نوصي باستخدام تطبيق + EI ومنصة businessONLINE لإنجاز معاملاتكم المصرفية بسهولة وأمان.
@@ -5214,41 +8194,41 @@
 Use EI + Mobile &amp;amp; Online Banking and businessONLINE with ease and security.</t>
         </is>
       </c>
-      <c r="J54" t="b">
-        <v>0</v>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
+      <c r="J87" t="b">
+        <v>0</v>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Mar 27</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
         <is>
           <t>Mar 27, 2026 · 9:30 AM UTC</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="O87" t="inlineStr">
         <is>
           <t>2026-03-27T09:30:00Z</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
         <v>1</v>
       </c>
-      <c r="T54" t="n">
+      <c r="T87" t="n">
         <v>2</v>
       </c>
-      <c r="U54" t="n">
-        <v>90</v>
-      </c>
-      <c r="V54" t="inlineStr">
+      <c r="U87" t="n">
+        <v>101</v>
+      </c>
+      <c r="V87" t="inlineStr">
         <is>
           <t>EI</t>
         </is>

--- a/EI_ENBD_3post.xlsx
+++ b/EI_ENBD_3post.xlsx
@@ -593,7 +593,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>9h</t>
+          <t>11h</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -704,7 +704,7 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>12h</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -790,7 +790,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -908,7 +908,7 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -994,7 +994,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1084,7 +1084,7 @@
         <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>641</v>
+        <v>651</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1432,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1518,7 +1518,7 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1688,7 +1688,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1778,7 +1778,7 @@
         <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1870,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1956,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2042,7 +2042,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>21h</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2128,7 +2128,7 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2224,7 +2224,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2322,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2420,7 +2420,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2518,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2608,7 +2608,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2698,7 +2698,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2878,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2968,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3060,7 +3060,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3150,7 +3150,7 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3240,7 +3240,7 @@
         <v>3</v>
       </c>
       <c r="U31" t="n">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3510,7 +3510,7 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3602,7 +3602,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3782,7 +3782,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3874,7 +3874,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3964,7 +3964,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4054,7 +4054,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4144,7 +4144,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4234,7 +4234,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4412,7 +4412,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>

--- a/EI_ENBD_3post.xlsx
+++ b/EI_ENBD_3post.xlsx
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -790,7 +790,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -994,7 +994,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1081,10 +1081,10 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>651</v>
+        <v>663</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1956,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2042,7 +2042,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2128,7 +2128,7 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>3</v>
       </c>
       <c r="U31" t="n">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -3874,7 +3874,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>

--- a/EI_ENBD_3post.xlsx
+++ b/EI_ENBD_3post.xlsx
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>13h</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -704,7 +704,7 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -908,7 +908,7 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>663</v>
+        <v>672</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1170,7 +1170,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>20h</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1518,7 +1518,7 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         <v>4</v>
       </c>
       <c r="U15" t="n">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>22h</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1870,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -2322,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2608,7 +2608,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2698,7 +2698,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2878,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2968,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3060,7 +3060,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3150,7 +3150,7 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3240,7 +3240,7 @@
         <v>3</v>
       </c>
       <c r="U31" t="n">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3420,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3602,7 +3602,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3782,7 +3782,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3874,7 +3874,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3964,7 +3964,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4054,7 +4054,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4144,7 +4144,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4234,7 +4234,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>23h</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4326,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -4412,7 +4412,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>

--- a/EI_ENBD_3post.xlsx
+++ b/EI_ENBD_3post.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V44"/>
+  <dimension ref="A1:V50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,43 +543,43 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2037955706662604958</t>
+          <t>2038194022280282249</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2038194022280282249</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/Rita09729643</t>
+          <t>https://x.com/EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Rita09729643</t>
+          <t>EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rita</t>
+          <t>EmiratesNBD KSA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1655465335775010816/KmAYkyBx_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hi I have a credit card of Emirates NBD, but I haven’t used it for many years, suddenly I received the email of statement that I need to pay 764.13AED as the total payment due, this is really unacceptable.</t>
+          <t>شكراً لتواصلك معنا وإظهار اهتمامك بمنتجنا. يرجى مشاركتنا برقم هاتفك الجوال المسجل ومكان السكن في المملكة العربية السعودية حتى نتمكن من ترتيب اتصال معك من قبل فريقنا. مع التحية</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Hi I have a credit card of Emirates NBD, but I haven’t used it for many years, suddenly I received the email of statement that I need to pay 764.13AED as the total payment due, this is really unacceptable.</t>
+          <t>شكراً لتواصلك معنا وإظهار اهتمامك بمنتجنا. يرجى مشاركتنا برقم هاتفك الجوال المسجل ومكان السكن في المملكة العربية السعودية حتى نتمكن من ترتيب اتصال معك من قبل فريقنا. مع التحية</t>
         </is>
       </c>
       <c r="J2" t="b">
@@ -588,22 +588,22 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['M17322417']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>7m</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 6:11 PM UTC</t>
+          <t>Mar 29, 2026 · 9:58 AM UTC</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-03-28T18:11:00Z</t>
+          <t>2026-03-29T09:58:00Z</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -618,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -629,43 +629,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2037936526093430909</t>
+          <t>2038193508092109170</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
+          <t>https://x.com/M17322417/status/2038193508092109170</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/M17322417</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>M17322417</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>M - #يارب_بلايستيشن5</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1288819440902078465/Twk32eXp_bigger.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>We regret to inform you that this process can be done only by a branch visit within the UAE.</t>
+          <t>قدمت اكثر من طلب استفسار للتمويل العقاري ومن نموذج الموقع وما وصلني اي اتصال او افادة</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>We regret to inform you that this process can be done only by a branch visit within the UAE.</t>
+          <t>قدمت اكثر من طلب استفسار للتمويل العقاري ومن نموذج الموقع وما وصلني اي اتصال او افادة</t>
         </is>
       </c>
       <c r="J3" t="b">
@@ -674,37 +674,37 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['cruizomfs']</t>
+          <t>['EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>9m</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 4:55 PM UTC</t>
+          <t>Mar 29, 2026 · 9:56 AM UTC</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-03-28T16:55:00Z</t>
+          <t>2026-03-29T09:56:00Z</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -715,82 +715,82 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2037928218003382573</t>
+          <t>2038172102902055221</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+          <t>https://x.com/a_m_alazizi/status/2038172102902055221</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/cruizomfs</t>
+          <t>https://x.com/a_m_alazizi</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>cruizomfs</t>
+          <t>a_m_alazizi</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Los 🥚 De Donald Trump 🇺🇸</t>
+          <t>عبدالرحمن مناور</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2030819740177063936/UWZXuDTH_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1745700634349764608/AVHo2vzs_bigger.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>I just got back from the UAE, is there any chance I can start the process online. I'll probably go again in august.</t>
+          <t>@EmiratesNBD_KSA ارجو الرد على الخاص</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>I just got back from the UAE, is there any chance I can start the process online. I&amp;#39;ll probably go again in august.</t>
+          <t>&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; ارجو الرد على الخاص</t>
         </is>
       </c>
       <c r="J4" t="b">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 4:22 PM UTC</t>
+          <t>Mar 29, 2026 · 8:31 AM UTC</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-03-28T16:22:00Z</t>
+          <t>2026-03-29T08:31:00Z</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_KSA']</t>
+        </is>
+      </c>
       <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>16</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -801,12 +801,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2037921044221010067</t>
+          <t>2038164256961540293</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037921044221010067</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2038164256961540293</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -831,6 +831,530 @@
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
+        <is>
+          <t>Avoid public Wi-Fi for banking. Data can be intercepted.
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+emiratesnbd.com/en/campaigns…</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Avoid public Wi-Fi for banking. Data can be intercepted.
+Stay Safe, Stay Vigilant. &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;
+&lt;a href="https://www.emiratesnbd.com/en/campaigns/united-against-fraud"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2h</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Mar 29, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-03-29T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud', 'https://www.emiratesnbd.com/en/campaigns/united-against-fraud']</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>268</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2038155820752339040</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2038155820752339040</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_KSA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>EmiratesNBD KSA</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>جمّع أميالك، من مشترياتك المحلية والدولية ✈️
+مع بطاقة رحالة الائتمانية من #بنك_الإمارات_دبي_الوطني 💙
+للتفاصيل:ms.spr.ly/6011QaU0Z</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>جمّع أميالك، من مشترياتك المحلية والدولية ✈️
+مع بطاقة رحالة الائتمانية من &lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_دبي_الوطني"&gt;#بنك_الإمارات_دبي_الوطني&lt;/a&gt; 💙
+للتفاصيل:&lt;a href="http://ms.spr.ly/6011QaU0Z"&gt;ms.spr.ly/6011QaU0Z&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2h</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Mar 29, 2026 · 7:26 AM UTC</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2026-03-29T07:26:00Z</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_دبي_الوطني', 'http://ms.spr.ly/6011QaU0Z']</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>355</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2038135700566970803</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2038135700566970803</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #990024 in the subject line.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #990024 in the subject line.</t>
+        </is>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>['Rita09729643']</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>3h</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Mar 29, 2026 · 6:06 AM UTC</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2026-03-29T06:06:00Z</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2037955706662604958</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://x.com/Rita09729643</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Rita09729643</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Rita</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1655465335775010816/KmAYkyBx_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Hi I have a credit card of Emirates NBD, but I haven’t used it for many years, suddenly I received the email of statement that I need to pay 764.13AED as the total payment due, this is really unacceptable.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Hi I have a credit card of Emirates NBD, but I haven’t used it for many years, suddenly I received the email of statement that I need to pay 764.13AED as the total payment due, this is really unacceptable.</t>
+        </is>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>15h</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:11 PM UTC</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2026-03-28T18:11:00Z</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>22</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2037936526093430909</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>We regret to inform you that this process can be done only by a branch visit within the UAE.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>We regret to inform you that this process can be done only by a branch visit within the UAE.</t>
+        </is>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>['cruizomfs']</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 4:55 PM UTC</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2026-03-28T16:55:00Z</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>30</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2037928218003382573</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://x.com/cruizomfs</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>cruizomfs</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Los 🥚 De Donald Trump 🇺🇸</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2030819740177063936/UWZXuDTH_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>I just got back from the UAE, is there any chance I can start the process online. I'll probably go again in august.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>I just got back from the UAE, is there any chance I can start the process online. I&amp;#39;ll probably go again in august.</t>
+        </is>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>17h</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 4:22 PM UTC</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2026-03-28T16:22:00Z</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>26</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2037921044221010067</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037921044221010067</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
         <is>
           <t>Hi, thank you for reaching out, please be informed that you can apply for non-resident account by a visit to one of our branches within the UAE.
 Documents:
@@ -851,7 +1375,7 @@
 (Bill should not be more than 3 months old)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Hi, thank you for reaching out, please be informed that you can apply for non-resident account by a visit to one of our branches within the UAE.
 Documents:
@@ -872,953 +1396,953 @@
 (Bill should not be more than 3 months old)</t>
         </is>
       </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>['cruizomfs']</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 3:53 PM UTC</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>2026-03-28T15:53:00Z</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="n">
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="n">
         <v>1</v>
       </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
-        <v>12</v>
-      </c>
-      <c r="V5" t="inlineStr">
+      <c r="U11" t="n">
+        <v>19</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2037911596106715381</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://x.com/cruizomfs/status/2037911596106715381</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>https://x.com/cruizomfs</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>cruizomfs</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Los 🥚 De Donald Trump 🇺🇸</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2030819740177063936/UWZXuDTH_bigger.jpg</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
         <is>
           <t>Hello. Do I need a residency in order to open an account?</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Hello. Do I need a residency in order to open an account?</t>
         </is>
       </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>14h</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>18h</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 3:16 PM UTC</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>2026-03-28T15:16:00Z</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="n">
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="n">
         <v>1</v>
       </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>6</v>
-      </c>
-      <c r="V6" t="inlineStr">
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>8</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>2037895388909142325</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037895388909142325</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
         <is>
           <t>Get guaranteed vouchers worth of AED750
 Apply for Emirates NBD noon One Visa Credit Card and receive a guaranteed Majid Al Futtaim voucher worth AED 750.
 emiratesnbd.com/en/campaigns…</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Get guaranteed vouchers worth of AED750
 Apply for Emirates NBD noon One Visa Credit Card and receive a guaranteed Majid Al Futtaim voucher worth AED 750.
 &lt;a href="https://www.emiratesnbd.com/en/campaigns/noon-one-credit-card"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>15h</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>19h</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 2:11 PM UTC</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>2026-03-28T14:11:00Z</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>['https://www.emiratesnbd.com/en/campaigns/noon-one-credit-card']</t>
         </is>
       </c>
-      <c r="R7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="R13" t="n">
+        <v>3</v>
+      </c>
+      <c r="S13" t="n">
         <v>1</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T13" t="n">
         <v>3</v>
       </c>
-      <c r="U7" t="n">
-        <v>672</v>
-      </c>
-      <c r="V7" t="inlineStr">
+      <c r="U13" t="n">
+        <v>766</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>2037873211728081164</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037873211728081164</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
         <is>
           <t>Please note that we don't have access to your profile from this channel due to security reasons, so kindly share the details through email, so we can check accordingly</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Please note that we don&amp;#39;t have access to your profile from this channel due to security reasons, so kindly share the details through email, so we can check accordingly</t>
         </is>
       </c>
-      <c r="J8" t="b">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>['rated_sm']</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 12:43 PM UTC</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>2026-03-28T12:43:00Z</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>12</v>
-      </c>
-      <c r="V8" t="inlineStr">
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>20</v>
+      </c>
+      <c r="V14" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>2037867679802122593</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>https://x.com/rated_sm/status/2037867679802122593</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>https://x.com/rated_sm</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>rated_sm</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>rated_sm</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1870693863452524544/xTAmP9KA_bigger.jpg</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
         <is>
           <t>I was hoping for a more immediate support and solution cause inability to make this payment will cause me to incur a large overlimit fee.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>I was hoping for a more immediate support and solution cause inability to make this payment will cause me to incur a large overlimit fee.</t>
         </is>
       </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 12:21 PM UTC</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>2026-03-28T12:21:00Z</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="n">
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="n">
         <v>1</v>
       </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>14</v>
-      </c>
-      <c r="V9" t="inlineStr">
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>23</v>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>2037866970410811411</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037866970410811411</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
         <is>
           <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at 
 social@emiratesnbd.com
 Quoting case #989891 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at 
 social@emiratesnbd.com
 Quoting case #989891 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
         </is>
       </c>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
         <is>
           <t>['rated_sm']</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 12:18 PM UTC</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>2026-03-28T12:18:00Z</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="n">
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>16</v>
-      </c>
-      <c r="V10" t="inlineStr">
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>21</v>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>2037865010320539854</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>https://x.com/rated_sm/status/2037865010320539854</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>https://x.com/rated_sm</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>rated_sm</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>rated_sm</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1870693863452524544/xTAmP9KA_bigger.jpg</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
         </is>
       </c>
-      <c r="J11" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>17h</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 12:10 PM UTC</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>2026-03-28T12:10:00Z</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>['https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="R11" t="n">
+      <c r="R17" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>20</v>
-      </c>
-      <c r="V11" t="inlineStr">
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>25</v>
+      </c>
+      <c r="V17" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>2037827252075839770</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_KSA/status/2037827252075839770</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_KSA</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>EmiratesNBD_KSA</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>EmiratesNBD KSA</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
         <is>
           <t>نعم يمكنك تقسيط المبلغ, لطلب التقسيط وتفاصيل أكثر قبل إجراء المعاملة يرجى الاتصال بنا على الرقم المجاني 8007547777</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>نعم يمكنك تقسيط المبلغ, لطلب التقسيط وتفاصيل أكثر قبل إجراء المعاملة يرجى الاتصال بنا على الرقم المجاني 8007547777</t>
         </is>
       </c>
-      <c r="J12" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
         <is>
           <t>['Talal_Hus']</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 9:40 AM UTC</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>2026-03-28T09:40:00Z</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>34</v>
-      </c>
-      <c r="V12" t="inlineStr">
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>46</v>
+      </c>
+      <c r="V18" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>2037818020597215557</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>https://x.com/Talal_Hus/status/2037818020597215557</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>https://x.com/Talal_Hus</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Talal_Hus</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>T.A</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1499888329797652480/UU2JVEEj_bigger.jpg</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA بالنسبة للتقسيط بدون هامش ربح هل لو سددت من خلال الفيزا ابل باي اقدر استفيد من العرض ؟ 
 يعني ععندب في نون اشتري ابل باي وبعدها اقسطها ؟</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; بالنسبة للتقسيط بدون هامش ربح هل لو سددت من خلال الفيزا ابل باي اقدر استفيد من العرض ؟ 
 يعني ععندب في نون اشتري ابل باي وبعدها اقسطها ؟</t>
         </is>
       </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>20h</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 9:04 AM UTC</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>2026-03-28T09:04:00Z</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>['https://x.com/EmiratesNBD_KSA']</t>
         </is>
       </c>
-      <c r="R13" t="n">
+      <c r="R19" t="n">
         <v>1</v>
       </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>23</v>
-      </c>
-      <c r="V13" t="inlineStr">
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>32</v>
+      </c>
+      <c r="V19" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>2037804608517509572</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>https://x.com/eazyislit/status/2037804608517509572</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>https://x.com/eazyislit</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>eazyislit</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Dat Dark Rich Dude 💎🇳🇬🇬🇧</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1920377756946169857/gG-ZA10q_bigger.jpg</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
         <is>
           <t>THE WOMAN DAT CARRIED YOU FOR 9 MONTHS MAY SHE LIVE LONG AND WITNESS YOU SUCCEED 🤍</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>THE WOMAN DAT CARRIED YOU FOR 9 MONTHS MAY SHE LIVE LONG AND WITNESS YOU SUCCEED 🤍</t>
         </is>
       </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 8:10 AM UTC</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>2026-03-28T08:10:00Z</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>9</v>
-      </c>
-      <c r="V14" t="inlineStr">
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>12</v>
+      </c>
+      <c r="V20" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>2037801868244533349</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
         <is>
           <t>What’s more suspicious?
 Stay Safe, Stay Vigilant. #UnitedAgainstFraud
 emiratesnbd.com/en/campaigns…</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>What’s more suspicious?
 Stay Safe, Stay Vigilant. &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;
 &lt;a href="https://www.emiratesnbd.com/en/campaigns/united-against-fraud"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J15" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 8:00 AM UTC</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>2026-03-28T08:00:00Z</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud', 'https://www.emiratesnbd.com/en/campaigns/united-against-fraud']</t>
         </is>
       </c>
-      <c r="R15" t="n">
+      <c r="R21" t="n">
         <v>2</v>
       </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
         <v>4</v>
       </c>
-      <c r="U15" t="n">
-        <v>517</v>
-      </c>
-      <c r="V15" t="inlineStr">
+      <c r="U21" t="n">
+        <v>567</v>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>2037799000171216897</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>https://x.com/argosaki/status/2037799000171216897</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>https://x.com/argosaki</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>argosaki</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>GP Q</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1346926049532080128/AZU6mAE-_bigger.jpg</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
         <is>
           <t>SOUNDS LIKE … QUANTUM 
 Emirates NBD enables instant trading account top-ups for UAE investors
@@ -1826,7 +2350,7 @@
 gulfnews.com/business/bankin…</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>SOUNDS LIKE … QUANTUM 
 Emirates NBD enables instant trading account top-ups for UAE investors
@@ -1834,341 +2358,341 @@
 &lt;a href="https://gulfnews.com/business/banking/emirates-nbd-enables-instant-trading-account-top-ups-for-uae-investors-1.500487960"&gt;gulfnews.com/business/bankin…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 7:48 AM UTC</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>2026-03-28T07:48:00Z</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>['https://gulfnews.com/business/banking/emirates-nbd-enables-instant-trading-account-top-ups-for-uae-investors-1.500487960']</t>
         </is>
       </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>1</v>
       </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>432</v>
-      </c>
-      <c r="V16" t="inlineStr">
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>437</v>
+      </c>
+      <c r="V22" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>2037796434725269639</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>https://x.com/ZaibKang/status/2037796434725269639</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>https://x.com/ZaibKang</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>ZaibKang</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Jahan Zaib Akbar Kang</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2028644994790436864/h-Avrj3s_bigger.jpg</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
         <is>
           <t>Thanks for your timely response.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Thanks for your timely response.</t>
         </is>
       </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 7:38 AM UTC</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>2026-03-28T07:38:00Z</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>17</v>
-      </c>
-      <c r="V17" t="inlineStr">
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>23</v>
+      </c>
+      <c r="V23" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>2037796009921900610</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>https://x.com/MazBalushi35285/status/2037796009921900610</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>https://x.com/MazBalushi35285</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>MazBalushi35285</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>مازن البلوشي</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2018589030322253824/-R_IX5Kh_bigger.jpg</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
         <is>
           <t>🥳مزيد من النواة الفн على مسابقة رابح صقر! راحت لكم الحفل العيد في الرياض! 🎉 فوق_النهاية فقط</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>🥳مزيد من النواة الفн على مسابقة رابح صقر! راحت لكم الحفل العيد في الرياض! 🎉 فوق_النهاية فقط</t>
         </is>
       </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
         <is>
           <t>['RotanaLive', 'Turki_alalshikh', 'RabehSaqer', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 7:36 AM UTC</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>2026-03-28T07:36:00Z</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>29</v>
-      </c>
-      <c r="V18" t="inlineStr">
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>33</v>
+      </c>
+      <c r="V24" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>2037792667782824069</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
         <is>
           <t>We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #989763 in the subject line.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #989763 in the subject line.</t>
         </is>
       </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
         <is>
           <t>['ZaibKang']</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 7:23 AM UTC</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>2026-03-28T07:23:00Z</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="n">
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="n">
         <v>1</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
         <v>1</v>
       </c>
-      <c r="U19" t="n">
-        <v>29</v>
-      </c>
-      <c r="V19" t="inlineStr">
+      <c r="U25" t="n">
+        <v>36</v>
+      </c>
+      <c r="V25" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>2037790087141101872</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037790087141101872</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>SelmaRomola</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Selma Romola</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1118152018995105792/5fyZOTth_bigger.jpg</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
         <is>
           <t>Fin well Financial well-being program with Emirates NBD 
 @Sabaashraff
@@ -2176,7 +2700,7 @@
 @Amanekhattab1</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Fin well Financial well-being program with Emirates NBD 
 &lt;a href="/Sabaashraff" title="Saba Ashraf"&gt;@Sabaashraff&lt;/a&gt;
@@ -2184,87 +2708,87 @@
 &lt;a href="/Amanekhattab1" title="Amanekhattab"&gt;@Amanekhattab1&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 7:13 AM UTC</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>2026-03-28T07:13:00Z</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
         <is>
           <t>['https://x.com/Sabaashraff', 'https://x.com/Sosomostafa729S', 'https://x.com/Amanekhattab1']</t>
         </is>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>10</v>
-      </c>
-      <c r="V20" t="inlineStr">
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>13</v>
+      </c>
+      <c r="V26" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>2037789707321622955</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037789707321622955</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>SelmaRomola</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Selma Romola</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1118152018995105792/5fyZOTth_bigger.jpg</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -2273,7 +2797,7 @@
 @Bushrasabih2</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -2282,87 +2806,87 @@
 &lt;a href="/Bushrasabih2" title="Bu_shaikh🌸❤️"&gt;@Bushrasabih2&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 7:11 AM UTC</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>2026-03-28T07:11:00Z</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
         <is>
           <t>['https://x.com/FazilAnas', 'https://x.com/Emy191990', 'https://x.com/Bushrasabih2']</t>
         </is>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>13</v>
-      </c>
-      <c r="V21" t="inlineStr">
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>15</v>
+      </c>
+      <c r="V27" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>2037789510478843981</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037789510478843981</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>SelmaRomola</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Selma Romola</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1118152018995105792/5fyZOTth_bigger.jpg</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -2371,7 +2895,7 @@
 @yasar8212</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -2380,87 +2904,87 @@
 &lt;a href="/yasar8212" title="shaniyadu"&gt;@yasar8212&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 7:10 AM UTC</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>2026-03-28T07:10:00Z</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
         <is>
           <t>['https://x.com/Sosomostafa729S', 'https://x.com/Nur_Munem', 'https://x.com/yasar8212']</t>
         </is>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>10</v>
-      </c>
-      <c r="V22" t="inlineStr">
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>13</v>
+      </c>
+      <c r="V28" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>2037788447910564341</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037788447910564341</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>SelmaRomola</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Selma Romola</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1118152018995105792/5fyZOTth_bigger.jpg</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -2469,7 +2993,7 @@
 @Sosomostafa729S</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -2478,638 +3002,100 @@
 &lt;a href="/Sosomostafa729S" title="Soha.mostafa77"&gt;@Sosomostafa729S&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J23" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>22h</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 7:06 AM UTC</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>2026-03-28T07:06:00Z</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
         <is>
           <t>['https://x.com/Bushrasabih2', 'https://x.com/AmalBeevi', 'https://x.com/Sosomostafa729S']</t>
         </is>
       </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>12</v>
-      </c>
-      <c r="V23" t="inlineStr">
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>14</v>
+      </c>
+      <c r="V29" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>2037785874474430532</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>https://x.com/ZaibKang/status/2037785874474430532</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>https://x.com/ZaibKang</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>ZaibKang</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Jahan Zaib Akbar Kang</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2028644994790436864/h-Avrj3s_bigger.jpg</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
         <is>
           <t>I applied for liv X account Still not received any response 
 Reference number 
 2026038379331830</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>I applied for liv X account Still not received any response 
 Reference number 
 2026038379331830</t>
         </is>
       </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Mar 28, 2026 · 6:56 AM UTC</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>2026-03-28T06:56:00Z</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>35</v>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2037785071189671937</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>https://x.com/ZaibKang</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>ZaibKang</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Jahan Zaib Akbar Kang</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2028644994790436864/h-Avrj3s_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible</t>
-        </is>
-      </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Mar 28, 2026 · 6:53 AM UTC</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>2026-03-28T06:53:00Z</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="n">
-        <v>16</v>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2037784853866029145</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784853866029145</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Soha.mostafa77</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>B- 1.89% @zeynp_qas @Salma2232019 @semeet 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>B- 1.89% &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>Mar 28, 2026 · 6:52 AM UTC</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>2026-03-28T06:52:00Z</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>['https://x.com/zeynp_qas', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
-        </is>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>5</v>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2037784763122217375</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784763122217375</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Soha.mostafa77</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>B- 1.89% &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="J27" t="b">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Mar 28, 2026 · 6:52 AM UTC</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>2026-03-28T06:52:00Z</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>['https://x.com/semeet', 'https://x.com/Salma2232019', 'https://x.com/SelmaRomola']</t>
-        </is>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>10</v>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2037784668028985459</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Soha.mostafa77</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>B- 1.89% @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>B- 1.89% &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="J28" t="b">
-        <v>0</v>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Mar 28, 2026 · 6:51 AM UTC</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>2026-03-28T06:51:00Z</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
-        </is>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>8</v>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2037784498885243377</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784498885243377</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Soha.mostafa77</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Exchanger volunteer program 
-@semeet @Emy191990 @ibushra_03 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Exchanger volunteer program 
-&lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="J29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Mar 28, 2026 · 6:50 AM UTC</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>2026-03-28T06:50:00Z</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>['https://x.com/semeet', 'https://x.com/Emy191990', 'https://x.com/ibushra_03']</t>
-        </is>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>8</v>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2037784405700419683</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Soha.mostafa77</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; 🌿🇦🇪❤️</t>
-        </is>
-      </c>
       <c r="J30" t="b">
         <v>0</v>
       </c>
@@ -3121,27 +3107,23 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>Mar 28</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 6:50 AM UTC</t>
+          <t>Mar 28, 2026 · 6:56 AM UTC</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-03-28T06:50:00Z</t>
+          <t>2026-03-28T06:56:00Z</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>['https://x.com/semeet', 'https://x.com/zeynp_qas', 'https://x.com/SelmaRomola']</t>
-        </is>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -3150,7 +3132,7 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -3161,628 +3143,628 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2037784344333275440</t>
+          <t>2037785071189671937</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
+          <t>https://x.com/ZaibKang/status/2037785071189671937</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/ZaibKang</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>ZaibKang</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Jahan Zaib Akbar Kang</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2028644994790436864/h-Avrj3s_bigger.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible</t>
+        </is>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:53 AM UTC</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:53:00Z</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>17</v>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2037784853866029145</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784853866029145</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>B- 1.89% @zeynp_qas @Salma2232019 @semeet 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>B- 1.89% &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:52 AM UTC</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:52:00Z</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>['https://x.com/zeynp_qas', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
+        </is>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>7</v>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2037784763122217375</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784763122217375</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>B- 1.89% &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:52 AM UTC</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:52:00Z</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>['https://x.com/semeet', 'https://x.com/Salma2232019', 'https://x.com/SelmaRomola']</t>
+        </is>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>13</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2037784668028985459</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>B- 1.89% @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>B- 1.89% &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:51 AM UTC</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:51:00Z</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
+        </is>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>12</v>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2037784498885243377</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784498885243377</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program 
+@semeet @Emy191990 @ibushra_03 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program 
+&lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:50 AM UTC</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:50:00Z</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>['https://x.com/semeet', 'https://x.com/Emy191990', 'https://x.com/ibushra_03']</t>
+        </is>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>11</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2037784405700419683</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J36" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:50 AM UTC</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:50:00Z</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>['https://x.com/semeet', 'https://x.com/zeynp_qas', 'https://x.com/SelmaRomola']</t>
+        </is>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>10</v>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2037784344333275440</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
         <is>
           <t>Before clicking a link, what do you do?
 Stay Safe, Stay Vigilant. #UnitedAgainstFraud
 emiratesnbd.com/en/campaigns…</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>Before clicking a link, what do you do?
 Stay Safe, Stay Vigilant. &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;
 &lt;a href="https://www.emiratesnbd.com/en/campaigns/united-against-fraud"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J31" t="b">
-        <v>0</v>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
+      <c r="J37" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 6:50 AM UTC</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>2026-03-28T06:50:00Z</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud', 'https://www.emiratesnbd.com/en/campaigns/united-against-fraud']</t>
-        </is>
-      </c>
-      <c r="R31" t="n">
-        <v>3</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3</v>
-      </c>
-      <c r="U31" t="n">
-        <v>535</v>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2037784337337532619</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784337337532619</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Soha.mostafa77</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="J32" t="b">
-        <v>0</v>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Mar 28, 2026 · 6:50 AM UTC</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>2026-03-28T06:50:00Z</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
-        </is>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>9</v>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2037784225022365938</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Soha.mostafa77</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Exchanger volunteer program @semeet @parulghalout @Salma2232019 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="J33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Mar 28, 2026 · 6:49 AM UTC</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>2026-03-28T06:49:00Z</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>['https://x.com/semeet', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
-        </is>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>7</v>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2037784141006344295</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784141006344295</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Soha.mostafa77</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Exchanger volunteer program @semeet @Salma2232019 @ibushra_03 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="J34" t="b">
-        <v>0</v>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Mar 28, 2026 · 6:49 AM UTC</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>2026-03-28T06:49:00Z</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>['https://x.com/semeet', 'https://x.com/Salma2232019', 'https://x.com/ibushra_03']</t>
-        </is>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>7</v>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2037784038774317555</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Soha.mostafa77</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Exchanger volunteer program 
-@Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Exchanger volunteer program 
-&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="J35" t="b">
-        <v>0</v>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Mar 28, 2026 · 6:49 AM UTC</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>2026-03-28T06:49:00Z</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
-        </is>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>8</v>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2037783859769876728</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783859769876728</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Soha.mostafa77</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>FINWELL ( Financial Well-being program) with Emirates NBD @semeet @zeynp_qas @Emy191990 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>FINWELL ( Financial Well-being program) with Emirates NBD &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="J36" t="b">
-        <v>0</v>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Mar 28, 2026 · 6:48 AM UTC</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>2026-03-28T06:48:00Z</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>['https://x.com/semeet', 'https://x.com/zeynp_qas', 'https://x.com/Emy191990']</t>
-        </is>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>7</v>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2037783775896313876</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783775896313876</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Soha.mostafa77</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>FINWELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Emy191990 @parulghalout 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>FINWELL ( Financial Well-being program) with Emirates NBD &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="J37" t="b">
-        <v>0</v>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>23h</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Mar 28, 2026 · 6:48 AM UTC</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>2026-03-28T06:48:00Z</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>['https://x.com/SelmaRomola', 'https://x.com/Emy191990', 'https://x.com/parulghalout']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud', 'https://www.emiratesnbd.com/en/campaigns/united-against-fraud']</t>
         </is>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U37" t="n">
-        <v>10</v>
+        <v>565</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -3793,12 +3775,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2037783673144230370</t>
+          <t>2037784337337532619</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783673144230370</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784337337532619</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3824,14 +3806,12 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>FINWELL ( Financial Well-being program) with Emirates NBD 
-@Emy191990 @ibushra_03 @SelmaRomola 🌿🇦🇪❤️</t>
+          <t>Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>FINWELL ( Financial Well-being program) with Emirates NBD 
-&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J38" t="b">
@@ -3845,23 +3825,23 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>Mar 28</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 6:47 AM UTC</t>
+          <t>Mar 28, 2026 · 6:50 AM UTC</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-03-28T06:47:00Z</t>
+          <t>2026-03-28T06:50:00Z</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/SelmaRomola']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
         </is>
       </c>
       <c r="R38" t="n">
@@ -3874,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -3885,12 +3865,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2037783477979091314</t>
+          <t>2037784225022365938</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783477979091314</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3916,12 +3896,12 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App @parulghalout @semeet @Emy191990 🌿🇦🇪❤️</t>
+          <t>Exchanger volunteer program @semeet @parulghalout @Salma2232019 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J39" t="b">
@@ -3935,23 +3915,23 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>Mar 28</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 6:46 AM UTC</t>
+          <t>Mar 28, 2026 · 6:49 AM UTC</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-03-28T06:46:00Z</t>
+          <t>2026-03-28T06:49:00Z</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>['https://x.com/parulghalout', 'https://x.com/semeet', 'https://x.com/Emy191990']</t>
+          <t>['https://x.com/semeet', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
       <c r="R39" t="n">
@@ -3964,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -3975,12 +3955,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2037783402758508685</t>
+          <t>2037784141006344295</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784141006344295</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4006,12 +3986,12 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
+          <t>Exchanger volunteer program @semeet @Salma2232019 @ibushra_03 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J40" t="b">
@@ -4025,23 +4005,23 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>Mar 28</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 6:46 AM UTC</t>
+          <t>Mar 28, 2026 · 6:49 AM UTC</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-03-28T06:46:00Z</t>
+          <t>2026-03-28T06:49:00Z</t>
         </is>
       </c>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>['https://x.com/zeynp_qas', 'https://x.com/SelmaRomola', 'https://x.com/Salma2232019']</t>
+          <t>['https://x.com/semeet', 'https://x.com/Salma2232019', 'https://x.com/ibushra_03']</t>
         </is>
       </c>
       <c r="R40" t="n">
@@ -4054,7 +4034,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -4065,12 +4045,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2037783335389540775</t>
+          <t>2037784038774317555</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783335389540775</t>
+          <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4096,12 +4076,14 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App @Emy191990 @parulghalout @ibushra_03 🌿🇦🇪❤️</t>
+          <t>Exchanger volunteer program 
+@Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>Exchanger volunteer program 
+&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J41" t="b">
@@ -4115,23 +4097,23 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>Mar 28</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 6:46 AM UTC</t>
+          <t>Mar 28, 2026 · 6:49 AM UTC</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-03-28T06:46:00Z</t>
+          <t>2026-03-28T06:49:00Z</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/ibushra_03']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
         </is>
       </c>
       <c r="R41" t="n">
@@ -4144,7 +4126,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -4155,12 +4137,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2037783125854679453</t>
+          <t>2037783859769876728</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783859769876728</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4186,12 +4168,12 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
+          <t>FINWELL ( Financial Well-being program) with Emirates NBD @semeet @zeynp_qas @Emy191990 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>FINWELL ( Financial Well-being program) with Emirates NBD &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J42" t="b">
@@ -4205,23 +4187,23 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>Mar 28</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 6:45 AM UTC</t>
+          <t>Mar 28, 2026 · 6:48 AM UTC</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-03-28T06:45:00Z</t>
+          <t>2026-03-28T06:48:00Z</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>['https://x.com/parulghalout', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
+          <t>['https://x.com/semeet', 'https://x.com/zeynp_qas', 'https://x.com/Emy191990']</t>
         </is>
       </c>
       <c r="R42" t="n">
@@ -4234,7 +4216,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -4245,12 +4227,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2037783049065390446</t>
+          <t>2037783775896313876</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783775896313876</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4276,14 +4258,12 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking's App 
-@Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
+          <t>FINWELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Emy191990 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Through ENBD X Mobile Banking&amp;#39;s App 
-&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; 🌿🇦🇪❤️</t>
+          <t>FINWELL ( Financial Well-being program) with Emirates NBD &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J43" t="b">
@@ -4297,23 +4277,23 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>Mar 28</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 6:45 AM UTC</t>
+          <t>Mar 28, 2026 · 6:48 AM UTC</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-03-28T06:45:00Z</t>
+          <t>2026-03-28T06:48:00Z</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/semeet']</t>
+          <t>['https://x.com/SelmaRomola', 'https://x.com/Emy191990', 'https://x.com/parulghalout']</t>
         </is>
       </c>
       <c r="R43" t="n">
@@ -4326,7 +4306,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -4337,43 +4317,45 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2037730056920088898</t>
+          <t>2037783673144230370</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://x.com/wil3020/status/2037730056920088898</t>
+          <t>https://x.com/Sosomostafa729S/status/2037783673144230370</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://x.com/wil3020</t>
+          <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>wil3020</t>
+          <t>Sosomostafa729S</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>wiil</t>
+          <t>Soha.mostafa77</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1939900695018106882/lxZGZx9Y_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
+          <t>FINWELL ( Financial Well-being program) with Emirates NBD 
+@Emy191990 @ibushra_03 @SelmaRomola 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
+          <t>FINWELL ( Financial Well-being program) with Emirates NBD 
+&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
       <c r="J44" t="b">
@@ -4392,29 +4374,571 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
+          <t>Mar 28, 2026 · 6:47 AM UTC</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:47:00Z</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/SelmaRomola']</t>
+        </is>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>12</v>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2037783477979091314</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783477979091314</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking's App @parulghalout @semeet @Emy191990 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J45" t="b">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:46 AM UTC</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:46:00Z</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>['https://x.com/parulghalout', 'https://x.com/semeet', 'https://x.com/Emy191990']</t>
+        </is>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>10</v>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2037783402758508685</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J46" t="b">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:46 AM UTC</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:46:00Z</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>['https://x.com/zeynp_qas', 'https://x.com/SelmaRomola', 'https://x.com/Salma2232019']</t>
+        </is>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>14</v>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2037783335389540775</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783335389540775</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking's App @Emy191990 @parulghalout @ibushra_03 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J47" t="b">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:46 AM UTC</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:46:00Z</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/ibushra_03']</t>
+        </is>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>10</v>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2037783125854679453</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J48" t="b">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:45 AM UTC</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:45:00Z</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>['https://x.com/parulghalout', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
+        </is>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>11</v>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2037783049065390446</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking's App 
+@Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App 
+&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J49" t="b">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:45 AM UTC</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:45:00Z</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/semeet']</t>
+        </is>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>9</v>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2037730056920088898</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>https://x.com/wil3020/status/2037730056920088898</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://x.com/wil3020</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>wil3020</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>wiil</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1939900695018106882/lxZGZx9Y_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
+        </is>
+      </c>
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
           <t>Mar 28, 2026 · 3:14 AM UTC</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>2026-03-28T03:14:00Z</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>36</v>
-      </c>
-      <c r="V44" t="inlineStr">
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>39</v>
+      </c>
+      <c r="V50" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>

--- a/EI_ENBD_3post.xlsx
+++ b/EI_ENBD_3post.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V50"/>
+  <dimension ref="A1:V67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,71 +543,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2038194022280282249</t>
+          <t>2038262791908250109</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2038194022280282249</t>
+          <t>https://x.com/EmiratesNBD_EGY/status/2038262791908250109</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA</t>
+          <t>https://x.com/EmiratesNBD_EGY</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA</t>
+          <t>EmiratesNBD_EGY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>EmiratesNBD KSA</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>شكراً لتواصلك معنا وإظهار اهتمامك بمنتجنا. يرجى مشاركتنا برقم هاتفك الجوال المسجل ومكان السكن في المملكة العربية السعودية حتى نتمكن من ترتيب اتصال معك من قبل فريقنا. مع التحية</t>
+          <t>فيديو تعريفي عن «منحة علماء المستقبل»، التي أطلقها البنك المركزي المصري ووزارة التعليم العالي والبحث العلمي يتضمن (وصف المنحة ومزاياها، الفئات المستفيدة، شروط الحصول عليها، طريقة التبرع).
+التبرع متاح عبر حساب 7070 في جميع البنوك المصرية أو من خلال تطبيق إنستاباي تحت مسمى " منحة علماء المستقبل 7070".
+اصنع مستقبل.. اصنع فرقًا يدوم.
+#منحة_علماء_المستقبل #البنك_المركزي_المصري #وزارة_التعليم_العالي #دعم_المتفوقين #المسؤولية_المجتمعية  #العلم_أساس_التنمية</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>شكراً لتواصلك معنا وإظهار اهتمامك بمنتجنا. يرجى مشاركتنا برقم هاتفك الجوال المسجل ومكان السكن في المملكة العربية السعودية حتى نتمكن من ترتيب اتصال معك من قبل فريقنا. مع التحية</t>
+          <t>فيديو تعريفي عن «منحة علماء المستقبل»، التي أطلقها البنك المركزي المصري ووزارة التعليم العالي والبحث العلمي يتضمن (وصف المنحة ومزاياها، الفئات المستفيدة، شروط الحصول عليها، طريقة التبرع).
+التبرع متاح عبر حساب 7070 في جميع البنوك المصرية أو من خلال تطبيق إنستاباي تحت مسمى &amp;#34; منحة علماء المستقبل 7070&amp;#34;.
+اصنع مستقبل.. اصنع فرقًا يدوم.
+&lt;a href="/search?f=tweets&amp;amp;q=%23منحة_علماء_المستقبل"&gt;#منحة_علماء_المستقبل&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23البنك_المركزي_المصري"&gt;#البنك_المركزي_المصري&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23وزارة_التعليم_العالي"&gt;#وزارة_التعليم_العالي&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23دعم_المتفوقين"&gt;#دعم_المتفوقين&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23المسؤولية_المجتمعية"&gt;#المسؤولية_المجتمعية&lt;/a&gt;  &lt;a href="/search?f=tweets&amp;amp;q=%23العلم_أساس_التنمية"&gt;#العلم_أساس_التنمية&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J2" t="b">
         <v>0</v>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>['M17322417']</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>7m</t>
+          <t>49m</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Mar 29, 2026 · 9:58 AM UTC</t>
+          <t>Mar 29, 2026 · 2:31 PM UTC</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-03-29T09:58:00Z</t>
+          <t>2026-03-29T14:31:00Z</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23منحة_علماء_المستقبل', 'https://x.com/search?f=tweets&amp;q=%23البنك_المركزي_المصري', 'https://x.com/search?f=tweets&amp;q=%23وزارة_التعليم_العالي', 'https://x.com/search?f=tweets&amp;q=%23دعم_المتفوقين', 'https://x.com/search?f=tweets&amp;q=%23المسؤولية_المجتمعية', 'https://x.com/search?f=tweets&amp;q=%23العلم_أساس_التنمية']</t>
+        </is>
+      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -618,7 +624,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -629,43 +635,51 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2038193508092109170</t>
+          <t>2038242857610260545</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://x.com/M17322417/status/2038193508092109170</t>
+          <t>https://x.com/Salma2232019/status/2038242857610260545</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/M17322417</t>
+          <t>https://x.com/Salma2232019</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>M17322417</t>
+          <t>Salma2232019</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>M - #يارب_بلايستيشن5</t>
+          <t>Salma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1288819440902078465/Twk32eXp_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2005729084433629184/I5VH__16_bigger.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>قدمت اكثر من طلب استفسار للتمويل العقاري ومن نموذج الموقع وما وصلني اي اتصال او افادة</t>
+          <t>Finewell
+(Financial Well-being program ) with Emirates NBD .
+@zeynp_qas 
+@Sosomostafa729S 
+@Emy191990</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>قدمت اكثر من طلب استفسار للتمويل العقاري ومن نموذج الموقع وما وصلني اي اتصال او افادة</t>
+          <t>Finewell
+(Financial Well-being program ) with Emirates NBD .
+&lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; 
+&lt;a href="/Sosomostafa729S" title="Soha.mostafa77"&gt;@Sosomostafa729S&lt;/a&gt; 
+&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J3" t="b">
@@ -674,37 +688,41 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_KSA']</t>
+          <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>9m</t>
+          <t>2h</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Mar 29, 2026 · 9:56 AM UTC</t>
+          <t>Mar 29, 2026 · 1:12 PM UTC</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-03-29T09:56:00Z</t>
+          <t>2026-03-29T13:12:00Z</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>['https://x.com/zeynp_qas', 'https://x.com/Sosomostafa729S', 'https://x.com/Emy191990']</t>
+        </is>
+      </c>
       <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
         <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>4</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -715,69 +733,79 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2038172102902055221</t>
+          <t>2038241936247549971</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://x.com/a_m_alazizi/status/2038172102902055221</t>
+          <t>https://x.com/Salma2232019/status/2038241936247549971</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/a_m_alazizi</t>
+          <t>https://x.com/Salma2232019</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>a_m_alazizi</t>
+          <t>Salma2232019</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>عبدالرحمن مناور</t>
+          <t>Salma</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1745700634349764608/AVHo2vzs_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2005729084433629184/I5VH__16_bigger.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA ارجو الرد على الخاص</t>
+          <t>Via the ENBD X Mobile App
+@Emy191990 
+@Sosomostafa729S 
+@zeynp_qas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; ارجو الرد على الخاص</t>
+          <t>Via the ENBD X Mobile App
+&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; 
+&lt;a href="/Sosomostafa729S" title="Soha.mostafa77"&gt;@Sosomostafa729S&lt;/a&gt; 
+&lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J4" t="b">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1h</t>
+          <t>2h</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Mar 29, 2026 · 8:31 AM UTC</t>
+          <t>Mar 29, 2026 · 1:08 PM UTC</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-03-29T08:31:00Z</t>
+          <t>2026-03-29T13:08:00Z</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>['https://x.com/EmiratesNBD_KSA']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/Sosomostafa729S', 'https://x.com/zeynp_qas']</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -790,7 +818,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -801,54 +829,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2038164256961540293</t>
+          <t>2038241868757033339</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2038164256961540293</t>
+          <t>https://x.com/Salma2232019/status/2038241868757033339</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/Salma2232019</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>Salma2232019</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Salma</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2005729084433629184/I5VH__16_bigger.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avoid public Wi-Fi for banking. Data can be intercepted.
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-emiratesnbd.com/en/campaigns…</t>
+          <t>Via the ENBD X Mobile App
+@Emy191990 
+@Sosomostafa729S 
+@zeynp_qas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Avoid public Wi-Fi for banking. Data can be intercepted.
-Stay Safe, Stay Vigilant. &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;
-&lt;a href="https://www.emiratesnbd.com/en/campaigns/united-against-fraud"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
+          <t>Via the ENBD X Mobile App
+&lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; 
+&lt;a href="/Sosomostafa729S" title="Soha.mostafa77"&gt;@Sosomostafa729S&lt;/a&gt; 
+&lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J5" t="b">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>2h</t>
@@ -856,31 +890,31 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Mar 29, 2026 · 8:00 AM UTC</t>
+          <t>Mar 29, 2026 · 1:08 PM UTC</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-03-29T08:00:00Z</t>
+          <t>2026-03-29T13:08:00Z</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud', 'https://www.emiratesnbd.com/en/campaigns/united-against-fraud']</t>
+          <t>['https://x.com/Emy191990', 'https://x.com/Sosomostafa729S', 'https://x.com/zeynp_qas']</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>268</v>
+        <v>0</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -891,54 +925,54 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2038155820752339040</t>
+          <t>2038234797839941987</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2038155820752339040</t>
+          <t>https://x.com/Lura____3/status/2038234797839941987</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA</t>
+          <t>https://x.com/Lura____3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA</t>
+          <t>Lura____3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>EmiratesNBD KSA</t>
+          <t>RERE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1880007160555294720/mqO0utK5_bigger.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>جمّع أميالك، من مشترياتك المحلية والدولية ✈️
-مع بطاقة رحالة الائتمانية من #بنك_الإمارات_دبي_الوطني 💙
-للتفاصيل:ms.spr.ly/6011QaU0Z</t>
+          <t>ما اقدر ارسل لكم</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>جمّع أميالك، من مشترياتك المحلية والدولية ✈️
-مع بطاقة رحالة الائتمانية من &lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_دبي_الوطني"&gt;#بنك_الإمارات_دبي_الوطني&lt;/a&gt; 💙
-للتفاصيل:&lt;a href="http://ms.spr.ly/6011QaU0Z"&gt;ms.spr.ly/6011QaU0Z&lt;/a&gt;</t>
+          <t>ما اقدر ارسل لكم</t>
         </is>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>2h</t>
@@ -946,22 +980,18 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Mar 29, 2026 · 7:26 AM UTC</t>
+          <t>Mar 29, 2026 · 12:40 PM UTC</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-03-29T07:26:00Z</t>
+          <t>2026-03-29T12:40:00Z</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_دبي_الوطني', 'http://ms.spr.ly/6011QaU0Z']</t>
-        </is>
-      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -970,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>355</v>
+        <v>2</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -981,12 +1011,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2038135700566970803</t>
+          <t>2038232771412308481</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2038135700566970803</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2038232771412308481</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1012,12 +1042,12 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #990024 in the subject line.</t>
+          <t>نأسف بشدة للتأخير، يُرجى تزويدنا برقم هاتفك المسجل عبر رسالة خاصة حتى نتمكن من ترتيب معاودة الاتصال بك من قِبل فريقنا. شكرًا.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #990024 in the subject line.</t>
+          <t>نأسف بشدة للتأخير، يُرجى تزويدنا برقم هاتفك المسجل عبر رسالة خاصة حتى نتمكن من ترتيب معاودة الاتصال بك من قِبل فريقنا. شكرًا.</t>
         </is>
       </c>
       <c r="J7" t="b">
@@ -1026,28 +1056,28 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>['Rita09729643']</t>
+          <t>['Lura____3']</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>3h</t>
+          <t>2h</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Mar 29, 2026 · 6:06 AM UTC</t>
+          <t>Mar 29, 2026 · 12:32 PM UTC</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-03-29T06:06:00Z</t>
+          <t>2026-03-29T12:32:00Z</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1056,7 +1086,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1067,43 +1097,43 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2037955706662604958</t>
+          <t>2038232336085426354</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
+          <t>https://x.com/Lura____3/status/2038232336085426354</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/Rita09729643</t>
+          <t>https://x.com/Lura____3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Rita09729643</t>
+          <t>Lura____3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Rita</t>
+          <t>RERE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1655465335775010816/KmAYkyBx_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1880007160555294720/mqO0utK5_bigger.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hi I have a credit card of Emirates NBD, but I haven’t used it for many years, suddenly I received the email of statement that I need to pay 764.13AED as the total payment due, this is really unacceptable.</t>
+          <t>سبق وتم تعببأته ماتلقيت اتصال</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Hi I have a credit card of Emirates NBD, but I haven’t used it for many years, suddenly I received the email of statement that I need to pay 764.13AED as the total payment due, this is really unacceptable.</t>
+          <t>سبق وتم تعببأته ماتلقيت اتصال</t>
         </is>
       </c>
       <c r="J8" t="b">
@@ -1117,23 +1147,23 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>2h</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 6:11 PM UTC</t>
+          <t>Mar 29, 2026 · 12:30 PM UTC</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-03-28T18:11:00Z</t>
+          <t>2026-03-29T12:30:00Z</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -1142,7 +1172,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1153,12 +1183,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2037936526093430909</t>
+          <t>2038232165763182691</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2038232165763182691</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1184,12 +1214,14 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>We regret to inform you that this process can be done only by a branch visit within the UAE.</t>
+          <t>نشكركم على اهتمامكم بمنتجاتنا، يرجى زيارة الرابط أدناه وتعبئة بياناتكم، وسيتواصل معكم فريق المبيعات لدينا خلال يومي عمل. الحد الأدنى للراتب المطلوب هو 5000 درهم إماراتي. شكرًا - زبير
+beta.emiratesnbd.com/en/Camp…</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>We regret to inform you that this process can be done only by a branch visit within the UAE.</t>
+          <t>نشكركم على اهتمامكم بمنتجاتنا، يرجى زيارة الرابط أدناه وتعبئة بياناتكم، وسيتواصل معكم فريق المبيعات لدينا خلال يومي عمل. الحد الأدنى للراتب المطلوب هو 5000 درهم إماراتي. شكرًا - زبير
+&lt;a href="https://beta.emiratesnbd.com/en/Campaigns/social-media-apply?SOURCE=&amp;amp;REF&amp;amp;ref=legacy&amp;amp;legacy_redirect=true"&gt;beta.emiratesnbd.com/en/Camp…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J9" t="b">
@@ -1198,37 +1230,41 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>['cruizomfs']</t>
+          <t>['Lura____3']</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>2h</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 4:55 PM UTC</t>
+          <t>Mar 29, 2026 · 12:29 PM UTC</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-03-28T16:55:00Z</t>
+          <t>2026-03-29T12:29:00Z</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>['https://beta.emiratesnbd.com/en/Campaigns/social-media-apply?SOURCE=&amp;REF&amp;ref=legacy&amp;legacy_redirect=true']</t>
+        </is>
+      </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1239,43 +1275,43 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2037928218003382573</t>
+          <t>2038231563272351811</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+          <t>https://x.com/Lura____3/status/2038231563272351811</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/cruizomfs</t>
+          <t>https://x.com/Lura____3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>cruizomfs</t>
+          <t>Lura____3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Los 🥚 De Donald Trump 🇺🇸</t>
+          <t>RERE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2030819740177063936/UWZXuDTH_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1880007160555294720/mqO0utK5_bigger.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>I just got back from the UAE, is there any chance I can start the process online. I'll probably go again in august.</t>
+          <t>ابي اقدم طلب تمويل شخصي كيف تساعدوني محد يرد</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>I just got back from the UAE, is there any chance I can start the process online. I&amp;#39;ll probably go again in august.</t>
+          <t>ابي اقدم طلب تمويل شخصي كيف تساعدوني محد يرد</t>
         </is>
       </c>
       <c r="J10" t="b">
@@ -1289,17 +1325,17 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>17h</t>
+          <t>2h</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Mar 28, 2026 · 4:22 PM UTC</t>
+          <t>Mar 29, 2026 · 12:27 PM UTC</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-03-28T16:22:00Z</t>
+          <t>2026-03-29T12:27:00Z</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1325,36 +1361,1514 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2037921044221010067</t>
+          <t>2038225382005146043</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2037921044221010067</t>
+          <t>https://x.com/zola_app/status/2038225382005146043</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/zola_app</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>zola_app</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Zola</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2026579810441678848/Bq-izqc4_bigger.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
+        <is>
+          <t>[5/8]
+Bank accounts are free to open at most banks.
+The catch: minimum deposits of AED 5,000-50,000 depending on the bank.
+Wio, Mashreq Neo, RAKBANK are friendlier to new free zone companies. Tier 1 banks like Emirates NBD want to see revenue first.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>[5/8]
+Bank accounts are free to open at most banks.
+The catch: minimum deposits of AED 5,000-50,000 depending on the bank.
+Wio, Mashreq Neo, RAKBANK are friendlier to new free zone companies. Tier 1 banks like Emirates NBD want to see revenue first.</t>
+        </is>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>3h</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Mar 29, 2026 · 12:02 PM UTC</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2026-03-29T12:02:00Z</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>10</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2038222517400392098</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://x.com/DigitalMedia_LM/status/2038222517400392098</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://x.com/DigitalMedia_LM</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>DigitalMedia_LM</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Laura McDonald</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1500138803381501952/VQ6j3ezr_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>🤔🤓</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>🤔🤓</t>
+        </is>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>3h</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Mar 29, 2026 · 11:51 AM UTC</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2026-03-29T11:51:00Z</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>13</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2038220563748098517</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://x.com/marcelraj/status/2038220563748098517</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://x.com/marcelraj</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>marcelraj</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Marcel Raj</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/980770440766517248/keE9mwcw_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Exchanger volunteering program 
+@parulghalout
+@Fr638
+@Fayaz01150103</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Exchanger volunteering program 
+&lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt;
+&lt;a href="/Fr638" title="Faris _m"&gt;@Fr638&lt;/a&gt;
+&lt;a href="/Fayaz01150103" title="Fayaz"&gt;@Fayaz01150103&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>3h</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Mar 29, 2026 · 11:43 AM UTC</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2026-03-29T11:43:00Z</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>['https://x.com/parulghalout', 'https://x.com/Fr638', 'https://x.com/Fayaz01150103']</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2038211361335824398</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2038211361335824398</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_KSA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>EmiratesNBD KSA</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>مرحباً, يرجى الاتصال بخدمة العملاء لدينا على الرقم  المجاني 8007547777 و من خارج المملكة على 009660112122333 وسيتمكن أحد موظفينا من مساعدتك بهذا الأمر.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>مرحباً, يرجى الاتصال بخدمة العملاء لدينا على الرقم  المجاني 8007547777 و من خارج المملكة على 009660112122333 وسيتمكن أحد موظفينا من مساعدتك بهذا الأمر.</t>
+        </is>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>['a_m_alazizi']</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Mar 29, 2026 · 11:07 AM UTC</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2026-03-29T11:07:00Z</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>17</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2038208875543884093</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://x.com/a_m_alazizi/status/2038208875543884093</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://x.com/a_m_alazizi</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>a_m_alazizi</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>عبدالرحمن مناور</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1745700634349764608/AVHo2vzs_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA ليش ماتردون على الخاص</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; ليش ماتردون على الخاص</t>
+        </is>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Mar 29, 2026 · 10:57 AM UTC</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2026-03-29T10:57:00Z</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>11</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2038208835433681181</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://x.com/a_m_alazizi/status/2038208835433681181</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://x.com/a_m_alazizi</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>a_m_alazizi</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>عبدالرحمن مناور</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1745700634349764608/AVHo2vzs_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ليش ماتردون على الخاص</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ليش ماتردون على الخاص</t>
+        </is>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Mar 29, 2026 · 10:57 AM UTC</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2026-03-29T10:57:00Z</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2038199951327457478</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2038199951327457478</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Hi Harsh, thanks for reaching us, please write us in details about your concern via direct message, and we will review and help you out accordingly. Thanks- Zubair</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Hi Harsh, thanks for reaching us, please write us in details about your concern via direct message, and we will review and help you out accordingly. Thanks- Zubair</t>
+        </is>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>['theHT4']</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>4h</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Mar 29, 2026 · 10:21 AM UTC</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2026-03-29T10:21:00Z</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>27</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2038199225138442421</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://x.com/theHT4/status/2038199225138442421</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://x.com/theHT4</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>theHT4</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Harsh T</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1681010934867697664/e3_79n4J_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE need help</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; need help</t>
+        </is>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Mar 29, 2026 · 10:18 AM UTC</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2026-03-29T10:18:00Z</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>7</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2038194022280282249</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2038194022280282249</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_KSA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>EmiratesNBD KSA</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>شكراً لتواصلك معنا وإظهار اهتمامك بمنتجنا. يرجى مشاركتنا برقم هاتفك الجوال المسجل ومكان السكن في المملكة العربية السعودية حتى نتمكن من ترتيب اتصال معك من قبل فريقنا. مع التحية</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>شكراً لتواصلك معنا وإظهار اهتمامك بمنتجنا. يرجى مشاركتنا برقم هاتفك الجوال المسجل ومكان السكن في المملكة العربية السعودية حتى نتمكن من ترتيب اتصال معك من قبل فريقنا. مع التحية</t>
+        </is>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>['M17322417']</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Mar 29, 2026 · 9:58 AM UTC</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2026-03-29T09:58:00Z</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>11</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2038193508092109170</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://x.com/M17322417/status/2038193508092109170</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://x.com/M17322417</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>M17322417</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>M - #يارب_بلايستيشن5</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1288819440902078465/Twk32eXp_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>قدمت اكثر من طلب استفسار للتمويل العقاري ومن نموذج الموقع وما وصلني اي اتصال او افادة</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>قدمت اكثر من طلب استفسار للتمويل العقاري ومن نموذج الموقع وما وصلني اي اتصال او افادة</t>
+        </is>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>5h</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Mar 29, 2026 · 9:56 AM UTC</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2026-03-29T09:56:00Z</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>13</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2038172102902055221</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://x.com/a_m_alazizi/status/2038172102902055221</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://x.com/a_m_alazizi</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>a_m_alazizi</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>عبدالرحمن مناور</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1745700634349764608/AVHo2vzs_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA ارجو الرد على الخاص</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; ارجو الرد على الخاص</t>
+        </is>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>6h</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Mar 29, 2026 · 8:31 AM UTC</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2026-03-29T08:31:00Z</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_KSA']</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2038164256961540293</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2038164256961540293</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Avoid public Wi-Fi for banking. Data can be intercepted.
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+emiratesnbd.com/en/campaigns…</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Avoid public Wi-Fi for banking. Data can be intercepted.
+Stay Safe, Stay Vigilant. &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;
+&lt;a href="https://www.emiratesnbd.com/en/campaigns/united-against-fraud"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>7h</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Mar 29, 2026 · 8:00 AM UTC</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2026-03-29T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud', 'https://www.emiratesnbd.com/en/campaigns/united-against-fraud']</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>595</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2038155820752339040</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2038155820752339040</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_KSA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>EmiratesNBD KSA</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>جمّع أميالك، من مشترياتك المحلية والدولية ✈️
+مع بطاقة رحالة الائتمانية من #بنك_الإمارات_دبي_الوطني 💙
+للتفاصيل:ms.spr.ly/6011QaU0Z</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>جمّع أميالك، من مشترياتك المحلية والدولية ✈️
+مع بطاقة رحالة الائتمانية من &lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_دبي_الوطني"&gt;#بنك_الإمارات_دبي_الوطني&lt;/a&gt; 💙
+للتفاصيل:&lt;a href="http://ms.spr.ly/6011QaU0Z"&gt;ms.spr.ly/6011QaU0Z&lt;/a&gt;</t>
+        </is>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>7h</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Mar 29, 2026 · 7:26 AM UTC</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2026-03-29T07:26:00Z</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_دبي_الوطني', 'http://ms.spr.ly/6011QaU0Z']</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>536</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2038135700566970803</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2038135700566970803</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #990024 in the subject line.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #990024 in the subject line.</t>
+        </is>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>['Rita09729643']</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>9h</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Mar 29, 2026 · 6:06 AM UTC</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2026-03-29T06:06:00Z</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>11</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2037955706662604958</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>https://x.com/Rita09729643/status/2037955706662604958</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://x.com/Rita09729643</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Rita09729643</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Rita</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1655465335775010816/KmAYkyBx_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Hi I have a credit card of Emirates NBD, but I haven’t used it for many years, suddenly I received the email of statement that I need to pay 764.13AED as the total payment due, this is really unacceptable.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Hi I have a credit card of Emirates NBD, but I haven’t used it for many years, suddenly I received the email of statement that I need to pay 764.13AED as the total payment due, this is really unacceptable.</t>
+        </is>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>21h</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:11 PM UTC</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2026-03-28T18:11:00Z</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>27</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2037936526093430909</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037936526093430909</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>We regret to inform you that this process can be done only by a branch visit within the UAE.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>We regret to inform you that this process can be done only by a branch visit within the UAE.</t>
+        </is>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>['cruizomfs']</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 4:55 PM UTC</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2026-03-28T16:55:00Z</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>34</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2037928218003382573</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>https://x.com/cruizomfs/status/2037928218003382573</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://x.com/cruizomfs</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>cruizomfs</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Los 🥚 De Donald Trump 🇺🇸</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2030819740177063936/UWZXuDTH_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>I just got back from the UAE, is there any chance I can start the process online. I'll probably go again in august.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>I just got back from the UAE, is there any chance I can start the process online. I&amp;#39;ll probably go again in august.</t>
+        </is>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>22h</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 4:22 PM UTC</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2026-03-28T16:22:00Z</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>32</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2037921044221010067</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2037921044221010067</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>EmiratesNBD_AE</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Emirates NBD</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
         <is>
           <t>Hi, thank you for reaching out, please be informed that you can apply for non-resident account by a visit to one of our branches within the UAE.
 Documents:
@@ -1375,7 +2889,7 @@
 (Bill should not be more than 3 months old)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>Hi, thank you for reaching out, please be informed that you can apply for non-resident account by a visit to one of our branches within the UAE.
 Documents:
@@ -1396,953 +2910,953 @@
 (Bill should not be more than 3 months old)</t>
         </is>
       </c>
-      <c r="J11" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
         <is>
           <t>['cruizomfs']</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>23h</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 3:53 PM UTC</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>2026-03-28T15:53:00Z</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="n">
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
         <v>1</v>
       </c>
-      <c r="U11" t="n">
-        <v>19</v>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="U28" t="n">
+        <v>24</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>2037911596106715381</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>https://x.com/cruizomfs/status/2037911596106715381</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>https://x.com/cruizomfs</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>cruizomfs</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Los 🥚 De Donald Trump 🇺🇸</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2030819740177063936/UWZXuDTH_bigger.jpg</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
         <is>
           <t>Hello. Do I need a residency in order to open an account?</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>Hello. Do I need a residency in order to open an account?</t>
         </is>
       </c>
-      <c r="J12" t="b">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>18h</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 3:16 PM UTC</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>2026-03-28T15:16:00Z</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="n">
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="n">
         <v>1</v>
       </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>8</v>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>10</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>2037895388909142325</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037895388909142325</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
         <is>
           <t>Get guaranteed vouchers worth of AED750
 Apply for Emirates NBD noon One Visa Credit Card and receive a guaranteed Majid Al Futtaim voucher worth AED 750.
 emiratesnbd.com/en/campaigns…</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>Get guaranteed vouchers worth of AED750
 Apply for Emirates NBD noon One Visa Credit Card and receive a guaranteed Majid Al Futtaim voucher worth AED 750.
 &lt;a href="https://www.emiratesnbd.com/en/campaigns/noon-one-credit-card"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J13" t="b">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>19h</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 2:11 PM UTC</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>2026-03-28T14:11:00Z</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
         <is>
           <t>['https://www.emiratesnbd.com/en/campaigns/noon-one-credit-card']</t>
         </is>
       </c>
-      <c r="R13" t="n">
+      <c r="R30" t="n">
         <v>3</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S30" t="n">
         <v>1</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T30" t="n">
         <v>3</v>
       </c>
-      <c r="U13" t="n">
-        <v>766</v>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="U30" t="n">
+        <v>856</v>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>2037873211728081164</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037873211728081164</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
         <is>
           <t>Please note that we don't have access to your profile from this channel due to security reasons, so kindly share the details through email, so we can check accordingly</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>Please note that we don&amp;#39;t have access to your profile from this channel due to security reasons, so kindly share the details through email, so we can check accordingly</t>
         </is>
       </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
         <is>
           <t>['rated_sm']</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 12:43 PM UTC</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>2026-03-28T12:43:00Z</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>20</v>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>26</v>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>2037867679802122593</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>https://x.com/rated_sm/status/2037867679802122593</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>https://x.com/rated_sm</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>rated_sm</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>rated_sm</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1870693863452524544/xTAmP9KA_bigger.jpg</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
         <is>
           <t>I was hoping for a more immediate support and solution cause inability to make this payment will cause me to incur a large overlimit fee.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>I was hoping for a more immediate support and solution cause inability to make this payment will cause me to incur a large overlimit fee.</t>
         </is>
       </c>
-      <c r="J15" t="b">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 12:21 PM UTC</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>2026-03-28T12:21:00Z</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="n">
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="n">
         <v>1</v>
       </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>23</v>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>30</v>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>2037866970410811411</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037866970410811411</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
         <is>
           <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at 
 social@emiratesnbd.com
 Quoting case #989891 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at 
 social@emiratesnbd.com
 Quoting case #989891 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
         </is>
       </c>
-      <c r="J16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
         <is>
           <t>['rated_sm']</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 12:18 PM UTC</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>2026-03-28T12:18:00Z</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="n">
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="n">
         <v>1</v>
       </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>21</v>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>23</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>2037865010320539854</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>https://x.com/rated_sm/status/2037865010320539854</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>https://x.com/rated_sm</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>rated_sm</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>rated_sm</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1870693863452524544/xTAmP9KA_bigger.jpg</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; My phone is broken and is pending repair with Apple. I need to make a payment and I logged into the website using OTP, but when attempting payment, its still asking for Smart Pass confirmation and no OTP option. Same when attempting to contact Whatsapp Support.</t>
         </is>
       </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>21h</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 12:10 PM UTC</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>2026-03-28T12:10:00Z</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
         <is>
           <t>['https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="R17" t="n">
+      <c r="R34" t="n">
         <v>1</v>
       </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>25</v>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>29</v>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>2037827252075839770</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_KSA/status/2037827252075839770</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_KSA</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>EmiratesNBD_KSA</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>EmiratesNBD KSA</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
         <is>
           <t>نعم يمكنك تقسيط المبلغ, لطلب التقسيط وتفاصيل أكثر قبل إجراء المعاملة يرجى الاتصال بنا على الرقم المجاني 8007547777</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>نعم يمكنك تقسيط المبلغ, لطلب التقسيط وتفاصيل أكثر قبل إجراء المعاملة يرجى الاتصال بنا على الرقم المجاني 8007547777</t>
         </is>
       </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
         <is>
           <t>['Talal_Hus']</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 9:40 AM UTC</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>2026-03-28T09:40:00Z</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>46</v>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>51</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>2037818020597215557</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>https://x.com/Talal_Hus/status/2037818020597215557</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>https://x.com/Talal_Hus</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Talal_Hus</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>T.A</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1499888329797652480/UU2JVEEj_bigger.jpg</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA بالنسبة للتقسيط بدون هامش ربح هل لو سددت من خلال الفيزا ابل باي اقدر استفيد من العرض ؟ 
 يعني ععندب في نون اشتري ابل باي وبعدها اقسطها ؟</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; بالنسبة للتقسيط بدون هامش ربح هل لو سددت من خلال الفيزا ابل باي اقدر استفيد من العرض ؟ 
 يعني ععندب في نون اشتري ابل باي وبعدها اقسطها ؟</t>
         </is>
       </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
+      <c r="J36" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 9:04 AM UTC</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>2026-03-28T09:04:00Z</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
         <is>
           <t>['https://x.com/EmiratesNBD_KSA']</t>
         </is>
       </c>
-      <c r="R19" t="n">
+      <c r="R36" t="n">
         <v>1</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>32</v>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>40</v>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>2037804608517509572</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>https://x.com/eazyislit/status/2037804608517509572</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>https://x.com/eazyislit</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>eazyislit</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Dat Dark Rich Dude 💎🇳🇬🇬🇧</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1920377756946169857/gG-ZA10q_bigger.jpg</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
         <is>
           <t>THE WOMAN DAT CARRIED YOU FOR 9 MONTHS MAY SHE LIVE LONG AND WITNESS YOU SUCCEED 🤍</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>THE WOMAN DAT CARRIED YOU FOR 9 MONTHS MAY SHE LIVE LONG AND WITNESS YOU SUCCEED 🤍</t>
         </is>
       </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
+      <c r="J37" t="b">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 8:10 AM UTC</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>2026-03-28T08:10:00Z</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>12</v>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>13</v>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>2037801868244533349</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037801868244533349</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
         <is>
           <t>What’s more suspicious?
 Stay Safe, Stay Vigilant. #UnitedAgainstFraud
 emiratesnbd.com/en/campaigns…</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>What’s more suspicious?
 Stay Safe, Stay Vigilant. &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;
 &lt;a href="https://www.emiratesnbd.com/en/campaigns/united-against-fraud"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
+      <c r="J38" t="b">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 8:00 AM UTC</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>2026-03-28T08:00:00Z</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud', 'https://www.emiratesnbd.com/en/campaigns/united-against-fraud']</t>
         </is>
       </c>
-      <c r="R21" t="n">
+      <c r="R38" t="n">
         <v>2</v>
       </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
         <v>4</v>
       </c>
-      <c r="U21" t="n">
-        <v>567</v>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="U38" t="n">
+        <v>615</v>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>2037799000171216897</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>https://x.com/argosaki/status/2037799000171216897</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>https://x.com/argosaki</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>argosaki</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>GP Q</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1346926049532080128/AZU6mAE-_bigger.jpg</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
         <is>
           <t>SOUNDS LIKE … QUANTUM 
 Emirates NBD enables instant trading account top-ups for UAE investors
@@ -2350,7 +3864,7 @@
 gulfnews.com/business/bankin…</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>SOUNDS LIKE … QUANTUM 
 Emirates NBD enables instant trading account top-ups for UAE investors
@@ -2358,341 +3872,341 @@
 &lt;a href="https://gulfnews.com/business/banking/emirates-nbd-enables-instant-trading-account-top-ups-for-uae-investors-1.500487960"&gt;gulfnews.com/business/bankin…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
+      <c r="J39" t="b">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 7:48 AM UTC</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>2026-03-28T07:48:00Z</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
         <is>
           <t>['https://gulfnews.com/business/banking/emirates-nbd-enables-instant-trading-account-top-ups-for-uae-investors-1.500487960']</t>
         </is>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
         <v>1</v>
       </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>437</v>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>441</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>2037796434725269639</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>https://x.com/ZaibKang/status/2037796434725269639</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>https://x.com/ZaibKang</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>ZaibKang</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Jahan Zaib Akbar Kang</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2028644994790436864/h-Avrj3s_bigger.jpg</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
         <is>
           <t>Thanks for your timely response.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>Thanks for your timely response.</t>
         </is>
       </c>
-      <c r="J23" t="b">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
+      <c r="J40" t="b">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 7:38 AM UTC</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>2026-03-28T07:38:00Z</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>23</v>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>26</v>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>2037796009921900610</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>https://x.com/MazBalushi35285/status/2037796009921900610</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>https://x.com/MazBalushi35285</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>MazBalushi35285</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>مازن البلوشي</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2018589030322253824/-R_IX5Kh_bigger.jpg</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
         <is>
           <t>🥳مزيد من النواة الفн على مسابقة رابح صقر! راحت لكم الحفل العيد في الرياض! 🎉 فوق_النهاية فقط</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>🥳مزيد من النواة الفн على مسابقة رابح صقر! راحت لكم الحفل العيد في الرياض! 🎉 فوق_النهاية فقط</t>
         </is>
       </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
+      <c r="J41" t="b">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
         <is>
           <t>['RotanaLive', 'Turki_alalshikh', 'RabehSaqer', 'GEA_SA', 'EidSeason', 'Mabdoarena', 'EmiratesNBD_KSA']</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 7:36 AM UTC</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>2026-03-28T07:36:00Z</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>33</v>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>35</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>2037792667782824069</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037792667782824069</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
         <is>
           <t>We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #989763 in the subject line.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #989763 in the subject line.</t>
         </is>
       </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
+      <c r="J42" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
         <is>
           <t>['ZaibKang']</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 7:23 AM UTC</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>2026-03-28T07:23:00Z</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="n">
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="n">
         <v>1</v>
       </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
         <v>1</v>
       </c>
-      <c r="U25" t="n">
-        <v>36</v>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="U42" t="n">
+        <v>43</v>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>2037790087141101872</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037790087141101872</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>SelmaRomola</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Selma Romola</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1118152018995105792/5fyZOTth_bigger.jpg</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
         <is>
           <t>Fin well Financial well-being program with Emirates NBD 
 @Sabaashraff
@@ -2700,7 +4214,7 @@
 @Amanekhattab1</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>Fin well Financial well-being program with Emirates NBD 
 &lt;a href="/Sabaashraff" title="Saba Ashraf"&gt;@Sabaashraff&lt;/a&gt;
@@ -2708,87 +4222,87 @@
 &lt;a href="/Amanekhattab1" title="Amanekhattab"&gt;@Amanekhattab1&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
+      <c r="J43" t="b">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 7:13 AM UTC</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>2026-03-28T07:13:00Z</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
         <is>
           <t>['https://x.com/Sabaashraff', 'https://x.com/Sosomostafa729S', 'https://x.com/Amanekhattab1']</t>
         </is>
       </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>13</v>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>14</v>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>2037789707321622955</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037789707321622955</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>SelmaRomola</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Selma Romola</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1118152018995105792/5fyZOTth_bigger.jpg</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -2797,7 +4311,7 @@
 @Bushrasabih2</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -2806,87 +4320,87 @@
 &lt;a href="/Bushrasabih2" title="Bu_shaikh🌸❤️"&gt;@Bushrasabih2&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J27" t="b">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
+      <c r="J44" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 7:11 AM UTC</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>2026-03-28T07:11:00Z</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
         <is>
           <t>['https://x.com/FazilAnas', 'https://x.com/Emy191990', 'https://x.com/Bushrasabih2']</t>
         </is>
       </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>15</v>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>17</v>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>2037789510478843981</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037789510478843981</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>SelmaRomola</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Selma Romola</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1118152018995105792/5fyZOTth_bigger.jpg</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -2895,7 +4409,7 @@
 @yasar8212</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -2904,87 +4418,87 @@
 &lt;a href="/yasar8212" title="shaniyadu"&gt;@yasar8212&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J28" t="b">
-        <v>0</v>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
+      <c r="J45" t="b">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 7:10 AM UTC</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>2026-03-28T07:10:00Z</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
         <is>
           <t>['https://x.com/Sosomostafa729S', 'https://x.com/Nur_Munem', 'https://x.com/yasar8212']</t>
         </is>
       </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>13</v>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>14</v>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>2037788447910564341</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola/status/2037788447910564341</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>https://x.com/SelmaRomola</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>SelmaRomola</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Selma Romola</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1118152018995105792/5fyZOTth_bigger.jpg</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -2993,7 +4507,7 @@
 @Sosomostafa729S</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>To buy gold and silver through Emirates NBD, the fastest way is using the ENBD X mobile app. 
 Tagging 
@@ -3002,1943 +4516,1943 @@
 &lt;a href="/Sosomostafa729S" title="Soha.mostafa77"&gt;@Sosomostafa729S&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
+      <c r="J46" t="b">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 7:06 AM UTC</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>2026-03-28T07:06:00Z</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
         <is>
           <t>['https://x.com/Bushrasabih2', 'https://x.com/AmalBeevi', 'https://x.com/Sosomostafa729S']</t>
         </is>
       </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>14</v>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>15</v>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>2037785874474430532</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>https://x.com/ZaibKang/status/2037785874474430532</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>https://x.com/ZaibKang</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>ZaibKang</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Jahan Zaib Akbar Kang</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2028644994790436864/h-Avrj3s_bigger.jpg</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
         <is>
           <t>I applied for liv X account Still not received any response 
 Reference number 
 2026038379331830</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>I applied for liv X account Still not received any response 
 Reference number 
 2026038379331830</t>
         </is>
       </c>
-      <c r="J30" t="b">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
+      <c r="J47" t="b">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 6:56 AM UTC</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>2026-03-28T06:56:00Z</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="n">
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="n">
         <v>1</v>
       </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>40</v>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>46</v>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>2037785071189671937</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>https://x.com/ZaibKang/status/2037785071189671937</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>https://x.com/ZaibKang</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>ZaibKang</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Jahan Zaib Akbar Kang</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2028644994790436864/h-Avrj3s_bigger.jpg</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; I applied for liv X account 3 days ago still not received any response please Check and respond as soon as possible</t>
         </is>
       </c>
-      <c r="J31" t="b">
-        <v>0</v>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
+      <c r="J48" t="b">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 6:53 AM UTC</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>2026-03-28T06:53:00Z</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
         <is>
           <t>['https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>17</v>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>18</v>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>2037784853866029145</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037784853866029145</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>Sosomostafa729S</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Soha.mostafa77</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
         <is>
           <t>B- 1.89% @zeynp_qas @Salma2232019 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>B- 1.89% &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="J32" t="b">
-        <v>0</v>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
+      <c r="J49" t="b">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 6:52 AM UTC</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>2026-03-28T06:52:00Z</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
         <is>
           <t>['https://x.com/zeynp_qas', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
         </is>
       </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>7</v>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>14</v>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>2037784763122217375</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037784763122217375</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Sosomostafa729S</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Soha.mostafa77</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
         <is>
           <t>B- 1.89% @semeet @Salma2232019 @SelmaRomola 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>B- 1.89% &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="J33" t="b">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 6:52 AM UTC</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>2026-03-28T06:52:00Z</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
         <is>
           <t>['https://x.com/semeet', 'https://x.com/Salma2232019', 'https://x.com/SelmaRomola']</t>
         </is>
       </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>20</v>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2037784668028985459</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>B- 1.89% @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>B- 1.89% &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:51 AM UTC</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:51:00Z</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
+        </is>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
         <v>13</v>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2037784668028985459</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784668028985459</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2037784498885243377</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784498885243377</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Sosomostafa729S</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Soha.mostafa77</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>B- 1.89% @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>B- 1.89% &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="J34" t="b">
-        <v>0</v>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Mar 28</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Mar 28, 2026 · 6:51 AM UTC</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>2026-03-28T06:51:00Z</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
-        </is>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>12</v>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2037784498885243377</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784498885243377</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Soha.mostafa77</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
         <is>
           <t>Exchanger volunteer program 
 @semeet @Emy191990 @ibushra_03 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>Exchanger volunteer program 
 &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="J35" t="b">
-        <v>0</v>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 6:50 AM UTC</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>2026-03-28T06:50:00Z</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
         <is>
           <t>['https://x.com/semeet', 'https://x.com/Emy191990', 'https://x.com/ibushra_03']</t>
         </is>
       </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>11</v>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>17</v>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>2037784405700419683</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037784405700419683</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Sosomostafa729S</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Soha.mostafa77</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
         <is>
           <t>Exchanger volunteer program @semeet @zeynp_qas @SelmaRomola 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="J36" t="b">
-        <v>0</v>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 6:50 AM UTC</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>2026-03-28T06:50:00Z</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
         <is>
           <t>['https://x.com/semeet', 'https://x.com/zeynp_qas', 'https://x.com/SelmaRomola']</t>
         </is>
       </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>10</v>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>16</v>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>2037784344333275440</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2037784344333275440</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>EmiratesNBD_AE</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Emirates NBD</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
         <is>
           <t>Before clicking a link, what do you do?
 Stay Safe, Stay Vigilant. #UnitedAgainstFraud
 emiratesnbd.com/en/campaigns…</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>Before clicking a link, what do you do?
 Stay Safe, Stay Vigilant. &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;
 &lt;a href="https://www.emiratesnbd.com/en/campaigns/united-against-fraud"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
         </is>
       </c>
-      <c r="J37" t="b">
-        <v>0</v>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
+      <c r="J54" t="b">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 6:50 AM UTC</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>2026-03-28T06:50:00Z</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
         <is>
           <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud', 'https://www.emiratesnbd.com/en/campaigns/united-against-fraud']</t>
         </is>
       </c>
-      <c r="R37" t="n">
+      <c r="R54" t="n">
         <v>3</v>
       </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
         <v>4</v>
       </c>
-      <c r="U37" t="n">
-        <v>565</v>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="U54" t="n">
+        <v>613</v>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>2037784337337532619</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037784337337532619</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Sosomostafa729S</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Soha.mostafa77</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
         <is>
           <t>Exchanger volunteer program @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>Exchanger volunteer program &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="J38" t="b">
-        <v>0</v>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
+      <c r="J55" t="b">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 6:50 AM UTC</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>2026-03-28T06:50:00Z</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
         <is>
           <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
         </is>
       </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>13</v>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>14</v>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>2037784225022365938</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037784225022365938</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Sosomostafa729S</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Soha.mostafa77</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
         <is>
           <t>Exchanger volunteer program @semeet @parulghalout @Salma2232019 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="J39" t="b">
-        <v>0</v>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
+      <c r="J56" t="b">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 6:49 AM UTC</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>2026-03-28T06:49:00Z</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
         <is>
           <t>['https://x.com/semeet', 'https://x.com/parulghalout', 'https://x.com/Salma2232019']</t>
         </is>
       </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>18</v>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2037784141006344295</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784141006344295</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program @semeet @Salma2232019 @ibushra_03 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J57" t="b">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:49 AM UTC</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:49:00Z</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>['https://x.com/semeet', 'https://x.com/Salma2232019', 'https://x.com/ibushra_03']</t>
+        </is>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
         <v>11</v>
       </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2037784141006344295</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784141006344295</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2037784038774317555</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Sosomostafa729S</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>Soha.mostafa77</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Exchanger volunteer program @semeet @Salma2232019 @ibushra_03 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Exchanger volunteer program &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="J40" t="b">
-        <v>0</v>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Mar 28</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Mar 28, 2026 · 6:49 AM UTC</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>2026-03-28T06:49:00Z</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>['https://x.com/semeet', 'https://x.com/Salma2232019', 'https://x.com/ibushra_03']</t>
-        </is>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>9</v>
-      </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2037784038774317555</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037784038774317555</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Soha.mostafa77</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
         <is>
           <t>Exchanger volunteer program 
 @Emy191990 @ibushra_03 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>Exchanger volunteer program 
 &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="J41" t="b">
-        <v>0</v>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
+      <c r="J58" t="b">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 6:49 AM UTC</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>2026-03-28T06:49:00Z</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
         <is>
           <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/parulghalout']</t>
         </is>
       </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
         <v>11</v>
       </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>2037783859769876728</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037783859769876728</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Sosomostafa729S</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Soha.mostafa77</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
         <is>
           <t>FINWELL ( Financial Well-being program) with Emirates NBD @semeet @zeynp_qas @Emy191990 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>FINWELL ( Financial Well-being program) with Emirates NBD &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="J42" t="b">
-        <v>0</v>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
+      <c r="J59" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 6:48 AM UTC</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>2026-03-28T06:48:00Z</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
         <is>
           <t>['https://x.com/semeet', 'https://x.com/zeynp_qas', 'https://x.com/Emy191990']</t>
         </is>
       </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>10</v>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>11</v>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>2037783775896313876</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037783775896313876</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>Sosomostafa729S</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>Soha.mostafa77</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
         <is>
           <t>FINWELL ( Financial Well-being program) with Emirates NBD @SelmaRomola @Emy191990 @parulghalout 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>FINWELL ( Financial Well-being program) with Emirates NBD &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="J43" t="b">
-        <v>0</v>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
+      <c r="J60" t="b">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 6:48 AM UTC</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>2026-03-28T06:48:00Z</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
         <is>
           <t>['https://x.com/SelmaRomola', 'https://x.com/Emy191990', 'https://x.com/parulghalout']</t>
         </is>
       </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>14</v>
-      </c>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>15</v>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>2037783673144230370</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S/status/2037783673144230370</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>Sosomostafa729S</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Soha.mostafa77</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
         <is>
           <t>FINWELL ( Financial Well-being program) with Emirates NBD 
 @Emy191990 @ibushra_03 @SelmaRomola 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>FINWELL ( Financial Well-being program) with Emirates NBD 
 &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="J44" t="b">
-        <v>0</v>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
+      <c r="J61" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 6:47 AM UTC</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>2026-03-28T06:47:00Z</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
         <is>
           <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/SelmaRomola']</t>
         </is>
       </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>13</v>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2037783477979091314</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783477979091314</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking's App @parulghalout @semeet @Emy191990 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:46 AM UTC</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:46:00Z</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>['https://x.com/parulghalout', 'https://x.com/semeet', 'https://x.com/Emy191990']</t>
+        </is>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
         <v>12</v>
       </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2037783477979091314</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783477979091314</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2037783402758508685</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>Sosomostafa729S</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Soha.mostafa77</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Through ENBD X Mobile Banking's App @parulghalout @semeet @Emy191990 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="J45" t="b">
-        <v>0</v>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J63" t="b">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 6:46 AM UTC</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>2026-03-28T06:46:00Z</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>['https://x.com/parulghalout', 'https://x.com/semeet', 'https://x.com/Emy191990']</t>
-        </is>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>['https://x.com/zeynp_qas', 'https://x.com/SelmaRomola', 'https://x.com/Salma2232019']</t>
+        </is>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>17</v>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2037783335389540775</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783335389540775</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Sosomostafa729S</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Soha.mostafa77</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking's App @Emy191990 @parulghalout @ibushra_03 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J64" t="b">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>['EmiratesNBD_AE']</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Mar 28</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:46 AM UTC</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:46:00Z</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/ibushra_03']</t>
+        </is>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" t="n">
         <v>10</v>
       </c>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2037783402758508685</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783402758508685</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2037783125854679453</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>Sosomostafa729S</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>Soha.mostafa77</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Through ENBD X Mobile Banking's App @zeynp_qas @SelmaRomola @Salma2232019 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/zeynp_qas" title="zeynab kasem"&gt;@zeynp_qas&lt;/a&gt; &lt;a href="/SelmaRomola" title="Selma Romola"&gt;@SelmaRomola&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="J46" t="b">
-        <v>0</v>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; 🌿🇦🇪❤️</t>
+        </is>
+      </c>
+      <c r="J65" t="b">
+        <v>0</v>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Mar 28, 2026 · 6:46 AM UTC</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>2026-03-28T06:46:00Z</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>['https://x.com/zeynp_qas', 'https://x.com/SelmaRomola', 'https://x.com/Salma2232019']</t>
-        </is>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>14</v>
-      </c>
-      <c r="V46" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2037783335389540775</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783335389540775</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Mar 28, 2026 · 6:45 AM UTC</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>2026-03-28T06:45:00Z</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>['https://x.com/parulghalout', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
+        </is>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>13</v>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2037783049065390446</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
         <is>
           <t>https://x.com/Sosomostafa729S</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>Sosomostafa729S</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Soha.mostafa77</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Through ENBD X Mobile Banking's App @Emy191990 @parulghalout @ibushra_03 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="J47" t="b">
-        <v>0</v>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Mar 28</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>Mar 28, 2026 · 6:46 AM UTC</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>2026-03-28T06:46:00Z</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>['https://x.com/Emy191990', 'https://x.com/parulghalout', 'https://x.com/ibushra_03']</t>
-        </is>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>10</v>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2037783125854679453</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783125854679453</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Soha.mostafa77</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Through ENBD X Mobile Banking's App @parulghalout @Salma2232019 @semeet 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Through ENBD X Mobile Banking&amp;#39;s App &lt;a href="/parulghalout" title="parul ghalout"&gt;@parulghalout&lt;/a&gt; &lt;a href="/Salma2232019" title="Salma"&gt;@Salma2232019&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; 🌿🇦🇪❤️</t>
-        </is>
-      </c>
-      <c r="J48" t="b">
-        <v>0</v>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Mar 28</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Mar 28, 2026 · 6:45 AM UTC</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>2026-03-28T06:45:00Z</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>['https://x.com/parulghalout', 'https://x.com/Salma2232019', 'https://x.com/semeet']</t>
-        </is>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>11</v>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2037783049065390446</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S/status/2037783049065390446</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>https://x.com/Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Sosomostafa729S</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Soha.mostafa77</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>https://pbs.twimg.com/profile_images/2034153587794972677/yhnd0_Le_bigger.jpg</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
         <is>
           <t>Through ENBD X Mobile Banking's App 
 @Emy191990 @ibushra_03 @semeet 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>Through ENBD X Mobile Banking&amp;#39;s App 
 &lt;a href="/Emy191990" title="Eman Mohamed"&gt;@Emy191990&lt;/a&gt; &lt;a href="/ibushra_03" title="Bushra Muhammad 🇦🇪"&gt;@ibushra_03&lt;/a&gt; &lt;a href="/semeet" title="seema shelat"&gt;@semeet&lt;/a&gt; 🌿🇦🇪❤️</t>
         </is>
       </c>
-      <c r="J49" t="b">
-        <v>0</v>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
+      <c r="J66" t="b">
+        <v>0</v>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 6:45 AM UTC</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>2026-03-28T06:45:00Z</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr">
         <is>
           <t>['https://x.com/Emy191990', 'https://x.com/ibushra_03', 'https://x.com/semeet']</t>
         </is>
       </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="n">
-        <v>9</v>
-      </c>
-      <c r="V49" t="inlineStr">
-        <is>
-          <t>ENBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="n">
+        <v>10</v>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>ENBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>2037730056920088898</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>https://x.com/wil3020/status/2037730056920088898</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>https://x.com/wil3020</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>wil3020</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>wiil</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>https://pbs.twimg.com/profile_images/1939900695018106882/lxZGZx9Y_bigger.jpg</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
         <is>
           <t>The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>The UAE is no longer safe Continuous and comprehensive bombing of the UAE now</t>
         </is>
       </c>
-      <c r="J50" t="b">
-        <v>0</v>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
+      <c r="J67" t="b">
+        <v>0</v>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
         <is>
           <t>['EmiratesNBD_AE']</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>Mar 28</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>Mar 28, 2026 · 3:14 AM UTC</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>2026-03-28T03:14:00Z</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
         <v>39</v>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="V67" t="inlineStr">
         <is>
           <t>ENBD</t>
         </is>

--- a/EI_ENBD_3post.xlsx
+++ b/EI_ENBD_3post.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V61"/>
+  <dimension ref="A1:V66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,47 +543,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2039191295608975760</t>
+          <t>2039549656296820889</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2039191295608975760</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2039549656296820889</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>EmiratesNBD KSA</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل إلى 
-social@EmiratesNBD.com 
-من بريدك الإلكتروني المسجل لنتمكن من المراجعة والمساعدة. يُرجى ذكر رقم القضية 991364 على مواقع التواصل الاجتماعي في موضوع البريد الإلكتروني.</t>
+          <t>عليكم السلام ورحمه الله وبركاته مرحبا سلمان يمكنك تحميل تطبيق بنك الإمارات دبي الوطني السعوديه من خلال هذا الرابط
+ms.spr.ly/6014QLbJw</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل إلى 
-social@EmiratesNBD.com 
-من بريدك الإلكتروني المسجل لنتمكن من المراجعة والمساعدة. يُرجى ذكر رقم القضية 991364 على مواقع التواصل الاجتماعي في موضوع البريد الإلكتروني.</t>
+          <t>عليكم السلام ورحمه الله وبركاته مرحبا سلمان يمكنك تحميل تطبيق بنك الإمارات دبي الوطني السعوديه من خلال هذا الرابط
+&lt;a href="http://ms.spr.ly/6014QLbJw"&gt;ms.spr.ly/6014QLbJw&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J2" t="b">
@@ -592,26 +590,30 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['AliAhmedk66633']</t>
+          <t>['s2022f']</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1m</t>
+          <t>17m</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Apr 1, 2026 · 4:01 AM UTC</t>
+          <t>Apr 2, 2026 · 3:45 AM UTC</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-04-01T04:01:00Z</t>
+          <t>2026-04-02T03:45:00Z</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>['http://ms.spr.ly/6014QLbJw']</t>
+        </is>
+      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -622,7 +624,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -633,47 +635,43 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2039188534628638839</t>
+          <t>2039547452303282649</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2039188534628638839</t>
+          <t>https://x.com/wooyleew/status/2039547452303282649</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/wooyleew</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>wooyleew</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>الذِيب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1912470073899413505/HEPmqq5d_bigger.jpg</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال شكواك إلي
-social@EmiratesNBD.com 
-من بريدك الإلكتروني المسجل لنتمكن من المراجعة والمساعدة. يُرجى ذكر رقم القضية991362  على مواقع التواصل الاجتماعي في موضوع البريد الإلكتروني حتي نتمكن من مساعدتك</t>
+          <t>روتانا وبنش مارك مع بعض ! 😂</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال شكواك إلي
-social@EmiratesNBD.com 
-من بريدك الإلكتروني المسجل لنتمكن من المراجعة والمساعدة. يُرجى ذكر رقم القضية991362  على مواقع التواصل الاجتماعي في موضوع البريد الإلكتروني حتي نتمكن من مساعدتك</t>
+          <t>روتانا وبنش مارك مع بعض ! 😂</t>
         </is>
       </c>
       <c r="J3" t="b">
@@ -682,22 +680,22 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['AliAhmedk66633']</t>
+          <t>['RotanaLive', 'RotanaMusic', 'RabehSaqer', 'JEDCalendar', 'EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>12m</t>
+          <t>26m</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Apr 1, 2026 · 3:50 AM UTC</t>
+          <t>Apr 2, 2026 · 3:36 AM UTC</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-04-01T03:50:00Z</t>
+          <t>2026-04-02T03:36:00Z</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -712,7 +710,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -723,83 +721,71 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2039088430731432020</t>
+          <t>2039545126632968318</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://x.com/ad_uae4ever/status/2039088430731432020</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2039545126632968318</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://x.com/ad_uae4ever</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ad_uae4ever</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Al..</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1929462306746081280/EnT7UGS4_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE 
-تجربة غير مرضية مع @EmiratesNBD_AE بخصوص بطاقة الاتحاد، وتحديداً فيما يتعلق بآلية احتساب الأميال.
-قمت بتحويل معاملة إلى أقساط، ولم يتم توضيح أي تأثير على الأميال أثناء العملية. لاحقاً تفاجأت بأن الرصيد أصبح بالسالب، وهو أمر يثير تساؤلات جدية حول مدى وضوح وآلية احتساب الأميال في مثل هذه العروض.
-من غير المقبول أن يتم تقديم خدمة أو عرض دون شرح كامل لانعكاساته، خصوصاً عندما يتعلق الأمر بمزايا أساسية يعتمد عليها العميل في قراراته.
-عند التواصل وفتح شكوى، تم إبلاغي بعدم توفر تسجيل المكالمة لأسباب تقنية، ثم أُغلقت الشكوى دون معالجة واضحة، مع عرض تعويض لا يعكس جوهر المشكلة.
-الموضوع هنا لا يتعلق بمعاملة واحدة فقط، بل بمدى الشفافية في طريقة إدارة واحتساب الأميال، والتي يفترض أن تكون واضحة ومفهومة للعميل بشكل كامل.
-نأمل مراجعة الحالة بشكل جدي، وتوضيح هذه الآلية بشكل صريح، ومعالجة الموضوع بما يحفظ حقوق العميل</t>
+          <t>مرحبا شكرا لتواصلك معنا برجاء توضيح إستفسارك بخصوص بنك الإمارات دبي الوطني الإمارات أو السعوديه</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
-تجربة غير مرضية مع &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; بخصوص بطاقة الاتحاد، وتحديداً فيما يتعلق بآلية احتساب الأميال.
-قمت بتحويل معاملة إلى أقساط، ولم يتم توضيح أي تأثير على الأميال أثناء العملية. لاحقاً تفاجأت بأن الرصيد أصبح بالسالب، وهو أمر يثير تساؤلات جدية حول مدى وضوح وآلية احتساب الأميال في مثل هذه العروض.
-من غير المقبول أن يتم تقديم خدمة أو عرض دون شرح كامل لانعكاساته، خصوصاً عندما يتعلق الأمر بمزايا أساسية يعتمد عليها العميل في قراراته.
-عند التواصل وفتح شكوى، تم إبلاغي بعدم توفر تسجيل المكالمة لأسباب تقنية، ثم أُغلقت الشكوى دون معالجة واضحة، مع عرض تعويض لا يعكس جوهر المشكلة.
-الموضوع هنا لا يتعلق بمعاملة واحدة فقط، بل بمدى الشفافية في طريقة إدارة واحتساب الأميال، والتي يفترض أن تكون واضحة ومفهومة للعميل بشكل كامل.
-نأمل مراجعة الحالة بشكل جدي، وتوضيح هذه الآلية بشكل صريح، ومعالجة الموضوع بما يحفظ حقوق العميل</t>
+          <t>مرحبا شكرا لتواصلك معنا برجاء توضيح إستفسارك بخصوص بنك الإمارات دبي الوطني الإمارات أو السعوديه</t>
         </is>
       </c>
       <c r="J4" t="b">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>['saharalnefaie']</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>6h</t>
+          <t>35m</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 9:12 PM UTC</t>
+          <t>Apr 2, 2026 · 3:27 AM UTC</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-03-31T21:12:00Z</t>
+          <t>2026-04-02T03:27:00Z</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>['https://x.com/EmiratesNBD_AE', 'https://x.com/EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -810,7 +796,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -821,22 +807,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2039082315767263660</t>
+          <t>2039544815637901543</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY/status/2039082315767263660</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2039544815637901543</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_EGY</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EmiratesNBD_EGY</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -846,52 +832,42 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Inside TMG? You’re already winning.
-From your morning coffee everyday outings, enjoy up to 5% cashback on your everyday spend across the TMG.
-More moments. More rewards.
-All in one place.
-Together – it pays off
-Apply now for Emirates NBD Mastercard credit card x TMG and turn all your spending into cashback.
-Terms and conditions apply
-Tax registration number: 204-897-319</t>
+          <t>مرحبا بشري شكرا لتواصلك معنا الرجاء مشاركه إستفسارك والبيانات الخاصه بك إلي رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Inside TMG? You’re already winning.
-From your morning coffee everyday outings, enjoy up to 5% cashback on your everyday spend across the TMG.
-More moments. More rewards.
-All in one place.
-Together – it pays off
-Apply now for Emirates NBD Mastercard credit card x TMG and turn all your spending into cashback.
-Terms and conditions apply
-Tax registration number: 204-897-319</t>
+          <t>مرحبا بشري شكرا لتواصلك معنا الرجاء مشاركه إستفسارك والبيانات الخاصه بك إلي رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
       <c r="J5" t="b">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>['boshbsh22']</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>7h</t>
+          <t>36m</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 8:48 PM UTC</t>
+          <t>Apr 2, 2026 · 3:25 AM UTC</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-03-31T20:48:00Z</t>
+          <t>2026-04-02T03:25:00Z</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -906,7 +882,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -917,67 +893,75 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2039029088149540917</t>
+          <t>2039526156907462747</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://x.com/abdullaah_mah/status/2039029088149540917</t>
+          <t>https://x.com/soso10191271/status/2039526156907462747</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://x.com/abdullaah_mah</t>
+          <t>https://x.com/soso10191271</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>abdullaah_mah</t>
+          <t>soso10191271</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Abdoullahi Ould Mahmoud</t>
+          <t>souaad🥀☂️🖤🥈</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1699209947995635712/eNjz6TMr_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1951117294530093057/abT0lRVI_bigger.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>La banque Emirates NBD annonce le succès de la mise en place d’un financement à long terme d’un montant de 2,25 milliards de dollars.</t>
+          <t>نبغي راشد @RotanaLive</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>La banque Emirates NBD annonce le succès de la mise en place d’un financement à long terme d’un montant de 2,25 milliards de dollars.</t>
+          <t>نبغي راشد &lt;a href="/RotanaLive" title="Rotana Live"&gt;@RotanaLive&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'RotanaMusic', 'RabehSaqer', 'JEDCalendar', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>10h</t>
+          <t>1h</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 5:16 PM UTC</t>
+          <t>Apr 2, 2026 · 2:11 AM UTC</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-03-31T17:16:00Z</t>
+          <t>2026-04-02T02:11:00Z</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>['https://x.com/RotanaLive']</t>
+        </is>
+      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -985,10 +969,10 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -999,77 +983,71 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2039017522863669449</t>
+          <t>2039515059873820748</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://x.com/nasnews_e/status/2039017522863669449</t>
+          <t>https://x.com/all3125/status/2039515059873820748</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://x.com/nasnews_e</t>
+          <t>https://x.com/all3125</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>nasnews_e</t>
+          <t>all3125</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nas News Emirates</t>
+          <t>الل اللل</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2034790571630575616/O8W30no3_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1826036614339985408/-VwKoemK_bigger.png</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>#Emirates #NBD has successfully closed a US$2.25 billion long-term financing transaction, reinforcing its strong credit profile and market confidence.
-The deal includes a US$1.75 billion oversubscribed sustainability-linked loan and a US$500 million Murabaha facility arranged through Emirates Islamic.
-This milestone strengthens liquidity, enhances funding diversification, and supports long-term growth.
-#UAE | #nas_news_emirates</t>
+          <t>طيب و الرياض لها الله</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23Emirates"&gt;#Emirates&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23NBD"&gt;#NBD&lt;/a&gt; has successfully closed a US$2.25 billion long-term financing transaction, reinforcing its strong credit profile and market confidence.
-The deal includes a US$1.75 billion oversubscribed sustainability-linked loan and a US$500 million Murabaha facility arranged through Emirates Islamic.
-This milestone strengthens liquidity, enhances funding diversification, and supports long-term growth.
-&lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt; | &lt;a href="/search?f=tweets&amp;amp;q=%23nas_news_emirates"&gt;#nas_news_emirates&lt;/a&gt;</t>
+          <t>طيب و الرياض لها الله</t>
         </is>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>['RotanaLive', 'RabehSaqer', 'JEDCalendar', 'EmiratesNBD_KSA']</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>2h</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 4:30 PM UTC</t>
+          <t>Apr 2, 2026 · 1:27 AM UTC</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-03-31T16:30:00Z</t>
+          <t>2026-04-02T01:27:00Z</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23Emirates', 'https://x.com/search?f=tweets&amp;q=%23NBD', 'https://x.com/search?f=tweets&amp;q=%23UAE', 'https://x.com/search?f=tweets&amp;q=%23nas_news_emirates']</t>
-        </is>
-      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1080,7 +1058,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1091,71 +1069,73 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2039012764744634665</t>
+          <t>2039483119829389625</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2039012764744634665</t>
+          <t>https://x.com/s2022f/status/2039483119829389625</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA</t>
+          <t>https://x.com/s2022f</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA</t>
+          <t>s2022f</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EmiratesNBD KSA</t>
+          <t>salman 🇸🇦</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2036907812618678272/m21MggIw_bigger.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>مرحبًا، هل يمكننا معرفة سبب عدم رضاك؟ سيكون من المفيد جدًا إذا كان بإمكانك مشاركة المزيد من التفاصيل حول ذلك ورقم اتصالك معنا عبر الرسائل الخاصة.</t>
+          <t>@EmiratesNBD_AE السلام عليكم 
+ممكن رابط البنك التطبيق في الايفون للبنك وهل انتم بنك دبي الوطني</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مرحبًا، هل يمكننا معرفة سبب عدم رضاك؟ سيكون من المفيد جدًا إذا كان بإمكانك مشاركة المزيد من التفاصيل حول ذلك ورقم اتصالك معنا عبر الرسائل الخاصة.</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; السلام عليكم 
+ممكن رابط البنك التطبيق في الايفون للبنك وهل انتم بنك دبي الوطني</t>
         </is>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>['AbduAlnahari']</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>4h</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 4:11 PM UTC</t>
+          <t>Apr 1, 2026 · 11:20 PM UTC</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-03-31T16:11:00Z</t>
+          <t>2026-04-01T23:20:00Z</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
+        </is>
+      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -1166,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1177,43 +1157,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2039012480580571231</t>
+          <t>2039481591001424306</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2039012480580571231</t>
+          <t>https://x.com/buib102/status/2039481591001424306</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/buib102</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>buib102</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>kal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>مرحباً، نأسف لسماع أنك تواجه مشكلة. يسعدنا مساعدتك وحلها. يرجى إرسال التفاصيل إلى social@EmiratesNBD.com من بريدك الإلكتروني المسجل حتى نتمكن من مراجعتها وتقديم المساعدة. يرجى ذكر "حالة وسائل التواصل الاجتماعي رقم 991207" في عنوان البريد الإلكتروني.</t>
+          <t>للاسف نفس الشي
+قبل تحويل الراتب حسب الموظف لي وقال نعطيك الحد الاعلى 
+بعد التحويل قالو تقييمك في سمة منخفض ولا نقدر نعطيك الحد الاعلى @Reda_Alidarous @MoneyAffairs هل يحق لي اشتكيهم ؟</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مرحباً، نأسف لسماع أنك تواجه مشكلة. يسعدنا مساعدتك وحلها. يرجى إرسال التفاصيل إلى social@EmiratesNBD.com من بريدك الإلكتروني المسجل حتى نتمكن من مراجعتها وتقديم المساعدة. يرجى ذكر &amp;#34;حالة وسائل التواصل الاجتماعي رقم 991207&amp;#34; في عنوان البريد الإلكتروني.</t>
+          <t>للاسف نفس الشي
+قبل تحويل الراتب حسب الموظف لي وقال نعطيك الحد الاعلى 
+بعد التحويل قالو تقييمك في سمة منخفض ولا نقدر نعطيك الحد الاعلى &lt;a href="/Reda_Alidarous" title="رضا العيدروس/مستشار مالي"&gt;@Reda_Alidarous&lt;/a&gt; &lt;a href="/MoneyAffairs" title="المستشار المالي/ أحمد المجلي"&gt;@MoneyAffairs&lt;/a&gt; هل يحق لي اشتكيهم ؟</t>
         </is>
       </c>
       <c r="J9" t="b">
@@ -1222,26 +1206,30 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>['SultanAlhreago']</t>
+          <t>['EmiratesNBD_AE', 'SultanAlhreago']</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>4h</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 4:10 PM UTC</t>
+          <t>Apr 1, 2026 · 11:14 PM UTC</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-03-31T16:10:00Z</t>
+          <t>2026-04-01T23:14:00Z</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>['https://x.com/Reda_Alidarous', 'https://x.com/MoneyAffairs']</t>
+        </is>
+      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -1252,7 +1240,7 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1263,43 +1251,43 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2039011993525399883</t>
+          <t>2039480998811869541</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAlhreago/status/2039011993525399883</t>
+          <t>https://x.com/frasalq68164244/status/2039480998811869541</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAlhreago</t>
+          <t>https://x.com/frasalq68164244</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SultanAlhreago</t>
+          <t>frasalq68164244</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sultan Al hrbi</t>
+          <t>الشيخ فراس القحطاني⚡️</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/2024533164123676672/R-sxy3-F_bigger.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0556591475</t>
+          <t>روتانا تكفى ابغى افوز تذاكر حفله رابح صقر ولله ولا مره حضرت حفله تكفى يا روتانا</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0556591475</t>
+          <t>روتانا تكفى ابغى افوز تذاكر حفله رابح صقر ولله ولا مره حضرت حفله تكفى يا روتانا</t>
         </is>
       </c>
       <c r="J10" t="b">
@@ -1308,28 +1296,28 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['RotanaLive', 'RotanaMusic', 'RabehSaqer', 'JEDCalendar', 'EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>4h</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 4:08 PM UTC</t>
+          <t>Apr 1, 2026 · 11:12 PM UTC</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-03-31T16:08:00Z</t>
+          <t>2026-04-01T23:12:00Z</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1338,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>9</v>
+        <v>212</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1349,45 +1337,43 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2039011794040070545</t>
+          <t>2039467199039963212</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://x.com/AbduAlnahari/status/2039011794040070545</t>
+          <t>https://x.com/huda_M199/status/2039467199039963212</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://x.com/AbduAlnahari</t>
+          <t>https://x.com/huda_M199</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AbduAlnahari</t>
+          <t>huda_M199</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Abdulrahman AlNahari</t>
+          <t>Hdo ♍️</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1193479361229459456/3jAF_JGC_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1794325204472119296/JGp9gTxL_bigger.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>اسوأ خدمة عملاء
-اسبوعين ما تقدرو تحدثوا معلومات</t>
+          <t>اللي يبي احجز له 🫡</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>اسوأ خدمة عملاء
-اسبوعين ما تقدرو تحدثوا معلومات</t>
+          <t>اللي يبي احجز له 🫡</t>
         </is>
       </c>
       <c r="J11" t="b">
@@ -1396,28 +1382,28 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_KSA']</t>
+          <t>['RotanaLive', 'RotanaMusic', 'RabehSaqer', 'JEDCalendar', 'EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>5h</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 4:07 PM UTC</t>
+          <t>Apr 1, 2026 · 10:17 PM UTC</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-03-31T16:07:00Z</t>
+          <t>2026-04-01T22:17:00Z</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1426,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>9</v>
+        <v>225</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1437,43 +1423,43 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2039011308712902849</t>
+          <t>2039452023532228961</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAlhreago/status/2039011308712902849</t>
+          <t>https://x.com/o05l_/status/2039452023532228961</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAlhreago</t>
+          <t>https://x.com/o05l_</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SultanAlhreago</t>
+          <t>o05l_</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sultan Al hrbi</t>
+          <t>تذاكر ‏| منصة On Ticket ‏</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/2036319819226611714/N4mcDWk8_bigger.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0556591475</t>
+          <t>خليكم جاهزين وفعلو التنبيهات بنوفر لكم التذاكر</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0556591475</t>
+          <t>خليكم جاهزين وفعلو التنبيهات بنوفر لكم التذاكر</t>
         </is>
       </c>
       <c r="J12" t="b">
@@ -1482,22 +1468,22 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['RotanaLive', 'salhendi', 'RabehSaqer', 'JEDCalendar', 'EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>6h</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 4:05 PM UTC</t>
+          <t>Apr 1, 2026 · 9:17 PM UTC</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-03-31T16:05:00Z</t>
+          <t>2026-04-01T21:17:00Z</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1509,10 +1495,10 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1523,43 +1509,43 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2039011275330429012</t>
+          <t>2039439218858967363</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2039011275330429012</t>
+          <t>https://x.com/A3043337833312/status/2039439218858967363</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/A3043337833312</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>A3043337833312</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>يرجى تزويدنا برقم هاتفك المسجل عبر رسالة خاصة، حتى يتمكن فريقنا من التواصل معك ومساعدتك. مع التحية.</t>
+          <t>نبغى ابو نوره</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>يرجى تزويدنا برقم هاتفك المسجل عبر رسالة خاصة، حتى يتمكن فريقنا من التواصل معك ومساعدتك. مع التحية.</t>
+          <t>نبغى ابو نوره</t>
         </is>
       </c>
       <c r="J13" t="b">
@@ -1568,37 +1554,37 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>['SultanAlhreago']</t>
+          <t>['RotanaLive', 'RabehSaqer', 'JEDCalendar', 'EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 4:05 PM UTC</t>
+          <t>Apr 1, 2026 · 8:26 PM UTC</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-03-31T16:05:00Z</t>
+          <t>2026-04-01T20:26:00Z</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
         <v>1</v>
       </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
       <c r="U13" t="n">
-        <v>11</v>
+        <v>310</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1609,45 +1595,65 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2039010680599175570</t>
+          <t>2039435601422762473</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAlhreago/status/2039010680599175570</t>
+          <t>https://x.com/alrythy59921/status/2039435601422762473</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAlhreago</t>
+          <t>https://x.com/alrythy59921</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SultanAlhreago</t>
+          <t>alrythy59921</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sultan Al hrbi</t>
+          <t>تذاكر سميره الريثي</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/2014642751564845056/rrssJwl__bigger.jpg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE 
-كنت ارغب بتمويل شخصي وراتبي على بنك الراجحي ف رحت لبنك الامارات وقالوا نعطيك قرض اذا حولت راتبك علينا تصير النسبة 1،85 ولما حولت الراتب وتعبت بعد شهر وتحول الراتب عندهم قالوا لا النسبة 3،49 لما شافوا اني حولته  . للعلم راتبي فوق 8000 ولا علي اي  التزام . 1</t>
+          <t>جدة غير و جمهور جدة غير😍
+جاهزين نولعها مع بو صقر!🔥🦅جد
+🗓️ 10 أبريل 2026
+📍جدة - عبادي الجوهر أرينا
+🎫تُطرح تذاكر غداً الساعة 4 مساءً عبر الرابط التالي 👇
+wa.me/966548025534
+#رابح_صقر_في_جدة 
+#موسم_جدة 
+#روتانا_لايف
+@RabehSaqer 
+@JEDCalendar
+@EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
-كنت ارغب بتمويل شخصي وراتبي على بنك الراجحي ف رحت لبنك الامارات وقالوا نعطيك قرض اذا حولت راتبك علينا تصير النسبة 1،85 ولما حولت الراتب وتعبت بعد شهر وتحول الراتب عندهم قالوا لا النسبة 3،49 لما شافوا اني حولته  . للعلم راتبي فوق 8000 ولا علي اي  التزام . 1</t>
+          <t>جدة غير و جمهور جدة غير😍
+جاهزين نولعها مع بو صقر!🔥🦅جد
+🗓️ 10 أبريل 2026
+📍جدة - عبادي الجوهر أرينا
+🎫تُطرح تذاكر غداً الساعة 4 مساءً عبر الرابط التالي 👇
+&lt;a href="http://wa.me/966548025534"&gt;wa.me/966548025534&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23رابح_صقر_في_جدة"&gt;#رابح_صقر_في_جدة&lt;/a&gt; 
+&lt;a href="/search?f=tweets&amp;amp;q=%23موسم_جدة"&gt;#موسم_جدة&lt;/a&gt; 
+&lt;a href="/search?f=tweets&amp;amp;q=%23روتانا_لايف"&gt;#روتانا_لايف&lt;/a&gt;
+&lt;a href="/RabehSaqer" title="Rabeh Saqer رابح صقر"&gt;@RabehSaqer&lt;/a&gt; 
+&lt;a href="/JEDCalendar" title="Jeddah Season | موسم جدة"&gt;@JEDCalendar&lt;/a&gt;
+&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J14" t="b">
@@ -1657,36 +1663,36 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>11h</t>
+          <t>7h</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 4:03 PM UTC</t>
+          <t>Apr 1, 2026 · 8:11 PM UTC</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-03-31T16:03:00Z</t>
+          <t>2026-04-01T20:11:00Z</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>['https://x.com/EmiratesNBD_AE']</t>
+          <t>['http://wa.me/966548025534', 'https://x.com/search?f=tweets&amp;q=%23رابح_صقر_في_جدة', 'https://x.com/search?f=tweets&amp;q=%23موسم_جدة', 'https://x.com/search?f=tweets&amp;q=%23روتانا_لايف', 'https://x.com/RabehSaqer', 'https://x.com/JEDCalendar', 'https://x.com/EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
         <v>1</v>
       </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1697,47 +1703,59 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2038998320215970027</t>
+          <t>2039426791496896596</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://x.com/AlBayanBusiness/status/2038998320215970027</t>
+          <t>https://x.com/Swagdero/status/2039426791496896596</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://x.com/AlBayanBusiness</t>
+          <t>https://x.com/Swagdero</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AlBayanBusiness</t>
+          <t>Swagdero</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>البيان الاقتصادي</t>
+          <t>ابو محمد:تذاكر:</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1706948588163465216/GdbiqZFo_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2038700181034594304/q43HSkaQ_bigger.jpg</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>«الإمارات دبي الوطني» يستكمل تمويلاً عالمياً بقيمة 2.25 مليار دولار
-albayan.ae/economy/business/…
-#البيان_الاقتصادي</t>
+          <t>جدة غير و جمهور جدة غير😍
+جاهزين نولعها مع بو صقر!🔥🦅
+🗓️ 10 أبريل 2026 
+📍جدة - عبادي الجوهر أرينا
+🎫تُطرح التذاكر غداً الساعة 4 مساءً
+Webook.com
+#رابح_صقر_ف#روتانا_لا@RabehSaqer 
+@JEDCalendar
+@EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>«الإمارات دبي الوطني» يستكمل تمويلاً عالمياً بقيمة 2.25 مليار دولار
-&lt;a href="https://www.albayan.ae/economy/business/uae-economy/1167079"&gt;albayan.ae/economy/business/…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23البيان_الاقتصادي"&gt;#البيان_الاقتصادي&lt;/a&gt;</t>
+          <t>جدة غير و جمهور جدة غير😍
+جاهزين نولعها مع بو صقر!🔥🦅
+🗓️ 10 أبريل 2026 
+📍جدة - عبادي الجوهر أرينا
+🎫تُطرح التذاكر غداً الساعة 4 مساءً
+&lt;a href="http://Webook.com"&gt;Webook.com&lt;/a&gt;
+#رابح_صقر_ف#روتانا_لا&lt;a href="/RabehSaqer" title="Rabeh Saqer رابح صقر"&gt;@RabehSaqer&lt;/a&gt; 
+&lt;a href="/JEDCalendar" title="Jeddah Season | موسم جدة"&gt;@JEDCalendar&lt;/a&gt;
+&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J15" t="b">
@@ -1747,36 +1765,36 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>12h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 3:14 PM UTC</t>
+          <t>Apr 1, 2026 · 7:36 PM UTC</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-03-31T15:14:00Z</t>
+          <t>2026-04-01T19:36:00Z</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>['https://www.albayan.ae/economy/business/uae-economy/1167079', 'https://x.com/search?f=tweets&amp;q=%23البيان_الاقتصادي']</t>
+          <t>['http://Webook.com', 'https://x.com/RabehSaqer', 'https://x.com/JEDCalendar', 'https://x.com/EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
+        <v>2</v>
+      </c>
+      <c r="T15" t="n">
         <v>3</v>
       </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
       <c r="U15" t="n">
-        <v>876</v>
+        <v>78</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1787,51 +1805,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2038995248009842862</t>
+          <t>2039422283807178938</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2038995248009842862</t>
+          <t>https://x.com/saharalnefaie/status/2039422283807178938</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/saharalnefaie</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>saharalnefaie</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Sahar Alnefaie</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1859259055144902656/P_FFuf4A_bigger.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Emirates NBD Group has successfully closed a USD 2.25 billion long‑term financing - one of the largest syndicated borrowings in the GCC.
-The transaction includes a USD 1.75 billion sustainability‑linked syndicated loan, alongside a USD 500 million five‑year Club Commodity Murabaha facility by @emiratesislamic .
-With participation from 15 leading global financial institutions, it reflects a strong market confidence while supporting funding diversification, liquidity and long-term growth.
-Read more here: emiratesnbd.com/en/media-cen…
-#EmiratesNBD #Banking #CapitalMarkets #SustainableFinance #UAE</t>
+          <t>@EmiratesNBD_AE لوسمحت ابغى اقفل بطاقة الائتمان كيف؟</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Emirates NBD Group has successfully closed a USD 2.25 billion long‑term financing - one of the largest syndicated borrowings in the GCC.
-The transaction includes a USD 1.75 billion sustainability‑linked syndicated loan, alongside a USD 500 million five‑year Club Commodity Murabaha facility by &lt;a href="/emiratesislamic" title="emiratesislamic"&gt;@emiratesislamic&lt;/a&gt; .
-With participation from 15 leading global financial institutions, it reflects a strong market confidence while supporting funding diversification, liquidity and long-term growth.
-Read more here: &lt;a href="https://www.emiratesnbd.com/en/media-center/emirates-nbd-group-successfully-closes-usd-2-25-billion-in-long-term-financing"&gt;emiratesnbd.com/en/media-cen…&lt;/a&gt;
-&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23Banking"&gt;#Banking&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23CapitalMarkets"&gt;#CapitalMarkets&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SustainableFinance"&gt;#SustainableFinance&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23UAE"&gt;#UAE&lt;/a&gt;</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; لوسمحت ابغى اقفل بطاقة الائتمان كيف؟</t>
         </is>
       </c>
       <c r="J16" t="b">
@@ -1841,36 +1851,36 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 3:02 PM UTC</t>
+          <t>Apr 1, 2026 · 7:18 PM UTC</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-03-31T15:02:00Z</t>
+          <t>2026-04-01T19:18:00Z</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>['https://x.com/emiratesislamic', 'https://www.emiratesnbd.com/en/media-center/emirates-nbd-group-successfully-closes-usd-2-25-billion-in-long-term-financing', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23Banking', 'https://x.com/search?f=tweets&amp;q=%23CapitalMarkets', 'https://x.com/search?f=tweets&amp;q=%23SustainableFinance', 'https://x.com/search?f=tweets&amp;q=%23UAE']</t>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1098</v>
+        <v>2</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1881,43 +1891,47 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2038994471031833010</t>
+          <t>2039415256783400999</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://x.com/deegrose/status/2038994471031833010</t>
+          <t>https://x.com/boshbsh22/status/2039415256783400999</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://x.com/deegrose</t>
+          <t>https://x.com/boshbsh22</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>deegrose</t>
+          <t>boshbsh22</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>DeeG (Maria)</t>
+          <t>بُشرى #حلمي</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1997531422886703104/CcsIqiYF_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1535777899944591362/x-gFuT33_bigger.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Emirates NBD closes $2.25bln in long-term financing zawya.com/en/capital-markets…</t>
+          <t>@EmiratesNBD_AE 
+السلام عليكم
+احتاج اتواصل معاكم بخصوص تاجير اله صراف لدى فندق بجدة</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Emirates NBD closes $2.25bln in long-term financing &lt;a href="https://www.zawya.com/en/capital-markets/loans/emirates-nbd-closes-225bln-in-long-term-financing-pengr2rl"&gt;zawya.com/en/capital-markets…&lt;/a&gt;</t>
+          <t>&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt; 
+السلام عليكم
+احتاج اتواصل معاكم بخصوص تاجير اله صراف لدى فندق بجدة</t>
         </is>
       </c>
       <c r="J17" t="b">
@@ -1927,23 +1941,23 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 2:58 PM UTC</t>
+          <t>Apr 1, 2026 · 6:51 PM UTC</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-03-31T14:58:00Z</t>
+          <t>2026-04-01T18:51:00Z</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>['https://www.zawya.com/en/capital-markets/loans/emirates-nbd-closes-225bln-in-long-term-financing-pengr2rl']</t>
+          <t>['https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="R17" t="n">
@@ -1953,10 +1967,10 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -1967,71 +1981,75 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2038993347155485168</t>
+          <t>2039410311430545491</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2038993347155485168</t>
+          <t>https://x.com/CircuitDotNews/status/2039410311430545491</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/CircuitDotNews</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>CircuitDotNews</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>The Circuit</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1478008411547750405/oKg08Wi3_bigger.jpg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>يُرجى تزويدنا برقم هاتفك المسجل لدينا حتى نتمكن من التواصل معك من قِبل فريقنا لمساعدتك. مع تحياتنا.</t>
+          <t>Today's The Daily Circuit: 🛢️ADNOC chief slams Iranian ‘extortion’ + Emirates NBD raises $2.25B
+Full briefing 👇
+the.circuit.news/4wy3q</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>يُرجى تزويدنا برقم هاتفك المسجل لدينا حتى نتمكن من التواصل معك من قِبل فريقنا لمساعدتك. مع تحياتنا.</t>
+          <t>Today&amp;#39;s The Daily Circuit: 🛢️ADNOC chief slams Iranian ‘extortion’ + Emirates NBD raises $2.25B
+Full briefing 👇
+&lt;a href="https://the.circuit.news/4wy3q"&gt;the.circuit.news/4wy3q&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J18" t="b">
         <v>0</v>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>['SultanAlhreago']</t>
-        </is>
-      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 2:54 PM UTC</t>
+          <t>Apr 1, 2026 · 6:31 PM UTC</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-03-31T14:54:00Z</t>
+          <t>2026-04-01T18:31:00Z</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>['https://the.circuit.news/4wy3q']</t>
+        </is>
+      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -2042,7 +2060,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -2053,43 +2071,43 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2038991386188406795</t>
+          <t>2039405025835770218</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAlhreago/status/2038991386188406795</t>
+          <t>https://x.com/marketgeniusx/status/2039405025835770218</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAlhreago</t>
+          <t>https://x.com/marketgeniusx</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SultanAlhreago</t>
+          <t>marketgeniusx</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sultan Al hrbi</t>
+          <t>Market Genius</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1923702004234268672/CCL_cyvQ_bigger.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>إدارة البنك ارغب إنصافي اخرتوني بالكذب</t>
+          <t>AWS me-south-1 (Bahrain) is their only Middle East region. Hosts critical workloads for Saudi Aramco, Emirates NBD, and most Gulf fintech. $AMZN at $211.50 +1.6% today but if this region goes offline for extended period, cloud revenue guidance gets messy. AWS does $100B+ annual run rate.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>إدارة البنك ارغب إنصافي اخرتوني بالكذب</t>
+          <t>AWS me-south-1 (Bahrain) is their only Middle East region. Hosts critical workloads for Saudi Aramco, Emirates NBD, and most Gulf fintech. &lt;a href="/search?f=tweets&amp;amp;q=%23AMZN"&gt;$AMZN&lt;/a&gt; at $211.50 +1.6% today but if this region goes offline for extended period, cloud revenue guidance gets messy. AWS does $100B+ annual run rate.</t>
         </is>
       </c>
       <c r="J19" t="b">
@@ -2098,37 +2116,41 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['KobeissiLetter']</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>9h</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 2:46 PM UTC</t>
+          <t>Apr 1, 2026 · 6:10 PM UTC</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-03-31T14:46:00Z</t>
+          <t>2026-04-01T18:10:00Z</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23AMZN']</t>
+        </is>
+      </c>
       <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>1</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>4</v>
+        <v>1192</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -2139,54 +2161,54 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2038990875565371722</t>
+          <t>2039352771435237886</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAlhreago/status/2038990875565371722</t>
+          <t>https://x.com/ArabianBusiness/status/2039352771435237886</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAlhreago</t>
+          <t>https://x.com/ArabianBusiness</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SultanAlhreago</t>
+          <t>ArabianBusiness</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sultan Al hrbi</t>
+          <t>ArabianBusiness.com</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1993579995382661127/_FaUxwqe_bigger.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>كنت ارغب بتمويل شخصي وراتبي على بنك الراجحي ف رحت لبنك الامارات وقالوا نعطيك قرض اذا حولت راتبك علينا تصير النسبة 1،85 ولما حولت الراتب وتعبت بعد شهر وتحول الراتب عندهم قالوا لا النسبة 3،49 لما شافوا اني حولته  . للعلم راتبي فوق 8000 ولا علي اي  التزام . ليه التلاعب ابغى سبب</t>
+          <t>Gulf stock markets ended higher on Wednesday amid hopes of a de-escalation in the Iran conflict, with Dubai leading gains as a AED 1 billion ($272.3 million) support package by the government and strong economic growth lifted investor sentiment.
+US President Donald Trump said on Tuesday that Washington could end its military campaign within two to three weeks and that Tehran is not required to reach a deal to halt the conflict, signalling his clearest intent yet to bring the month-long war to a close.
+Dubai’s main stock index advanced 2 per cent, led by a 5.6 per cent surge in blue-chip developer Emaar Properties and a 4.7 per cent jump in top lender Emirates NBD.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>كنت ارغب بتمويل شخصي وراتبي على بنك الراجحي ف رحت لبنك الامارات وقالوا نعطيك قرض اذا حولت راتبك علينا تصير النسبة 1،85 ولما حولت الراتب وتعبت بعد شهر وتحول الراتب عندهم قالوا لا النسبة 3،49 لما شافوا اني حولته  . للعلم راتبي فوق 8000 ولا علي اي  التزام . ليه التلاعب ابغى سبب</t>
+          <t>Gulf stock markets ended higher on Wednesday amid hopes of a de-escalation in the Iran conflict, with Dubai leading gains as a AED 1 billion ($272.3 million) support package by the government and strong economic growth lifted investor sentiment.
+US President Donald Trump said on Tuesday that Washington could end its military campaign within two to three weeks and that Tehran is not required to reach a deal to halt the conflict, signalling his clearest intent yet to bring the month-long war to a close.
+Dubai’s main stock index advanced 2 per cent, led by a 5.6 per cent surge in blue-chip developer Emaar Properties and a 4.7 per cent jump in top lender Emirates NBD.</t>
         </is>
       </c>
       <c r="J20" t="b">
         <v>0</v>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>13h</t>
@@ -2194,27 +2216,27 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 2:44 PM UTC</t>
+          <t>Apr 1, 2026 · 2:42 PM UTC</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-03-31T14:44:00Z</t>
+          <t>2026-04-01T14:42:00Z</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
-        <v>49</v>
+        <v>551</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -2225,69 +2247,67 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2038986467318677604</t>
+          <t>2039335940305408232</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://x.com/ali4bit/status/2038986467318677604</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2039335940305408232</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://x.com/ali4bit</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ali4bit</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>راکی زیر خاکی 👑 Rocky Antiquey</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2015894831462301696/T3XcXmSt_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>دو  صرافی Royal Lion و Crypto از عمده‌ترین ماموران سپاه پاسداران و پتروشیمی در دوبی هستند:
-No. 808,ENBD Building, Baniyas Road
- No 409, 4 floor, The Plaza, Baniyas Rd, Deira Al Rigga, 
-و برایان اعتماد بزرگترین عامل پولشویی سپاه است.</t>
+          <t>يرجى متابعة صفحتنا ثم إرسال رسالة مباشرة. شكرًا.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>دو  صرافی Royal Lion و Crypto از عمده‌ترین ماموران سپاه پاسداران و پتروشیمی در دوبی هستند:
-No. 808,ENBD Building, Baniyas Road
- No 409, 4 floor, The Plaza, Baniyas Rd, Deira Al Rigga, 
-و برایان اعتماد بزرگترین عامل پولشویی سپاه است.</t>
+          <t>يرجى متابعة صفحتنا ثم إرسال رسالة مباشرة. شكرًا.</t>
         </is>
       </c>
       <c r="J21" t="b">
         <v>0</v>
       </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>['AliAhmedk66633']</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>13h</t>
+          <t>14h</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 2:27 PM UTC</t>
+          <t>Apr 1, 2026 · 1:35 PM UTC</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-03-31T14:27:00Z</t>
+          <t>2026-04-01T13:35:00Z</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -2296,13 +2316,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>124</v>
+        <v>7</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -2313,43 +2333,57 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2038976125725249571</t>
+          <t>2039324999652127042</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://x.com/CNNBusinessAr/status/2038976125725249571</t>
+          <t>https://x.com/EmiratesNBD_EGY/status/2039324999652127042</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://x.com/CNNBusinessAr</t>
+          <t>https://x.com/EmiratesNBD_EGY</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CNNBusinessAr</t>
+          <t>EmiratesNBD_EGY</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>الاقتصادية CNN</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1983169168221581314/PRz7ULw2_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>أغلقت مجموعة الإمارات دبي الوطني جولة تمويل طويلة الأجل بقيمة 2.25 مليار دولار، في واحدة من أكبر الصفقات المجمعة في الخليج، مدعومة بإقبال قوي من 15 مؤسسة عالمية</t>
+          <t>انت داخل مجموعة طلعت مصطفى ؟ إنت كسبان من غير ما تفكر.
+من القهوة الصبح للتسوق والخروجات، استمتع بكاش باك يصل إلى 5% على كل معاملاتك داخل مجموعة طلعت مصطفى.
+لحظات أكتر… ومكاسب أكتر.
+في مكان واحد
+مع بعض .. تفرق
+ قدّم على بطاقة بنك الإمارات دبي الوطني ماستركارد الائتمانية بالتعاون مع مجموعة طلعت مصطفى وخلي كل مصاريفك ترجع لك بكاش باك.
+تطبق الشروط والأحكام
+رقم التسجيل الضريبي: 319-897-204</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>أغلقت مجموعة الإمارات دبي الوطني جولة تمويل طويلة الأجل بقيمة 2.25 مليار دولار، في واحدة من أكبر الصفقات المجمعة في الخليج، مدعومة بإقبال قوي من 15 مؤسسة عالمية</t>
+          <t>انت داخل مجموعة طلعت مصطفى ؟ إنت كسبان من غير ما تفكر.
+من القهوة الصبح للتسوق والخروجات، استمتع بكاش باك يصل إلى 5% على كل معاملاتك داخل مجموعة طلعت مصطفى.
+لحظات أكتر… ومكاسب أكتر.
+في مكان واحد
+مع بعض .. تفرق
+ قدّم على بطاقة بنك الإمارات دبي الوطني ماستركارد الائتمانية بالتعاون مع مجموعة طلعت مصطفى وخلي كل مصاريفك ترجع لك بكاش باك.
+تطبق الشروط والأحكام
+رقم التسجيل الضريبي: 319-897-204</t>
         </is>
       </c>
       <c r="J22" t="b">
@@ -2359,17 +2393,17 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>14h</t>
+          <t>15h</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 1:46 PM UTC</t>
+          <t>Apr 1, 2026 · 12:52 PM UTC</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-03-31T13:46:00Z</t>
+          <t>2026-04-01T12:52:00Z</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -2378,13 +2412,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>603</v>
+        <v>111</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2395,52 +2429,54 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2038964528314986898</t>
+          <t>2039324080675909710</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2038964528314986898</t>
+          <t>https://x.com/just_ittihad/status/2039324080675909710</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA</t>
+          <t>https://x.com/just_ittihad</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA</t>
+          <t>just_ittihad</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>EmiratesNBD KSA</t>
+          <t>just ittihad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/421787065533988864/jmRtKrQm_bigger.jpeg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>قبل أي خطوة، استشر المختصين📱
-تواصل مع المستشار الائتماني في ⁧#بنك_الإمارات_دبي_الوطني⁩ وخذ القرار بثقة✨</t>
+          <t>هل لديكم ما يمنع من منح عملائكم هذه الخدمات @EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>قبل أي خطوة، استشر المختصين📱
-تواصل مع المستشار الائتماني في ⁧&lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_دبي_الوطني"&gt;#بنك_الإمارات_دبي_الوطني&lt;/a&gt;⁩ وخذ القرار بثقة✨</t>
+          <t>هل لديكم ما يمنع من منح عملائكم هذه الخدمات &lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J23" t="b">
         <v>0</v>
       </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>['iD7oom911']</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>15h</t>
@@ -2448,22 +2484,22 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 1:00 PM UTC</t>
+          <t>Apr 1, 2026 · 12:48 PM UTC</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-03-31T13:00:00Z</t>
+          <t>2026-04-01T12:48:00Z</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_دبي_الوطني']</t>
+          <t>['https://x.com/EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -2472,7 +2508,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>451</v>
+        <v>113</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -2483,43 +2519,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2038956251225129344</t>
+          <t>2039314462910328865</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2038956251225129344</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2039314462910328865</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>EmiratesNBD KSA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>مرحبًا، هل يمكننا معرفة سبب عدم رضاك؟ سيكون من المفيد جدًا إذا كان بإمكانك مشاركة المزيد من التفاصيل حول ذلك ورقم اتصالك معنا عبر الرسائل الخاصة.</t>
+          <t>مرحباً, يرجى الاتصال بخدمة العملاء لدينا على الرقم  المجاني 8007547777 و من خارج المملكة على 009660112122333 وسيتمكن أحد موظفينا من مساعدتك بهذا الأمر.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>مرحبًا، هل يمكننا معرفة سبب عدم رضاك؟ سيكون من المفيد جدًا إذا كان بإمكانك مشاركة المزيد من التفاصيل حول ذلك ورقم اتصالك معنا عبر الرسائل الخاصة.</t>
+          <t>مرحباً, يرجى الاتصال بخدمة العملاء لدينا على الرقم  المجاني 8007547777 و من خارج المملكة على 009660112122333 وسيتمكن أحد موظفينا من مساعدتك بهذا الأمر.</t>
         </is>
       </c>
       <c r="J24" t="b">
@@ -2528,7 +2564,7 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>['SultanAlhreago']</t>
+          <t>['mo7d_19']</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2538,18 +2574,18 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 12:27 PM UTC</t>
+          <t>Apr 1, 2026 · 12:10 PM UTC</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-03-31T12:27:00Z</t>
+          <t>2026-04-01T12:10:00Z</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -2558,7 +2594,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -2569,43 +2605,43 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2038954975590588824</t>
+          <t>2039313457938366666</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAlhreago/status/2038954975590588824</t>
+          <t>https://x.com/mo7d_19/status/2039313457938366666</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAlhreago</t>
+          <t>https://x.com/mo7d_19</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SultanAlhreago</t>
+          <t>mo7d_19</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sultan Al hrbi</t>
+          <t>Mo7d_19</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1729555669131436033/rzkWj8Vg_bigger.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>اتمنى ان يرد على رسالتي البنك بكل وضوح</t>
+          <t>هل شحن المحافظ الرقمية و البنوك الرقمية من الفيزا عليها رسوم ؟</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>اتمنى ان يرد على رسالتي البنك بكل وضوح</t>
+          <t>هل شحن المحافظ الرقمية و البنوك الرقمية من الفيزا عليها رسوم ؟</t>
         </is>
       </c>
       <c r="J25" t="b">
@@ -2614,7 +2650,7 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['EmiratesNBD_KSA']</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2624,12 +2660,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 12:22 PM UTC</t>
+          <t>Apr 1, 2026 · 12:06 PM UTC</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-03-31T12:22:00Z</t>
+          <t>2026-04-01T12:06:00Z</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -2644,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2655,71 +2691,73 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2038954879092445695</t>
+          <t>2039305085402894553</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2038954879092445695</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2039305085402894553</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide</t>
+          <t>https://x.com/EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>dcgguide</t>
+          <t>EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>DUBAI CITY GUIDE from Cyber Gear</t>
+          <t>EmiratesNBD KSA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1780203891230945280/ODQLZiT__bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Emirates NBD Group Successfully Closes USD 2.25 Billion In Long-Term Financing blog.dubaicityguide.com/site…</t>
+          <t>عليكم السلام.
+مرحباً بك, يرجى الاتصال بخدمة العملاء لدينا على الرقم  المجاني 8007547777 و من خارج المملكة على 009660112122333 وسيتمكن أحد موظفينا من مساعدتك بهذا الأمر.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Emirates NBD Group Successfully Closes USD 2.25 Billion In Long-Term Financing &lt;a href="https://blog.dubaicityguide.com/site/emirates-nbd-group-successfully-closes-usd-2-25-billion-in-long-term-financing/"&gt;blog.dubaicityguide.com/site…&lt;/a&gt;</t>
+          <t>عليكم السلام.
+مرحباً بك, يرجى الاتصال بخدمة العملاء لدينا على الرقم  المجاني 8007547777 و من خارج المملكة على 009660112122333 وسيتمكن أحد موظفينا من مساعدتك بهذا الأمر.</t>
         </is>
       </c>
       <c r="J26" t="b">
         <v>0</v>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>['0_ab1172']</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 12:21 PM UTC</t>
+          <t>Apr 1, 2026 · 11:33 AM UTC</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-03-31T12:21:00Z</t>
+          <t>2026-04-01T11:33:00Z</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>['https://blog.dubaicityguide.com/site/emirates-nbd-group-successfully-closes-usd-2-25-billion-in-long-term-financing/']</t>
-        </is>
-      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -2730,7 +2768,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>139</v>
+        <v>35</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -2741,82 +2779,86 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2038954812801191946</t>
+          <t>2039302658217902234</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAlhreago/status/2038954812801191946</t>
+          <t>https://x.com/0_ab1172/status/2039302658217902234</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://x.com/SultanAlhreago</t>
+          <t>https://x.com/0_ab1172</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>SultanAlhreago</t>
+          <t>0_ab1172</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sultan Al hrbi</t>
+          <t>Abdulrahman</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1951463642324467712/XQYKCCfL_bigger.jpg</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>من اسوا البنوك . جيتهم باخذ تمويل وكان راتبي على الراجحي فقالوا اذا تحول الراتب علينا نعطيك نسبة 1:85 . ولما حولت الراتب عليهم قلت يلا ابغى التمويل على اساس انه 1:85  . فقالوا لا نعطيك تمويل بنسبة 3:49 . ليه اللعب هذا بعد ماتعبت وحولت الراتب غيروا كلامهم . حسبي الله ونعم الوكيل</t>
+          <t>@EmiratesNBD_KSA 
+سلام عليكم ورحمة الله وبركاته 
+اقول بتحويل بملغ لبنك محلي ولا توصل ؟</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>من اسوا البنوك . جيتهم باخذ تمويل وكان راتبي على الراجحي فقالوا اذا تحول الراتب علينا نعطيك نسبة 1:85 . ولما حولت الراتب عليهم قلت يلا ابغى التمويل على اساس انه 1:85  . فقالوا لا نعطيك تمويل بنسبة 3:49 . ليه اللعب هذا بعد ماتعبت وحولت الراتب غيروا كلامهم . حسبي الله ونعم الوكيل</t>
+          <t>&lt;a href="/EmiratesNBD_KSA" title="EmiratesNBD KSA"&gt;@EmiratesNBD_KSA&lt;/a&gt; 
+سلام عليكم ورحمة الله وبركاته 
+اقول بتحويل بملغ لبنك محلي ولا توصل ؟</t>
         </is>
       </c>
       <c r="J27" t="b">
         <v>0</v>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>15h</t>
+          <t>16h</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 12:21 PM UTC</t>
+          <t>Apr 1, 2026 · 11:23 AM UTC</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-03-31T12:21:00Z</t>
+          <t>2026-04-01T11:23:00Z</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>['https://x.com/EmiratesNBD_KSA']</t>
+        </is>
+      </c>
       <c r="R27" t="n">
         <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -2827,43 +2869,43 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2038948346396655877</t>
+          <t>2039290820038152549</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://x.com/alqreshe/status/2038948346396655877</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2039290820038152549</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://x.com/alqreshe</t>
+          <t>https://x.com/EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>alqreshe</t>
+          <t>EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>راعي الاوله ❤️</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1808896727937687552/54A2iFyt_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>ياليت عالخاص</t>
+          <t>Hi Koko, thanks for reaching out. We're sorry to hear you're facing an issue. We have replied to your post privately.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ياليت عالخاص</t>
+          <t>Hi Koko, thanks for reaching out. We&amp;#39;re sorry to hear you&amp;#39;re facing an issue. We have replied to your post privately.</t>
         </is>
       </c>
       <c r="J28" t="b">
@@ -2872,22 +2914,22 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>['t14l7', 'bandr88081', 'Vc7Jy', 'AskCFO', 'EmiratesNBD_KSA']</t>
+          <t>['koko_isa8']</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>16h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 11:55 AM UTC</t>
+          <t>Apr 1, 2026 · 10:36 AM UTC</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-03-31T11:55:00Z</t>
+          <t>2026-04-01T10:36:00Z</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -2902,7 +2944,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -2913,59 +2955,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2038919235049849068</t>
+          <t>2039287061870411951</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://x.com/proofoftalk/status/2038919235049849068</t>
+          <t>https://x.com/YemenOnlineinfo/status/2039287061870411951</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://x.com/proofoftalk</t>
+          <t>https://x.com/YemenOnlineinfo</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>proofoftalk</t>
+          <t>YemenOnlineinfo</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Proof of Talk</t>
+          <t>YemenOnline</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1995454205461762048/NF7boqts_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1692006817860120577/5snhVEeA_bigger.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Julian Sawyer @julian_sawyer, CEO of @ZodiaCustody, joins the Proof of Talk stage.
-$36M raised to scale institutional crypto custody. Backed by Standard Chartered, Northern Trust, SBI Holdings, NAB National Australia Bank, and Emirates NBD.
-Julian leads one of the fastest-growing institution-first digital asset custodians, building the infrastructure global banks and asset managers rely on to securely access digital markets.
-Before Zodia, he served as CEO of @Bitstamp by Robinhood, one of the world’s longest-running crypto exchanges, and previously co-founded Starling, one of Europe’s most successful digital banks.
-His career spans fintech, banking, and digital asset markets, placing him at the center of how institutional capital moves into crypto.
-Now, Julian takes the stage at Proof of Talk this June to discuss the infrastructure required for institutions to operate safely at scale in digital assets.
-Meet the operators defining the next phase of institutional crypto.
-June 2&amp;3, 2026 | Louvre Palace, Paris
-tickets.proofoftalk.io/passe…</t>
+          <t>#Emirates NBD Completes $2.25 Billion Financing 
+Dubai — Emirates NBD announced the successful completion of a long-term financing package worth $2.25 billion ... More :
+yemenonline.info/gulf-news/1…</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Julian Sawyer &lt;a href="/julian_sawyer" title="Julian Sawyer"&gt;@julian_sawyer&lt;/a&gt;, CEO of &lt;a href="/ZodiaCustody" title="Zodia"&gt;@ZodiaCustody&lt;/a&gt;, joins the Proof of Talk stage.
-$36M raised to scale institutional crypto custody. Backed by Standard Chartered, Northern Trust, SBI Holdings, NAB National Australia Bank, and Emirates NBD.
-Julian leads one of the fastest-growing institution-first digital asset custodians, building the infrastructure global banks and asset managers rely on to securely access digital markets.
-Before Zodia, he served as CEO of &lt;a href="/Bitstamp" title="Bitstamp by Robinhood"&gt;@Bitstamp&lt;/a&gt; by Robinhood, one of the world’s longest-running crypto exchanges, and previously co-founded Starling, one of Europe’s most successful digital banks.
-His career spans fintech, banking, and digital asset markets, placing him at the center of how institutional capital moves into crypto.
-Now, Julian takes the stage at Proof of Talk this June to discuss the infrastructure required for institutions to operate safely at scale in digital assets.
-Meet the operators defining the next phase of institutional crypto.
-June 2&amp;amp;3, 2026 | Louvre Palace, Paris
-&lt;a href="https://tickets.proofoftalk.io/passes"&gt;tickets.proofoftalk.io/passe…&lt;/a&gt;</t>
+          <t>&lt;a href="/search?f=tweets&amp;amp;q=%23Emirates"&gt;#Emirates&lt;/a&gt; NBD Completes $2.25 Billion Financing 
+Dubai — Emirates NBD announced the successful completion of a long-term financing package worth $2.25 billion ... More :
+&lt;a href="http://yemenonline.info/gulf-news/12159"&gt;yemenonline.info/gulf-news/1…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J29" t="b">
@@ -2975,36 +3005,36 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 10:00 AM UTC</t>
+          <t>Apr 1, 2026 · 10:21 AM UTC</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-03-31T10:00:00Z</t>
+          <t>2026-04-01T10:21:00Z</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>['https://x.com/julian_sawyer', 'https://x.com/ZodiaCustody', 'https://x.com/Bitstamp', 'https://tickets.proofoftalk.io/passes']</t>
+          <t>['https://x.com/search?f=tweets&amp;q=%23Emirates', 'http://yemenonline.info/gulf-news/12159']</t>
         </is>
       </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>247</v>
+        <v>307</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -3015,82 +3045,86 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2038911516687163856</t>
+          <t>2039286665143886059</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://x.com/theeb20202/status/2038911516687163856</t>
+          <t>https://x.com/aijesinfo/status/2039286665143886059</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://x.com/theeb20202</t>
+          <t>https://x.com/aijesinfo</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>theeb20202</t>
+          <t>aijesinfo</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ⒶⓁⓏⒶⒾⓂ</t>
+          <t>AIJES News</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1517954735902441472/qwtsMbj0_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1572885037577560064/pCe_YrrE_bigger.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>ابي قرض شخصي كيف</t>
+          <t>Emirates NBD finalise un financement de 2,25 milliards USD
+Dubaï — Emirates NBD a annoncé avoir finalisé avec succès un financement à long terme d’une valeur de 2,25 milliards de dollars ... Plus :
+ aijesnews.com/fr/business/ne…</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ابي قرض شخصي كيف</t>
+          <t>Emirates NBD finalise un financement de 2,25 milliards USD
+Dubaï — Emirates NBD a annoncé avoir finalisé avec succès un financement à long terme d’une valeur de 2,25 milliards de dollars ... Plus :
+ &lt;a href="http://aijesnews.com/fr/business/news32599.html"&gt;aijesnews.com/fr/business/ne…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J30" t="b">
         <v>0</v>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>18h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 9:29 AM UTC</t>
+          <t>Apr 1, 2026 · 10:20 AM UTC</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-03-31T09:29:00Z</t>
+          <t>2026-04-01T10:20:00Z</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>['http://aijesnews.com/fr/business/news32599.html']</t>
+        </is>
+      </c>
       <c r="R30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -3101,71 +3135,75 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2038903815626281446</t>
+          <t>2039286086199918686</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://x.com/AymanAlHarbiSF/status/2038903815626281446</t>
+          <t>https://x.com/aijesinfo/status/2039286086199918686</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://x.com/AymanAlHarbiSF</t>
+          <t>https://x.com/aijesinfo</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AymanAlHarbiSF</t>
+          <t>aijesinfo</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AymanAlHarbi-SF</t>
+          <t>AIJES News</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/646693781132152832/IIqkzitH_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1572885037577560064/pCe_YrrE_bigger.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>عزيزي تم الرد و التواصل و البطاقة لم تلغى و طلبتوا مبلغ تجديد البطاقة و البطاقة و الحساب مغلق من شهر ٣ ٢٠٢٥</t>
+          <t>Emirates NBD Completes $2.25 Billion Financing 
+#Dubai — Emirates NBD announced the successful completion of a long-term financing package worth $2.25 billion ... More :
+aijesnews.com/en/business/ne…</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>عزيزي تم الرد و التواصل و البطاقة لم تلغى و طلبتوا مبلغ تجديد البطاقة و البطاقة و الحساب مغلق من شهر ٣ ٢٠٢٥</t>
+          <t>Emirates NBD Completes $2.25 Billion Financing 
+&lt;a href="/search?f=tweets&amp;amp;q=%23Dubai"&gt;#Dubai&lt;/a&gt; — Emirates NBD announced the successful completion of a long-term financing package worth $2.25 billion ... More :
+&lt;a href="http://aijesnews.com/en/business/news32598.html"&gt;aijesnews.com/en/business/ne…&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J31" t="b">
         <v>0</v>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_KSA']</t>
-        </is>
-      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>19h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 8:58 AM UTC</t>
+          <t>Apr 1, 2026 · 10:17 AM UTC</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-03-31T08:58:00Z</t>
+          <t>2026-04-01T10:17:00Z</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23Dubai', 'http://aijesnews.com/en/business/news32598.html']</t>
+        </is>
+      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -3176,7 +3214,7 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>4</v>
+        <v>118</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -3187,49 +3225,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2038889033028325720</t>
+          <t>2039283443331191058</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2038889033028325720</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2039283443331191058</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>EmiratesNBD KSA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>At Emirates NBD, we are committed to staying at the forefront of digital transformation. By partnering with AlphaSense, we’re equipping our teams with cutting-edge AI to surface high-value insights and drive faster, smarter decisions.
-Hear directly from our experts on how this technology is redefining our research and strategy.
-في بنك الإمارات دبي الوطني، نواصل تعزيز موقعنا في صدارة التحول الرقمي. ومن خلال شراكتنا مع AlphaSense، نزوّد فرقنا بأدوات ذكاء اصطناعي متقدمة تتيح استخلاص معطيات تحليلية قيّمة، وتسريع عملية اتخاذ القرار بثقة وكفاءة أكبر. 
-تعرّفوا على آراء خبرائنا حول الدور الذي تلعبه هذه التقنية في إعادة صياغة مستقبل صناعة القرار.</t>
+          <t>مقاضيك من السوبرماركت تعطيك كاش باك 5% 🛒
+مع بطاقة مزيد الائتمانية من #بنك_الإمارات_دبي_الوطني 💙
+للتفاصيل:ms.spr.ly/6015QIxfB</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>At Emirates NBD, we are committed to staying at the forefront of digital transformation. By partnering with AlphaSense, we’re equipping our teams with cutting-edge AI to surface high-value insights and drive faster, smarter decisions.
-Hear directly from our experts on how this technology is redefining our research and strategy.
-في بنك الإمارات دبي الوطني، نواصل تعزيز موقعنا في صدارة التحول الرقمي. ومن خلال شراكتنا مع AlphaSense، نزوّد فرقنا بأدوات ذكاء اصطناعي متقدمة تتيح استخلاص معطيات تحليلية قيّمة، وتسريع عملية اتخاذ القرار بثقة وكفاءة أكبر. 
-تعرّفوا على آراء خبرائنا حول الدور الذي تلعبه هذه التقنية في إعادة صياغة مستقبل صناعة القرار.</t>
+          <t>مقاضيك من السوبرماركت تعطيك كاش باك 5% 🛒
+مع بطاقة مزيد الائتمانية من &lt;a href="/search?f=tweets&amp;amp;q=%23بنك_الإمارات_دبي_الوطني"&gt;#بنك_الإمارات_دبي_الوطني&lt;/a&gt; 💙
+للتفاصيل:&lt;a href="http://ms.spr.ly/6015QIxfB"&gt;ms.spr.ly/6015QIxfB&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J32" t="b">
@@ -3239,32 +3275,36 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>17h</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 8:00 AM UTC</t>
+          <t>Apr 1, 2026 · 10:07 AM UTC</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-03-31T08:00:00Z</t>
+          <t>2026-04-01T10:07:00Z</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>['https://x.com/search?f=tweets&amp;q=%23بنك_الإمارات_دبي_الوطني', 'http://ms.spr.ly/6015QIxfB']</t>
+        </is>
+      </c>
       <c r="R32" t="n">
         <v>1</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>2216</v>
+        <v>623</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -3275,22 +3315,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2038889032826982535</t>
+          <t>2039281627226845227</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2038889032826982535</t>
+          <t>https://x.com/EmiratesNBD_EGY/status/2039281627226845227</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/EmiratesNBD_EGY</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>EmiratesNBD_EGY</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3300,22 +3340,24 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Scammers can pretend to be banks. Avoid unknown callers. 
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-emiratesnbd.com/en/campaigns…</t>
+          <t>بمناسبة اليوم العربي للشمول المالى، دلوقتي تقدرتفتح حساب مع بنك الإمارات دبي الوطني مجانًا وتحصل على بطاقة خصم مباشر بدون مصاريف إصدار وذلك ضمن مبادرات الشمول المالي تحت رعاية البنك المركزي المصري.
+هذا العرض مخصص للأفراد ضمن باقة الشمول المالي خلال الفترة من 1 إبريل حتى 30  إبريل 2026.
+تطبق الشروط والأحكام.
+رقم التسجيل الضريبي: 319-897-204</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Scammers can pretend to be banks. Avoid unknown callers. 
-Stay Safe, Stay Vigilant. &lt;a href="/search?f=tweets&amp;amp;q=%23UnitedAgainstFraud"&gt;#UnitedAgainstFraud&lt;/a&gt;
-&lt;a href="https://www.emiratesnbd.com/en/campaigns/united-against-fraud"&gt;emiratesnbd.com/en/campaigns…&lt;/a&gt;</t>
+          <t>بمناسبة اليوم العربي للشمول المالى، دلوقتي تقدرتفتح حساب مع بنك الإمارات دبي الوطني مجانًا وتحصل على بطاقة خصم مباشر بدون مصاريف إصدار وذلك ضمن مبادرات الشمول المالي تحت رعاية البنك المركزي المصري.
+هذا العرض مخصص للأفراد ضمن باقة الشمول المالي خلال الفترة من 1 إبريل حتى 30  إبريل 2026.
+تطبق الشروط والأحكام.
+رقم التسجيل الضريبي: 319-897-204</t>
         </is>
       </c>
       <c r="J33" t="b">
@@ -3325,25 +3367,21 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 8:00 AM UTC</t>
+          <t>Apr 1, 2026 · 10:00 AM UTC</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-03-31T08:00:00Z</t>
+          <t>2026-04-01T10:00:00Z</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>['https://x.com/search?f=tweets&amp;q=%23UnitedAgainstFraud', 'https://www.emiratesnbd.com/en/campaigns/united-against-fraud']</t>
-        </is>
-      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -3351,10 +3389,10 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>430</v>
+        <v>163</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -3365,45 +3403,49 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2038888971627897329</t>
+          <t>2039281627109449892</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2038888971627897329</t>
+          <t>https://x.com/EmiratesNBD_EGY/status/2039281627109449892</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA</t>
+          <t>https://x.com/EmiratesNBD_EGY</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA</t>
+          <t>EmiratesNBD_EGY</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>EmiratesNBD KSA</t>
+          <t>Emirates NBD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427762424385536/iUFFKIOK_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1762427526482108416/qjFPlJ1n_bigger.jpg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>رأيك يهمنا 💬
-تواصل معنا عبر التطبيق أو الموقع أو الهاتف، وخلنا نجاوب على استفسارك</t>
+          <t>In celebration of Arab Financial Inclusion Day ! You can now open your bank account for free with Emirates NBD and get a debit card with no issuance fees as part of the Financial Inclusion Initiatives powered by the Central bank of Egypt
+This offer is eligible for individuals within the financial inclusion package during the period from 1st  of April till 30th of April 2026.
+Terms and conditions apply.
+Tax registration number: 204-897-319</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>رأيك يهمنا 💬
-تواصل معنا عبر التطبيق أو الموقع أو الهاتف، وخلنا نجاوب على استفسارك</t>
+          <t>In celebration of Arab Financial Inclusion Day ! You can now open your bank account for free with Emirates NBD and get a debit card with no issuance fees as part of the Financial Inclusion Initiatives powered by the Central bank of Egypt
+This offer is eligible for individuals within the financial inclusion package during the period from 1st  of April till 30th of April 2026.
+Terms and conditions apply.
+Tax registration number: 204-897-319</t>
         </is>
       </c>
       <c r="J34" t="b">
@@ -3413,32 +3455,32 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 7:59 AM UTC</t>
+          <t>Apr 1, 2026 · 10:00 AM UTC</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2026-03-31T07:59:00Z</t>
+          <t>2026-04-01T10:00:00Z</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>666</v>
+        <v>41</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -3449,43 +3491,43 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2038884971977314696</t>
+          <t>2039279412903047462</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://x.com/mms5350/status/2038884971977314696</t>
+          <t>https://x.com/koko_isa8/status/2039279412903047462</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://x.com/mms5350</t>
+          <t>https://x.com/koko_isa8</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>mms5350</t>
+          <t>koko_isa8</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>🇸🇦🇸🇦🇸🇦 مم</t>
+          <t>κoκo мadeмöıseιιe⁸ 💅🏽</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1846628803612639232/GNQdlN9v_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/2035262775103242240/J6m7iJmF_bigger.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>@SAMA_GOV معالي المحافظ لدي شكوى على @alrajhibank لم تعالج والرد في الخاص جاري معالجه الشكوى او تم تصعيدها لماذا التأخير في معالجة الشكاوي؟ انا متضرر من التأخير في حل شكواي</t>
+          <t>So its been a week since the last call with no updates yet from IT or operation ? To fix my issue</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>&lt;a href="/SAMA_GOV" title="SAMA | البنك المركزي السعودي"&gt;@SAMA_GOV&lt;/a&gt; معالي المحافظ لدي شكوى على &lt;a href="/alrajhibank" title="مصرف الراجحي"&gt;@alrajhibank&lt;/a&gt; لم تعالج والرد في الخاص جاري معالجه الشكوى او تم تصعيدها لماذا التأخير في معالجة الشكاوي؟ انا متضرر من التأخير في حل شكواي</t>
+          <t>So its been a week since the last call with no updates yet from IT or operation ? To fix my issue</t>
         </is>
       </c>
       <c r="J35" t="b">
@@ -3494,32 +3536,28 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>['SAMAcares', 'AymanAlHarbiSF', 'EmiratesNBD_KSA']</t>
+          <t>['koko_isa8', 'EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 7:43 AM UTC</t>
+          <t>Apr 1, 2026 · 9:51 AM UTC</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2026-03-31T07:43:00Z</t>
+          <t>2026-04-01T09:51:00Z</t>
         </is>
       </c>
       <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>['https://x.com/SAMA_GOV', 'https://x.com/alrajhibank']</t>
-        </is>
-      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -3528,7 +3566,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -3539,75 +3577,73 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2038884890695831893</t>
+          <t>2039276112245916006</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2038884890695831893</t>
+          <t>https://x.com/GCCBusinessNews/status/2039276112245916006</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/GCCBusinessNews</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>GCCBusinessNews</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>GCC Business News</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1253796411872862212/h2Q8-9rJ_bigger.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>نشكركم على اهتمامكم بمنتجاتنا، يرجى زيارة الرابط أدناه وملء بياناتكم وسيتصل بكم فريق المبيعات لدينا في غضون يومي عمل.
-ms.spr.ly/6015QxfsS</t>
+          <t>Emirates NBD has successfully closed $2.25 billion in long-term financing, marking a significant milestone in the region’s financial landscape.
+gccbusinessnews.com/emirates…
+#EmiratesNBD #SyndicatedLoan #SustainabilityLinkedLoan #CommodityMurabaha  #GCCBusinessNews @EmiratesNBD_AE</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>نشكركم على اهتمامكم بمنتجاتنا، يرجى زيارة الرابط أدناه وملء بياناتكم وسيتصل بكم فريق المبيعات لدينا في غضون يومي عمل.
-&lt;a href="http://ms.spr.ly/6015QxfsS"&gt;ms.spr.ly/6015QxfsS&lt;/a&gt;</t>
+          <t>Emirates NBD has successfully closed $2.25 billion in long-term financing, marking a significant milestone in the region’s financial landscape.
+&lt;a href="https://www.gccbusinessnews.com/emirates-nbd-group-long-term-financing/"&gt;gccbusinessnews.com/emirates…&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23EmiratesNBD"&gt;#EmiratesNBD&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SyndicatedLoan"&gt;#SyndicatedLoan&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23SustainabilityLinkedLoan"&gt;#SustainabilityLinkedLoan&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23CommodityMurabaha"&gt;#CommodityMurabaha&lt;/a&gt;  &lt;a href="/search?f=tweets&amp;amp;q=%23GCCBusinessNews"&gt;#GCCBusinessNews&lt;/a&gt; &lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J36" t="b">
         <v>0</v>
       </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>['Sd67239684']</t>
-        </is>
-      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 7:43 AM UTC</t>
+          <t>Apr 1, 2026 · 9:38 AM UTC</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-03-31T07:43:00Z</t>
+          <t>2026-04-01T09:38:00Z</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>['http://ms.spr.ly/6015QxfsS']</t>
+          <t>['https://www.gccbusinessnews.com/emirates-nbd-group-long-term-financing/', 'https://x.com/search?f=tweets&amp;q=%23EmiratesNBD', 'https://x.com/search?f=tweets&amp;q=%23SyndicatedLoan', 'https://x.com/search?f=tweets&amp;q=%23SustainabilityLinkedLoan', 'https://x.com/search?f=tweets&amp;q=%23CommodityMurabaha', 'https://x.com/search?f=tweets&amp;q=%23GCCBusinessNews', 'https://x.com/EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="R36" t="n">
@@ -3620,7 +3656,7 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -3631,43 +3667,43 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2038875337212170347</t>
+          <t>2039274083985084797</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://x.com/SAMAcares/status/2038875337212170347</t>
+          <t>https://x.com/ConmanNickJ/status/2039274083985084797</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://x.com/SAMAcares</t>
+          <t>https://x.com/ConmanNickJ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>SAMAcares</t>
+          <t>ConmanNickJ</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SAMACares | ساما تهتم</t>
+          <t>conman Nick</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/2008124521111252992/bcIs6E4Y_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1945509816476094464/YIU-DVu4_bigger.jpg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>عزيزنا العميل شكراً لتواصلكم عبر حساب البنك المركزي السعودي ، بإمكانك رفع الطلب الخاص بك عن طريق زيارة الموقع التالي : complaints-consumer.sama.gov….</t>
+          <t>I am very confused by your statement, specifically in regards to your oil &amp;gas in regards to Dubai, there is none.The original intention was to coordinate profitable assets such as ENBD, Maydan and a number of disparate assets under control of one entity.Also RAK has a small Sovreign fund that is also none oil and gas, ceramic profit etc, there is NO unified strategy for the UAE funds they are each independent .</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>عزيزنا العميل شكراً لتواصلكم عبر حساب البنك المركزي السعودي ، بإمكانك رفع الطلب الخاص بك عن طريق زيارة الموقع التالي : &lt;a href="https://complaints-consumer.sama.gov.sa"&gt;complaints-consumer.sama.gov…&lt;/a&gt;.</t>
+          <t>I am very confused by your statement, specifically in regards to your oil &amp;amp;gas in regards to Dubai, there is none.The original intention was to coordinate profitable assets such as ENBD, Maydan and a number of disparate assets under control of one entity.Also RAK has a small Sovreign fund that is also none oil and gas, ceramic profit etc, there is NO unified strategy for the UAE funds they are each independent .</t>
         </is>
       </c>
       <c r="J37" t="b">
@@ -3676,30 +3712,26 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>['AymanAlHarbiSF', 'EmiratesNBD_KSA', 'SAMA_GOV']</t>
+          <t>['makerofthings22', 'LondonRealTV']</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>20h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 7:05 AM UTC</t>
+          <t>Apr 1, 2026 · 9:30 AM UTC</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-03-31T07:05:00Z</t>
+          <t>2026-04-01T09:30:00Z</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>['https://complaints-consumer.sama.gov.sa']</t>
-        </is>
-      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="n">
         <v>1</v>
       </c>
@@ -3710,7 +3742,7 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -3721,43 +3753,43 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2038863571656770036</t>
+          <t>2039271367246295390</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2038863571656770036</t>
+          <t>https://x.com/yzood556/status/2039271367246295390</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/yzood556</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>yzood556</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>يزيد آل مستور القحطاني</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1207517911960707072/fLUY0-vB_bigger.jpg</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Thanks</t>
+          <t>مشكور اخوي محمد وباذن الله راح افتح حساب فيه 👍🏼</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Thanks</t>
+          <t>مشكور اخوي محمد وباذن الله راح افتح حساب فيه 👍🏼</t>
         </is>
       </c>
       <c r="J38" t="b">
@@ -3766,22 +3798,22 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>['ASaleemLaw']</t>
+          <t>['TheDigitalEngi1', 'EmiratesNBD_KSA', 'EmiratesNBD_AE']</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>21h</t>
+          <t>18h</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 6:18 AM UTC</t>
+          <t>Apr 1, 2026 · 9:19 AM UTC</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-03-31T06:18:00Z</t>
+          <t>2026-04-01T09:19:00Z</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>
@@ -3793,10 +3825,10 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -3807,43 +3839,43 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2038859041032843469</t>
+          <t>2039265742336499976</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://x.com/ASaleemLaw/status/2038859041032843469</t>
+          <t>https://x.com/marketgeniusx/status/2039265742336499976</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://x.com/ASaleemLaw</t>
+          <t>https://x.com/marketgeniusx</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ASaleemLaw</t>
+          <t>marketgeniusx</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ASaleem</t>
+          <t>Market Genius</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1923702004234268672/CCL_cyvQ_bigger.jpg</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Appreciate</t>
+          <t>DFM alone lost $45bn of that $120bn. Dubai down 16% since Feb 28, Abu Dhabi down 9%. The financial hub pitch works until your nearest neighbor is getting bombed. Emirates NBD dropped 3.2% in a single session last week. Decades of diversification stress-tested in 30 days.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Appreciate</t>
+          <t>DFM alone lost $45bn of that $120bn. Dubai down 16% since Feb 28, Abu Dhabi down 9%. The financial hub pitch works until your nearest neighbor is getting bombed. Emirates NBD dropped 3.2% in a single session last week. Decades of diversification stress-tested in 30 days.</t>
         </is>
       </c>
       <c r="J39" t="b">
@@ -3852,28 +3884,28 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>['EmiratesNBD_AE']</t>
+          <t>['clashreport']</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 6:00 AM UTC</t>
+          <t>Apr 1, 2026 · 8:56 AM UTC</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-03-31T06:00:00Z</t>
+          <t>2026-04-01T08:56:00Z</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -3882,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>8</v>
+        <v>3156</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -3893,43 +3925,43 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2038853926556938342</t>
+          <t>2039262663033639378</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2038853926556938342</t>
+          <t>https://x.com/ahmadingreen/status/2039262663033639378</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/ahmadingreen</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>ahmadingreen</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>Robo Crop</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1865036993647812608/KoQJBg1y_bigger.png</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Thank you! Our team will check and revert to you.</t>
+          <t>اللافت أن جزءاً من التمويل مرتبط بالاستدامة. هذا النوع من التمويل يفتح المجال لتسريع مشاريع الطاقة المتجددة والبنية التحتية للمياه، وهي بالضبط المجالات التي تحتاجها المنطقة لدفع التحول المستدام.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Thank you! Our team will check and revert to you.</t>
+          <t>اللافت أن جزءاً من التمويل مرتبط بالاستدامة. هذا النوع من التمويل يفتح المجال لتسريع مشاريع الطاقة المتجددة والبنية التحتية للمياه، وهي بالضبط المجالات التي تحتاجها المنطقة لدفع التحول المستدام.</t>
         </is>
       </c>
       <c r="J40" t="b">
@@ -3938,28 +3970,28 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>['ASaleemLaw']</t>
+          <t>['Almalchannel']</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 5:40 AM UTC</t>
+          <t>Apr 1, 2026 · 8:44 AM UTC</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-03-31T05:40:00Z</t>
+          <t>2026-04-01T08:44:00Z</t>
         </is>
       </c>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3968,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -3979,12 +4011,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2038848292981715352</t>
+          <t>2039261337365213687</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2038848292981715352</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2039261337365213687</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4010,16 +4042,12 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at 
-social@emiratesnbd.com 
-Quoting case #990937  in the subject line of the email from your registered email address We will make every effort to address the matter promptly and provide the necessary support. Thanks</t>
+          <t>مرحبا, نأسف لسماع أنك تواجه هذه التجربة, يرجى إرسال رقم هاتفك و رقم الهوية عبر الخاص ليمكننا مساعدتك, شكرا</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at 
-social@emiratesnbd.com 
-Quoting case #990937  in the subject line of the email from your registered email address We will make every effort to address the matter promptly and provide the necessary support. Thanks</t>
+          <t>مرحبا, نأسف لسماع أنك تواجه هذه التجربة, يرجى إرسال رقم هاتفك و رقم الهوية عبر الخاص ليمكننا مساعدتك, شكرا</t>
         </is>
       </c>
       <c r="J41" t="b">
@@ -4028,28 +4056,28 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>['goaroundflaps15']</t>
+          <t>['AliAhmedk66633']</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 5:18 AM UTC</t>
+          <t>Apr 1, 2026 · 8:39 AM UTC</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-03-31T05:18:00Z</t>
+          <t>2026-04-01T08:39:00Z</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -4058,7 +4086,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -4069,73 +4097,81 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2038844822153498658</t>
+          <t>2039254054069501982</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://x.com/ASaleemLaw/status/2038844822153498658</t>
+          <t>https://x.com/FintechGate1/status/2039254054069501982</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://x.com/ASaleemLaw</t>
+          <t>https://x.com/FintechGate1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ASaleemLaw</t>
+          <t>FintechGate1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ASaleem</t>
+          <t>FinTech Gate-بوابة التكنولوجيا المالية</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/abs.twimg.com/sticky/default_profile_images/default_profile_bigger.png</t>
+          <t>https://pbs.twimg.com/profile_images/1630704388531470336/_2WZb_12_bigger.jpg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Thankyou for your reply I have already send email waiting your urgent action and reply</t>
+          <t>«الإمارات الإسلامي» يستكمل تمويل مرابحة مشترك بقيمة 500 مليون دولار
+fintechgate.net/tz49 | التفاصيل 
+@EmiratesNBD_AE
+#fintech_gate
+#الإمارات_الإسلامي</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Thankyou for your reply I have already send email waiting your urgent action and reply</t>
+          <t>«الإمارات الإسلامي» يستكمل تمويل مرابحة مشترك بقيمة 500 مليون دولار
+&lt;a href="https://fintechgate.net/tz49"&gt;fintechgate.net/tz49&lt;/a&gt; | التفاصيل 
+&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23fintech_gate"&gt;#fintech_gate&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_الإسلامي"&gt;#الإمارات_الإسلامي&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J42" t="b">
         <v>0</v>
       </c>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>['EmiratesNBD_AE']</t>
-        </is>
-      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>22h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 5:04 AM UTC</t>
+          <t>Apr 1, 2026 · 8:10 AM UTC</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2026-03-31T05:04:00Z</t>
+          <t>2026-04-01T08:10:00Z</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>['https://fintechgate.net/tz49', 'https://x.com/EmiratesNBD_AE', 'https://x.com/search?f=tweets&amp;q=%23fintech_gate', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_الإسلامي']</t>
+        </is>
+      </c>
       <c r="R42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -4144,7 +4180,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -4155,86 +4191,90 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2038842011344674994</t>
+          <t>2039253680906445167</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2038842011344674994</t>
+          <t>https://x.com/FintechGate1/status/2039253680906445167</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE</t>
+          <t>https://x.com/FintechGate1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EmiratesNBD_AE</t>
+          <t>FintechGate1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Emirates NBD</t>
+          <t>FinTech Gate-بوابة التكنولوجيا المالية</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://pbs.twimg.com/profile_images/1762427651271110656/jOUBidn8_bigger.jpg</t>
+          <t>https://pbs.twimg.com/profile_images/1630704388531470336/_2WZb_12_bigger.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us
-social@emiratesnbd.com
- Quoting case #990917 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
+          <t>«الإمارات دبي الوطني» يستكمل بنجاح تمويل طويل الأجل بقيمة 2.25 مليار دولار
+fintechgate.net/j421 | التفاصيل 
+@EmiratesNBD_AE
+#fintech_gate
+#الإمارات_دبي_الوطني #تمويل</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us
-social@emiratesnbd.com
- Quoting case #990917 in the subject line of the email from your registered email address We will make every effort to address the matter</t>
+          <t>«الإمارات دبي الوطني» يستكمل بنجاح تمويل طويل الأجل بقيمة 2.25 مليار دولار
+&lt;a href="https://fintechgate.net/j421"&gt;fintechgate.net/j421&lt;/a&gt; | التفاصيل 
+&lt;a href="/EmiratesNBD_AE" title="Emirates NBD"&gt;@EmiratesNBD_AE&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23fintech_gate"&gt;#fintech_gate&lt;/a&gt;
+&lt;a href="/search?f=tweets&amp;amp;q=%23الإمارات_دبي_الوطني"&gt;#الإمارات_دبي_الوطني&lt;/a&gt; &lt;a href="/search?f=tweets&amp;amp;q=%23تمويل"&gt;#تمويل&lt;/a&gt;</t>
         </is>
       </c>
       <c r="J43" t="b">
         <v>0</v>
       </c>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>['ASaleemLaw']</t>
-        </is>
-      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>23h</t>
+          <t>19h</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Mar 31, 2026 · 4:53 AM UTC</t>
+          <t>Apr 1, 2026 · 8:08 AM UTC</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-03-31T04:53:00Z</t>
+          <t>2026-04-01T08:08:00Z</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>['https://fintechgate.net/j421', 'https://x.com/EmiratesNBD_AE', 'https://x.com/search?f=tweets&amp;q=%23fintech_gate', 'https://x.com/search?f=tweets&amp;q=%23الإمارات_دبي_الوطني', 'https://x.com/search?f=tweets&amp;q=%23تمويل']</t>
+        </is>
+      </c>
       <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
         <v>1</v>
       </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
       <c r="T43" t="n">
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -4245,43 +4285,43 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2038834682196849032</t>
+          <t>2039243786618806350</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2038834682196849032</t>
+          <t>https://x.com/yzood556/status/2039243786618806350</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA</t>
+          <t>https://x.com/yzood556</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>EmiratesNBD_KSA</t>
+          <t>yzood556</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>EmiratesNBD KSA</t>
+          <t>يزيد آل مستور القحطاني</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
      